--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -10424,16 +10424,16 @@
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S62">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T62">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U62">
         <v>0</v>
@@ -10448,31 +10448,31 @@
         <v>0</v>
       </c>
       <c r="Y62">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z62">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA62">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB62">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC62">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD62">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE62">
         <v>0</v>
       </c>
       <c r="AF62">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG62">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK62">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16974,10 +16974,10 @@
         <v>0</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G106">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G115">
@@ -19706,13 +19706,13 @@
         </is>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O119">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P119">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q119">
         <v>0</v>
@@ -19745,10 +19745,10 @@
         <v>0</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC119">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O107">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P107">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q107">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU119"/>
+  <dimension ref="A1:AU118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Albacete II</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G72">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G76">
@@ -12813,27 +12813,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G77">
@@ -12856,17 +12856,17 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-10-04 12:00:00</t>
+          <t>2026-10-04 12:30:00</t>
         </is>
       </c>
     </row>
@@ -12981,22 +12981,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G78">
@@ -13019,17 +13019,17 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N78">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O78">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P78">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13062,10 +13062,10 @@
         <v>0</v>
       </c>
       <c r="AA78">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB78">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC78">
         <v>0</v>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G79">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13388,10 +13388,10 @@
         <v>0</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC80">
         <v>0</v>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O81">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P81">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>0</v>
       </c>
       <c r="AA81">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB81">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC81">
         <v>0</v>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G82">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-10-04 12:30:00</t>
+          <t>2026-10-04 13:00:00</t>
         </is>
       </c>
     </row>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G83">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="G84">
@@ -14117,12 +14117,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-10-04 13:00:00</t>
+          <t>2026-10-04 13:30:00</t>
         </is>
       </c>
     </row>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.13</v>
+        <v>1.26</v>
       </c>
       <c r="O86">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="P86">
-        <v>3.67</v>
+        <v>10.5</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="O87">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="P87">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G88">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-10-04 13:30:00</t>
+          <t>2026-10-04 13:45:00</t>
         </is>
       </c>
     </row>
@@ -14769,27 +14769,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-10-04 13:45:00</t>
+          <t>2026-10-04 14:00:00</t>
         </is>
       </c>
     </row>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Ciudad de Lucena</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O90">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15095,12 +15095,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ciudad de Lucena</t>
+          <t>Valencia W</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G91">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-10-04 14:00:00</t>
+          <t>2026-10-04 14:30:00</t>
         </is>
       </c>
     </row>
@@ -15258,27 +15258,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Valencia W</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G92">
@@ -15301,68 +15301,68 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S92">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T92">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-10-04 14:30:00</t>
+          <t>2026-10-04 15:00:00</t>
         </is>
       </c>
     </row>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G93">
@@ -15464,68 +15464,68 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N93">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O93">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P93">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q93">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R93">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S93">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T93">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U93">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="V93">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W93">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X93">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y93">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z93">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA93">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB93">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC93">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD93">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE93">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF93">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK93">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15584,27 +15584,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G94">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-10-04 15:00:00</t>
+          <t>2026-10-04 15:30:00</t>
         </is>
       </c>
     </row>
@@ -15752,22 +15752,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G95">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G96">
@@ -16078,22 +16078,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G98">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G100">
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16811,10 +16811,10 @@
         <v>0</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC101">
         <v>0</v>
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-10-04 15:30:00</t>
+          <t>2026-10-04 16:00:00</t>
         </is>
       </c>
     </row>
@@ -16888,27 +16888,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -16974,10 +16974,10 @@
         <v>0</v>
       </c>
       <c r="AA102">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB102">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC102">
         <v>0</v>
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-10-04 16:00:00</t>
+          <t>2026-10-04 17:00:00</t>
         </is>
       </c>
     </row>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G105">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>1.63</v>
+        <v>7.15</v>
       </c>
       <c r="O107">
-        <v>3.88</v>
+        <v>5</v>
       </c>
       <c r="P107">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17866,12 +17866,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G108">
@@ -17909,68 +17909,68 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N108">
-        <v>7.15</v>
+        <v>2.02</v>
       </c>
       <c r="O108">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="P108">
+        <v>2.85</v>
+      </c>
+      <c r="Q108">
+        <v>2.5</v>
+      </c>
+      <c r="R108">
+        <v>2.23</v>
+      </c>
+      <c r="S108">
         <v>1.3</v>
       </c>
-      <c r="Q108">
-        <v>0</v>
-      </c>
-      <c r="R108">
-        <v>0</v>
-      </c>
-      <c r="S108">
-        <v>0</v>
-      </c>
       <c r="T108">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-10-04 17:00:00</t>
+          <t>2026-10-04 17:30:00</t>
         </is>
       </c>
     </row>
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G109">
@@ -18072,68 +18072,68 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N109">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O109">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P109">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q109">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R109">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S109">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T109">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="U109">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="V109">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W109">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X109">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y109">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z109">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AA109">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB109">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC109">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD109">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE109">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF109">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG109">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK109">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18197,22 +18197,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G114">
@@ -19007,27 +19007,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G115">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-10-04 17:30:00</t>
+          <t>2026-10-04 18:00:00</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G116">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-10-04 18:00:00</t>
+          <t>2026-10-04 18:30:00</t>
         </is>
       </c>
     </row>
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-10-04 18:30:00</t>
+          <t>2026-10-04 19:00:00</t>
         </is>
       </c>
     </row>
@@ -19496,12 +19496,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19582,10 +19582,10 @@
         <v>0</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC118">
         <v>0</v>
@@ -19646,169 +19646,6 @@
         <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
-        <is>
-          <t>2026-10-04 19:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>Houston Dash</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Washington Spirit</t>
-        </is>
-      </c>
-      <c r="G119">
-        <v>0</v>
-      </c>
-      <c r="H119">
-        <v>0</v>
-      </c>
-      <c r="I119">
-        <v>0</v>
-      </c>
-      <c r="J119">
-        <v>0</v>
-      </c>
-      <c r="K119">
-        <v>0</v>
-      </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N119">
-        <v>3.73</v>
-      </c>
-      <c r="O119">
-        <v>3.62</v>
-      </c>
-      <c r="P119">
-        <v>1.77</v>
-      </c>
-      <c r="Q119">
-        <v>0</v>
-      </c>
-      <c r="R119">
-        <v>0</v>
-      </c>
-      <c r="S119">
-        <v>0</v>
-      </c>
-      <c r="T119">
-        <v>0</v>
-      </c>
-      <c r="U119">
-        <v>0</v>
-      </c>
-      <c r="V119">
-        <v>0</v>
-      </c>
-      <c r="W119">
-        <v>0</v>
-      </c>
-      <c r="X119">
-        <v>0</v>
-      </c>
-      <c r="Y119">
-        <v>0</v>
-      </c>
-      <c r="Z119">
-        <v>0</v>
-      </c>
-      <c r="AA119">
-        <v>1.83</v>
-      </c>
-      <c r="AB119">
-        <v>1.92</v>
-      </c>
-      <c r="AC119">
-        <v>0</v>
-      </c>
-      <c r="AD119">
-        <v>0</v>
-      </c>
-      <c r="AE119">
-        <v>0</v>
-      </c>
-      <c r="AF119">
-        <v>0</v>
-      </c>
-      <c r="AG119">
-        <v>0</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ119">
-        <v>0</v>
-      </c>
-      <c r="AK119">
-        <v>0</v>
-      </c>
-      <c r="AL119">
-        <v>0</v>
-      </c>
-      <c r="AM119">
-        <v>-1</v>
-      </c>
-      <c r="AN119">
-        <v>-1</v>
-      </c>
-      <c r="AO119">
-        <v>-1</v>
-      </c>
-      <c r="AP119">
-        <v>-1</v>
-      </c>
-      <c r="AQ119">
-        <v>0</v>
-      </c>
-      <c r="AR119">
-        <v>0</v>
-      </c>
-      <c r="AS119">
-        <v>0</v>
-      </c>
-      <c r="AT119">
-        <v>0</v>
-      </c>
-      <c r="AU119" t="inlineStr">
         <is>
           <t>2026-10-04 20:00:00</t>
         </is>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G17">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G22">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Q117">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G17">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G25">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G36">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G38">

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU118"/>
+  <dimension ref="A1:AU122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,55 +644,55 @@
         <v>1.65</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,34 +807,34 @@
         <v>2.8</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA3">
         <v>1.82</v>
@@ -843,19 +843,19 @@
         <v>1.93</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,55 +970,55 @@
         <v>2.2</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G36">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-10-04 09:30:00</t>
+          <t>2026-10-04 09:00:00</t>
         </is>
       </c>
     </row>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G37">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G38">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,22 +6787,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6950,22 +6950,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G42">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N42">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-10-04 10:00:00</t>
+          <t>2026-10-04 09:30:00</t>
         </is>
       </c>
     </row>
@@ -7276,22 +7276,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="G43">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N43">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,22 +7928,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>13.66</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>8.76</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8504,10 +8504,10 @@
         <v>0</v>
       </c>
       <c r="AC50">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD50">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.4</v>
+        <v>13.66</v>
       </c>
       <c r="O51">
-        <v>3.3</v>
+        <v>8.76</v>
       </c>
       <c r="P51">
-        <v>2.51</v>
+        <v>1.1</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8661,16 +8661,16 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB51">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE51">
         <v>0</v>
@@ -8738,12 +8738,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8824,10 +8824,10 @@
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC52">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-10-04 11:00:00</t>
+          <t>2026-10-04 10:00:00</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G53">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>5.82</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-10-04 11:15:00</t>
+          <t>2026-10-04 11:00:00</t>
         </is>
       </c>
     </row>
@@ -9227,12 +9227,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G55">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-10-04 11:30:00</t>
+          <t>2026-10-04 11:00:00</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-10-04 11:30:00</t>
+          <t>2026-10-04 11:15:00</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Santa Clara II</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Real SC</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G57">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>De Graafschap W</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G58">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-10-04 11:45:00</t>
+          <t>2026-10-04 11:30:00</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Santa Clara II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Real SC</t>
         </is>
       </c>
       <c r="G59">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-10-04 11:45:00</t>
+          <t>2026-10-04 11:30:00</t>
         </is>
       </c>
     </row>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>De Graafschap W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G61">
@@ -10368,27 +10368,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G62">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-10-04 12:00:00</t>
+          <t>2026-10-04 11:45:00</t>
         </is>
       </c>
     </row>
@@ -10531,27 +10531,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G63">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-10-04 12:00:00</t>
+          <t>2026-10-04 11:45:00</t>
         </is>
       </c>
     </row>
@@ -10699,22 +10699,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Calamocha</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G64">
@@ -10862,22 +10862,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G65">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Calamocha</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G68">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Atletico Madrid III</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G69">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Atlético Tordesillas</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="G70">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Atletico Madrid III</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Atlético Tordesillas</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G72">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G73">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G74">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G76">
@@ -12813,27 +12813,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="G77">
@@ -12856,17 +12856,17 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N77">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O77">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P77">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12899,10 +12899,10 @@
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB77">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC77">
         <v>0</v>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-10-04 12:30:00</t>
+          <t>2026-10-04 12:00:00</t>
         </is>
       </c>
     </row>
@@ -12976,12 +12976,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G78">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-10-04 12:30:00</t>
+          <t>2026-10-04 12:00:00</t>
         </is>
       </c>
     </row>
@@ -13144,22 +13144,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G79">
@@ -13182,17 +13182,17 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O80">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P80">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13388,10 +13388,10 @@
         <v>0</v>
       </c>
       <c r="AA80">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB80">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC80">
         <v>0</v>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Savoia</t>
         </is>
       </c>
       <c r="G81">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13714,10 +13714,10 @@
         <v>0</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC82">
         <v>0</v>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-10-04 13:00:00</t>
+          <t>2026-10-04 12:30:00</t>
         </is>
       </c>
     </row>
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G83">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-10-04 13:00:00</t>
+          <t>2026-10-04 12:30:00</t>
         </is>
       </c>
     </row>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G84">
@@ -14117,12 +14117,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O85">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P85">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>2026-10-04 13:30:00</t>
+          <t>2026-10-04 13:00:00</t>
         </is>
       </c>
     </row>
@@ -14280,12 +14280,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="O86">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="P86">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>2026-10-04 13:30:00</t>
+          <t>2026-10-04 13:00:00</t>
         </is>
       </c>
     </row>
@@ -14443,12 +14443,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G87">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-10-04 13:30:00</t>
+          <t>2026-10-04 13:00:00</t>
         </is>
       </c>
     </row>
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G88">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-10-04 13:45:00</t>
+          <t>2026-10-04 13:00:00</t>
         </is>
       </c>
     </row>
@@ -14769,27 +14769,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.77</v>
+        <v>2.13</v>
       </c>
       <c r="O89">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P89">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-10-04 14:00:00</t>
+          <t>2026-10-04 13:30:00</t>
         </is>
       </c>
     </row>
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ciudad de Lucena</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-10-04 14:00:00</t>
+          <t>2026-10-04 13:30:00</t>
         </is>
       </c>
     </row>
@@ -15095,12 +15095,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Valencia W</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G91">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-10-04 14:30:00</t>
+          <t>2026-10-04 13:30:00</t>
         </is>
       </c>
     </row>
@@ -15258,27 +15258,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G92">
@@ -15301,68 +15301,68 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N92">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O92">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P92">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q92">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R92">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S92">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T92">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U92">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="V92">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W92">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X92">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y92">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z92">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA92">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB92">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC92">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD92">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE92">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF92">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG92">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK92">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-10-04 15:00:00</t>
+          <t>2026-10-04 13:45:00</t>
         </is>
       </c>
     </row>
@@ -15421,12 +15421,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.23</v>
+        <v>1.77</v>
       </c>
       <c r="O93">
-        <v>2.83</v>
+        <v>3.5</v>
       </c>
       <c r="P93">
-        <v>3.29</v>
+        <v>3.88</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-10-04 15:00:00</t>
+          <t>2026-10-04 14:00:00</t>
         </is>
       </c>
     </row>
@@ -15584,12 +15584,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Ciudad de Lucena</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ostia Mare Lidocalcio</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G94">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-10-04 15:30:00</t>
+          <t>2026-10-04 14:00:00</t>
         </is>
       </c>
     </row>
@@ -15747,27 +15747,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Valencia W</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O95">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="P95">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15898,7 +15898,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>2026-10-04 15:30:00</t>
+          <t>2026-10-04 14:30:00</t>
         </is>
       </c>
     </row>
@@ -15910,12 +15910,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G96">
@@ -15953,68 +15953,68 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N96">
-        <v>2.02</v>
+        <v>2.75</v>
       </c>
       <c r="O96">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="P96">
-        <v>3.79</v>
+        <v>2.37</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-10-04 15:30:00</t>
+          <t>2026-10-04 15:00:00</t>
         </is>
       </c>
     </row>
@@ -16073,27 +16073,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-10-04 15:30:00</t>
+          <t>2026-10-04 15:00:00</t>
         </is>
       </c>
     </row>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ostia Mare Lidocalcio</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,22 +16404,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16567,22 +16567,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O101">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="P101">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16811,10 +16811,10 @@
         <v>0</v>
       </c>
       <c r="AA101">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB101">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC101">
         <v>0</v>
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-10-04 16:00:00</t>
+          <t>2026-10-04 15:30:00</t>
         </is>
       </c>
     </row>
@@ -16888,27 +16888,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="P102">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-10-04 17:00:00</t>
+          <t>2026-10-04 15:30:00</t>
         </is>
       </c>
     </row>
@@ -17051,27 +17051,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O103">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P103">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q103">
         <v>0</v>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-10-04 17:00:00</t>
+          <t>2026-10-04 15:30:00</t>
         </is>
       </c>
     </row>
@@ -17214,27 +17214,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G104">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-10-04 17:00:00</t>
+          <t>2026-10-04 15:30:00</t>
         </is>
       </c>
     </row>
@@ -17377,27 +17377,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.49</v>
+        <v>2.16</v>
       </c>
       <c r="O105">
-        <v>3.52</v>
+        <v>3.63</v>
       </c>
       <c r="P105">
-        <v>6.63</v>
+        <v>3.3</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17463,10 +17463,10 @@
         <v>0</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC105">
         <v>0</v>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>2026-10-04 17:00:00</t>
+          <t>2026-10-04 16:00:00</t>
         </is>
       </c>
     </row>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>1.63</v>
+        <v>2.16</v>
       </c>
       <c r="O106">
-        <v>3.88</v>
+        <v>2.71</v>
       </c>
       <c r="P106">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>7.15</v>
+        <v>2.27</v>
       </c>
       <c r="O107">
-        <v>5</v>
+        <v>2.74</v>
       </c>
       <c r="P107">
-        <v>1.3</v>
+        <v>3.33</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -17866,12 +17866,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G108">
@@ -17909,68 +17909,68 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N108">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O108">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P108">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q108">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R108">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S108">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T108">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="U108">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="V108">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W108">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X108">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y108">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z108">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AA108">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB108">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC108">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD108">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE108">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF108">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG108">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK108">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18017,7 +18017,7 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>2026-10-04 17:30:00</t>
+          <t>2026-10-04 17:00:00</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q109">
         <v>0</v>
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>2026-10-04 17:30:00</t>
+          <t>2026-10-04 17:00:00</t>
         </is>
       </c>
     </row>
@@ -18192,27 +18192,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q110">
         <v>0</v>
@@ -18343,7 +18343,7 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>2026-10-04 17:30:00</t>
+          <t>2026-10-04 17:00:00</t>
         </is>
       </c>
     </row>
@@ -18355,27 +18355,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-10-04 17:30:00</t>
+          <t>2026-10-04 17:00:00</t>
         </is>
       </c>
     </row>
@@ -18523,22 +18523,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G112">
@@ -18561,68 +18561,68 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18686,22 +18686,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G114">
@@ -19007,27 +19007,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O115">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P115">
-        <v>6.31</v>
+        <v>0</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-10-04 18:00:00</t>
+          <t>2026-10-04 17:30:00</t>
         </is>
       </c>
     </row>
@@ -19170,27 +19170,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G116">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-10-04 18:30:00</t>
+          <t>2026-10-04 17:30:00</t>
         </is>
       </c>
     </row>
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O117">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P117">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-10-04 19:00:00</t>
+          <t>2026-10-04 17:30:00</t>
         </is>
       </c>
     </row>
@@ -19496,156 +19496,808 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Montego Bay United</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Dunbeholden</t>
+        </is>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
+      </c>
+      <c r="Q118">
+        <v>0</v>
+      </c>
+      <c r="R118">
+        <v>0</v>
+      </c>
+      <c r="S118">
+        <v>0</v>
+      </c>
+      <c r="T118">
+        <v>0</v>
+      </c>
+      <c r="U118">
+        <v>0</v>
+      </c>
+      <c r="V118">
+        <v>0</v>
+      </c>
+      <c r="W118">
+        <v>0</v>
+      </c>
+      <c r="X118">
+        <v>0</v>
+      </c>
+      <c r="Y118">
+        <v>0</v>
+      </c>
+      <c r="Z118">
+        <v>0</v>
+      </c>
+      <c r="AA118">
+        <v>0</v>
+      </c>
+      <c r="AB118">
+        <v>0</v>
+      </c>
+      <c r="AC118">
+        <v>0</v>
+      </c>
+      <c r="AD118">
+        <v>0</v>
+      </c>
+      <c r="AE118">
+        <v>0</v>
+      </c>
+      <c r="AF118">
+        <v>0</v>
+      </c>
+      <c r="AG118">
+        <v>0</v>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ118">
+        <v>0</v>
+      </c>
+      <c r="AK118">
+        <v>0</v>
+      </c>
+      <c r="AL118">
+        <v>0</v>
+      </c>
+      <c r="AM118">
+        <v>-1</v>
+      </c>
+      <c r="AN118">
+        <v>-1</v>
+      </c>
+      <c r="AO118">
+        <v>-1</v>
+      </c>
+      <c r="AP118">
+        <v>-1</v>
+      </c>
+      <c r="AQ118">
+        <v>0</v>
+      </c>
+      <c r="AR118">
+        <v>0</v>
+      </c>
+      <c r="AS118">
+        <v>0</v>
+      </c>
+      <c r="AT118">
+        <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>2026-10-04 17:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N119">
+        <v>1.57</v>
+      </c>
+      <c r="O119">
+        <v>3.22</v>
+      </c>
+      <c r="P119">
+        <v>6.31</v>
+      </c>
+      <c r="Q119">
+        <v>0</v>
+      </c>
+      <c r="R119">
+        <v>0</v>
+      </c>
+      <c r="S119">
+        <v>0</v>
+      </c>
+      <c r="T119">
+        <v>0</v>
+      </c>
+      <c r="U119">
+        <v>0</v>
+      </c>
+      <c r="V119">
+        <v>0</v>
+      </c>
+      <c r="W119">
+        <v>0</v>
+      </c>
+      <c r="X119">
+        <v>0</v>
+      </c>
+      <c r="Y119">
+        <v>0</v>
+      </c>
+      <c r="Z119">
+        <v>0</v>
+      </c>
+      <c r="AA119">
+        <v>0</v>
+      </c>
+      <c r="AB119">
+        <v>0</v>
+      </c>
+      <c r="AC119">
+        <v>0</v>
+      </c>
+      <c r="AD119">
+        <v>0</v>
+      </c>
+      <c r="AE119">
+        <v>0</v>
+      </c>
+      <c r="AF119">
+        <v>0</v>
+      </c>
+      <c r="AG119">
+        <v>0</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ119">
+        <v>0</v>
+      </c>
+      <c r="AK119">
+        <v>0</v>
+      </c>
+      <c r="AL119">
+        <v>0</v>
+      </c>
+      <c r="AM119">
+        <v>-1</v>
+      </c>
+      <c r="AN119">
+        <v>-1</v>
+      </c>
+      <c r="AO119">
+        <v>-1</v>
+      </c>
+      <c r="AP119">
+        <v>-1</v>
+      </c>
+      <c r="AQ119">
+        <v>0</v>
+      </c>
+      <c r="AR119">
+        <v>0</v>
+      </c>
+      <c r="AS119">
+        <v>0</v>
+      </c>
+      <c r="AT119">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>2026-10-04 18:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>San Martín Tucumán</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro</t>
+        </is>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>0</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="Q120">
+        <v>0</v>
+      </c>
+      <c r="R120">
+        <v>0</v>
+      </c>
+      <c r="S120">
+        <v>0</v>
+      </c>
+      <c r="T120">
+        <v>0</v>
+      </c>
+      <c r="U120">
+        <v>0</v>
+      </c>
+      <c r="V120">
+        <v>0</v>
+      </c>
+      <c r="W120">
+        <v>0</v>
+      </c>
+      <c r="X120">
+        <v>0</v>
+      </c>
+      <c r="Y120">
+        <v>0</v>
+      </c>
+      <c r="Z120">
+        <v>0</v>
+      </c>
+      <c r="AA120">
+        <v>0</v>
+      </c>
+      <c r="AB120">
+        <v>0</v>
+      </c>
+      <c r="AC120">
+        <v>0</v>
+      </c>
+      <c r="AD120">
+        <v>0</v>
+      </c>
+      <c r="AE120">
+        <v>0</v>
+      </c>
+      <c r="AF120">
+        <v>0</v>
+      </c>
+      <c r="AG120">
+        <v>0</v>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ120">
+        <v>0</v>
+      </c>
+      <c r="AK120">
+        <v>0</v>
+      </c>
+      <c r="AL120">
+        <v>0</v>
+      </c>
+      <c r="AM120">
+        <v>-1</v>
+      </c>
+      <c r="AN120">
+        <v>-1</v>
+      </c>
+      <c r="AO120">
+        <v>-1</v>
+      </c>
+      <c r="AP120">
+        <v>-1</v>
+      </c>
+      <c r="AQ120">
+        <v>0</v>
+      </c>
+      <c r="AR120">
+        <v>0</v>
+      </c>
+      <c r="AS120">
+        <v>0</v>
+      </c>
+      <c r="AT120">
+        <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>2026-10-04 18:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N121">
+        <v>1.98</v>
+      </c>
+      <c r="O121">
+        <v>3.6</v>
+      </c>
+      <c r="P121">
+        <v>3.09</v>
+      </c>
+      <c r="Q121">
+        <v>0</v>
+      </c>
+      <c r="R121">
+        <v>0</v>
+      </c>
+      <c r="S121">
+        <v>0</v>
+      </c>
+      <c r="T121">
+        <v>0</v>
+      </c>
+      <c r="U121">
+        <v>0</v>
+      </c>
+      <c r="V121">
+        <v>0</v>
+      </c>
+      <c r="W121">
+        <v>0</v>
+      </c>
+      <c r="X121">
+        <v>0</v>
+      </c>
+      <c r="Y121">
+        <v>0</v>
+      </c>
+      <c r="Z121">
+        <v>0</v>
+      </c>
+      <c r="AA121">
+        <v>0</v>
+      </c>
+      <c r="AB121">
+        <v>0</v>
+      </c>
+      <c r="AC121">
+        <v>0</v>
+      </c>
+      <c r="AD121">
+        <v>0</v>
+      </c>
+      <c r="AE121">
+        <v>0</v>
+      </c>
+      <c r="AF121">
+        <v>0</v>
+      </c>
+      <c r="AG121">
+        <v>0</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ121">
+        <v>0</v>
+      </c>
+      <c r="AK121">
+        <v>0</v>
+      </c>
+      <c r="AL121">
+        <v>0</v>
+      </c>
+      <c r="AM121">
+        <v>-1</v>
+      </c>
+      <c r="AN121">
+        <v>-1</v>
+      </c>
+      <c r="AO121">
+        <v>-1</v>
+      </c>
+      <c r="AP121">
+        <v>-1</v>
+      </c>
+      <c r="AQ121">
+        <v>0</v>
+      </c>
+      <c r="AR121">
+        <v>0</v>
+      </c>
+      <c r="AS121">
+        <v>0</v>
+      </c>
+      <c r="AT121">
+        <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>2026-10-04 19:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="E122" t="inlineStr">
         <is>
           <t>Houston Dash</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>Washington Spirit</t>
         </is>
       </c>
-      <c r="G118">
-        <v>0</v>
-      </c>
-      <c r="H118">
-        <v>0</v>
-      </c>
-      <c r="I118">
-        <v>0</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-      <c r="K118">
-        <v>0</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="M118" t="inlineStr">
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N118">
+      <c r="N122">
         <v>3.73</v>
       </c>
-      <c r="O118">
+      <c r="O122">
         <v>3.62</v>
       </c>
-      <c r="P118">
+      <c r="P122">
         <v>1.77</v>
       </c>
-      <c r="Q118">
-        <v>0</v>
-      </c>
-      <c r="R118">
-        <v>0</v>
-      </c>
-      <c r="S118">
-        <v>0</v>
-      </c>
-      <c r="T118">
-        <v>0</v>
-      </c>
-      <c r="U118">
-        <v>0</v>
-      </c>
-      <c r="V118">
-        <v>0</v>
-      </c>
-      <c r="W118">
-        <v>0</v>
-      </c>
-      <c r="X118">
-        <v>0</v>
-      </c>
-      <c r="Y118">
-        <v>0</v>
-      </c>
-      <c r="Z118">
-        <v>0</v>
-      </c>
-      <c r="AA118">
+      <c r="Q122">
+        <v>0</v>
+      </c>
+      <c r="R122">
+        <v>0</v>
+      </c>
+      <c r="S122">
+        <v>0</v>
+      </c>
+      <c r="T122">
+        <v>0</v>
+      </c>
+      <c r="U122">
+        <v>0</v>
+      </c>
+      <c r="V122">
+        <v>0</v>
+      </c>
+      <c r="W122">
+        <v>0</v>
+      </c>
+      <c r="X122">
+        <v>0</v>
+      </c>
+      <c r="Y122">
+        <v>0</v>
+      </c>
+      <c r="Z122">
+        <v>0</v>
+      </c>
+      <c r="AA122">
         <v>1.83</v>
       </c>
-      <c r="AB118">
+      <c r="AB122">
         <v>1.92</v>
       </c>
-      <c r="AC118">
-        <v>0</v>
-      </c>
-      <c r="AD118">
-        <v>0</v>
-      </c>
-      <c r="AE118">
-        <v>0</v>
-      </c>
-      <c r="AF118">
-        <v>0</v>
-      </c>
-      <c r="AG118">
-        <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>0</v>
-      </c>
-      <c r="AK118">
-        <v>0</v>
-      </c>
-      <c r="AL118">
-        <v>0</v>
-      </c>
-      <c r="AM118">
-        <v>-1</v>
-      </c>
-      <c r="AN118">
-        <v>-1</v>
-      </c>
-      <c r="AO118">
-        <v>-1</v>
-      </c>
-      <c r="AP118">
-        <v>-1</v>
-      </c>
-      <c r="AQ118">
-        <v>0</v>
-      </c>
-      <c r="AR118">
-        <v>0</v>
-      </c>
-      <c r="AS118">
-        <v>0</v>
-      </c>
-      <c r="AT118">
-        <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
+      <c r="AC122">
+        <v>0</v>
+      </c>
+      <c r="AD122">
+        <v>0</v>
+      </c>
+      <c r="AE122">
+        <v>0</v>
+      </c>
+      <c r="AF122">
+        <v>0</v>
+      </c>
+      <c r="AG122">
+        <v>0</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ122">
+        <v>0</v>
+      </c>
+      <c r="AK122">
+        <v>0</v>
+      </c>
+      <c r="AL122">
+        <v>0</v>
+      </c>
+      <c r="AM122">
+        <v>-1</v>
+      </c>
+      <c r="AN122">
+        <v>-1</v>
+      </c>
+      <c r="AO122">
+        <v>-1</v>
+      </c>
+      <c r="AP122">
+        <v>-1</v>
+      </c>
+      <c r="AQ122">
+        <v>0</v>
+      </c>
+      <c r="AR122">
+        <v>0</v>
+      </c>
+      <c r="AS122">
+        <v>0</v>
+      </c>
+      <c r="AT122">
+        <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
         <is>
           <t>2026-10-04 20:00:00</t>
         </is>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G25">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G43">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43">
@@ -7439,22 +7439,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G47">
@@ -8091,22 +8091,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>13.66</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>8.76</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8667,10 +8667,10 @@
         <v>0</v>
       </c>
       <c r="AC51">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD51">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.4</v>
+        <v>13.66</v>
       </c>
       <c r="O52">
-        <v>3.3</v>
+        <v>8.76</v>
       </c>
       <c r="P52">
-        <v>2.51</v>
+        <v>1.1</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8824,16 +8824,16 @@
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB52">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE52">
         <v>0</v>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-10-04 11:00:00</t>
+          <t>2026-10-04 10:00:00</t>
         </is>
       </c>
     </row>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Santa Clara II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Real SC</t>
         </is>
       </c>
       <c r="G54">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-10-04 11:00:00</t>
+          <t>2026-10-04 10:30:00</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G55">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O56">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="P56">
-        <v>5.82</v>
+        <v>0</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-10-04 11:15:00</t>
+          <t>2026-10-04 11:00:00</t>
         </is>
       </c>
     </row>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-10-04 11:30:00</t>
+          <t>2026-10-04 11:15:00</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G58">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Santa Clara II</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Real SC</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G59">

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G25">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X33">
         <v>0</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X73">
         <v>0</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q104">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -1133,34 +1133,34 @@
         <v>2.89</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AA5">
         <v>1.97</v>
@@ -1169,19 +1169,19 @@
         <v>1.79</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2274,34 +2274,34 @@
         <v>2.18</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AA12">
         <v>1.8</v>
@@ -2310,19 +2310,19 @@
         <v>1.96</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="O15">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P15">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="O16">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
+        <v>4.25</v>
+      </c>
+      <c r="Q16">
+        <v>2.42</v>
+      </c>
+      <c r="R16">
         <v>2.3</v>
       </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q17">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G25">
@@ -5860,34 +5860,34 @@
         <v>2.94</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA34">
         <v>1.96</v>
@@ -5896,19 +5896,19 @@
         <v>1.85</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>3.89</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X49">
         <v>0</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X50">
         <v>0</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>13.66</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>8.76</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>13.66</v>
+        <v>2.4</v>
       </c>
       <c r="O52">
-        <v>8.76</v>
+        <v>3.3</v>
       </c>
       <c r="P52">
-        <v>1.1</v>
+        <v>2.51</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8824,16 +8824,16 @@
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC52">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD52">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P53">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="AB53">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9609,55 +9609,55 @@
         <v>5.82</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G59">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Calamocha</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Calamocha</t>
         </is>
       </c>
       <c r="G69">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,34 +13684,34 @@
         <v>2.44</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="AA82">
         <v>1.82</v>
@@ -13720,19 +13720,19 @@
         <v>1.94</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14825,55 +14825,55 @@
         <v>3.67</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14988,55 +14988,55 @@
         <v>10.5</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16811,10 +16811,10 @@
         <v>0</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC101">
         <v>0</v>
@@ -16935,13 +16935,13 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q102">
         <v>0</v>
@@ -17098,13 +17098,13 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="Q103">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q16">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X16">
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="O49">
-        <v>4.56</v>
+        <v>3.96</v>
       </c>
       <c r="P49">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q49">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R49">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T49">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U49">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="V49">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W49">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
         <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z49">
-        <v>4.06</v>
+        <v>3.9</v>
       </c>
       <c r="AA49">
         <v>1.71</v>
       </c>
       <c r="AB49">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="AC49">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="AD49">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="AE49">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF49">
         <v>1.65</v>
       </c>
       <c r="AG49">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK49">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.89</v>
+        <v>13.66</v>
       </c>
       <c r="O50">
-        <v>3.96</v>
+        <v>8.76</v>
       </c>
       <c r="P50">
-        <v>3.75</v>
+        <v>1.1</v>
       </c>
       <c r="Q50">
-        <v>2.32</v>
+        <v>10</v>
       </c>
       <c r="R50">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="S50">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="T50">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>2.54</v>
+        <v>1.95</v>
       </c>
       <c r="V50">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="W50">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="Z50">
-        <v>3.9</v>
+        <v>6.36</v>
       </c>
       <c r="AA50">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="AB50">
-        <v>2.04</v>
+        <v>2.87</v>
       </c>
       <c r="AC50">
-        <v>2.82</v>
+        <v>1.87</v>
       </c>
       <c r="AD50">
-        <v>1.34</v>
+        <v>1.87</v>
       </c>
       <c r="AE50">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="AF50">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG50">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.19</v>
+        <v>5</v>
       </c>
       <c r="AK50">
-        <v>1.85</v>
+        <v>1.03</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>13.66</v>
+        <v>2.4</v>
       </c>
       <c r="O51">
-        <v>8.76</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>1.1</v>
+        <v>2.51</v>
       </c>
       <c r="Q51">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S51">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T51">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U51">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V51">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W51">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y51">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z51">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="AA51">
-        <v>1.39</v>
+        <v>1.82</v>
       </c>
       <c r="AB51">
-        <v>2.87</v>
+        <v>1.93</v>
       </c>
       <c r="AC51">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD51">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE51">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG51">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK51">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
+        <v>1.57</v>
+      </c>
+      <c r="O52">
+        <v>4.56</v>
+      </c>
+      <c r="P52">
+        <v>5.2</v>
+      </c>
+      <c r="Q52">
+        <v>2.3</v>
+      </c>
+      <c r="R52">
+        <v>2.36</v>
+      </c>
+      <c r="S52">
+        <v>1.3</v>
+      </c>
+      <c r="T52">
+        <v>3.3</v>
+      </c>
+      <c r="U52">
         <v>2.4</v>
       </c>
-      <c r="O52">
-        <v>3.3</v>
-      </c>
-      <c r="P52">
-        <v>2.51</v>
-      </c>
-      <c r="Q52">
-        <v>0</v>
-      </c>
-      <c r="R52">
-        <v>0</v>
-      </c>
-      <c r="S52">
-        <v>0</v>
-      </c>
-      <c r="T52">
-        <v>0</v>
-      </c>
-      <c r="U52">
-        <v>0</v>
-      </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X52">
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AA52">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AB52">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10750,16 +10750,16 @@
         <v>0</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U64">
         <v>0</v>
@@ -10774,31 +10774,31 @@
         <v>0</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE64">
         <v>0</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -15477,55 +15477,55 @@
         <v>3.88</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G118">

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.89</v>
+        <v>13.66</v>
       </c>
       <c r="O49">
-        <v>3.96</v>
+        <v>8.76</v>
       </c>
       <c r="P49">
-        <v>3.75</v>
+        <v>1.1</v>
       </c>
       <c r="Q49">
-        <v>2.32</v>
+        <v>10</v>
       </c>
       <c r="R49">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="S49">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="T49">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>2.54</v>
+        <v>1.95</v>
       </c>
       <c r="V49">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="Z49">
-        <v>3.9</v>
+        <v>6.36</v>
       </c>
       <c r="AA49">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="AB49">
-        <v>2.04</v>
+        <v>2.87</v>
       </c>
       <c r="AC49">
-        <v>2.82</v>
+        <v>1.87</v>
       </c>
       <c r="AD49">
-        <v>1.34</v>
+        <v>1.87</v>
       </c>
       <c r="AE49">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="AF49">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG49">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.19</v>
+        <v>5</v>
       </c>
       <c r="AK49">
-        <v>1.85</v>
+        <v>1.03</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>13.66</v>
+        <v>2.4</v>
       </c>
       <c r="O50">
-        <v>8.76</v>
+        <v>3.3</v>
       </c>
       <c r="P50">
-        <v>1.1</v>
+        <v>2.51</v>
       </c>
       <c r="Q50">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S50">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U50">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V50">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z50">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="AA50">
-        <v>1.39</v>
+        <v>1.82</v>
       </c>
       <c r="AB50">
-        <v>2.87</v>
+        <v>1.93</v>
       </c>
       <c r="AC50">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD50">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE50">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG50">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK50">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
+        <v>1.57</v>
+      </c>
+      <c r="O51">
+        <v>4.56</v>
+      </c>
+      <c r="P51">
+        <v>5.2</v>
+      </c>
+      <c r="Q51">
+        <v>2.3</v>
+      </c>
+      <c r="R51">
+        <v>2.36</v>
+      </c>
+      <c r="S51">
+        <v>1.3</v>
+      </c>
+      <c r="T51">
+        <v>3.3</v>
+      </c>
+      <c r="U51">
         <v>2.4</v>
       </c>
-      <c r="O51">
-        <v>3.3</v>
-      </c>
-      <c r="P51">
-        <v>2.51</v>
-      </c>
-      <c r="Q51">
-        <v>0</v>
-      </c>
-      <c r="R51">
-        <v>0</v>
-      </c>
-      <c r="S51">
-        <v>0</v>
-      </c>
-      <c r="T51">
-        <v>0</v>
-      </c>
-      <c r="U51">
-        <v>0</v>
-      </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X51">
         <v>0</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AA51">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AB51">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U52">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V52">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W52">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X52">
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z52">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AB52">
-        <v>2.13</v>
+        <v>2.62</v>
       </c>
       <c r="AC52">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD52">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE52">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF52">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG52">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK52">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X53">
         <v>0</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA53">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AB53">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G59">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Calamocha</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Calamocha</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atletico Madrid III</t>
+          <t>Atlético Tordesillas</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="O71">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P71">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB71">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atlético Tordesillas</t>
+          <t>Atletico Madrid III</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,14 +12045,14 @@
         </is>
       </c>
       <c r="N72">
+        <v>2.38</v>
+      </c>
+      <c r="O72">
+        <v>3.2</v>
+      </c>
+      <c r="P72">
         <v>2.63</v>
       </c>
-      <c r="O72">
-        <v>3.1</v>
-      </c>
-      <c r="P72">
-        <v>2.45</v>
-      </c>
       <c r="Q72">
         <v>0</v>
       </c>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.13</v>
+        <v>1.26</v>
       </c>
       <c r="O89">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="P89">
-        <v>3.67</v>
+        <v>10.5</v>
       </c>
       <c r="Q89">
-        <v>2.8</v>
+        <v>1.59</v>
       </c>
       <c r="R89">
-        <v>2.1</v>
+        <v>2.96</v>
       </c>
       <c r="S89">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="T89">
-        <v>2.56</v>
+        <v>4.5</v>
       </c>
       <c r="U89">
-        <v>2.81</v>
+        <v>1.95</v>
       </c>
       <c r="V89">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="W89">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="Z89">
-        <v>3.2</v>
+        <v>6.25</v>
       </c>
       <c r="AA89">
-        <v>2.09</v>
+        <v>1.3</v>
       </c>
       <c r="AB89">
-        <v>1.79</v>
+        <v>2.97</v>
       </c>
       <c r="AC89">
-        <v>3.14</v>
+        <v>1.86</v>
       </c>
       <c r="AD89">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="AE89">
-        <v>1.06</v>
+        <v>1.35</v>
       </c>
       <c r="AF89">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG89">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AK89">
-        <v>1.65</v>
+        <v>3.84</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.26</v>
+        <v>2.13</v>
       </c>
       <c r="O90">
-        <v>6.4</v>
+        <v>3.35</v>
       </c>
       <c r="P90">
-        <v>10.5</v>
+        <v>3.67</v>
       </c>
       <c r="Q90">
-        <v>1.59</v>
+        <v>2.8</v>
       </c>
       <c r="R90">
-        <v>2.96</v>
+        <v>2.1</v>
       </c>
       <c r="S90">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="T90">
-        <v>4.5</v>
+        <v>2.56</v>
       </c>
       <c r="U90">
-        <v>1.95</v>
+        <v>2.81</v>
       </c>
       <c r="V90">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="W90">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
+        <v>1.26</v>
+      </c>
+      <c r="Z90">
+        <v>3.2</v>
+      </c>
+      <c r="AA90">
+        <v>2.09</v>
+      </c>
+      <c r="AB90">
+        <v>1.79</v>
+      </c>
+      <c r="AC90">
+        <v>3.14</v>
+      </c>
+      <c r="AD90">
+        <v>1.27</v>
+      </c>
+      <c r="AE90">
         <v>1.06</v>
       </c>
-      <c r="Z90">
-        <v>6.25</v>
-      </c>
-      <c r="AA90">
-        <v>1.3</v>
-      </c>
-      <c r="AB90">
-        <v>2.97</v>
-      </c>
-      <c r="AC90">
-        <v>1.86</v>
-      </c>
-      <c r="AD90">
-        <v>1.88</v>
-      </c>
-      <c r="AE90">
-        <v>1.35</v>
-      </c>
       <c r="AF90">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG90">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AK90">
-        <v>3.84</v>
+        <v>1.65</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="O99">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="P99">
-        <v>3.11</v>
+        <v>3.79</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="O100">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="P100">
-        <v>3.79</v>
+        <v>3.11</v>
       </c>
       <c r="Q100">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2600,55 +2600,55 @@
         <v>2.8</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="O15">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
+        <v>4.25</v>
+      </c>
+      <c r="Q15">
+        <v>2.42</v>
+      </c>
+      <c r="R15">
         <v>2.3</v>
       </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
+        <v>3</v>
+      </c>
+      <c r="O16">
+        <v>2.9</v>
+      </c>
+      <c r="P16">
+        <v>2.3</v>
+      </c>
+      <c r="Q16">
+        <v>3.88</v>
+      </c>
+      <c r="R16">
+        <v>2.06</v>
+      </c>
+      <c r="S16">
+        <v>1.52</v>
+      </c>
+      <c r="T16">
+        <v>2.49</v>
+      </c>
+      <c r="U16">
+        <v>3.2</v>
+      </c>
+      <c r="V16">
+        <v>1.31</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>1.03</v>
+      </c>
+      <c r="Y16">
+        <v>1.44</v>
+      </c>
+      <c r="Z16">
+        <v>2.69</v>
+      </c>
+      <c r="AA16">
+        <v>2.26</v>
+      </c>
+      <c r="AB16">
+        <v>1.63</v>
+      </c>
+      <c r="AC16">
+        <v>4.17</v>
+      </c>
+      <c r="AD16">
+        <v>1.19</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
         <v>1.95</v>
       </c>
-      <c r="O16">
-        <v>3.2</v>
-      </c>
-      <c r="P16">
-        <v>3.5</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
-      <c r="V16">
-        <v>0</v>
-      </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>0</v>
-      </c>
-      <c r="Y16">
-        <v>0</v>
-      </c>
-      <c r="Z16">
-        <v>0</v>
-      </c>
-      <c r="AA16">
-        <v>0</v>
-      </c>
-      <c r="AB16">
-        <v>0</v>
-      </c>
-      <c r="AC16">
-        <v>0</v>
-      </c>
-      <c r="AD16">
-        <v>0</v>
-      </c>
-      <c r="AE16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>0</v>
-      </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q17">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="R17">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T17">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
-        <v>2.67</v>
+        <v>2.94</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z17">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="AA17">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AB17">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AC17">
-        <v>3.09</v>
+        <v>3.48</v>
       </c>
       <c r="AD17">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AG17">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.73</v>
+        <v>2.39</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.43</v>
       </c>
       <c r="P18">
-        <v>4.2</v>
+        <v>2.95</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,28 +3406,28 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.39</v>
+        <v>1.48</v>
       </c>
       <c r="O19">
-        <v>3.43</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>2.95</v>
+        <v>6.25</v>
       </c>
       <c r="Q19">
-        <v>3.22</v>
+        <v>2.21</v>
       </c>
       <c r="R19">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="S19">
         <v>1.49</v>
       </c>
       <c r="T19">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="U19">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="V19">
         <v>1.34</v>
@@ -3460,10 +3460,10 @@
         <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="AG19">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK19">
-        <v>1.48</v>
+        <v>2.32</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -10750,16 +10750,16 @@
         <v>0</v>
       </c>
       <c r="Q64">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R64">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S64">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T64">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U64">
         <v>0</v>
@@ -10774,31 +10774,31 @@
         <v>0</v>
       </c>
       <c r="Y64">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z64">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA64">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB64">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC64">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD64">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE64">
         <v>0</v>
       </c>
       <c r="AF64">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG64">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK64">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atlético Tordesillas</t>
+          <t>Atletico Madrid III</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,14 +11882,14 @@
         </is>
       </c>
       <c r="N71">
+        <v>2.38</v>
+      </c>
+      <c r="O71">
+        <v>3.2</v>
+      </c>
+      <c r="P71">
         <v>2.63</v>
       </c>
-      <c r="O71">
-        <v>3.1</v>
-      </c>
-      <c r="P71">
-        <v>2.45</v>
-      </c>
       <c r="Q71">
         <v>0</v>
       </c>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atletico Madrid III</t>
+          <t>Atlético Tordesillas</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="O72">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P72">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB72">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -15181,10 +15181,10 @@
         <v>0</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC91">
         <v>0</v>
@@ -15640,55 +15640,55 @@
         <v>2.8</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X94">
         <v>0</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -16292,55 +16292,55 @@
         <v>3.26</v>
       </c>
       <c r="Q98">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R98">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U98">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V98">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z98">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC98">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD98">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF98">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG98">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16781,34 +16781,34 @@
         <v>4.37</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="AA101">
         <v>1.8</v>
@@ -16817,19 +16817,19 @@
         <v>2</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16944,55 +16944,55 @@
         <v>2.94</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17107,55 +17107,55 @@
         <v>5.05</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17270,55 +17270,55 @@
         <v>2.47</v>
       </c>
       <c r="Q104">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R104">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S104">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T104">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U104">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V104">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W104">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X104">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y104">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z104">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AA104">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB104">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC104">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AD104">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE104">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF104">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG104">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK104">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL104">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.73</v>
+        <v>2.39</v>
       </c>
       <c r="O101">
-        <v>4.16</v>
+        <v>3.46</v>
       </c>
       <c r="P101">
-        <v>4.37</v>
+        <v>2.94</v>
       </c>
       <c r="Q101">
+        <v>3.1</v>
+      </c>
+      <c r="R101">
+        <v>2</v>
+      </c>
+      <c r="S101">
+        <v>1.4</v>
+      </c>
+      <c r="T101">
+        <v>2.75</v>
+      </c>
+      <c r="U101">
+        <v>3.2</v>
+      </c>
+      <c r="V101">
+        <v>1.3</v>
+      </c>
+      <c r="W101">
+        <v>1.06</v>
+      </c>
+      <c r="X101">
+        <v>1.02</v>
+      </c>
+      <c r="Y101">
+        <v>1.34</v>
+      </c>
+      <c r="Z101">
+        <v>2.78</v>
+      </c>
+      <c r="AA101">
         <v>2.12</v>
       </c>
-      <c r="R101">
-        <v>2.41</v>
-      </c>
-      <c r="S101">
-        <v>1.34</v>
-      </c>
-      <c r="T101">
-        <v>3.09</v>
-      </c>
-      <c r="U101">
-        <v>2.49</v>
-      </c>
-      <c r="V101">
-        <v>1.52</v>
-      </c>
-      <c r="W101">
-        <v>1.09</v>
-      </c>
-      <c r="X101">
-        <v>1.03</v>
-      </c>
-      <c r="Y101">
-        <v>1.22</v>
-      </c>
-      <c r="Z101">
-        <v>3.83</v>
-      </c>
-      <c r="AA101">
-        <v>1.8</v>
-      </c>
       <c r="AB101">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AC101">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="AD101">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AE101">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF101">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AG101">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AK101">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.39</v>
+        <v>1.66</v>
       </c>
       <c r="O102">
-        <v>3.46</v>
+        <v>4.01</v>
       </c>
       <c r="P102">
-        <v>2.94</v>
+        <v>5.05</v>
       </c>
       <c r="Q102">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="R102">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S102">
+        <v>1.42</v>
+      </c>
+      <c r="T102">
+        <v>2.74</v>
+      </c>
+      <c r="U102">
+        <v>2.82</v>
+      </c>
+      <c r="V102">
         <v>1.4</v>
       </c>
-      <c r="T102">
-        <v>2.75</v>
-      </c>
-      <c r="U102">
-        <v>3.2</v>
-      </c>
-      <c r="V102">
-        <v>1.3</v>
-      </c>
       <c r="W102">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X102">
         <v>1.02</v>
       </c>
       <c r="Y102">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z102">
-        <v>2.78</v>
+        <v>3.22</v>
       </c>
       <c r="AA102">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AB102">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC102">
-        <v>3.85</v>
+        <v>3.28</v>
       </c>
       <c r="AD102">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AE102">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF102">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG102">
+        <v>1.81</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
+        <v>1.25</v>
+      </c>
+      <c r="AK102">
         <v>1.83</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.26</v>
-      </c>
-      <c r="AK102">
-        <v>1.5</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,80 +17098,80 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="O103">
-        <v>4.01</v>
+        <v>4.16</v>
       </c>
       <c r="P103">
-        <v>5.05</v>
+        <v>4.37</v>
       </c>
       <c r="Q103">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="R103">
+        <v>2.41</v>
+      </c>
+      <c r="S103">
+        <v>1.34</v>
+      </c>
+      <c r="T103">
+        <v>3.09</v>
+      </c>
+      <c r="U103">
+        <v>2.49</v>
+      </c>
+      <c r="V103">
+        <v>1.52</v>
+      </c>
+      <c r="W103">
+        <v>1.09</v>
+      </c>
+      <c r="X103">
+        <v>1.03</v>
+      </c>
+      <c r="Y103">
+        <v>1.22</v>
+      </c>
+      <c r="Z103">
+        <v>3.83</v>
+      </c>
+      <c r="AA103">
+        <v>1.8</v>
+      </c>
+      <c r="AB103">
+        <v>2</v>
+      </c>
+      <c r="AC103">
+        <v>2.75</v>
+      </c>
+      <c r="AD103">
+        <v>1.42</v>
+      </c>
+      <c r="AE103">
+        <v>1.1</v>
+      </c>
+      <c r="AF103">
+        <v>1.76</v>
+      </c>
+      <c r="AG103">
+        <v>1.88</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ103">
+        <v>1.17</v>
+      </c>
+      <c r="AK103">
         <v>2.1</v>
-      </c>
-      <c r="S103">
-        <v>1.42</v>
-      </c>
-      <c r="T103">
-        <v>2.74</v>
-      </c>
-      <c r="U103">
-        <v>2.82</v>
-      </c>
-      <c r="V103">
-        <v>1.4</v>
-      </c>
-      <c r="W103">
-        <v>1.04</v>
-      </c>
-      <c r="X103">
-        <v>1.02</v>
-      </c>
-      <c r="Y103">
-        <v>1.31</v>
-      </c>
-      <c r="Z103">
-        <v>3.22</v>
-      </c>
-      <c r="AA103">
-        <v>2.05</v>
-      </c>
-      <c r="AB103">
-        <v>1.75</v>
-      </c>
-      <c r="AC103">
-        <v>3.28</v>
-      </c>
-      <c r="AD103">
-        <v>1.3</v>
-      </c>
-      <c r="AE103">
-        <v>1.06</v>
-      </c>
-      <c r="AF103">
-        <v>1.83</v>
-      </c>
-      <c r="AG103">
-        <v>1.81</v>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ103">
-        <v>1.25</v>
-      </c>
-      <c r="AK103">
-        <v>1.83</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17433,34 +17433,34 @@
         <v>3.3</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA105">
         <v>2.02</v>
@@ -17469,19 +17469,19 @@
         <v>1.87</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL105">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="O14">
         <v>3.2</v>
       </c>
       <c r="P14">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q14">
-        <v>3.11</v>
+        <v>2.62</v>
       </c>
       <c r="R14">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="S14">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T14">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="U14">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W14">
+        <v>1.02</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>1.34</v>
+      </c>
+      <c r="Z14">
+        <v>3.06</v>
+      </c>
+      <c r="AA14">
+        <v>2.15</v>
+      </c>
+      <c r="AB14">
+        <v>1.66</v>
+      </c>
+      <c r="AC14">
+        <v>3.48</v>
+      </c>
+      <c r="AD14">
+        <v>1.27</v>
+      </c>
+      <c r="AE14">
         <v>1.04</v>
       </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>1.31</v>
-      </c>
-      <c r="Z14">
-        <v>3.22</v>
-      </c>
-      <c r="AA14">
-        <v>2.05</v>
-      </c>
-      <c r="AB14">
-        <v>1.84</v>
-      </c>
-      <c r="AC14">
-        <v>3.28</v>
-      </c>
-      <c r="AD14">
-        <v>1.3</v>
-      </c>
-      <c r="AE14">
-        <v>1.06</v>
-      </c>
       <c r="AF14">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AG14">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK14">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="O15">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="P15">
-        <v>4.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
-        <v>2.42</v>
+        <v>3.88</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="S15">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="T15">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="U15">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
+        <v>1.44</v>
+      </c>
+      <c r="Z15">
+        <v>2.69</v>
+      </c>
+      <c r="AA15">
+        <v>2.26</v>
+      </c>
+      <c r="AB15">
+        <v>1.63</v>
+      </c>
+      <c r="AC15">
+        <v>4.17</v>
+      </c>
+      <c r="AD15">
+        <v>1.19</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>1.95</v>
+      </c>
+      <c r="AG15">
+        <v>1.74</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.28</v>
       </c>
-      <c r="Z15">
-        <v>3.4</v>
-      </c>
-      <c r="AA15">
-        <v>1.9</v>
-      </c>
-      <c r="AB15">
-        <v>1.9</v>
-      </c>
-      <c r="AC15">
-        <v>3.09</v>
-      </c>
-      <c r="AD15">
-        <v>1.34</v>
-      </c>
-      <c r="AE15">
-        <v>1.08</v>
-      </c>
-      <c r="AF15">
-        <v>1.78</v>
-      </c>
-      <c r="AG15">
-        <v>1.91</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.19</v>
-      </c>
       <c r="AK15">
-        <v>1.96</v>
+        <v>1.3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O16">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
-        <v>3.88</v>
+        <v>3.11</v>
       </c>
       <c r="R16">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="S16">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="T16">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="U16">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="V16">
+        <v>1.4</v>
+      </c>
+      <c r="W16">
+        <v>1.04</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
         <v>1.31</v>
       </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>1.03</v>
-      </c>
-      <c r="Y16">
-        <v>1.44</v>
-      </c>
       <c r="Z16">
-        <v>2.69</v>
+        <v>3.22</v>
       </c>
       <c r="AA16">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="AB16">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AC16">
-        <v>4.17</v>
+        <v>3.28</v>
       </c>
       <c r="AD16">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AG16">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="Q17">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
+        <v>1.38</v>
+      </c>
+      <c r="T17">
+        <v>2.88</v>
+      </c>
+      <c r="U17">
+        <v>2.67</v>
+      </c>
+      <c r="V17">
         <v>1.45</v>
       </c>
-      <c r="T17">
-        <v>2.65</v>
-      </c>
-      <c r="U17">
-        <v>2.94</v>
-      </c>
-      <c r="V17">
-        <v>1.37</v>
-      </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
+        <v>1.28</v>
+      </c>
+      <c r="Z17">
+        <v>3.4</v>
+      </c>
+      <c r="AA17">
+        <v>1.9</v>
+      </c>
+      <c r="AB17">
+        <v>1.9</v>
+      </c>
+      <c r="AC17">
+        <v>3.09</v>
+      </c>
+      <c r="AD17">
         <v>1.34</v>
       </c>
-      <c r="Z17">
-        <v>3.06</v>
-      </c>
-      <c r="AA17">
-        <v>2.15</v>
-      </c>
-      <c r="AB17">
-        <v>1.66</v>
-      </c>
-      <c r="AC17">
-        <v>3.48</v>
-      </c>
-      <c r="AD17">
-        <v>1.27</v>
-      </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK17">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,80 +3406,80 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q19">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="R19">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S19">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="T19">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="U19">
-        <v>3.07</v>
+        <v>2.78</v>
       </c>
       <c r="V19">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Z19">
-        <v>2.81</v>
+        <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="AB19">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AC19">
-        <v>3.91</v>
+        <v>3.14</v>
       </c>
       <c r="AD19">
+        <v>1.32</v>
+      </c>
+      <c r="AE19">
+        <v>1.07</v>
+      </c>
+      <c r="AF19">
+        <v>1.84</v>
+      </c>
+      <c r="AG19">
+        <v>1.85</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
         <v>1.21</v>
       </c>
-      <c r="AE19">
-        <v>1.02</v>
-      </c>
-      <c r="AF19">
-        <v>2.23</v>
-      </c>
-      <c r="AG19">
-        <v>1.55</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.18</v>
-      </c>
       <c r="AK19">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="Q20">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="R20">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="T20">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="U20">
-        <v>2.78</v>
+        <v>3.07</v>
       </c>
       <c r="V20">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="W20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z20">
-        <v>3.34</v>
+        <v>2.81</v>
       </c>
       <c r="AA20">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="AB20">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AC20">
-        <v>3.14</v>
+        <v>3.91</v>
       </c>
       <c r="AD20">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF20">
-        <v>1.84</v>
+        <v>2.23</v>
       </c>
       <c r="AG20">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK20">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q34">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="R34">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
+        <v>1.43</v>
+      </c>
+      <c r="T34">
+        <v>2.72</v>
+      </c>
+      <c r="U34">
+        <v>3.19</v>
+      </c>
+      <c r="V34">
+        <v>1.33</v>
+      </c>
+      <c r="W34">
+        <v>1.03</v>
+      </c>
+      <c r="X34">
+        <v>1.03</v>
+      </c>
+      <c r="Y34">
         <v>1.36</v>
       </c>
-      <c r="T34">
-        <v>3</v>
-      </c>
-      <c r="U34">
-        <v>2.7</v>
-      </c>
-      <c r="V34">
-        <v>1.4</v>
-      </c>
-      <c r="W34">
-        <v>1.08</v>
-      </c>
-      <c r="X34">
-        <v>1</v>
-      </c>
-      <c r="Y34">
-        <v>1.3</v>
-      </c>
       <c r="Z34">
-        <v>3.4</v>
+        <v>3.01</v>
       </c>
       <c r="AA34">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="AB34">
+        <v>1.7</v>
+      </c>
+      <c r="AC34">
+        <v>3.87</v>
+      </c>
+      <c r="AD34">
+        <v>1.23</v>
+      </c>
+      <c r="AE34">
+        <v>1.03</v>
+      </c>
+      <c r="AF34">
         <v>1.85</v>
       </c>
-      <c r="AC34">
-        <v>3.4</v>
-      </c>
-      <c r="AD34">
-        <v>1.29</v>
-      </c>
-      <c r="AE34">
-        <v>1.07</v>
-      </c>
-      <c r="AF34">
-        <v>1.73</v>
-      </c>
       <c r="AG34">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK34">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-10-04 09:00:00</t>
+          <t>2026-10-04 08:30:00</t>
         </is>
       </c>
     </row>
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>4.37</v>
+        <v>1.92</v>
       </c>
       <c r="O37">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="P37">
-        <v>1.81</v>
+        <v>3.8</v>
       </c>
       <c r="Q37">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK37">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-10-04 09:30:00</t>
+          <t>2026-10-04 09:00:00</t>
         </is>
       </c>
     </row>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.12</v>
+        <v>4.37</v>
       </c>
       <c r="O38">
-        <v>3.53</v>
+        <v>3.75</v>
       </c>
       <c r="P38">
-        <v>3.41</v>
+        <v>1.81</v>
       </c>
       <c r="Q38">
-        <v>2.72</v>
+        <v>5.55</v>
       </c>
       <c r="R38">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="T38">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="U38">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
       <c r="V38">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W38">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="Z38">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="AA38">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AB38">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AC38">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="AD38">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE38">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF38">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG38">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK38">
-        <v>1.61</v>
+        <v>1.13</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,65 +6666,65 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="O39">
-        <v>3.2</v>
+        <v>3.53</v>
       </c>
       <c r="P39">
-        <v>3.35</v>
+        <v>3.41</v>
       </c>
       <c r="Q39">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R39">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="S39">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="T39">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="U39">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="V39">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W39">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="Z39">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="AA39">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB39">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AC39">
-        <v>3.35</v>
+        <v>3.92</v>
       </c>
       <c r="AD39">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE39">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF39">
+        <v>1.9</v>
+      </c>
+      <c r="AG39">
         <v>1.78</v>
       </c>
-      <c r="AG39">
-        <v>1.89</v>
-      </c>
       <c r="AH39" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.57</v>
+        <v>2.14</v>
       </c>
       <c r="O40">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="P40">
+        <v>3.35</v>
+      </c>
+      <c r="Q40">
         <v>2.68</v>
       </c>
-      <c r="Q40">
-        <v>3.22</v>
-      </c>
       <c r="R40">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="S40">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T40">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="U40">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="V40">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W40">
+        <v>1.04</v>
+      </c>
+      <c r="X40">
         <v>1.02</v>
       </c>
-      <c r="X40">
-        <v>1.01</v>
-      </c>
       <c r="Y40">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="Z40">
-        <v>2.88</v>
+        <v>3.16</v>
       </c>
       <c r="AA40">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AB40">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AC40">
-        <v>3.78</v>
+        <v>3.35</v>
       </c>
       <c r="AD40">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AE40">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF40">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AG40">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK40">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6950,22 +6950,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.79</v>
+        <v>2.57</v>
       </c>
       <c r="O41">
-        <v>3.8</v>
+        <v>3.46</v>
       </c>
       <c r="P41">
-        <v>3.89</v>
+        <v>2.68</v>
       </c>
       <c r="Q41">
-        <v>2.25</v>
+        <v>3.22</v>
       </c>
       <c r="R41">
-        <v>2.45</v>
+        <v>1.99</v>
       </c>
       <c r="S41">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="T41">
-        <v>3.7</v>
+        <v>2.66</v>
       </c>
       <c r="U41">
-        <v>2.1</v>
+        <v>2.94</v>
       </c>
       <c r="V41">
-        <v>1.63</v>
+        <v>1.37</v>
       </c>
       <c r="W41">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="X41">
         <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="Z41">
-        <v>5.25</v>
+        <v>2.88</v>
       </c>
       <c r="AA41">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="AB41">
-        <v>2.36</v>
+        <v>1.66</v>
       </c>
       <c r="AC41">
-        <v>2.18</v>
+        <v>3.78</v>
       </c>
       <c r="AD41">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AE41">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="AF41">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="AG41">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK41">
-        <v>2</v>
+        <v>1.39</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,16 +7155,16 @@
         </is>
       </c>
       <c r="N42">
+        <v>1.79</v>
+      </c>
+      <c r="O42">
+        <v>3.8</v>
+      </c>
+      <c r="P42">
+        <v>3.89</v>
+      </c>
+      <c r="Q42">
         <v>2.25</v>
-      </c>
-      <c r="O42">
-        <v>3.7</v>
-      </c>
-      <c r="P42">
-        <v>2.5</v>
-      </c>
-      <c r="Q42">
-        <v>2.75</v>
       </c>
       <c r="R42">
         <v>2.45</v>
@@ -7173,46 +7173,46 @@
         <v>1.25</v>
       </c>
       <c r="T42">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U42">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V42">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X42">
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z42">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA42">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB42">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="AC42">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AD42">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AE42">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF42">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG42">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK42">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-10-04 10:00:00</t>
+          <t>2026-10-04 09:30:00</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44">
@@ -7602,22 +7602,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="G45">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N45">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G48">
@@ -8254,22 +8254,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>13.66</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>8.76</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q49">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V49">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z49">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC49">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD49">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE49">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG49">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK49">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.4</v>
+        <v>13.66</v>
       </c>
       <c r="O50">
-        <v>3.3</v>
+        <v>8.76</v>
       </c>
       <c r="P50">
-        <v>2.51</v>
+        <v>1.1</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="AA50">
-        <v>1.82</v>
+        <v>1.39</v>
       </c>
       <c r="AB50">
-        <v>1.93</v>
+        <v>2.87</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="O51">
-        <v>4.56</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>5.2</v>
+        <v>2.51</v>
       </c>
       <c r="Q51">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T51">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U51">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W51">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X51">
         <v>0</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z51">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="AA51">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="AB51">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AC51">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD51">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE51">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF51">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG51">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK51">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X52">
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AA52">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AB52">
+        <v>2.13</v>
+      </c>
+      <c r="AC52">
         <v>2.62</v>
       </c>
-      <c r="AC52">
-        <v>0</v>
-      </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P53">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q53">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R53">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S53">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T53">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U53">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="V53">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W53">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X53">
         <v>0</v>
       </c>
       <c r="Y53">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z53">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA53">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AB53">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="AC53">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AD53">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE53">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF53">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG53">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK53">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Santa Clara II</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Real SC</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X54">
         <v>0</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-10-04 10:30:00</t>
+          <t>2026-10-04 10:00:00</t>
         </is>
       </c>
     </row>
@@ -9227,12 +9227,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Santa Clara II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Real SC</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O55">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="P55">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Q55">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="R55">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S55">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T55">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U55">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V55">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W55">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y55">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z55">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA55">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AB55">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AC55">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD55">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE55">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF55">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG55">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK55">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-10-04 11:00:00</t>
+          <t>2026-10-04 10:30:00</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O57">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="P57">
-        <v>5.82</v>
+        <v>0</v>
       </c>
       <c r="Q57">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="R57">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S57">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T57">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U57">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="V57">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W57">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y57">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z57">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="AA57">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB57">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AC57">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD57">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE57">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF57">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG57">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK57">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-10-04 11:15:00</t>
+          <t>2026-10-04 11:00:00</t>
         </is>
       </c>
     </row>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-10-04 11:30:00</t>
+          <t>2026-10-04 11:15:00</t>
         </is>
       </c>
     </row>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G59">
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>De Graafschap W</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G60">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-10-04 11:45:00</t>
+          <t>2026-10-04 11:30:00</t>
         </is>
       </c>
     </row>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>De Graafschap W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G61">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G62">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G63">
@@ -10694,27 +10694,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G64">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-10-04 12:00:00</t>
+          <t>2026-10-04 11:45:00</t>
         </is>
       </c>
     </row>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G65">
@@ -10913,16 +10913,16 @@
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U65">
         <v>0</v>
@@ -10937,31 +10937,31 @@
         <v>0</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE65">
         <v>0</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11025,22 +11025,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Arnedo</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G66">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Arnedo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Calamocha</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>Calamocha</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="G70">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atletico Madrid III</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O71">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P71">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB71">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atlético Tordesillas</t>
+          <t>Atletico Madrid III</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,14 +12045,14 @@
         </is>
       </c>
       <c r="N72">
+        <v>2.38</v>
+      </c>
+      <c r="O72">
+        <v>3.2</v>
+      </c>
+      <c r="P72">
         <v>2.63</v>
       </c>
-      <c r="O72">
-        <v>3.1</v>
-      </c>
-      <c r="P72">
-        <v>2.45</v>
-      </c>
       <c r="Q72">
         <v>0</v>
       </c>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB72">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Atlético Tordesillas</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>3.22</v>
+        <v>2.63</v>
       </c>
       <c r="O73">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="P73">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="Q73">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R73">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S73">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T73">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U73">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="V73">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W73">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X73">
         <v>0</v>
       </c>
       <c r="Y73">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z73">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA73">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB73">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AC73">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD73">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE73">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF73">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG73">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK73">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X74">
         <v>0</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G75">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="G78">
@@ -13139,27 +13139,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G79">
@@ -13182,17 +13182,17 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N79">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O79">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P79">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB79">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>2026-10-04 12:30:00</t>
+          <t>2026-10-04 12:00:00</t>
         </is>
       </c>
     </row>
@@ -13307,22 +13307,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G80">
@@ -13345,68 +13345,68 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N80">
-        <v>2.53</v>
+        <v>1.41</v>
       </c>
       <c r="O80">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="P80">
-        <v>2.66</v>
+        <v>7.1</v>
       </c>
       <c r="Q80">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="R80">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S80">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T80">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U80">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V80">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W80">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X80">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y80">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z80">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="AA80">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AB80">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AC80">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="AD80">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE80">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF80">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG80">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK80">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Savoia</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>1.8</v>
+        <v>2.53</v>
       </c>
       <c r="O81">
-        <v>3.8</v>
+        <v>3.56</v>
       </c>
       <c r="P81">
-        <v>4.39</v>
+        <v>2.66</v>
       </c>
       <c r="Q81">
-        <v>2.27</v>
+        <v>3.29</v>
       </c>
       <c r="R81">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="S81">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T81">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U81">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="V81">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W81">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X81">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z81">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="AA81">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AB81">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC81">
-        <v>3.43</v>
+        <v>3.47</v>
       </c>
       <c r="AD81">
         <v>1.27</v>
       </c>
       <c r="AE81">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF81">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="AG81">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK81">
-        <v>1.95</v>
+        <v>1.41</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,80 +16935,80 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="O102">
-        <v>4.01</v>
+        <v>4.16</v>
       </c>
       <c r="P102">
-        <v>5.05</v>
+        <v>4.37</v>
       </c>
       <c r="Q102">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="R102">
+        <v>2.41</v>
+      </c>
+      <c r="S102">
+        <v>1.34</v>
+      </c>
+      <c r="T102">
+        <v>3.09</v>
+      </c>
+      <c r="U102">
+        <v>2.49</v>
+      </c>
+      <c r="V102">
+        <v>1.52</v>
+      </c>
+      <c r="W102">
+        <v>1.09</v>
+      </c>
+      <c r="X102">
+        <v>1.03</v>
+      </c>
+      <c r="Y102">
+        <v>1.22</v>
+      </c>
+      <c r="Z102">
+        <v>3.83</v>
+      </c>
+      <c r="AA102">
+        <v>1.8</v>
+      </c>
+      <c r="AB102">
+        <v>2</v>
+      </c>
+      <c r="AC102">
+        <v>2.75</v>
+      </c>
+      <c r="AD102">
+        <v>1.42</v>
+      </c>
+      <c r="AE102">
+        <v>1.1</v>
+      </c>
+      <c r="AF102">
+        <v>1.76</v>
+      </c>
+      <c r="AG102">
+        <v>1.88</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ102">
+        <v>1.17</v>
+      </c>
+      <c r="AK102">
         <v>2.1</v>
-      </c>
-      <c r="S102">
-        <v>1.42</v>
-      </c>
-      <c r="T102">
-        <v>2.74</v>
-      </c>
-      <c r="U102">
-        <v>2.82</v>
-      </c>
-      <c r="V102">
-        <v>1.4</v>
-      </c>
-      <c r="W102">
-        <v>1.04</v>
-      </c>
-      <c r="X102">
-        <v>1.02</v>
-      </c>
-      <c r="Y102">
-        <v>1.31</v>
-      </c>
-      <c r="Z102">
-        <v>3.22</v>
-      </c>
-      <c r="AA102">
-        <v>2.05</v>
-      </c>
-      <c r="AB102">
-        <v>1.75</v>
-      </c>
-      <c r="AC102">
-        <v>3.28</v>
-      </c>
-      <c r="AD102">
-        <v>1.3</v>
-      </c>
-      <c r="AE102">
-        <v>1.06</v>
-      </c>
-      <c r="AF102">
-        <v>1.83</v>
-      </c>
-      <c r="AG102">
-        <v>1.81</v>
-      </c>
-      <c r="AH102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ102">
-        <v>1.25</v>
-      </c>
-      <c r="AK102">
-        <v>1.83</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="O103">
-        <v>4.16</v>
+        <v>4.01</v>
       </c>
       <c r="P103">
-        <v>4.37</v>
+        <v>5.05</v>
       </c>
       <c r="Q103">
-        <v>2.12</v>
+        <v>2.6</v>
       </c>
       <c r="R103">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="S103">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="T103">
-        <v>3.09</v>
+        <v>2.74</v>
       </c>
       <c r="U103">
-        <v>2.49</v>
+        <v>2.82</v>
       </c>
       <c r="V103">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W103">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X103">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="Z103">
-        <v>3.83</v>
+        <v>3.22</v>
       </c>
       <c r="AA103">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AB103">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AC103">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="AD103">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE103">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF103">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AG103">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK103">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -18278,10 +18278,10 @@
         <v>0</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC110">
         <v>0</v>
@@ -18411,55 +18411,55 @@
         <v>1.3</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -20041,55 +20041,55 @@
         <v>3.09</v>
       </c>
       <c r="Q121">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R121">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S121">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T121">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U121">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V121">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W121">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y121">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z121">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA121">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB121">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC121">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD121">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE121">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF121">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG121">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK121">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20204,34 +20204,34 @@
         <v>1.77</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA122">
         <v>1.83</v>
@@ -20240,19 +20240,19 @@
         <v>1.92</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL122">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
+        <v>3</v>
+      </c>
+      <c r="O14">
+        <v>2.9</v>
+      </c>
+      <c r="P14">
+        <v>2.3</v>
+      </c>
+      <c r="Q14">
+        <v>3.88</v>
+      </c>
+      <c r="R14">
+        <v>2.06</v>
+      </c>
+      <c r="S14">
+        <v>1.52</v>
+      </c>
+      <c r="T14">
+        <v>2.49</v>
+      </c>
+      <c r="U14">
+        <v>3.2</v>
+      </c>
+      <c r="V14">
+        <v>1.31</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>1.03</v>
+      </c>
+      <c r="Y14">
+        <v>1.44</v>
+      </c>
+      <c r="Z14">
+        <v>2.69</v>
+      </c>
+      <c r="AA14">
+        <v>2.26</v>
+      </c>
+      <c r="AB14">
+        <v>1.63</v>
+      </c>
+      <c r="AC14">
+        <v>4.17</v>
+      </c>
+      <c r="AD14">
+        <v>1.19</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
         <v>1.95</v>
       </c>
-      <c r="O14">
-        <v>3.2</v>
-      </c>
-      <c r="P14">
-        <v>3.5</v>
-      </c>
-      <c r="Q14">
-        <v>2.62</v>
-      </c>
-      <c r="R14">
-        <v>2</v>
-      </c>
-      <c r="S14">
-        <v>1.45</v>
-      </c>
-      <c r="T14">
-        <v>2.65</v>
-      </c>
-      <c r="U14">
-        <v>2.94</v>
-      </c>
-      <c r="V14">
-        <v>1.37</v>
-      </c>
-      <c r="W14">
-        <v>1.02</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>1.34</v>
-      </c>
-      <c r="Z14">
-        <v>3.06</v>
-      </c>
-      <c r="AA14">
-        <v>2.15</v>
-      </c>
-      <c r="AB14">
-        <v>1.66</v>
-      </c>
-      <c r="AC14">
-        <v>3.48</v>
-      </c>
-      <c r="AD14">
-        <v>1.27</v>
-      </c>
-      <c r="AE14">
-        <v>1.04</v>
-      </c>
-      <c r="AF14">
-        <v>1.86</v>
-      </c>
       <c r="AG14">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK14">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O15">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q15">
-        <v>3.88</v>
+        <v>3.11</v>
       </c>
       <c r="R15">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="S15">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="T15">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="U15">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="V15">
+        <v>1.4</v>
+      </c>
+      <c r="W15">
+        <v>1.04</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
         <v>1.31</v>
       </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>1.03</v>
-      </c>
-      <c r="Y15">
-        <v>1.44</v>
-      </c>
       <c r="Z15">
-        <v>2.69</v>
+        <v>3.22</v>
       </c>
       <c r="AA15">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="AB15">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AC15">
-        <v>4.17</v>
+        <v>3.28</v>
       </c>
       <c r="AD15">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AG15">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="Q16">
-        <v>3.11</v>
+        <v>2.42</v>
       </c>
       <c r="R16">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U16">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z16">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="AA16">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB16">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC16">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="AD16">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE16">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG16">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK16">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q17">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="R17">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T17">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
-        <v>2.67</v>
+        <v>2.94</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z17">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="AA17">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AB17">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AC17">
-        <v>3.09</v>
+        <v>3.48</v>
       </c>
       <c r="AD17">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AG17">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O109">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P109">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q109">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="O15">
         <v>3.2</v>
       </c>
       <c r="P15">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q15">
-        <v>3.11</v>
+        <v>2.62</v>
       </c>
       <c r="R15">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="S15">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T15">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="U15">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W15">
+        <v>1.02</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>1.34</v>
+      </c>
+      <c r="Z15">
+        <v>3.06</v>
+      </c>
+      <c r="AA15">
+        <v>2.15</v>
+      </c>
+      <c r="AB15">
+        <v>1.66</v>
+      </c>
+      <c r="AC15">
+        <v>3.48</v>
+      </c>
+      <c r="AD15">
+        <v>1.27</v>
+      </c>
+      <c r="AE15">
         <v>1.04</v>
       </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <v>1.31</v>
-      </c>
-      <c r="Z15">
-        <v>3.22</v>
-      </c>
-      <c r="AA15">
-        <v>2.05</v>
-      </c>
-      <c r="AB15">
-        <v>1.84</v>
-      </c>
-      <c r="AC15">
-        <v>3.28</v>
-      </c>
-      <c r="AD15">
-        <v>1.3</v>
-      </c>
-      <c r="AE15">
-        <v>1.06</v>
-      </c>
       <c r="AF15">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AG15">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK15">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>4.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
-        <v>2.42</v>
+        <v>3.11</v>
       </c>
       <c r="R16">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S16">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T16">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="U16">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="V16">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z16">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="AA16">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB16">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AC16">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="AD16">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE16">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG16">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.96</v>
+        <v>1.49</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="Q17">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
+        <v>1.38</v>
+      </c>
+      <c r="T17">
+        <v>2.88</v>
+      </c>
+      <c r="U17">
+        <v>2.67</v>
+      </c>
+      <c r="V17">
         <v>1.45</v>
       </c>
-      <c r="T17">
-        <v>2.65</v>
-      </c>
-      <c r="U17">
-        <v>2.94</v>
-      </c>
-      <c r="V17">
-        <v>1.37</v>
-      </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
+        <v>1.28</v>
+      </c>
+      <c r="Z17">
+        <v>3.4</v>
+      </c>
+      <c r="AA17">
+        <v>1.9</v>
+      </c>
+      <c r="AB17">
+        <v>1.9</v>
+      </c>
+      <c r="AC17">
+        <v>3.09</v>
+      </c>
+      <c r="AD17">
         <v>1.34</v>
       </c>
-      <c r="Z17">
-        <v>3.06</v>
-      </c>
-      <c r="AA17">
-        <v>2.15</v>
-      </c>
-      <c r="AB17">
-        <v>1.66</v>
-      </c>
-      <c r="AC17">
-        <v>3.48</v>
-      </c>
-      <c r="AD17">
-        <v>1.27</v>
-      </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK17">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
         <v>0</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X70">
         <v>0</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X78">
         <v>0</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE79">
         <v>0</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X85">
         <v>0</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.26</v>
+        <v>2.13</v>
       </c>
       <c r="O89">
-        <v>6.4</v>
+        <v>3.35</v>
       </c>
       <c r="P89">
-        <v>10.5</v>
+        <v>3.67</v>
       </c>
       <c r="Q89">
-        <v>1.59</v>
+        <v>2.8</v>
       </c>
       <c r="R89">
-        <v>2.96</v>
+        <v>2.1</v>
       </c>
       <c r="S89">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="T89">
-        <v>4.5</v>
+        <v>2.56</v>
       </c>
       <c r="U89">
-        <v>1.95</v>
+        <v>2.81</v>
       </c>
       <c r="V89">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="W89">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
+        <v>1.26</v>
+      </c>
+      <c r="Z89">
+        <v>3.2</v>
+      </c>
+      <c r="AA89">
+        <v>2.09</v>
+      </c>
+      <c r="AB89">
+        <v>1.79</v>
+      </c>
+      <c r="AC89">
+        <v>3.14</v>
+      </c>
+      <c r="AD89">
+        <v>1.27</v>
+      </c>
+      <c r="AE89">
         <v>1.06</v>
       </c>
-      <c r="Z89">
-        <v>6.25</v>
-      </c>
-      <c r="AA89">
-        <v>1.3</v>
-      </c>
-      <c r="AB89">
-        <v>2.97</v>
-      </c>
-      <c r="AC89">
-        <v>1.86</v>
-      </c>
-      <c r="AD89">
-        <v>1.88</v>
-      </c>
-      <c r="AE89">
-        <v>1.35</v>
-      </c>
       <c r="AF89">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG89">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AK89">
-        <v>3.84</v>
+        <v>1.65</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.13</v>
+        <v>1.26</v>
       </c>
       <c r="O90">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="P90">
-        <v>3.67</v>
+        <v>10.5</v>
       </c>
       <c r="Q90">
-        <v>2.8</v>
+        <v>1.59</v>
       </c>
       <c r="R90">
-        <v>2.1</v>
+        <v>2.96</v>
       </c>
       <c r="S90">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="T90">
-        <v>2.56</v>
+        <v>4.5</v>
       </c>
       <c r="U90">
-        <v>2.81</v>
+        <v>1.95</v>
       </c>
       <c r="V90">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="W90">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="Z90">
-        <v>3.2</v>
+        <v>6.25</v>
       </c>
       <c r="AA90">
-        <v>2.09</v>
+        <v>1.3</v>
       </c>
       <c r="AB90">
-        <v>1.79</v>
+        <v>2.97</v>
       </c>
       <c r="AC90">
-        <v>3.14</v>
+        <v>1.86</v>
       </c>
       <c r="AD90">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="AE90">
-        <v>1.06</v>
+        <v>1.35</v>
       </c>
       <c r="AF90">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG90">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AK90">
-        <v>1.65</v>
+        <v>3.84</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,13 +17913,13 @@
         </is>
       </c>
       <c r="N108">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="O108">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P108">
-        <v>6.63</v>
+        <v>0</v>
       </c>
       <c r="Q108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,13 +18076,13 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="Q109">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Vanraure Hachinohe</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>4.6</v>
+        <v>2.15</v>
       </c>
       <c r="O2">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="Q2">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="R2">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S2">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="T2">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="U2">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="V2">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="Z2">
-        <v>3.14</v>
+        <v>3.78</v>
       </c>
       <c r="AA2">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AB2">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AC2">
-        <v>3.49</v>
+        <v>2.66</v>
       </c>
       <c r="AD2">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AE2">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF2">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AG2">
-        <v>1.88</v>
+        <v>2.23</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Vanraure Hachinohe</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.15</v>
+        <v>4.6</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P3">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="Q3">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="R3">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S3">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="U3">
-        <v>2.45</v>
+        <v>2.61</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W3">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="Z3">
-        <v>3.78</v>
+        <v>3.14</v>
       </c>
       <c r="AA3">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AB3">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AC3">
-        <v>2.66</v>
+        <v>3.49</v>
       </c>
       <c r="AD3">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AE3">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF3">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AG3">
-        <v>2.23</v>
+        <v>1.88</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK3">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G10">
@@ -1948,55 +1948,55 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O14">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q14">
-        <v>3.88</v>
+        <v>3.11</v>
       </c>
       <c r="R14">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="S14">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="U14">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="V14">
+        <v>1.4</v>
+      </c>
+      <c r="W14">
+        <v>1.04</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
         <v>1.31</v>
       </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>1.03</v>
-      </c>
-      <c r="Y14">
-        <v>1.44</v>
-      </c>
       <c r="Z14">
-        <v>2.69</v>
+        <v>3.22</v>
       </c>
       <c r="AA14">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="AB14">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AC14">
-        <v>4.17</v>
+        <v>3.28</v>
       </c>
       <c r="AD14">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AG14">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="O16">
+        <v>2.9</v>
+      </c>
+      <c r="P16">
+        <v>2.3</v>
+      </c>
+      <c r="Q16">
+        <v>3.88</v>
+      </c>
+      <c r="R16">
+        <v>2.06</v>
+      </c>
+      <c r="S16">
+        <v>1.52</v>
+      </c>
+      <c r="T16">
+        <v>2.49</v>
+      </c>
+      <c r="U16">
         <v>3.2</v>
       </c>
-      <c r="P16">
-        <v>2.8</v>
-      </c>
-      <c r="Q16">
-        <v>3.11</v>
-      </c>
-      <c r="R16">
-        <v>2.19</v>
-      </c>
-      <c r="S16">
-        <v>1.42</v>
-      </c>
-      <c r="T16">
-        <v>2.74</v>
-      </c>
-      <c r="U16">
-        <v>2.82</v>
-      </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="W16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="Z16">
-        <v>3.22</v>
+        <v>2.69</v>
       </c>
       <c r="AA16">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="AB16">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AC16">
-        <v>3.28</v>
+        <v>4.17</v>
       </c>
       <c r="AD16">
+        <v>1.19</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>1.95</v>
+      </c>
+      <c r="AG16">
+        <v>1.74</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.28</v>
+      </c>
+      <c r="AK16">
         <v>1.3</v>
-      </c>
-      <c r="AE16">
-        <v>1.06</v>
-      </c>
-      <c r="AF16">
-        <v>1.77</v>
-      </c>
-      <c r="AG16">
-        <v>1.92</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.25</v>
-      </c>
-      <c r="AK16">
-        <v>1.49</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="Q19">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="R19">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="T19">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="U19">
-        <v>2.78</v>
+        <v>3.07</v>
       </c>
       <c r="V19">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z19">
-        <v>3.34</v>
+        <v>2.81</v>
       </c>
       <c r="AA19">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="AB19">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AC19">
-        <v>3.14</v>
+        <v>3.91</v>
       </c>
       <c r="AD19">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AE19">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>1.84</v>
+        <v>2.23</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK19">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q20">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="R20">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S20">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="T20">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="U20">
-        <v>3.07</v>
+        <v>2.78</v>
       </c>
       <c r="V20">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="W20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Z20">
-        <v>2.81</v>
+        <v>3.34</v>
       </c>
       <c r="AA20">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="AB20">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AC20">
-        <v>3.91</v>
+        <v>3.14</v>
       </c>
       <c r="AD20">
+        <v>1.32</v>
+      </c>
+      <c r="AE20">
+        <v>1.07</v>
+      </c>
+      <c r="AF20">
+        <v>1.84</v>
+      </c>
+      <c r="AG20">
+        <v>1.85</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
         <v>1.21</v>
       </c>
-      <c r="AE20">
-        <v>1.02</v>
-      </c>
-      <c r="AF20">
-        <v>2.23</v>
-      </c>
-      <c r="AG20">
-        <v>1.55</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.18</v>
-      </c>
       <c r="AK20">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X53">
         <v>0</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA53">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AB53">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q54">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R54">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S54">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T54">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U54">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="V54">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W54">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X54">
         <v>0</v>
       </c>
       <c r="Y54">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z54">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA54">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AB54">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="AC54">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AD54">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE54">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF54">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG54">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK54">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9935,55 +9935,55 @@
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Calamocha</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.68</v>
+        <v>1.8</v>
       </c>
       <c r="O68">
-        <v>3.48</v>
+        <v>3.69</v>
       </c>
       <c r="P68">
-        <v>2.55</v>
+        <v>4.52</v>
       </c>
       <c r="Q68">
-        <v>3.46</v>
+        <v>2.4</v>
       </c>
       <c r="R68">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S68">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T68">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="U68">
-        <v>2.93</v>
+        <v>3.2</v>
       </c>
       <c r="V68">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W68">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z68">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="AA68">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AB68">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AC68">
-        <v>3.66</v>
+        <v>3.82</v>
       </c>
       <c r="AD68">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE68">
         <v>1.03</v>
       </c>
       <c r="AF68">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AG68">
+        <v>1.72</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <v>1.22</v>
+      </c>
+      <c r="AK68">
         <v>1.86</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.26</v>
-      </c>
-      <c r="AK68">
-        <v>1.38</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Calamocha</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
+        <v>1.85</v>
+      </c>
+      <c r="O69">
+        <v>3.4</v>
+      </c>
+      <c r="P69">
+        <v>3.75</v>
+      </c>
+      <c r="Q69">
+        <v>2.63</v>
+      </c>
+      <c r="R69">
+        <v>2.23</v>
+      </c>
+      <c r="S69">
+        <v>1.41</v>
+      </c>
+      <c r="T69">
+        <v>2.78</v>
+      </c>
+      <c r="U69">
+        <v>2.78</v>
+      </c>
+      <c r="V69">
+        <v>1.41</v>
+      </c>
+      <c r="W69">
+        <v>1.04</v>
+      </c>
+      <c r="X69">
+        <v>0</v>
+      </c>
+      <c r="Y69">
+        <v>1.32</v>
+      </c>
+      <c r="Z69">
+        <v>3.19</v>
+      </c>
+      <c r="AA69">
+        <v>1.98</v>
+      </c>
+      <c r="AB69">
+        <v>1.83</v>
+      </c>
+      <c r="AC69">
+        <v>3.32</v>
+      </c>
+      <c r="AD69">
+        <v>1.29</v>
+      </c>
+      <c r="AE69">
+        <v>1.06</v>
+      </c>
+      <c r="AF69">
         <v>1.8</v>
       </c>
-      <c r="O69">
-        <v>3.69</v>
-      </c>
-      <c r="P69">
-        <v>4.52</v>
-      </c>
-      <c r="Q69">
-        <v>2.4</v>
-      </c>
-      <c r="R69">
-        <v>2.1</v>
-      </c>
-      <c r="S69">
-        <v>1.4</v>
-      </c>
-      <c r="T69">
-        <v>2.75</v>
-      </c>
-      <c r="U69">
-        <v>3.2</v>
-      </c>
-      <c r="V69">
-        <v>1.3</v>
-      </c>
-      <c r="W69">
-        <v>1.06</v>
-      </c>
-      <c r="X69">
-        <v>1.02</v>
-      </c>
-      <c r="Y69">
-        <v>1.35</v>
-      </c>
-      <c r="Z69">
-        <v>2.74</v>
-      </c>
-      <c r="AA69">
-        <v>2.13</v>
-      </c>
-      <c r="AB69">
-        <v>1.61</v>
-      </c>
-      <c r="AC69">
-        <v>3.82</v>
-      </c>
-      <c r="AD69">
-        <v>1.18</v>
-      </c>
-      <c r="AE69">
-        <v>1.03</v>
-      </c>
-      <c r="AF69">
-        <v>1.98</v>
-      </c>
       <c r="AG69">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>1.22</v>
       </c>
       <c r="AK69">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.85</v>
+        <v>2.72</v>
       </c>
       <c r="O70">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="P70">
-        <v>3.75</v>
+        <v>2.59</v>
       </c>
       <c r="Q70">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S70">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T70">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="U70">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="V70">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W70">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X70">
         <v>0</v>
       </c>
       <c r="Y70">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z70">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB70">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC70">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AD70">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE70">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF70">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG70">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK70">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="O71">
-        <v>3.33</v>
+        <v>3.48</v>
       </c>
       <c r="P71">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,80 +12697,80 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.33</v>
+        <v>2.68</v>
       </c>
       <c r="O76">
-        <v>3.48</v>
+        <v>3.68</v>
       </c>
       <c r="P76">
-        <v>3.02</v>
+        <v>2.45</v>
       </c>
       <c r="Q76">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="R76">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S76">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="T76">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="U76">
-        <v>2.98</v>
+        <v>2.67</v>
       </c>
       <c r="V76">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="W76">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X76">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y76">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="Z76">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="AA76">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="AB76">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC76">
-        <v>3.74</v>
+        <v>3.04</v>
       </c>
       <c r="AD76">
+        <v>1.35</v>
+      </c>
+      <c r="AE76">
+        <v>1.08</v>
+      </c>
+      <c r="AF76">
+        <v>1.7</v>
+      </c>
+      <c r="AG76">
+        <v>2.01</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
         <v>1.23</v>
       </c>
-      <c r="AE76">
-        <v>1.03</v>
-      </c>
-      <c r="AF76">
-        <v>1.86</v>
-      </c>
-      <c r="AG76">
-        <v>1.83</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ76">
-        <v>1.27</v>
-      </c>
       <c r="AK76">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="O77">
-        <v>3.39</v>
+        <v>3.27</v>
       </c>
       <c r="P77">
-        <v>3.11</v>
+        <v>3.17</v>
       </c>
       <c r="Q77">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="R77">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S77">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="T77">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="U77">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="V77">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W77">
+        <v>1.04</v>
+      </c>
+      <c r="X77">
         <v>1.05</v>
       </c>
-      <c r="X77">
-        <v>1.02</v>
-      </c>
       <c r="Y77">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="Z77">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="AA77">
-        <v>2.22</v>
+        <v>2.43</v>
       </c>
       <c r="AB77">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AC77">
-        <v>3.94</v>
+        <v>4.69</v>
       </c>
       <c r="AD77">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AE77">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF77">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AG77">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK77">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,80 +13023,80 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.68</v>
+        <v>2.31</v>
       </c>
       <c r="O78">
-        <v>3.68</v>
+        <v>3.39</v>
       </c>
       <c r="P78">
-        <v>2.45</v>
+        <v>3.11</v>
       </c>
       <c r="Q78">
-        <v>3.32</v>
+        <v>2.88</v>
       </c>
       <c r="R78">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S78">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T78">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="U78">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="V78">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="W78">
         <v>1.05</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
+        <v>1.41</v>
+      </c>
+      <c r="Z78">
+        <v>2.79</v>
+      </c>
+      <c r="AA78">
+        <v>2.22</v>
+      </c>
+      <c r="AB78">
+        <v>1.56</v>
+      </c>
+      <c r="AC78">
+        <v>3.94</v>
+      </c>
+      <c r="AD78">
+        <v>1.21</v>
+      </c>
+      <c r="AE78">
+        <v>1.02</v>
+      </c>
+      <c r="AF78">
+        <v>1.92</v>
+      </c>
+      <c r="AG78">
+        <v>1.77</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
         <v>1.27</v>
       </c>
-      <c r="Z78">
-        <v>3.45</v>
-      </c>
-      <c r="AA78">
-        <v>1.98</v>
-      </c>
-      <c r="AB78">
-        <v>1.83</v>
-      </c>
-      <c r="AC78">
-        <v>3.04</v>
-      </c>
-      <c r="AD78">
-        <v>1.35</v>
-      </c>
-      <c r="AE78">
-        <v>1.08</v>
-      </c>
-      <c r="AF78">
-        <v>1.7</v>
-      </c>
-      <c r="AG78">
-        <v>2.01</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.23</v>
-      </c>
       <c r="AK78">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="O79">
-        <v>3.27</v>
+        <v>3.48</v>
       </c>
       <c r="P79">
-        <v>3.17</v>
+        <v>3.02</v>
       </c>
       <c r="Q79">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="R79">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="S79">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="T79">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="U79">
-        <v>3.34</v>
+        <v>2.98</v>
       </c>
       <c r="V79">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W79">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X79">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="Z79">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="AA79">
-        <v>2.43</v>
+        <v>2.13</v>
       </c>
       <c r="AB79">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="AC79">
-        <v>4.69</v>
+        <v>3.74</v>
       </c>
       <c r="AD79">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF79">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AG79">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK79">
         <v>1.51</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15344,10 +15344,10 @@
         <v>0</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC92">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q10">
-        <v>2.24</v>
+        <v>2.65</v>
       </c>
       <c r="R10">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="S10">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="T10">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="U10">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="V10">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z10">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="AA10">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AB10">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AC10">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AD10">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
         <v>1.83</v>
       </c>
       <c r="AG10">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.65</v>
+        <v>2.24</v>
       </c>
       <c r="R11">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="S11">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T11">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="U11">
-        <v>2.83</v>
+        <v>2.67</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z11">
-        <v>3.2</v>
+        <v>3.64</v>
       </c>
       <c r="AA11">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AB11">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AC11">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE11">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
         <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK11">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="O14">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P14">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="Q14">
-        <v>3.11</v>
+        <v>2.42</v>
       </c>
       <c r="R14">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S14">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T14">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U14">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W14">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z14">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="AA14">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB14">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC14">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="AD14">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE14">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF14">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG14">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK14">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
+        <v>3</v>
+      </c>
+      <c r="O15">
+        <v>2.9</v>
+      </c>
+      <c r="P15">
+        <v>2.3</v>
+      </c>
+      <c r="Q15">
+        <v>3.88</v>
+      </c>
+      <c r="R15">
+        <v>2.06</v>
+      </c>
+      <c r="S15">
+        <v>1.52</v>
+      </c>
+      <c r="T15">
+        <v>2.49</v>
+      </c>
+      <c r="U15">
+        <v>3.2</v>
+      </c>
+      <c r="V15">
+        <v>1.31</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>1.03</v>
+      </c>
+      <c r="Y15">
+        <v>1.44</v>
+      </c>
+      <c r="Z15">
+        <v>2.69</v>
+      </c>
+      <c r="AA15">
+        <v>2.26</v>
+      </c>
+      <c r="AB15">
+        <v>1.63</v>
+      </c>
+      <c r="AC15">
+        <v>4.17</v>
+      </c>
+      <c r="AD15">
+        <v>1.19</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
         <v>1.95</v>
       </c>
-      <c r="O15">
-        <v>3.2</v>
-      </c>
-      <c r="P15">
-        <v>3.5</v>
-      </c>
-      <c r="Q15">
-        <v>2.62</v>
-      </c>
-      <c r="R15">
-        <v>2</v>
-      </c>
-      <c r="S15">
-        <v>1.45</v>
-      </c>
-      <c r="T15">
-        <v>2.65</v>
-      </c>
-      <c r="U15">
-        <v>2.94</v>
-      </c>
-      <c r="V15">
-        <v>1.37</v>
-      </c>
-      <c r="W15">
-        <v>1.02</v>
-      </c>
-      <c r="X15">
-        <v>0</v>
-      </c>
-      <c r="Y15">
-        <v>1.34</v>
-      </c>
-      <c r="Z15">
-        <v>3.06</v>
-      </c>
-      <c r="AA15">
-        <v>2.15</v>
-      </c>
-      <c r="AB15">
-        <v>1.66</v>
-      </c>
-      <c r="AC15">
-        <v>3.48</v>
-      </c>
-      <c r="AD15">
-        <v>1.27</v>
-      </c>
-      <c r="AE15">
-        <v>1.04</v>
-      </c>
-      <c r="AF15">
-        <v>1.86</v>
-      </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK15">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O16">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
-        <v>3.88</v>
+        <v>3.11</v>
       </c>
       <c r="R16">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="S16">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="T16">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="U16">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="V16">
+        <v>1.4</v>
+      </c>
+      <c r="W16">
+        <v>1.04</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
         <v>1.31</v>
       </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>1.03</v>
-      </c>
-      <c r="Y16">
-        <v>1.44</v>
-      </c>
       <c r="Z16">
-        <v>2.69</v>
+        <v>3.22</v>
       </c>
       <c r="AA16">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="AB16">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AC16">
-        <v>4.17</v>
+        <v>3.28</v>
       </c>
       <c r="AD16">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AG16">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q17">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="R17">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T17">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
-        <v>2.67</v>
+        <v>2.94</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z17">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="AA17">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AB17">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AC17">
-        <v>3.09</v>
+        <v>3.48</v>
       </c>
       <c r="AD17">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AG17">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,80 +3406,80 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q19">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="R19">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S19">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="T19">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="U19">
-        <v>3.07</v>
+        <v>2.78</v>
       </c>
       <c r="V19">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Z19">
-        <v>2.81</v>
+        <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="AB19">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AC19">
-        <v>3.91</v>
+        <v>3.14</v>
       </c>
       <c r="AD19">
+        <v>1.32</v>
+      </c>
+      <c r="AE19">
+        <v>1.07</v>
+      </c>
+      <c r="AF19">
+        <v>1.84</v>
+      </c>
+      <c r="AG19">
+        <v>1.85</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
         <v>1.21</v>
       </c>
-      <c r="AE19">
-        <v>1.02</v>
-      </c>
-      <c r="AF19">
-        <v>2.23</v>
-      </c>
-      <c r="AG19">
-        <v>1.55</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.18</v>
-      </c>
       <c r="AK19">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="Q20">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="R20">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="T20">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="U20">
-        <v>2.78</v>
+        <v>3.07</v>
       </c>
       <c r="V20">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="W20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z20">
-        <v>3.34</v>
+        <v>2.81</v>
       </c>
       <c r="AA20">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="AB20">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AC20">
-        <v>3.14</v>
+        <v>3.91</v>
       </c>
       <c r="AD20">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF20">
-        <v>1.84</v>
+        <v>2.23</v>
       </c>
       <c r="AG20">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK20">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.5</v>
+        <v>2.04</v>
       </c>
       <c r="O23">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>3.98</v>
       </c>
       <c r="Q23">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="R23">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S23">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="T23">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="U23">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="V23">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="W23">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y23">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="Z23">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AA23">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="AB23">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AC23">
-        <v>4.85</v>
+        <v>5.38</v>
       </c>
       <c r="AD23">
         <v>1.11</v>
       </c>
       <c r="AE23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AG23">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.19</v>
+        <v>1.73</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.04</v>
+        <v>3.5</v>
       </c>
       <c r="O25">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="P25">
-        <v>3.98</v>
+        <v>2</v>
       </c>
       <c r="Q25">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="R25">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="S25">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="T25">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="U25">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="V25">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="Z25">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AA25">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="AB25">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AC25">
-        <v>5.38</v>
+        <v>4.85</v>
       </c>
       <c r="AD25">
         <v>1.11</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF25">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AG25">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK25">
-        <v>1.73</v>
+        <v>1.19</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>13.66</v>
+        <v>2.4</v>
       </c>
       <c r="O50">
-        <v>8.76</v>
+        <v>3.3</v>
       </c>
       <c r="P50">
-        <v>1.1</v>
+        <v>2.51</v>
       </c>
       <c r="Q50">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S50">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U50">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V50">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z50">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="AA50">
-        <v>1.39</v>
+        <v>1.82</v>
       </c>
       <c r="AB50">
-        <v>2.87</v>
+        <v>1.93</v>
       </c>
       <c r="AC50">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD50">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE50">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG50">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK50">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.4</v>
+        <v>1.89</v>
       </c>
       <c r="O51">
-        <v>3.3</v>
+        <v>3.96</v>
       </c>
       <c r="P51">
-        <v>2.51</v>
+        <v>3.75</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
         <v>0</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA51">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AB51">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.57</v>
+        <v>13.66</v>
       </c>
       <c r="O52">
-        <v>4.56</v>
+        <v>8.76</v>
       </c>
       <c r="P52">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="Q52">
-        <v>2.3</v>
+        <v>10</v>
       </c>
       <c r="R52">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U52">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="V52">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="W52">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="Z52">
-        <v>4.06</v>
+        <v>6.36</v>
       </c>
       <c r="AA52">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="AB52">
-        <v>2.13</v>
+        <v>2.87</v>
       </c>
       <c r="AC52">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="AD52">
-        <v>1.46</v>
+        <v>1.87</v>
       </c>
       <c r="AE52">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AF52">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG52">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="AK52">
-        <v>1.95</v>
+        <v>1.03</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="O53">
-        <v>3.96</v>
+        <v>4.56</v>
       </c>
       <c r="P53">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="Q53">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R53">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="S53">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T53">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U53">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="V53">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W53">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X53">
         <v>0</v>
       </c>
       <c r="Y53">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z53">
-        <v>3.9</v>
+        <v>4.06</v>
       </c>
       <c r="AA53">
         <v>1.71</v>
       </c>
       <c r="AB53">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="AC53">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="AD53">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AE53">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF53">
         <v>1.65</v>
       </c>
       <c r="AG53">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9227,12 +9227,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Santa Clara II</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real SC</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-10-04 10:30:00</t>
+          <t>2026-10-04 11:00:00</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>12</v>
+        <v>1.77</v>
       </c>
       <c r="O56">
-        <v>6.35</v>
+        <v>3.5</v>
       </c>
       <c r="P56">
-        <v>1.14</v>
+        <v>4.14</v>
       </c>
       <c r="Q56">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="R56">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S56">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T56">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U56">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V56">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W56">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X56">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y56">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z56">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA56">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AB56">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AC56">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD56">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE56">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF56">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG56">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK56">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="O57">
-        <v>3.5</v>
+        <v>4.38</v>
       </c>
       <c r="P57">
-        <v>4.14</v>
+        <v>5.82</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-10-04 11:00:00</t>
+          <t>2026-10-04 11:15:00</t>
         </is>
       </c>
     </row>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,81 +9763,81 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O58">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="P58">
-        <v>5.82</v>
+        <v>0</v>
       </c>
       <c r="Q58">
+        <v>2.44</v>
+      </c>
+      <c r="R58">
+        <v>2.19</v>
+      </c>
+      <c r="S58">
+        <v>1.45</v>
+      </c>
+      <c r="T58">
+        <v>2.65</v>
+      </c>
+      <c r="U58">
+        <v>2.94</v>
+      </c>
+      <c r="V58">
+        <v>1.37</v>
+      </c>
+      <c r="W58">
+        <v>1.02</v>
+      </c>
+      <c r="X58">
+        <v>1.01</v>
+      </c>
+      <c r="Y58">
+        <v>1.35</v>
+      </c>
+      <c r="Z58">
+        <v>3.04</v>
+      </c>
+      <c r="AA58">
+        <v>2.07</v>
+      </c>
+      <c r="AB58">
+        <v>1.72</v>
+      </c>
+      <c r="AC58">
+        <v>3.5</v>
+      </c>
+      <c r="AD58">
+        <v>1.26</v>
+      </c>
+      <c r="AE58">
+        <v>1.03</v>
+      </c>
+      <c r="AF58">
+        <v>1.92</v>
+      </c>
+      <c r="AG58">
+        <v>1.77</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
+        <v>1.11</v>
+      </c>
+      <c r="AK58">
         <v>1.96</v>
       </c>
-      <c r="R58">
-        <v>2.38</v>
-      </c>
-      <c r="S58">
-        <v>1.3</v>
-      </c>
-      <c r="T58">
-        <v>3.2</v>
-      </c>
-      <c r="U58">
-        <v>2.64</v>
-      </c>
-      <c r="V58">
-        <v>1.46</v>
-      </c>
-      <c r="W58">
-        <v>1.1</v>
-      </c>
-      <c r="X58">
-        <v>1.02</v>
-      </c>
-      <c r="Y58">
-        <v>1.18</v>
-      </c>
-      <c r="Z58">
-        <v>3.97</v>
-      </c>
-      <c r="AA58">
-        <v>1.73</v>
-      </c>
-      <c r="AB58">
-        <v>2.09</v>
-      </c>
-      <c r="AC58">
-        <v>2.92</v>
-      </c>
-      <c r="AD58">
-        <v>1.4</v>
-      </c>
-      <c r="AE58">
-        <v>1.12</v>
-      </c>
-      <c r="AF58">
-        <v>1.8</v>
-      </c>
-      <c r="AG58">
-        <v>1.96</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.19</v>
-      </c>
-      <c r="AK58">
-        <v>2.26</v>
-      </c>
       <c r="AL58">
         <v>0</v>
       </c>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-10-04 11:15:00</t>
+          <t>2026-10-04 11:30:00</t>
         </is>
       </c>
     </row>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q59">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="R59">
-        <v>2.19</v>
+        <v>1.94</v>
       </c>
       <c r="S59">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="T59">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="U59">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="V59">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W59">
         <v>1.02</v>
       </c>
       <c r="X59">
+        <v>1.02</v>
+      </c>
+      <c r="Y59">
+        <v>1.42</v>
+      </c>
+      <c r="Z59">
+        <v>2.74</v>
+      </c>
+      <c r="AA59">
+        <v>2.25</v>
+      </c>
+      <c r="AB59">
+        <v>1.61</v>
+      </c>
+      <c r="AC59">
+        <v>3.96</v>
+      </c>
+      <c r="AD59">
+        <v>1.17</v>
+      </c>
+      <c r="AE59">
         <v>1.01</v>
       </c>
-      <c r="Y59">
-        <v>1.35</v>
-      </c>
-      <c r="Z59">
-        <v>3.04</v>
-      </c>
-      <c r="AA59">
-        <v>2.07</v>
-      </c>
-      <c r="AB59">
-        <v>1.72</v>
-      </c>
-      <c r="AC59">
-        <v>3.5</v>
-      </c>
-      <c r="AD59">
-        <v>1.26</v>
-      </c>
-      <c r="AE59">
-        <v>1.03</v>
-      </c>
       <c r="AF59">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AG59">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AK59">
-        <v>1.96</v>
+        <v>1.38</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Santa Clara II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Real SC</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q60">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R60">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S60">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T60">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U60">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="V60">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W60">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X60">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y60">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z60">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA60">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB60">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC60">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="AD60">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE60">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF60">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG60">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK60">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,80 +14001,80 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.38</v>
+        <v>4.3</v>
       </c>
       <c r="O84">
-        <v>3.46</v>
+        <v>3.74</v>
       </c>
       <c r="P84">
-        <v>2.94</v>
+        <v>1.83</v>
       </c>
       <c r="Q84">
-        <v>3</v>
+        <v>4.78</v>
       </c>
       <c r="R84">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="S84">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T84">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="U84">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="V84">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="W84">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y84">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z84">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="AA84">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AB84">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC84">
-        <v>3.76</v>
+        <v>3.59</v>
       </c>
       <c r="AD84">
+        <v>1.25</v>
+      </c>
+      <c r="AE84">
+        <v>1.04</v>
+      </c>
+      <c r="AF84">
+        <v>1.87</v>
+      </c>
+      <c r="AG84">
+        <v>1.82</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ84">
         <v>1.23</v>
       </c>
-      <c r="AE84">
-        <v>1.03</v>
-      </c>
-      <c r="AF84">
-        <v>1.83</v>
-      </c>
-      <c r="AG84">
-        <v>1.86</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ84">
-        <v>1.3</v>
-      </c>
       <c r="AK84">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>4.3</v>
+        <v>2.38</v>
       </c>
       <c r="O85">
-        <v>3.74</v>
+        <v>3.46</v>
       </c>
       <c r="P85">
+        <v>2.94</v>
+      </c>
+      <c r="Q85">
+        <v>3</v>
+      </c>
+      <c r="R85">
+        <v>2</v>
+      </c>
+      <c r="S85">
+        <v>1.4</v>
+      </c>
+      <c r="T85">
+        <v>2.75</v>
+      </c>
+      <c r="U85">
+        <v>2.94</v>
+      </c>
+      <c r="V85">
+        <v>1.3</v>
+      </c>
+      <c r="W85">
+        <v>1.06</v>
+      </c>
+      <c r="X85">
+        <v>1.01</v>
+      </c>
+      <c r="Y85">
+        <v>1.38</v>
+      </c>
+      <c r="Z85">
+        <v>2.89</v>
+      </c>
+      <c r="AA85">
+        <v>2.13</v>
+      </c>
+      <c r="AB85">
+        <v>1.71</v>
+      </c>
+      <c r="AC85">
+        <v>3.76</v>
+      </c>
+      <c r="AD85">
+        <v>1.23</v>
+      </c>
+      <c r="AE85">
+        <v>1.03</v>
+      </c>
+      <c r="AF85">
         <v>1.83</v>
       </c>
-      <c r="Q85">
-        <v>4.78</v>
-      </c>
-      <c r="R85">
-        <v>2.21</v>
-      </c>
-      <c r="S85">
-        <v>1.43</v>
-      </c>
-      <c r="T85">
-        <v>2.71</v>
-      </c>
-      <c r="U85">
-        <v>2.86</v>
-      </c>
-      <c r="V85">
-        <v>1.39</v>
-      </c>
-      <c r="W85">
-        <v>1.03</v>
-      </c>
-      <c r="X85">
-        <v>0</v>
-      </c>
-      <c r="Y85">
-        <v>1.36</v>
-      </c>
-      <c r="Z85">
-        <v>2.99</v>
-      </c>
-      <c r="AA85">
-        <v>2.08</v>
-      </c>
-      <c r="AB85">
-        <v>1.75</v>
-      </c>
-      <c r="AC85">
-        <v>3.59</v>
-      </c>
-      <c r="AD85">
-        <v>1.25</v>
-      </c>
-      <c r="AE85">
-        <v>1.04</v>
-      </c>
-      <c r="AF85">
-        <v>1.87</v>
-      </c>
       <c r="AG85">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK85">
-        <v>1.15</v>
+        <v>1.53</v>
       </c>
       <c r="AL85">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.65</v>
+        <v>2.24</v>
       </c>
       <c r="R10">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="S10">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T10">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="U10">
-        <v>2.83</v>
+        <v>2.67</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z10">
-        <v>3.2</v>
+        <v>3.64</v>
       </c>
       <c r="AA10">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AB10">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AC10">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD10">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE10">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
         <v>1.83</v>
       </c>
       <c r="AG10">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK10">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q11">
-        <v>2.24</v>
+        <v>2.65</v>
       </c>
       <c r="R11">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="S11">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="T11">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="U11">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="V11">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z11">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="AA11">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AB11">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AC11">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AD11">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
         <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="O14">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>4.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q14">
-        <v>2.42</v>
+        <v>3.11</v>
       </c>
       <c r="R14">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S14">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="U14">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="V14">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z14">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="AA14">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB14">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AC14">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="AD14">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE14">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG14">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.96</v>
+        <v>1.49</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="Q16">
-        <v>3.11</v>
+        <v>2.42</v>
       </c>
       <c r="R16">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U16">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z16">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="AA16">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB16">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC16">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="AD16">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE16">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG16">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK16">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="Q19">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="R19">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="T19">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="U19">
-        <v>2.78</v>
+        <v>3.07</v>
       </c>
       <c r="V19">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z19">
-        <v>3.34</v>
+        <v>2.81</v>
       </c>
       <c r="AA19">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="AB19">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AC19">
-        <v>3.14</v>
+        <v>3.91</v>
       </c>
       <c r="AD19">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AE19">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>1.84</v>
+        <v>2.23</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK19">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q20">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="R20">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S20">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="T20">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="U20">
-        <v>3.07</v>
+        <v>2.78</v>
       </c>
       <c r="V20">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="W20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Z20">
-        <v>2.81</v>
+        <v>3.34</v>
       </c>
       <c r="AA20">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="AB20">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AC20">
-        <v>3.91</v>
+        <v>3.14</v>
       </c>
       <c r="AD20">
+        <v>1.32</v>
+      </c>
+      <c r="AE20">
+        <v>1.07</v>
+      </c>
+      <c r="AF20">
+        <v>1.84</v>
+      </c>
+      <c r="AG20">
+        <v>1.85</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
         <v>1.21</v>
       </c>
-      <c r="AE20">
-        <v>1.02</v>
-      </c>
-      <c r="AF20">
-        <v>2.23</v>
-      </c>
-      <c r="AG20">
-        <v>1.55</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.18</v>
-      </c>
       <c r="AK20">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.04</v>
+        <v>3.5</v>
       </c>
       <c r="O23">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="P23">
-        <v>3.98</v>
+        <v>2</v>
       </c>
       <c r="Q23">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="R23">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="S23">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="T23">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="U23">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="V23">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W23">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X23">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="Z23">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AA23">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="AB23">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AC23">
-        <v>5.38</v>
+        <v>4.85</v>
       </c>
       <c r="AD23">
         <v>1.11</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF23">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AG23">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK23">
-        <v>1.73</v>
+        <v>1.19</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.5</v>
+        <v>2.04</v>
       </c>
       <c r="O25">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="P25">
-        <v>2</v>
+        <v>3.98</v>
       </c>
       <c r="Q25">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S25">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="T25">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="U25">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="V25">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y25">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="Z25">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AA25">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="AB25">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AC25">
-        <v>4.85</v>
+        <v>5.38</v>
       </c>
       <c r="AD25">
         <v>1.11</v>
       </c>
       <c r="AE25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AG25">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.19</v>
+        <v>1.73</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>13.66</v>
+        <v>1.57</v>
       </c>
       <c r="O52">
-        <v>8.76</v>
+        <v>4.56</v>
       </c>
       <c r="P52">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="Q52">
-        <v>10</v>
+        <v>2.3</v>
       </c>
       <c r="R52">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="S52">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
+        <v>2.4</v>
+      </c>
+      <c r="V52">
+        <v>1.51</v>
+      </c>
+      <c r="W52">
+        <v>1.12</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <v>1.2</v>
+      </c>
+      <c r="Z52">
+        <v>4.06</v>
+      </c>
+      <c r="AA52">
+        <v>1.71</v>
+      </c>
+      <c r="AB52">
+        <v>2.13</v>
+      </c>
+      <c r="AC52">
+        <v>2.62</v>
+      </c>
+      <c r="AD52">
+        <v>1.46</v>
+      </c>
+      <c r="AE52">
+        <v>1.14</v>
+      </c>
+      <c r="AF52">
+        <v>1.65</v>
+      </c>
+      <c r="AG52">
+        <v>2.15</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
+        <v>1.25</v>
+      </c>
+      <c r="AK52">
         <v>1.95</v>
-      </c>
-      <c r="V52">
-        <v>1.73</v>
-      </c>
-      <c r="W52">
-        <v>1.2</v>
-      </c>
-      <c r="X52">
-        <v>1.01</v>
-      </c>
-      <c r="Y52">
-        <v>1.07</v>
-      </c>
-      <c r="Z52">
-        <v>6.36</v>
-      </c>
-      <c r="AA52">
-        <v>1.39</v>
-      </c>
-      <c r="AB52">
-        <v>2.87</v>
-      </c>
-      <c r="AC52">
-        <v>1.87</v>
-      </c>
-      <c r="AD52">
-        <v>1.87</v>
-      </c>
-      <c r="AE52">
-        <v>1.35</v>
-      </c>
-      <c r="AF52">
-        <v>2</v>
-      </c>
-      <c r="AG52">
-        <v>1.75</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>5</v>
-      </c>
-      <c r="AK52">
-        <v>1.03</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="P53">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="Q53">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R53">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S53">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T53">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U53">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V53">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W53">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X53">
         <v>0</v>
       </c>
       <c r="Y53">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z53">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="AA53">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AB53">
-        <v>2.13</v>
+        <v>2.62</v>
       </c>
       <c r="AC53">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AD53">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE53">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF53">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG53">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK53">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>13.66</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>8.76</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="AA54">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AB54">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>4.3</v>
+        <v>2.38</v>
       </c>
       <c r="O84">
-        <v>3.74</v>
+        <v>3.46</v>
       </c>
       <c r="P84">
+        <v>2.94</v>
+      </c>
+      <c r="Q84">
+        <v>3</v>
+      </c>
+      <c r="R84">
+        <v>2</v>
+      </c>
+      <c r="S84">
+        <v>1.4</v>
+      </c>
+      <c r="T84">
+        <v>2.75</v>
+      </c>
+      <c r="U84">
+        <v>2.94</v>
+      </c>
+      <c r="V84">
+        <v>1.3</v>
+      </c>
+      <c r="W84">
+        <v>1.06</v>
+      </c>
+      <c r="X84">
+        <v>1.01</v>
+      </c>
+      <c r="Y84">
+        <v>1.38</v>
+      </c>
+      <c r="Z84">
+        <v>2.89</v>
+      </c>
+      <c r="AA84">
+        <v>2.13</v>
+      </c>
+      <c r="AB84">
+        <v>1.71</v>
+      </c>
+      <c r="AC84">
+        <v>3.76</v>
+      </c>
+      <c r="AD84">
+        <v>1.23</v>
+      </c>
+      <c r="AE84">
+        <v>1.03</v>
+      </c>
+      <c r="AF84">
         <v>1.83</v>
       </c>
-      <c r="Q84">
-        <v>4.78</v>
-      </c>
-      <c r="R84">
-        <v>2.21</v>
-      </c>
-      <c r="S84">
-        <v>1.43</v>
-      </c>
-      <c r="T84">
-        <v>2.71</v>
-      </c>
-      <c r="U84">
-        <v>2.86</v>
-      </c>
-      <c r="V84">
-        <v>1.39</v>
-      </c>
-      <c r="W84">
-        <v>1.03</v>
-      </c>
-      <c r="X84">
-        <v>0</v>
-      </c>
-      <c r="Y84">
-        <v>1.36</v>
-      </c>
-      <c r="Z84">
-        <v>2.99</v>
-      </c>
-      <c r="AA84">
-        <v>2.08</v>
-      </c>
-      <c r="AB84">
-        <v>1.75</v>
-      </c>
-      <c r="AC84">
-        <v>3.59</v>
-      </c>
-      <c r="AD84">
-        <v>1.25</v>
-      </c>
-      <c r="AE84">
-        <v>1.04</v>
-      </c>
-      <c r="AF84">
-        <v>1.87</v>
-      </c>
       <c r="AG84">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK84">
-        <v>1.15</v>
+        <v>1.53</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,80 +14164,80 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.38</v>
+        <v>4.3</v>
       </c>
       <c r="O85">
-        <v>3.46</v>
+        <v>3.74</v>
       </c>
       <c r="P85">
-        <v>2.94</v>
+        <v>1.83</v>
       </c>
       <c r="Q85">
-        <v>3</v>
+        <v>4.78</v>
       </c>
       <c r="R85">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="S85">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T85">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="U85">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="V85">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="W85">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y85">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z85">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="AA85">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AB85">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC85">
-        <v>3.76</v>
+        <v>3.59</v>
       </c>
       <c r="AD85">
+        <v>1.25</v>
+      </c>
+      <c r="AE85">
+        <v>1.04</v>
+      </c>
+      <c r="AF85">
+        <v>1.87</v>
+      </c>
+      <c r="AG85">
+        <v>1.82</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ85">
         <v>1.23</v>
       </c>
-      <c r="AE85">
-        <v>1.03</v>
-      </c>
-      <c r="AF85">
-        <v>1.83</v>
-      </c>
-      <c r="AG85">
-        <v>1.86</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ85">
-        <v>1.3</v>
-      </c>
       <c r="AK85">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.13</v>
+        <v>1.26</v>
       </c>
       <c r="O89">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="P89">
-        <v>3.67</v>
+        <v>10.5</v>
       </c>
       <c r="Q89">
-        <v>2.8</v>
+        <v>1.59</v>
       </c>
       <c r="R89">
-        <v>2.1</v>
+        <v>2.96</v>
       </c>
       <c r="S89">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="T89">
-        <v>2.56</v>
+        <v>4.5</v>
       </c>
       <c r="U89">
-        <v>2.81</v>
+        <v>1.95</v>
       </c>
       <c r="V89">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="W89">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="Z89">
-        <v>3.2</v>
+        <v>6.25</v>
       </c>
       <c r="AA89">
-        <v>2.09</v>
+        <v>1.3</v>
       </c>
       <c r="AB89">
-        <v>1.79</v>
+        <v>2.97</v>
       </c>
       <c r="AC89">
-        <v>3.14</v>
+        <v>1.86</v>
       </c>
       <c r="AD89">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="AE89">
-        <v>1.06</v>
+        <v>1.35</v>
       </c>
       <c r="AF89">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG89">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="AK89">
-        <v>1.65</v>
+        <v>3.84</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.26</v>
+        <v>2.13</v>
       </c>
       <c r="O90">
-        <v>6.4</v>
+        <v>3.35</v>
       </c>
       <c r="P90">
-        <v>10.5</v>
+        <v>3.67</v>
       </c>
       <c r="Q90">
-        <v>1.59</v>
+        <v>2.8</v>
       </c>
       <c r="R90">
-        <v>2.96</v>
+        <v>2.1</v>
       </c>
       <c r="S90">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="T90">
-        <v>4.5</v>
+        <v>2.56</v>
       </c>
       <c r="U90">
-        <v>1.95</v>
+        <v>2.81</v>
       </c>
       <c r="V90">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="W90">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="X90">
         <v>1.01</v>
       </c>
       <c r="Y90">
+        <v>1.26</v>
+      </c>
+      <c r="Z90">
+        <v>3.2</v>
+      </c>
+      <c r="AA90">
+        <v>2.09</v>
+      </c>
+      <c r="AB90">
+        <v>1.79</v>
+      </c>
+      <c r="AC90">
+        <v>3.14</v>
+      </c>
+      <c r="AD90">
+        <v>1.27</v>
+      </c>
+      <c r="AE90">
         <v>1.06</v>
       </c>
-      <c r="Z90">
-        <v>6.25</v>
-      </c>
-      <c r="AA90">
-        <v>1.3</v>
-      </c>
-      <c r="AB90">
-        <v>2.97</v>
-      </c>
-      <c r="AC90">
-        <v>1.86</v>
-      </c>
-      <c r="AD90">
-        <v>1.88</v>
-      </c>
-      <c r="AE90">
-        <v>1.35</v>
-      </c>
       <c r="AF90">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG90">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AK90">
-        <v>3.84</v>
+        <v>1.65</v>
       </c>
       <c r="AL90">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q10">
-        <v>2.24</v>
+        <v>2.65</v>
       </c>
       <c r="R10">
-        <v>2.34</v>
+        <v>2.21</v>
       </c>
       <c r="S10">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="T10">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="U10">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="V10">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z10">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="AA10">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AB10">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="AC10">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AD10">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
         <v>1.83</v>
       </c>
       <c r="AG10">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.65</v>
+        <v>2.24</v>
       </c>
       <c r="R11">
-        <v>2.21</v>
+        <v>2.34</v>
       </c>
       <c r="S11">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="T11">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="U11">
-        <v>2.83</v>
+        <v>2.67</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z11">
-        <v>3.2</v>
+        <v>3.64</v>
       </c>
       <c r="AA11">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AB11">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="AC11">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AE11">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
         <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK11">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="O14">
         <v>3.2</v>
       </c>
       <c r="P14">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q14">
-        <v>3.11</v>
+        <v>2.62</v>
       </c>
       <c r="R14">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="S14">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T14">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="U14">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W14">
+        <v>1.02</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>1.34</v>
+      </c>
+      <c r="Z14">
+        <v>3.06</v>
+      </c>
+      <c r="AA14">
+        <v>2.15</v>
+      </c>
+      <c r="AB14">
+        <v>1.66</v>
+      </c>
+      <c r="AC14">
+        <v>3.48</v>
+      </c>
+      <c r="AD14">
+        <v>1.27</v>
+      </c>
+      <c r="AE14">
         <v>1.04</v>
       </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>1.31</v>
-      </c>
-      <c r="Z14">
-        <v>3.22</v>
-      </c>
-      <c r="AA14">
-        <v>2.05</v>
-      </c>
-      <c r="AB14">
-        <v>1.84</v>
-      </c>
-      <c r="AC14">
-        <v>3.28</v>
-      </c>
-      <c r="AD14">
-        <v>1.3</v>
-      </c>
-      <c r="AE14">
-        <v>1.06</v>
-      </c>
       <c r="AF14">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AG14">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK14">
-        <v>1.49</v>
+        <v>1.68</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O15">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q15">
-        <v>3.88</v>
+        <v>3.11</v>
       </c>
       <c r="R15">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="S15">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="T15">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="U15">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="V15">
+        <v>1.4</v>
+      </c>
+      <c r="W15">
+        <v>1.04</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
         <v>1.31</v>
       </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>1.03</v>
-      </c>
-      <c r="Y15">
-        <v>1.44</v>
-      </c>
       <c r="Z15">
-        <v>2.69</v>
+        <v>3.22</v>
       </c>
       <c r="AA15">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="AB15">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AC15">
-        <v>4.17</v>
+        <v>3.28</v>
       </c>
       <c r="AD15">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AG15">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="P16">
-        <v>4.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q16">
-        <v>2.42</v>
+        <v>3.88</v>
       </c>
       <c r="R16">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="S16">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="T16">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="U16">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="V16">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
+        <v>1.44</v>
+      </c>
+      <c r="Z16">
+        <v>2.69</v>
+      </c>
+      <c r="AA16">
+        <v>2.26</v>
+      </c>
+      <c r="AB16">
+        <v>1.63</v>
+      </c>
+      <c r="AC16">
+        <v>4.17</v>
+      </c>
+      <c r="AD16">
+        <v>1.19</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>1.95</v>
+      </c>
+      <c r="AG16">
+        <v>1.74</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
         <v>1.28</v>
       </c>
-      <c r="Z16">
-        <v>3.4</v>
-      </c>
-      <c r="AA16">
-        <v>1.9</v>
-      </c>
-      <c r="AB16">
-        <v>1.9</v>
-      </c>
-      <c r="AC16">
-        <v>3.09</v>
-      </c>
-      <c r="AD16">
-        <v>1.34</v>
-      </c>
-      <c r="AE16">
-        <v>1.08</v>
-      </c>
-      <c r="AF16">
-        <v>1.78</v>
-      </c>
-      <c r="AG16">
-        <v>1.91</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.19</v>
-      </c>
       <c r="AK16">
-        <v>1.96</v>
+        <v>1.3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="Q17">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
+        <v>1.38</v>
+      </c>
+      <c r="T17">
+        <v>2.88</v>
+      </c>
+      <c r="U17">
+        <v>2.67</v>
+      </c>
+      <c r="V17">
         <v>1.45</v>
       </c>
-      <c r="T17">
-        <v>2.65</v>
-      </c>
-      <c r="U17">
-        <v>2.94</v>
-      </c>
-      <c r="V17">
-        <v>1.37</v>
-      </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
+        <v>1.28</v>
+      </c>
+      <c r="Z17">
+        <v>3.4</v>
+      </c>
+      <c r="AA17">
+        <v>1.9</v>
+      </c>
+      <c r="AB17">
+        <v>1.9</v>
+      </c>
+      <c r="AC17">
+        <v>3.09</v>
+      </c>
+      <c r="AD17">
         <v>1.34</v>
       </c>
-      <c r="Z17">
-        <v>3.06</v>
-      </c>
-      <c r="AA17">
-        <v>2.15</v>
-      </c>
-      <c r="AB17">
-        <v>1.66</v>
-      </c>
-      <c r="AC17">
-        <v>3.48</v>
-      </c>
-      <c r="AD17">
-        <v>1.27</v>
-      </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK17">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,80 +3406,80 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q19">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="R19">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S19">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="T19">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="U19">
-        <v>3.07</v>
+        <v>2.78</v>
       </c>
       <c r="V19">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Z19">
-        <v>2.81</v>
+        <v>3.34</v>
       </c>
       <c r="AA19">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="AB19">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AC19">
-        <v>3.91</v>
+        <v>3.14</v>
       </c>
       <c r="AD19">
+        <v>1.32</v>
+      </c>
+      <c r="AE19">
+        <v>1.07</v>
+      </c>
+      <c r="AF19">
+        <v>1.84</v>
+      </c>
+      <c r="AG19">
+        <v>1.85</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
         <v>1.21</v>
       </c>
-      <c r="AE19">
-        <v>1.02</v>
-      </c>
-      <c r="AF19">
-        <v>2.23</v>
-      </c>
-      <c r="AG19">
-        <v>1.55</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.18</v>
-      </c>
       <c r="AK19">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="Q20">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="R20">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="T20">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="U20">
-        <v>2.78</v>
+        <v>3.07</v>
       </c>
       <c r="V20">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="W20">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z20">
-        <v>3.34</v>
+        <v>2.81</v>
       </c>
       <c r="AA20">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="AB20">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AC20">
-        <v>3.14</v>
+        <v>3.91</v>
       </c>
       <c r="AD20">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF20">
-        <v>1.84</v>
+        <v>2.23</v>
       </c>
       <c r="AG20">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK20">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.5</v>
+        <v>2.04</v>
       </c>
       <c r="O23">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>3.98</v>
       </c>
       <c r="Q23">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="R23">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S23">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="T23">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="U23">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="V23">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="W23">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y23">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="Z23">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="AA23">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="AB23">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AC23">
-        <v>4.85</v>
+        <v>5.38</v>
       </c>
       <c r="AD23">
         <v>1.11</v>
       </c>
       <c r="AE23">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AG23">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK23">
-        <v>1.19</v>
+        <v>1.73</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P24">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="Q24">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="R24">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="S24">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="T24">
-        <v>2.64</v>
+        <v>2.35</v>
       </c>
       <c r="U24">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="V24">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="W24">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X24">
+        <v>1.04</v>
+      </c>
+      <c r="Y24">
+        <v>1.44</v>
+      </c>
+      <c r="Z24">
+        <v>2.43</v>
+      </c>
+      <c r="AA24">
+        <v>2.44</v>
+      </c>
+      <c r="AB24">
+        <v>1.47</v>
+      </c>
+      <c r="AC24">
+        <v>4.85</v>
+      </c>
+      <c r="AD24">
+        <v>1.11</v>
+      </c>
+      <c r="AE24">
         <v>1.01</v>
       </c>
-      <c r="Y24">
-        <v>1.35</v>
-      </c>
-      <c r="Z24">
-        <v>3.01</v>
-      </c>
-      <c r="AA24">
-        <v>2.06</v>
-      </c>
-      <c r="AB24">
-        <v>1.76</v>
-      </c>
-      <c r="AC24">
-        <v>3.56</v>
-      </c>
-      <c r="AD24">
-        <v>1.26</v>
-      </c>
-      <c r="AE24">
-        <v>1.04</v>
-      </c>
       <c r="AF24">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AG24">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK24">
-        <v>1.83</v>
+        <v>1.19</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="O25">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="Q25">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="R25">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="S25">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="T25">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="U25">
-        <v>3.52</v>
+        <v>2.96</v>
       </c>
       <c r="V25">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X25">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="Z25">
-        <v>2.33</v>
+        <v>3.01</v>
       </c>
       <c r="AA25">
-        <v>2.64</v>
+        <v>2.06</v>
       </c>
       <c r="AB25">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="AC25">
-        <v>5.38</v>
+        <v>3.56</v>
       </c>
       <c r="AD25">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF25">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="AG25">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="O51">
-        <v>3.96</v>
+        <v>4.56</v>
       </c>
       <c r="P51">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="Q51">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R51">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="S51">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U51">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="V51">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X51">
         <v>0</v>
       </c>
       <c r="Y51">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
-        <v>3.9</v>
+        <v>4.06</v>
       </c>
       <c r="AA51">
         <v>1.71</v>
       </c>
       <c r="AB51">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="AC51">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="AD51">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AE51">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF51">
         <v>1.65</v>
       </c>
       <c r="AG51">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK51">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="O52">
-        <v>4.56</v>
+        <v>3.96</v>
       </c>
       <c r="P52">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q52">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R52">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U52">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="V52">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W52">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X52">
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z52">
-        <v>4.06</v>
+        <v>3.9</v>
       </c>
       <c r="AA52">
         <v>1.71</v>
       </c>
       <c r="AB52">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="AC52">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="AD52">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="AE52">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF52">
         <v>1.65</v>
       </c>
       <c r="AG52">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10913,16 +10913,16 @@
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R65">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S65">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T65">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U65">
         <v>0</v>
@@ -10937,31 +10937,31 @@
         <v>0</v>
       </c>
       <c r="Y65">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z65">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA65">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB65">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC65">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD65">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE65">
         <v>0</v>
       </c>
       <c r="AF65">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG65">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK65">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="O78">
-        <v>3.39</v>
+        <v>3.48</v>
       </c>
       <c r="P78">
-        <v>3.11</v>
+        <v>3.02</v>
       </c>
       <c r="Q78">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="R78">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="S78">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T78">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U78">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="V78">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W78">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z78">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="AA78">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="AB78">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AC78">
-        <v>3.94</v>
+        <v>3.74</v>
       </c>
       <c r="AD78">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE78">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF78">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AG78">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>1.27</v>
       </c>
       <c r="AK78">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="O79">
-        <v>3.48</v>
+        <v>3.39</v>
       </c>
       <c r="P79">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="Q79">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="R79">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="S79">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T79">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="U79">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="V79">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W79">
+        <v>1.05</v>
+      </c>
+      <c r="X79">
         <v>1.02</v>
       </c>
-      <c r="X79">
-        <v>1.01</v>
-      </c>
       <c r="Y79">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z79">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="AA79">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AB79">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AC79">
-        <v>3.74</v>
+        <v>3.94</v>
       </c>
       <c r="AD79">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE79">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF79">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AG79">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>1.27</v>
       </c>
       <c r="AK79">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AL79">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
+        <v>3</v>
+      </c>
+      <c r="O14">
+        <v>2.9</v>
+      </c>
+      <c r="P14">
+        <v>2.3</v>
+      </c>
+      <c r="Q14">
+        <v>3.88</v>
+      </c>
+      <c r="R14">
+        <v>2.06</v>
+      </c>
+      <c r="S14">
+        <v>1.52</v>
+      </c>
+      <c r="T14">
+        <v>2.49</v>
+      </c>
+      <c r="U14">
+        <v>3.2</v>
+      </c>
+      <c r="V14">
+        <v>1.31</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>1.03</v>
+      </c>
+      <c r="Y14">
+        <v>1.44</v>
+      </c>
+      <c r="Z14">
+        <v>2.69</v>
+      </c>
+      <c r="AA14">
+        <v>2.26</v>
+      </c>
+      <c r="AB14">
+        <v>1.63</v>
+      </c>
+      <c r="AC14">
+        <v>4.17</v>
+      </c>
+      <c r="AD14">
+        <v>1.19</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
         <v>1.95</v>
       </c>
-      <c r="O14">
-        <v>3.2</v>
-      </c>
-      <c r="P14">
-        <v>3.5</v>
-      </c>
-      <c r="Q14">
-        <v>2.62</v>
-      </c>
-      <c r="R14">
-        <v>2</v>
-      </c>
-      <c r="S14">
-        <v>1.45</v>
-      </c>
-      <c r="T14">
-        <v>2.65</v>
-      </c>
-      <c r="U14">
-        <v>2.94</v>
-      </c>
-      <c r="V14">
-        <v>1.37</v>
-      </c>
-      <c r="W14">
-        <v>1.02</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>1.34</v>
-      </c>
-      <c r="Z14">
-        <v>3.06</v>
-      </c>
-      <c r="AA14">
-        <v>2.15</v>
-      </c>
-      <c r="AB14">
-        <v>1.66</v>
-      </c>
-      <c r="AC14">
-        <v>3.48</v>
-      </c>
-      <c r="AD14">
-        <v>1.27</v>
-      </c>
-      <c r="AE14">
-        <v>1.04</v>
-      </c>
-      <c r="AF14">
-        <v>1.86</v>
-      </c>
       <c r="AG14">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK14">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="O15">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="Q15">
-        <v>3.11</v>
+        <v>2.42</v>
       </c>
       <c r="R15">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T15">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U15">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z15">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="AA15">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB15">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC15">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="AD15">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG15">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK15">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O16">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
-        <v>3.88</v>
+        <v>3.11</v>
       </c>
       <c r="R16">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="S16">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="T16">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="U16">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="V16">
+        <v>1.4</v>
+      </c>
+      <c r="W16">
+        <v>1.04</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
         <v>1.31</v>
       </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>1.03</v>
-      </c>
-      <c r="Y16">
-        <v>1.44</v>
-      </c>
       <c r="Z16">
-        <v>2.69</v>
+        <v>3.22</v>
       </c>
       <c r="AA16">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="AB16">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AC16">
-        <v>4.17</v>
+        <v>3.28</v>
       </c>
       <c r="AD16">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AG16">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q17">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="R17">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T17">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
-        <v>2.67</v>
+        <v>2.94</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z17">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="AA17">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AB17">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AC17">
-        <v>3.09</v>
+        <v>3.48</v>
       </c>
       <c r="AD17">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AG17">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.04</v>
+        <v>3.5</v>
       </c>
       <c r="O23">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="P23">
-        <v>3.98</v>
+        <v>2</v>
       </c>
       <c r="Q23">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="R23">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="S23">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="T23">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="U23">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="V23">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W23">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X23">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="Z23">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AA23">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="AB23">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AC23">
-        <v>5.38</v>
+        <v>4.85</v>
       </c>
       <c r="AD23">
         <v>1.11</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF23">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AG23">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK23">
-        <v>1.73</v>
+        <v>1.19</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="O24">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>2</v>
+        <v>4.33</v>
       </c>
       <c r="Q24">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="R24">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="S24">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="T24">
-        <v>2.35</v>
+        <v>2.64</v>
       </c>
       <c r="U24">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="V24">
+        <v>1.37</v>
+      </c>
+      <c r="W24">
+        <v>1.02</v>
+      </c>
+      <c r="X24">
+        <v>1.01</v>
+      </c>
+      <c r="Y24">
+        <v>1.35</v>
+      </c>
+      <c r="Z24">
+        <v>3.01</v>
+      </c>
+      <c r="AA24">
+        <v>2.06</v>
+      </c>
+      <c r="AB24">
+        <v>1.76</v>
+      </c>
+      <c r="AC24">
+        <v>3.56</v>
+      </c>
+      <c r="AD24">
         <v>1.26</v>
       </c>
-      <c r="W24">
+      <c r="AE24">
         <v>1.04</v>
       </c>
-      <c r="X24">
-        <v>1.04</v>
-      </c>
-      <c r="Y24">
-        <v>1.44</v>
-      </c>
-      <c r="Z24">
-        <v>2.43</v>
-      </c>
-      <c r="AA24">
-        <v>2.44</v>
-      </c>
-      <c r="AB24">
-        <v>1.47</v>
-      </c>
-      <c r="AC24">
-        <v>4.85</v>
-      </c>
-      <c r="AD24">
-        <v>1.11</v>
-      </c>
-      <c r="AE24">
-        <v>1.01</v>
-      </c>
       <c r="AF24">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AG24">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK24">
-        <v>1.19</v>
+        <v>1.83</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P25">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="Q25">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="S25">
+        <v>1.53</v>
+      </c>
+      <c r="T25">
+        <v>2.38</v>
+      </c>
+      <c r="U25">
+        <v>3.52</v>
+      </c>
+      <c r="V25">
+        <v>1.22</v>
+      </c>
+      <c r="W25">
+        <v>1.03</v>
+      </c>
+      <c r="X25">
+        <v>1.07</v>
+      </c>
+      <c r="Y25">
+        <v>1.59</v>
+      </c>
+      <c r="Z25">
+        <v>2.33</v>
+      </c>
+      <c r="AA25">
+        <v>2.64</v>
+      </c>
+      <c r="AB25">
         <v>1.46</v>
       </c>
-      <c r="T25">
-        <v>2.64</v>
-      </c>
-      <c r="U25">
-        <v>2.96</v>
-      </c>
-      <c r="V25">
-        <v>1.37</v>
-      </c>
-      <c r="W25">
-        <v>1.02</v>
-      </c>
-      <c r="X25">
-        <v>1.01</v>
-      </c>
-      <c r="Y25">
-        <v>1.35</v>
-      </c>
-      <c r="Z25">
-        <v>3.01</v>
-      </c>
-      <c r="AA25">
-        <v>2.06</v>
-      </c>
-      <c r="AB25">
-        <v>1.76</v>
-      </c>
       <c r="AC25">
-        <v>3.56</v>
+        <v>5.38</v>
       </c>
       <c r="AD25">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AE25">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="AG25">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q34">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK34">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.57</v>
+        <v>13.66</v>
       </c>
       <c r="O51">
-        <v>4.56</v>
+        <v>8.76</v>
       </c>
       <c r="P51">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="Q51">
-        <v>2.3</v>
+        <v>10</v>
       </c>
       <c r="R51">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="T51">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U51">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="W51">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="Z51">
-        <v>4.06</v>
+        <v>6.36</v>
       </c>
       <c r="AA51">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="AB51">
-        <v>2.13</v>
+        <v>2.87</v>
       </c>
       <c r="AC51">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="AD51">
-        <v>1.46</v>
+        <v>1.87</v>
       </c>
       <c r="AE51">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AF51">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG51">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="AK51">
-        <v>1.95</v>
+        <v>1.03</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O52">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P52">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q52">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S52">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T52">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U52">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="V52">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W52">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X52">
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z52">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="AB52">
-        <v>2.04</v>
+        <v>2.62</v>
       </c>
       <c r="AC52">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AD52">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE52">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF52">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG52">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK52">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X53">
         <v>0</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AA53">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AB53">
+        <v>2.13</v>
+      </c>
+      <c r="AC53">
         <v>2.62</v>
       </c>
-      <c r="AC53">
-        <v>0</v>
-      </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,80 +9111,80 @@
         </is>
       </c>
       <c r="N54">
-        <v>13.66</v>
+        <v>1.89</v>
       </c>
       <c r="O54">
-        <v>8.76</v>
+        <v>3.96</v>
       </c>
       <c r="P54">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="Q54">
-        <v>10</v>
+        <v>2.32</v>
       </c>
       <c r="R54">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="S54">
+        <v>1.32</v>
+      </c>
+      <c r="T54">
+        <v>3.12</v>
+      </c>
+      <c r="U54">
+        <v>2.54</v>
+      </c>
+      <c r="V54">
+        <v>1.47</v>
+      </c>
+      <c r="W54">
+        <v>1.11</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <v>1.21</v>
+      </c>
+      <c r="Z54">
+        <v>3.9</v>
+      </c>
+      <c r="AA54">
+        <v>1.71</v>
+      </c>
+      <c r="AB54">
+        <v>2.04</v>
+      </c>
+      <c r="AC54">
+        <v>2.82</v>
+      </c>
+      <c r="AD54">
+        <v>1.34</v>
+      </c>
+      <c r="AE54">
+        <v>1.09</v>
+      </c>
+      <c r="AF54">
+        <v>1.65</v>
+      </c>
+      <c r="AG54">
+        <v>2.05</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ54">
         <v>1.19</v>
       </c>
-      <c r="T54">
-        <v>4</v>
-      </c>
-      <c r="U54">
-        <v>1.95</v>
-      </c>
-      <c r="V54">
-        <v>1.73</v>
-      </c>
-      <c r="W54">
-        <v>1.2</v>
-      </c>
-      <c r="X54">
-        <v>1.01</v>
-      </c>
-      <c r="Y54">
-        <v>1.07</v>
-      </c>
-      <c r="Z54">
-        <v>6.36</v>
-      </c>
-      <c r="AA54">
-        <v>1.39</v>
-      </c>
-      <c r="AB54">
-        <v>2.87</v>
-      </c>
-      <c r="AC54">
-        <v>1.87</v>
-      </c>
-      <c r="AD54">
-        <v>1.87</v>
-      </c>
-      <c r="AE54">
-        <v>1.35</v>
-      </c>
-      <c r="AF54">
-        <v>2</v>
-      </c>
-      <c r="AG54">
-        <v>1.75</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ54">
-        <v>5</v>
-      </c>
       <c r="AK54">
-        <v>1.03</v>
+        <v>1.85</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -10913,16 +10913,16 @@
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U65">
         <v>0</v>
@@ -10937,31 +10937,31 @@
         <v>0</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE65">
         <v>0</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,80 +14001,80 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.38</v>
+        <v>4.3</v>
       </c>
       <c r="O84">
-        <v>3.46</v>
+        <v>3.74</v>
       </c>
       <c r="P84">
-        <v>2.94</v>
+        <v>1.83</v>
       </c>
       <c r="Q84">
-        <v>3</v>
+        <v>4.78</v>
       </c>
       <c r="R84">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="S84">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T84">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="U84">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="V84">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="W84">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y84">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z84">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="AA84">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AB84">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC84">
-        <v>3.76</v>
+        <v>3.59</v>
       </c>
       <c r="AD84">
+        <v>1.25</v>
+      </c>
+      <c r="AE84">
+        <v>1.04</v>
+      </c>
+      <c r="AF84">
+        <v>1.87</v>
+      </c>
+      <c r="AG84">
+        <v>1.82</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ84">
         <v>1.23</v>
       </c>
-      <c r="AE84">
-        <v>1.03</v>
-      </c>
-      <c r="AF84">
-        <v>1.83</v>
-      </c>
-      <c r="AG84">
-        <v>1.86</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ84">
-        <v>1.3</v>
-      </c>
       <c r="AK84">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>4.3</v>
+        <v>2.38</v>
       </c>
       <c r="O85">
-        <v>3.74</v>
+        <v>3.46</v>
       </c>
       <c r="P85">
+        <v>2.94</v>
+      </c>
+      <c r="Q85">
+        <v>3</v>
+      </c>
+      <c r="R85">
+        <v>2</v>
+      </c>
+      <c r="S85">
+        <v>1.4</v>
+      </c>
+      <c r="T85">
+        <v>2.75</v>
+      </c>
+      <c r="U85">
+        <v>2.94</v>
+      </c>
+      <c r="V85">
+        <v>1.3</v>
+      </c>
+      <c r="W85">
+        <v>1.06</v>
+      </c>
+      <c r="X85">
+        <v>1.01</v>
+      </c>
+      <c r="Y85">
+        <v>1.38</v>
+      </c>
+      <c r="Z85">
+        <v>2.89</v>
+      </c>
+      <c r="AA85">
+        <v>2.13</v>
+      </c>
+      <c r="AB85">
+        <v>1.71</v>
+      </c>
+      <c r="AC85">
+        <v>3.76</v>
+      </c>
+      <c r="AD85">
+        <v>1.23</v>
+      </c>
+      <c r="AE85">
+        <v>1.03</v>
+      </c>
+      <c r="AF85">
         <v>1.83</v>
       </c>
-      <c r="Q85">
-        <v>4.78</v>
-      </c>
-      <c r="R85">
-        <v>2.21</v>
-      </c>
-      <c r="S85">
-        <v>1.43</v>
-      </c>
-      <c r="T85">
-        <v>2.71</v>
-      </c>
-      <c r="U85">
-        <v>2.86</v>
-      </c>
-      <c r="V85">
-        <v>1.39</v>
-      </c>
-      <c r="W85">
-        <v>1.03</v>
-      </c>
-      <c r="X85">
-        <v>0</v>
-      </c>
-      <c r="Y85">
-        <v>1.36</v>
-      </c>
-      <c r="Z85">
-        <v>2.99</v>
-      </c>
-      <c r="AA85">
-        <v>2.08</v>
-      </c>
-      <c r="AB85">
-        <v>1.75</v>
-      </c>
-      <c r="AC85">
-        <v>3.59</v>
-      </c>
-      <c r="AD85">
-        <v>1.25</v>
-      </c>
-      <c r="AE85">
-        <v>1.04</v>
-      </c>
-      <c r="AF85">
-        <v>1.87</v>
-      </c>
       <c r="AG85">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK85">
-        <v>1.15</v>
+        <v>1.53</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G116">
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,13 +19380,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="Q117">
         <v>0</v>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-10-04 17:30:00</t>
+          <t>2026-10-04 18:00:00</t>
         </is>
       </c>
     </row>
@@ -19496,27 +19496,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G118">
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-10-04 17:30:00</t>
+          <t>2026-10-04 18:30:00</t>
         </is>
       </c>
     </row>
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
+        <v>1.98</v>
+      </c>
+      <c r="O119">
+        <v>3.6</v>
+      </c>
+      <c r="P119">
+        <v>3.09</v>
+      </c>
+      <c r="Q119">
+        <v>2.53</v>
+      </c>
+      <c r="R119">
+        <v>2.3</v>
+      </c>
+      <c r="S119">
+        <v>1.22</v>
+      </c>
+      <c r="T119">
+        <v>3.44</v>
+      </c>
+      <c r="U119">
+        <v>2.27</v>
+      </c>
+      <c r="V119">
         <v>1.57</v>
       </c>
-      <c r="O119">
-        <v>3.22</v>
-      </c>
-      <c r="P119">
-        <v>6.31</v>
-      </c>
-      <c r="Q119">
-        <v>0</v>
-      </c>
-      <c r="R119">
-        <v>0</v>
-      </c>
-      <c r="S119">
-        <v>0</v>
-      </c>
-      <c r="T119">
-        <v>0</v>
-      </c>
-      <c r="U119">
-        <v>0</v>
-      </c>
-      <c r="V119">
-        <v>0</v>
-      </c>
       <c r="W119">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y119">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z119">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA119">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB119">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC119">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD119">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE119">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF119">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG119">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK119">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-10-04 18:00:00</t>
+          <t>2026-10-04 19:00:00</t>
         </is>
       </c>
     </row>
@@ -19822,27 +19822,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-10-04 18:30:00</t>
+          <t>2026-10-04 19:00:00</t>
         </is>
       </c>
     </row>
@@ -19985,12 +19985,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,81 +20032,81 @@
         </is>
       </c>
       <c r="N121">
-        <v>1.98</v>
+        <v>3.73</v>
       </c>
       <c r="O121">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P121">
-        <v>3.09</v>
+        <v>1.77</v>
       </c>
       <c r="Q121">
-        <v>2.53</v>
+        <v>4.2</v>
       </c>
       <c r="R121">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S121">
+        <v>1.29</v>
+      </c>
+      <c r="T121">
+        <v>3.3</v>
+      </c>
+      <c r="U121">
+        <v>2.45</v>
+      </c>
+      <c r="V121">
+        <v>1.45</v>
+      </c>
+      <c r="W121">
+        <v>1.08</v>
+      </c>
+      <c r="X121">
+        <v>1.04</v>
+      </c>
+      <c r="Y121">
+        <v>1.17</v>
+      </c>
+      <c r="Z121">
+        <v>2.9</v>
+      </c>
+      <c r="AA121">
+        <v>1.83</v>
+      </c>
+      <c r="AB121">
+        <v>1.92</v>
+      </c>
+      <c r="AC121">
+        <v>2.38</v>
+      </c>
+      <c r="AD121">
+        <v>1.42</v>
+      </c>
+      <c r="AE121">
+        <v>1.09</v>
+      </c>
+      <c r="AF121">
+        <v>1.5</v>
+      </c>
+      <c r="AG121">
+        <v>1.85</v>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ121">
+        <v>1.25</v>
+      </c>
+      <c r="AK121">
         <v>1.22</v>
       </c>
-      <c r="T121">
-        <v>3.44</v>
-      </c>
-      <c r="U121">
-        <v>2.27</v>
-      </c>
-      <c r="V121">
-        <v>1.57</v>
-      </c>
-      <c r="W121">
-        <v>1.1</v>
-      </c>
-      <c r="X121">
-        <v>1</v>
-      </c>
-      <c r="Y121">
-        <v>1.16</v>
-      </c>
-      <c r="Z121">
-        <v>4.65</v>
-      </c>
-      <c r="AA121">
-        <v>1.54</v>
-      </c>
-      <c r="AB121">
-        <v>2.27</v>
-      </c>
-      <c r="AC121">
-        <v>2.35</v>
-      </c>
-      <c r="AD121">
-        <v>1.47</v>
-      </c>
-      <c r="AE121">
-        <v>1.15</v>
-      </c>
-      <c r="AF121">
-        <v>1.48</v>
-      </c>
-      <c r="AG121">
-        <v>2.45</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ121">
-        <v>1.19</v>
-      </c>
-      <c r="AK121">
-        <v>1.62</v>
-      </c>
       <c r="AL121">
         <v>0</v>
       </c>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-10-04 19:00:00</t>
+          <t>2026-10-04 20:00:00</t>
         </is>
       </c>
     </row>
@@ -20148,27 +20148,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="O122">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="P122">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q122">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R122">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S122">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T122">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U122">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V122">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W122">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X122">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y122">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z122">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AA122">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB122">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC122">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD122">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE122">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF122">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG122">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK122">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20299,7 +20299,7 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>2026-10-04 20:00:00</t>
+          <t>2026-10-04 21:30:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2111,55 +2111,55 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X11">
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O14">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q14">
-        <v>3.88</v>
+        <v>3.11</v>
       </c>
       <c r="R14">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="S14">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="U14">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="V14">
+        <v>1.4</v>
+      </c>
+      <c r="W14">
+        <v>1.04</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
         <v>1.31</v>
       </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>1.03</v>
-      </c>
-      <c r="Y14">
-        <v>1.44</v>
-      </c>
       <c r="Z14">
-        <v>2.69</v>
+        <v>3.22</v>
       </c>
       <c r="AA14">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="AB14">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AC14">
-        <v>4.17</v>
+        <v>3.28</v>
       </c>
       <c r="AD14">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AG14">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="O15">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q15">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S15">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T15">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U15">
-        <v>2.67</v>
+        <v>2.94</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z15">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="AA15">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AB15">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AC15">
-        <v>3.09</v>
+        <v>3.48</v>
       </c>
       <c r="AD15">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AE15">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF15">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AG15">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK15">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="O16">
+        <v>2.9</v>
+      </c>
+      <c r="P16">
+        <v>2.3</v>
+      </c>
+      <c r="Q16">
+        <v>3.88</v>
+      </c>
+      <c r="R16">
+        <v>2.06</v>
+      </c>
+      <c r="S16">
+        <v>1.52</v>
+      </c>
+      <c r="T16">
+        <v>2.49</v>
+      </c>
+      <c r="U16">
         <v>3.2</v>
       </c>
-      <c r="P16">
-        <v>2.8</v>
-      </c>
-      <c r="Q16">
-        <v>3.11</v>
-      </c>
-      <c r="R16">
-        <v>2.19</v>
-      </c>
-      <c r="S16">
-        <v>1.42</v>
-      </c>
-      <c r="T16">
-        <v>2.74</v>
-      </c>
-      <c r="U16">
-        <v>2.82</v>
-      </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="W16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="Z16">
-        <v>3.22</v>
+        <v>2.69</v>
       </c>
       <c r="AA16">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="AB16">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AC16">
-        <v>3.28</v>
+        <v>4.17</v>
       </c>
       <c r="AD16">
+        <v>1.19</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>1.95</v>
+      </c>
+      <c r="AG16">
+        <v>1.74</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.28</v>
+      </c>
+      <c r="AK16">
         <v>1.3</v>
-      </c>
-      <c r="AE16">
-        <v>1.06</v>
-      </c>
-      <c r="AF16">
-        <v>1.77</v>
-      </c>
-      <c r="AG16">
-        <v>1.92</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.25</v>
-      </c>
-      <c r="AK16">
-        <v>1.49</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="Q17">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
+        <v>1.38</v>
+      </c>
+      <c r="T17">
+        <v>2.88</v>
+      </c>
+      <c r="U17">
+        <v>2.67</v>
+      </c>
+      <c r="V17">
         <v>1.45</v>
       </c>
-      <c r="T17">
-        <v>2.65</v>
-      </c>
-      <c r="U17">
-        <v>2.94</v>
-      </c>
-      <c r="V17">
-        <v>1.37</v>
-      </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
+        <v>1.28</v>
+      </c>
+      <c r="Z17">
+        <v>3.4</v>
+      </c>
+      <c r="AA17">
+        <v>1.9</v>
+      </c>
+      <c r="AB17">
+        <v>1.9</v>
+      </c>
+      <c r="AC17">
+        <v>3.09</v>
+      </c>
+      <c r="AD17">
         <v>1.34</v>
       </c>
-      <c r="Z17">
-        <v>3.06</v>
-      </c>
-      <c r="AA17">
-        <v>2.15</v>
-      </c>
-      <c r="AB17">
-        <v>1.66</v>
-      </c>
-      <c r="AC17">
-        <v>3.48</v>
-      </c>
-      <c r="AD17">
-        <v>1.27</v>
-      </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK17">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P24">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="Q24">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="R24">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="S24">
+        <v>1.53</v>
+      </c>
+      <c r="T24">
+        <v>2.38</v>
+      </c>
+      <c r="U24">
+        <v>3.52</v>
+      </c>
+      <c r="V24">
+        <v>1.22</v>
+      </c>
+      <c r="W24">
+        <v>1.03</v>
+      </c>
+      <c r="X24">
+        <v>1.07</v>
+      </c>
+      <c r="Y24">
+        <v>1.59</v>
+      </c>
+      <c r="Z24">
+        <v>2.33</v>
+      </c>
+      <c r="AA24">
+        <v>2.64</v>
+      </c>
+      <c r="AB24">
         <v>1.46</v>
       </c>
-      <c r="T24">
-        <v>2.64</v>
-      </c>
-      <c r="U24">
-        <v>2.96</v>
-      </c>
-      <c r="V24">
-        <v>1.37</v>
-      </c>
-      <c r="W24">
-        <v>1.02</v>
-      </c>
-      <c r="X24">
-        <v>1.01</v>
-      </c>
-      <c r="Y24">
-        <v>1.35</v>
-      </c>
-      <c r="Z24">
-        <v>3.01</v>
-      </c>
-      <c r="AA24">
-        <v>2.06</v>
-      </c>
-      <c r="AB24">
-        <v>1.76</v>
-      </c>
       <c r="AC24">
-        <v>3.56</v>
+        <v>5.38</v>
       </c>
       <c r="AD24">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AE24">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="AG24">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="O25">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="Q25">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="R25">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="S25">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="T25">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="U25">
-        <v>3.52</v>
+        <v>2.96</v>
       </c>
       <c r="V25">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X25">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="Z25">
-        <v>2.33</v>
+        <v>3.01</v>
       </c>
       <c r="AA25">
-        <v>2.64</v>
+        <v>2.06</v>
       </c>
       <c r="AB25">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="AC25">
-        <v>5.38</v>
+        <v>3.56</v>
       </c>
       <c r="AD25">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF25">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="AG25">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>13.66</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>8.76</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S51">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T51">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U51">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V51">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W51">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y51">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z51">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="AA51">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB51">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="AC51">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD51">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE51">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG51">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK51">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X52">
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA52">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AB52">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.89</v>
+        <v>13.66</v>
       </c>
       <c r="O54">
-        <v>3.96</v>
+        <v>8.76</v>
       </c>
       <c r="P54">
-        <v>3.75</v>
+        <v>1.1</v>
       </c>
       <c r="Q54">
-        <v>2.32</v>
+        <v>10</v>
       </c>
       <c r="R54">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="S54">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="T54">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="U54">
-        <v>2.54</v>
+        <v>1.95</v>
       </c>
       <c r="V54">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="W54">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="Z54">
-        <v>3.9</v>
+        <v>6.36</v>
       </c>
       <c r="AA54">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="AB54">
-        <v>2.04</v>
+        <v>2.87</v>
       </c>
       <c r="AC54">
-        <v>2.82</v>
+        <v>1.87</v>
       </c>
       <c r="AD54">
-        <v>1.34</v>
+        <v>1.87</v>
       </c>
       <c r="AE54">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="AF54">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG54">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.19</v>
+        <v>5</v>
       </c>
       <c r="AK54">
-        <v>1.85</v>
+        <v>1.03</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9772,55 +9772,55 @@
         <v>0</v>
       </c>
       <c r="Q58">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="R58">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S58">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T58">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U58">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="V58">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W58">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y58">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z58">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA58">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB58">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC58">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD58">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE58">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF58">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG58">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK58">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>4.3</v>
+        <v>2.38</v>
       </c>
       <c r="O84">
-        <v>3.74</v>
+        <v>3.46</v>
       </c>
       <c r="P84">
+        <v>2.94</v>
+      </c>
+      <c r="Q84">
+        <v>3</v>
+      </c>
+      <c r="R84">
+        <v>2</v>
+      </c>
+      <c r="S84">
+        <v>1.4</v>
+      </c>
+      <c r="T84">
+        <v>2.75</v>
+      </c>
+      <c r="U84">
+        <v>2.94</v>
+      </c>
+      <c r="V84">
+        <v>1.3</v>
+      </c>
+      <c r="W84">
+        <v>1.06</v>
+      </c>
+      <c r="X84">
+        <v>1.01</v>
+      </c>
+      <c r="Y84">
+        <v>1.38</v>
+      </c>
+      <c r="Z84">
+        <v>2.89</v>
+      </c>
+      <c r="AA84">
+        <v>2.13</v>
+      </c>
+      <c r="AB84">
+        <v>1.71</v>
+      </c>
+      <c r="AC84">
+        <v>3.76</v>
+      </c>
+      <c r="AD84">
+        <v>1.23</v>
+      </c>
+      <c r="AE84">
+        <v>1.03</v>
+      </c>
+      <c r="AF84">
         <v>1.83</v>
       </c>
-      <c r="Q84">
-        <v>4.78</v>
-      </c>
-      <c r="R84">
-        <v>2.21</v>
-      </c>
-      <c r="S84">
-        <v>1.43</v>
-      </c>
-      <c r="T84">
-        <v>2.71</v>
-      </c>
-      <c r="U84">
-        <v>2.86</v>
-      </c>
-      <c r="V84">
-        <v>1.39</v>
-      </c>
-      <c r="W84">
-        <v>1.03</v>
-      </c>
-      <c r="X84">
-        <v>0</v>
-      </c>
-      <c r="Y84">
-        <v>1.36</v>
-      </c>
-      <c r="Z84">
-        <v>2.99</v>
-      </c>
-      <c r="AA84">
-        <v>2.08</v>
-      </c>
-      <c r="AB84">
-        <v>1.75</v>
-      </c>
-      <c r="AC84">
-        <v>3.59</v>
-      </c>
-      <c r="AD84">
-        <v>1.25</v>
-      </c>
-      <c r="AE84">
-        <v>1.04</v>
-      </c>
-      <c r="AF84">
-        <v>1.87</v>
-      </c>
       <c r="AG84">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK84">
-        <v>1.15</v>
+        <v>1.53</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,80 +14164,80 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.38</v>
+        <v>4.3</v>
       </c>
       <c r="O85">
-        <v>3.46</v>
+        <v>3.74</v>
       </c>
       <c r="P85">
-        <v>2.94</v>
+        <v>1.83</v>
       </c>
       <c r="Q85">
-        <v>3</v>
+        <v>4.78</v>
       </c>
       <c r="R85">
-        <v>2</v>
+        <v>2.21</v>
       </c>
       <c r="S85">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T85">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="U85">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="V85">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="W85">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y85">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z85">
-        <v>2.89</v>
+        <v>2.99</v>
       </c>
       <c r="AA85">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AB85">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC85">
-        <v>3.76</v>
+        <v>3.59</v>
       </c>
       <c r="AD85">
+        <v>1.25</v>
+      </c>
+      <c r="AE85">
+        <v>1.04</v>
+      </c>
+      <c r="AF85">
+        <v>1.87</v>
+      </c>
+      <c r="AG85">
+        <v>1.82</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ85">
         <v>1.23</v>
       </c>
-      <c r="AE85">
-        <v>1.03</v>
-      </c>
-      <c r="AF85">
-        <v>1.83</v>
-      </c>
-      <c r="AG85">
-        <v>1.86</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ85">
-        <v>1.3</v>
-      </c>
       <c r="AK85">
-        <v>1.53</v>
+        <v>1.15</v>
       </c>
       <c r="AL85">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="O15">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="Q15">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="R15">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
+        <v>1.38</v>
+      </c>
+      <c r="T15">
+        <v>2.88</v>
+      </c>
+      <c r="U15">
+        <v>2.67</v>
+      </c>
+      <c r="V15">
         <v>1.45</v>
       </c>
-      <c r="T15">
-        <v>2.65</v>
-      </c>
-      <c r="U15">
-        <v>2.94</v>
-      </c>
-      <c r="V15">
-        <v>1.37</v>
-      </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
         <v>0</v>
       </c>
       <c r="Y15">
+        <v>1.28</v>
+      </c>
+      <c r="Z15">
+        <v>3.4</v>
+      </c>
+      <c r="AA15">
+        <v>1.9</v>
+      </c>
+      <c r="AB15">
+        <v>1.9</v>
+      </c>
+      <c r="AC15">
+        <v>3.09</v>
+      </c>
+      <c r="AD15">
         <v>1.34</v>
       </c>
-      <c r="Z15">
-        <v>3.06</v>
-      </c>
-      <c r="AA15">
-        <v>2.15</v>
-      </c>
-      <c r="AB15">
-        <v>1.66</v>
-      </c>
-      <c r="AC15">
-        <v>3.48</v>
-      </c>
-      <c r="AD15">
-        <v>1.27</v>
-      </c>
       <c r="AE15">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF15">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK15">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q17">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="R17">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T17">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
-        <v>2.67</v>
+        <v>2.94</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z17">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="AA17">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AB17">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AC17">
-        <v>3.09</v>
+        <v>3.48</v>
       </c>
       <c r="AD17">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AG17">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="O24">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="Q24">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="R24">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="S24">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="T24">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="U24">
-        <v>3.52</v>
+        <v>2.96</v>
       </c>
       <c r="V24">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="W24">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X24">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="Z24">
-        <v>2.33</v>
+        <v>3.01</v>
       </c>
       <c r="AA24">
-        <v>2.64</v>
+        <v>2.06</v>
       </c>
       <c r="AB24">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="AC24">
-        <v>5.38</v>
+        <v>3.56</v>
       </c>
       <c r="AD24">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="AG24">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK24">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P25">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="Q25">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="S25">
+        <v>1.53</v>
+      </c>
+      <c r="T25">
+        <v>2.38</v>
+      </c>
+      <c r="U25">
+        <v>3.52</v>
+      </c>
+      <c r="V25">
+        <v>1.22</v>
+      </c>
+      <c r="W25">
+        <v>1.03</v>
+      </c>
+      <c r="X25">
+        <v>1.07</v>
+      </c>
+      <c r="Y25">
+        <v>1.59</v>
+      </c>
+      <c r="Z25">
+        <v>2.33</v>
+      </c>
+      <c r="AA25">
+        <v>2.64</v>
+      </c>
+      <c r="AB25">
         <v>1.46</v>
       </c>
-      <c r="T25">
-        <v>2.64</v>
-      </c>
-      <c r="U25">
-        <v>2.96</v>
-      </c>
-      <c r="V25">
-        <v>1.37</v>
-      </c>
-      <c r="W25">
-        <v>1.02</v>
-      </c>
-      <c r="X25">
-        <v>1.01</v>
-      </c>
-      <c r="Y25">
-        <v>1.35</v>
-      </c>
-      <c r="Z25">
-        <v>3.01</v>
-      </c>
-      <c r="AA25">
-        <v>2.06</v>
-      </c>
-      <c r="AB25">
-        <v>1.76</v>
-      </c>
       <c r="AC25">
-        <v>3.56</v>
+        <v>5.38</v>
       </c>
       <c r="AD25">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AE25">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="AG25">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.89</v>
+        <v>13.66</v>
       </c>
       <c r="O52">
-        <v>3.96</v>
+        <v>8.76</v>
       </c>
       <c r="P52">
-        <v>3.75</v>
+        <v>1.1</v>
       </c>
       <c r="Q52">
-        <v>2.32</v>
+        <v>10</v>
       </c>
       <c r="R52">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="S52">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="T52">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="U52">
-        <v>2.54</v>
+        <v>1.95</v>
       </c>
       <c r="V52">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="W52">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="Z52">
-        <v>3.9</v>
+        <v>6.36</v>
       </c>
       <c r="AA52">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="AB52">
-        <v>2.04</v>
+        <v>2.87</v>
       </c>
       <c r="AC52">
-        <v>2.82</v>
+        <v>1.87</v>
       </c>
       <c r="AD52">
-        <v>1.34</v>
+        <v>1.87</v>
       </c>
       <c r="AE52">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="AF52">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG52">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.19</v>
+        <v>5</v>
       </c>
       <c r="AK52">
-        <v>1.85</v>
+        <v>1.03</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="O53">
-        <v>4.56</v>
+        <v>3.96</v>
       </c>
       <c r="P53">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q53">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R53">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="S53">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T53">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U53">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="V53">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W53">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X53">
         <v>0</v>
       </c>
       <c r="Y53">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z53">
-        <v>4.06</v>
+        <v>3.9</v>
       </c>
       <c r="AA53">
         <v>1.71</v>
       </c>
       <c r="AB53">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="AC53">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="AD53">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="AE53">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF53">
         <v>1.65</v>
       </c>
       <c r="AG53">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK53">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,80 +9111,80 @@
         </is>
       </c>
       <c r="N54">
-        <v>13.66</v>
+        <v>1.57</v>
       </c>
       <c r="O54">
-        <v>8.76</v>
+        <v>4.56</v>
       </c>
       <c r="P54">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="Q54">
-        <v>10</v>
+        <v>2.3</v>
       </c>
       <c r="R54">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="S54">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="T54">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U54">
+        <v>2.4</v>
+      </c>
+      <c r="V54">
+        <v>1.51</v>
+      </c>
+      <c r="W54">
+        <v>1.12</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <v>1.2</v>
+      </c>
+      <c r="Z54">
+        <v>4.06</v>
+      </c>
+      <c r="AA54">
+        <v>1.71</v>
+      </c>
+      <c r="AB54">
+        <v>2.13</v>
+      </c>
+      <c r="AC54">
+        <v>2.62</v>
+      </c>
+      <c r="AD54">
+        <v>1.46</v>
+      </c>
+      <c r="AE54">
+        <v>1.14</v>
+      </c>
+      <c r="AF54">
+        <v>1.65</v>
+      </c>
+      <c r="AG54">
+        <v>2.15</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ54">
+        <v>1.25</v>
+      </c>
+      <c r="AK54">
         <v>1.95</v>
-      </c>
-      <c r="V54">
-        <v>1.73</v>
-      </c>
-      <c r="W54">
-        <v>1.2</v>
-      </c>
-      <c r="X54">
-        <v>1.01</v>
-      </c>
-      <c r="Y54">
-        <v>1.07</v>
-      </c>
-      <c r="Z54">
-        <v>6.36</v>
-      </c>
-      <c r="AA54">
-        <v>1.39</v>
-      </c>
-      <c r="AB54">
-        <v>2.87</v>
-      </c>
-      <c r="AC54">
-        <v>1.87</v>
-      </c>
-      <c r="AD54">
-        <v>1.87</v>
-      </c>
-      <c r="AE54">
-        <v>1.35</v>
-      </c>
-      <c r="AF54">
-        <v>2</v>
-      </c>
-      <c r="AG54">
-        <v>1.75</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ54">
-        <v>5</v>
-      </c>
-      <c r="AK54">
-        <v>1.03</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9802,10 +9802,10 @@
         <v>0</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC58">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2111,34 +2111,34 @@
         <v>4.82</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AA11">
         <v>1.88</v>
@@ -2147,19 +2147,19 @@
         <v>1.93</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="O14">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P14">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="Q14">
-        <v>3.11</v>
+        <v>2.42</v>
       </c>
       <c r="R14">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S14">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T14">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U14">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W14">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z14">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="AA14">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB14">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC14">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="AD14">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE14">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF14">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG14">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK14">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="O15">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q15">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S15">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T15">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U15">
-        <v>2.67</v>
+        <v>2.94</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z15">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="AA15">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AB15">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AC15">
-        <v>3.09</v>
+        <v>3.48</v>
       </c>
       <c r="AD15">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AE15">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF15">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AG15">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK15">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O16">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
-        <v>3.88</v>
+        <v>3.11</v>
       </c>
       <c r="R16">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="S16">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="T16">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="U16">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="V16">
+        <v>1.4</v>
+      </c>
+      <c r="W16">
+        <v>1.04</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
         <v>1.31</v>
       </c>
-      <c r="W16">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>1.03</v>
-      </c>
-      <c r="Y16">
-        <v>1.44</v>
-      </c>
       <c r="Z16">
-        <v>2.69</v>
+        <v>3.22</v>
       </c>
       <c r="AA16">
-        <v>2.26</v>
+        <v>2.05</v>
       </c>
       <c r="AB16">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AC16">
-        <v>4.17</v>
+        <v>3.28</v>
       </c>
       <c r="AD16">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AG16">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
+        <v>3</v>
+      </c>
+      <c r="O17">
+        <v>2.9</v>
+      </c>
+      <c r="P17">
+        <v>2.3</v>
+      </c>
+      <c r="Q17">
+        <v>3.88</v>
+      </c>
+      <c r="R17">
+        <v>2.06</v>
+      </c>
+      <c r="S17">
+        <v>1.52</v>
+      </c>
+      <c r="T17">
+        <v>2.49</v>
+      </c>
+      <c r="U17">
+        <v>3.2</v>
+      </c>
+      <c r="V17">
+        <v>1.31</v>
+      </c>
+      <c r="W17">
+        <v>1.05</v>
+      </c>
+      <c r="X17">
+        <v>1.03</v>
+      </c>
+      <c r="Y17">
+        <v>1.44</v>
+      </c>
+      <c r="Z17">
+        <v>2.69</v>
+      </c>
+      <c r="AA17">
+        <v>2.26</v>
+      </c>
+      <c r="AB17">
+        <v>1.63</v>
+      </c>
+      <c r="AC17">
+        <v>4.17</v>
+      </c>
+      <c r="AD17">
+        <v>1.19</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
         <v>1.95</v>
       </c>
-      <c r="O17">
-        <v>3.2</v>
-      </c>
-      <c r="P17">
-        <v>3.5</v>
-      </c>
-      <c r="Q17">
-        <v>2.62</v>
-      </c>
-      <c r="R17">
-        <v>2</v>
-      </c>
-      <c r="S17">
-        <v>1.45</v>
-      </c>
-      <c r="T17">
-        <v>2.65</v>
-      </c>
-      <c r="U17">
-        <v>2.94</v>
-      </c>
-      <c r="V17">
-        <v>1.37</v>
-      </c>
-      <c r="W17">
-        <v>1.02</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>1.34</v>
-      </c>
-      <c r="Z17">
-        <v>3.06</v>
-      </c>
-      <c r="AA17">
-        <v>2.15</v>
-      </c>
-      <c r="AB17">
-        <v>1.66</v>
-      </c>
-      <c r="AC17">
-        <v>3.48</v>
-      </c>
-      <c r="AD17">
-        <v>1.27</v>
-      </c>
-      <c r="AE17">
-        <v>1.04</v>
-      </c>
-      <c r="AF17">
-        <v>1.86</v>
-      </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK17">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4435,7 +4435,7 @@
         <v>1.11</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF25">
         <v>2.28</v>
@@ -5718,7 +5718,7 @@
         <v>1.03</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
         <v>1.34</v>
@@ -5860,55 +5860,55 @@
         <v>2.86</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>13.66</v>
+        <v>1.89</v>
       </c>
       <c r="O52">
-        <v>8.76</v>
+        <v>3.96</v>
       </c>
       <c r="P52">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="Q52">
-        <v>10</v>
+        <v>2.32</v>
       </c>
       <c r="R52">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="S52">
+        <v>1.32</v>
+      </c>
+      <c r="T52">
+        <v>3.12</v>
+      </c>
+      <c r="U52">
+        <v>2.54</v>
+      </c>
+      <c r="V52">
+        <v>1.47</v>
+      </c>
+      <c r="W52">
+        <v>1.11</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <v>1.21</v>
+      </c>
+      <c r="Z52">
+        <v>3.9</v>
+      </c>
+      <c r="AA52">
+        <v>1.71</v>
+      </c>
+      <c r="AB52">
+        <v>2.04</v>
+      </c>
+      <c r="AC52">
+        <v>2.82</v>
+      </c>
+      <c r="AD52">
+        <v>1.34</v>
+      </c>
+      <c r="AE52">
+        <v>1.09</v>
+      </c>
+      <c r="AF52">
+        <v>1.65</v>
+      </c>
+      <c r="AG52">
+        <v>2.05</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
         <v>1.19</v>
       </c>
-      <c r="T52">
-        <v>4</v>
-      </c>
-      <c r="U52">
-        <v>1.95</v>
-      </c>
-      <c r="V52">
-        <v>1.73</v>
-      </c>
-      <c r="W52">
-        <v>1.2</v>
-      </c>
-      <c r="X52">
-        <v>1.01</v>
-      </c>
-      <c r="Y52">
-        <v>1.07</v>
-      </c>
-      <c r="Z52">
-        <v>6.36</v>
-      </c>
-      <c r="AA52">
-        <v>1.39</v>
-      </c>
-      <c r="AB52">
-        <v>2.87</v>
-      </c>
-      <c r="AC52">
-        <v>1.87</v>
-      </c>
-      <c r="AD52">
-        <v>1.87</v>
-      </c>
-      <c r="AE52">
-        <v>1.35</v>
-      </c>
-      <c r="AF52">
-        <v>2</v>
-      </c>
-      <c r="AG52">
-        <v>1.75</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>5</v>
-      </c>
       <c r="AK52">
-        <v>1.03</v>
+        <v>1.85</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="O53">
-        <v>3.96</v>
+        <v>4.56</v>
       </c>
       <c r="P53">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="Q53">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R53">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="S53">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T53">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U53">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="V53">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W53">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X53">
         <v>0</v>
       </c>
       <c r="Y53">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z53">
-        <v>3.9</v>
+        <v>4.06</v>
       </c>
       <c r="AA53">
         <v>1.71</v>
       </c>
       <c r="AB53">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="AC53">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="AD53">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AE53">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF53">
         <v>1.65</v>
       </c>
       <c r="AG53">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK53">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.57</v>
+        <v>13.66</v>
       </c>
       <c r="O54">
-        <v>4.56</v>
+        <v>8.76</v>
       </c>
       <c r="P54">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="Q54">
-        <v>2.3</v>
+        <v>10</v>
       </c>
       <c r="R54">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="S54">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="T54">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U54">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="V54">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="W54">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="Z54">
-        <v>4.06</v>
+        <v>6.36</v>
       </c>
       <c r="AA54">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="AB54">
-        <v>2.13</v>
+        <v>2.87</v>
       </c>
       <c r="AC54">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="AD54">
-        <v>1.46</v>
+        <v>1.87</v>
       </c>
       <c r="AE54">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AF54">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG54">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="AK54">
-        <v>1.95</v>
+        <v>1.03</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9772,34 +9772,34 @@
         <v>4.53</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA58">
         <v>1.92</v>
@@ -9808,19 +9808,19 @@
         <v>1.82</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL58">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,80 +2591,80 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="O14">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="P14">
-        <v>4.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q14">
-        <v>2.42</v>
+        <v>3.88</v>
       </c>
       <c r="R14">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="S14">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="T14">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="U14">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="V14">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="W14">
         <v>1.05</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
+        <v>1.44</v>
+      </c>
+      <c r="Z14">
+        <v>2.69</v>
+      </c>
+      <c r="AA14">
+        <v>2.26</v>
+      </c>
+      <c r="AB14">
+        <v>1.63</v>
+      </c>
+      <c r="AC14">
+        <v>4.17</v>
+      </c>
+      <c r="AD14">
+        <v>1.19</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>1.95</v>
+      </c>
+      <c r="AG14">
+        <v>1.74</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
         <v>1.28</v>
       </c>
-      <c r="Z14">
-        <v>3.4</v>
-      </c>
-      <c r="AA14">
-        <v>1.9</v>
-      </c>
-      <c r="AB14">
-        <v>1.9</v>
-      </c>
-      <c r="AC14">
-        <v>3.09</v>
-      </c>
-      <c r="AD14">
-        <v>1.34</v>
-      </c>
-      <c r="AE14">
-        <v>1.08</v>
-      </c>
-      <c r="AF14">
-        <v>1.78</v>
-      </c>
-      <c r="AG14">
-        <v>1.91</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.19</v>
-      </c>
       <c r="AK14">
-        <v>1.96</v>
+        <v>1.3</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O15">
         <v>3.2</v>
       </c>
       <c r="P15">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q15">
-        <v>2.62</v>
+        <v>3.11</v>
       </c>
       <c r="R15">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="S15">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T15">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="U15">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="V15">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z15">
-        <v>3.06</v>
+        <v>3.22</v>
       </c>
       <c r="AA15">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB15">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AC15">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="AD15">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE15">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="Q16">
-        <v>3.11</v>
+        <v>2.42</v>
       </c>
       <c r="R16">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U16">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z16">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="AA16">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB16">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC16">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="AD16">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE16">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG16">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK16">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="O17">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q17">
-        <v>3.88</v>
+        <v>2.62</v>
       </c>
       <c r="R17">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="T17">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="V17">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="Z17">
-        <v>2.69</v>
+        <v>3.06</v>
       </c>
       <c r="AA17">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AB17">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AC17">
-        <v>4.17</v>
+        <v>3.48</v>
       </c>
       <c r="AD17">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG17">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P24">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="Q24">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="R24">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="S24">
+        <v>1.53</v>
+      </c>
+      <c r="T24">
+        <v>2.38</v>
+      </c>
+      <c r="U24">
+        <v>3.52</v>
+      </c>
+      <c r="V24">
+        <v>1.22</v>
+      </c>
+      <c r="W24">
+        <v>1.03</v>
+      </c>
+      <c r="X24">
+        <v>1.07</v>
+      </c>
+      <c r="Y24">
+        <v>1.59</v>
+      </c>
+      <c r="Z24">
+        <v>2.33</v>
+      </c>
+      <c r="AA24">
+        <v>2.64</v>
+      </c>
+      <c r="AB24">
         <v>1.46</v>
       </c>
-      <c r="T24">
-        <v>2.64</v>
-      </c>
-      <c r="U24">
-        <v>2.96</v>
-      </c>
-      <c r="V24">
-        <v>1.37</v>
-      </c>
-      <c r="W24">
-        <v>1.02</v>
-      </c>
-      <c r="X24">
+      <c r="AC24">
+        <v>5.38</v>
+      </c>
+      <c r="AD24">
+        <v>1.11</v>
+      </c>
+      <c r="AE24">
         <v>1.01</v>
       </c>
-      <c r="Y24">
-        <v>1.35</v>
-      </c>
-      <c r="Z24">
-        <v>3.01</v>
-      </c>
-      <c r="AA24">
-        <v>2.06</v>
-      </c>
-      <c r="AB24">
-        <v>1.76</v>
-      </c>
-      <c r="AC24">
-        <v>3.56</v>
-      </c>
-      <c r="AD24">
-        <v>1.26</v>
-      </c>
-      <c r="AE24">
-        <v>1.04</v>
-      </c>
       <c r="AF24">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="AG24">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="O25">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="Q25">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="R25">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="S25">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="T25">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="U25">
-        <v>3.52</v>
+        <v>2.96</v>
       </c>
       <c r="V25">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X25">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="Z25">
-        <v>2.33</v>
+        <v>3.01</v>
       </c>
       <c r="AA25">
-        <v>2.64</v>
+        <v>2.06</v>
       </c>
       <c r="AB25">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="AC25">
-        <v>5.38</v>
+        <v>3.56</v>
       </c>
       <c r="AD25">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AE25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF25">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="AG25">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -10913,16 +10913,16 @@
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R65">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S65">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T65">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U65">
         <v>0</v>
@@ -10937,31 +10937,31 @@
         <v>0</v>
       </c>
       <c r="Y65">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z65">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA65">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB65">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC65">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD65">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE65">
         <v>0</v>
       </c>
       <c r="AF65">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG65">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK65">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL65">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="O14">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q14">
-        <v>3.88</v>
+        <v>2.62</v>
       </c>
       <c r="R14">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S14">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="T14">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="U14">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="V14">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="Z14">
-        <v>2.69</v>
+        <v>3.06</v>
       </c>
       <c r="AA14">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AB14">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AC14">
-        <v>4.17</v>
+        <v>3.48</v>
       </c>
       <c r="AD14">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF14">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG14">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK14">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="O15">
+        <v>2.9</v>
+      </c>
+      <c r="P15">
+        <v>2.3</v>
+      </c>
+      <c r="Q15">
+        <v>3.88</v>
+      </c>
+      <c r="R15">
+        <v>2.06</v>
+      </c>
+      <c r="S15">
+        <v>1.52</v>
+      </c>
+      <c r="T15">
+        <v>2.49</v>
+      </c>
+      <c r="U15">
         <v>3.2</v>
       </c>
-      <c r="P15">
-        <v>2.8</v>
-      </c>
-      <c r="Q15">
-        <v>3.11</v>
-      </c>
-      <c r="R15">
-        <v>2.19</v>
-      </c>
-      <c r="S15">
-        <v>1.42</v>
-      </c>
-      <c r="T15">
-        <v>2.74</v>
-      </c>
-      <c r="U15">
-        <v>2.82</v>
-      </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="W15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="Z15">
-        <v>3.22</v>
+        <v>2.69</v>
       </c>
       <c r="AA15">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="AB15">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AC15">
-        <v>3.28</v>
+        <v>4.17</v>
       </c>
       <c r="AD15">
+        <v>1.19</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>1.95</v>
+      </c>
+      <c r="AG15">
+        <v>1.74</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>1.28</v>
+      </c>
+      <c r="AK15">
         <v>1.3</v>
-      </c>
-      <c r="AE15">
-        <v>1.06</v>
-      </c>
-      <c r="AF15">
-        <v>1.77</v>
-      </c>
-      <c r="AG15">
-        <v>1.92</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.25</v>
-      </c>
-      <c r="AK15">
-        <v>1.49</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>4.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q16">
-        <v>2.42</v>
+        <v>3.11</v>
       </c>
       <c r="R16">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S16">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T16">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="U16">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="V16">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z16">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="AA16">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB16">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AC16">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="AD16">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE16">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG16">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.96</v>
+        <v>1.49</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="Q17">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
+        <v>1.38</v>
+      </c>
+      <c r="T17">
+        <v>2.88</v>
+      </c>
+      <c r="U17">
+        <v>2.67</v>
+      </c>
+      <c r="V17">
         <v>1.45</v>
       </c>
-      <c r="T17">
-        <v>2.65</v>
-      </c>
-      <c r="U17">
-        <v>2.94</v>
-      </c>
-      <c r="V17">
-        <v>1.37</v>
-      </c>
       <c r="W17">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17">
+        <v>1.28</v>
+      </c>
+      <c r="Z17">
+        <v>3.4</v>
+      </c>
+      <c r="AA17">
+        <v>1.9</v>
+      </c>
+      <c r="AB17">
+        <v>1.9</v>
+      </c>
+      <c r="AC17">
+        <v>3.09</v>
+      </c>
+      <c r="AD17">
         <v>1.34</v>
       </c>
-      <c r="Z17">
-        <v>3.06</v>
-      </c>
-      <c r="AA17">
-        <v>2.15</v>
-      </c>
-      <c r="AB17">
-        <v>1.66</v>
-      </c>
-      <c r="AC17">
-        <v>3.48</v>
-      </c>
-      <c r="AD17">
-        <v>1.27</v>
-      </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK17">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="O24">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="Q24">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="R24">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="S24">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="T24">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="U24">
-        <v>3.52</v>
+        <v>2.96</v>
       </c>
       <c r="V24">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="W24">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X24">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="Z24">
-        <v>2.33</v>
+        <v>3.01</v>
       </c>
       <c r="AA24">
-        <v>2.64</v>
+        <v>2.06</v>
       </c>
       <c r="AB24">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="AC24">
-        <v>5.38</v>
+        <v>3.56</v>
       </c>
       <c r="AD24">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AE24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="AG24">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK24">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P25">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="Q25">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="S25">
+        <v>1.53</v>
+      </c>
+      <c r="T25">
+        <v>2.38</v>
+      </c>
+      <c r="U25">
+        <v>3.52</v>
+      </c>
+      <c r="V25">
+        <v>1.22</v>
+      </c>
+      <c r="W25">
+        <v>1.03</v>
+      </c>
+      <c r="X25">
+        <v>1.07</v>
+      </c>
+      <c r="Y25">
+        <v>1.59</v>
+      </c>
+      <c r="Z25">
+        <v>2.33</v>
+      </c>
+      <c r="AA25">
+        <v>2.64</v>
+      </c>
+      <c r="AB25">
         <v>1.46</v>
       </c>
-      <c r="T25">
-        <v>2.64</v>
-      </c>
-      <c r="U25">
-        <v>2.96</v>
-      </c>
-      <c r="V25">
-        <v>1.37</v>
-      </c>
-      <c r="W25">
-        <v>1.02</v>
-      </c>
-      <c r="X25">
+      <c r="AC25">
+        <v>5.38</v>
+      </c>
+      <c r="AD25">
+        <v>1.11</v>
+      </c>
+      <c r="AE25">
         <v>1.01</v>
       </c>
-      <c r="Y25">
-        <v>1.35</v>
-      </c>
-      <c r="Z25">
-        <v>3.01</v>
-      </c>
-      <c r="AA25">
-        <v>2.06</v>
-      </c>
-      <c r="AB25">
-        <v>1.76</v>
-      </c>
-      <c r="AC25">
-        <v>3.56</v>
-      </c>
-      <c r="AD25">
-        <v>1.26</v>
-      </c>
-      <c r="AE25">
-        <v>1.04</v>
-      </c>
       <c r="AF25">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="AG25">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.76</v>
+        <v>2.66</v>
       </c>
       <c r="O58">
-        <v>3.82</v>
+        <v>3.38</v>
       </c>
       <c r="P58">
-        <v>4.53</v>
+        <v>2.62</v>
       </c>
       <c r="Q58">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="R58">
-        <v>2.33</v>
+        <v>1.94</v>
       </c>
       <c r="S58">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="T58">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="U58">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="V58">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W58">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X58">
+        <v>1.02</v>
+      </c>
+      <c r="Y58">
+        <v>1.42</v>
+      </c>
+      <c r="Z58">
+        <v>2.74</v>
+      </c>
+      <c r="AA58">
+        <v>2.25</v>
+      </c>
+      <c r="AB58">
+        <v>1.61</v>
+      </c>
+      <c r="AC58">
+        <v>3.96</v>
+      </c>
+      <c r="AD58">
+        <v>1.17</v>
+      </c>
+      <c r="AE58">
         <v>1.01</v>
       </c>
-      <c r="Y58">
-        <v>1.24</v>
-      </c>
-      <c r="Z58">
-        <v>3.7</v>
-      </c>
-      <c r="AA58">
-        <v>1.92</v>
-      </c>
-      <c r="AB58">
-        <v>1.82</v>
-      </c>
-      <c r="AC58">
-        <v>2.99</v>
-      </c>
-      <c r="AD58">
-        <v>1.35</v>
-      </c>
-      <c r="AE58">
-        <v>1.11</v>
-      </c>
       <c r="AF58">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AG58">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK58">
-        <v>1.99</v>
+        <v>1.38</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.66</v>
+        <v>1.76</v>
       </c>
       <c r="O59">
-        <v>3.38</v>
+        <v>3.82</v>
       </c>
       <c r="P59">
-        <v>2.62</v>
+        <v>4.53</v>
       </c>
       <c r="Q59">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="R59">
-        <v>1.94</v>
+        <v>2.33</v>
       </c>
       <c r="S59">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="T59">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="U59">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="V59">
+        <v>1.44</v>
+      </c>
+      <c r="W59">
+        <v>1.1</v>
+      </c>
+      <c r="X59">
+        <v>1.01</v>
+      </c>
+      <c r="Y59">
+        <v>1.24</v>
+      </c>
+      <c r="Z59">
+        <v>3.7</v>
+      </c>
+      <c r="AA59">
+        <v>1.92</v>
+      </c>
+      <c r="AB59">
+        <v>1.82</v>
+      </c>
+      <c r="AC59">
+        <v>2.99</v>
+      </c>
+      <c r="AD59">
         <v>1.35</v>
       </c>
-      <c r="W59">
-        <v>1.02</v>
-      </c>
-      <c r="X59">
-        <v>1.02</v>
-      </c>
-      <c r="Y59">
-        <v>1.42</v>
-      </c>
-      <c r="Z59">
-        <v>2.74</v>
-      </c>
-      <c r="AA59">
-        <v>2.25</v>
-      </c>
-      <c r="AB59">
-        <v>1.61</v>
-      </c>
-      <c r="AC59">
-        <v>3.96</v>
-      </c>
-      <c r="AD59">
-        <v>1.17</v>
-      </c>
       <c r="AE59">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AF59">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AG59">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>1.38</v>
+        <v>1.99</v>
       </c>
       <c r="AL59">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="Q16">
-        <v>3.11</v>
+        <v>2.42</v>
       </c>
       <c r="R16">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T16">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U16">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
         <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z16">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="AA16">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB16">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC16">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="AD16">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE16">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG16">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK16">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>4.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q17">
-        <v>2.42</v>
+        <v>3.11</v>
       </c>
       <c r="R17">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="S17">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T17">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="U17">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z17">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="AA17">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB17">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AC17">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="AD17">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF17">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG17">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>1.96</v>
+        <v>1.49</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P24">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="Q24">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="R24">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="S24">
+        <v>1.53</v>
+      </c>
+      <c r="T24">
+        <v>2.38</v>
+      </c>
+      <c r="U24">
+        <v>3.52</v>
+      </c>
+      <c r="V24">
+        <v>1.22</v>
+      </c>
+      <c r="W24">
+        <v>1.03</v>
+      </c>
+      <c r="X24">
+        <v>1.07</v>
+      </c>
+      <c r="Y24">
+        <v>1.59</v>
+      </c>
+      <c r="Z24">
+        <v>2.33</v>
+      </c>
+      <c r="AA24">
+        <v>2.64</v>
+      </c>
+      <c r="AB24">
         <v>1.46</v>
       </c>
-      <c r="T24">
-        <v>2.64</v>
-      </c>
-      <c r="U24">
-        <v>2.96</v>
-      </c>
-      <c r="V24">
-        <v>1.37</v>
-      </c>
-      <c r="W24">
-        <v>1.02</v>
-      </c>
-      <c r="X24">
+      <c r="AC24">
+        <v>5.38</v>
+      </c>
+      <c r="AD24">
+        <v>1.11</v>
+      </c>
+      <c r="AE24">
         <v>1.01</v>
       </c>
-      <c r="Y24">
-        <v>1.35</v>
-      </c>
-      <c r="Z24">
-        <v>3.01</v>
-      </c>
-      <c r="AA24">
-        <v>2.06</v>
-      </c>
-      <c r="AB24">
-        <v>1.76</v>
-      </c>
-      <c r="AC24">
-        <v>3.56</v>
-      </c>
-      <c r="AD24">
-        <v>1.26</v>
-      </c>
-      <c r="AE24">
-        <v>1.04</v>
-      </c>
       <c r="AF24">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="AG24">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="O25">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="Q25">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="R25">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="S25">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="T25">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="U25">
-        <v>3.52</v>
+        <v>2.96</v>
       </c>
       <c r="V25">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X25">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="Z25">
-        <v>2.33</v>
+        <v>3.01</v>
       </c>
       <c r="AA25">
-        <v>2.64</v>
+        <v>2.06</v>
       </c>
       <c r="AB25">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="AC25">
-        <v>5.38</v>
+        <v>3.56</v>
       </c>
       <c r="AD25">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AE25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF25">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="AG25">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="O24">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P24">
-        <v>3.98</v>
+        <v>4.33</v>
       </c>
       <c r="Q24">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="R24">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="S24">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="T24">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="U24">
-        <v>3.52</v>
+        <v>2.96</v>
       </c>
       <c r="V24">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="W24">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X24">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="Z24">
-        <v>2.33</v>
+        <v>3.01</v>
       </c>
       <c r="AA24">
-        <v>2.64</v>
+        <v>2.06</v>
       </c>
       <c r="AB24">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="AC24">
-        <v>5.38</v>
+        <v>3.56</v>
       </c>
       <c r="AD24">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AE24">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF24">
-        <v>2.28</v>
+        <v>1.94</v>
       </c>
       <c r="AG24">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK24">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P25">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="Q25">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="S25">
+        <v>1.53</v>
+      </c>
+      <c r="T25">
+        <v>2.38</v>
+      </c>
+      <c r="U25">
+        <v>3.52</v>
+      </c>
+      <c r="V25">
+        <v>1.22</v>
+      </c>
+      <c r="W25">
+        <v>1.03</v>
+      </c>
+      <c r="X25">
+        <v>1.07</v>
+      </c>
+      <c r="Y25">
+        <v>1.59</v>
+      </c>
+      <c r="Z25">
+        <v>2.33</v>
+      </c>
+      <c r="AA25">
+        <v>2.64</v>
+      </c>
+      <c r="AB25">
         <v>1.46</v>
       </c>
-      <c r="T25">
-        <v>2.64</v>
-      </c>
-      <c r="U25">
-        <v>2.96</v>
-      </c>
-      <c r="V25">
-        <v>1.37</v>
-      </c>
-      <c r="W25">
-        <v>1.02</v>
-      </c>
-      <c r="X25">
+      <c r="AC25">
+        <v>5.38</v>
+      </c>
+      <c r="AD25">
+        <v>1.11</v>
+      </c>
+      <c r="AE25">
         <v>1.01</v>
       </c>
-      <c r="Y25">
-        <v>1.35</v>
-      </c>
-      <c r="Z25">
-        <v>3.01</v>
-      </c>
-      <c r="AA25">
-        <v>2.06</v>
-      </c>
-      <c r="AB25">
-        <v>1.76</v>
-      </c>
-      <c r="AC25">
-        <v>3.56</v>
-      </c>
-      <c r="AD25">
-        <v>1.26</v>
-      </c>
-      <c r="AE25">
-        <v>1.04</v>
-      </c>
       <c r="AF25">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="AG25">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="O14">
         <v>3.2</v>
       </c>
       <c r="P14">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q14">
-        <v>2.62</v>
+        <v>3.11</v>
       </c>
       <c r="R14">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="S14">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="U14">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="V14">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z14">
-        <v>3.06</v>
+        <v>3.22</v>
       </c>
       <c r="AA14">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB14">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AC14">
-        <v>3.48</v>
+        <v>3.28</v>
       </c>
       <c r="AD14">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE14">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AG14">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="O15">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q15">
-        <v>3.88</v>
+        <v>2.62</v>
       </c>
       <c r="R15">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S15">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="T15">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="U15">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="V15">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="Z15">
-        <v>2.69</v>
+        <v>3.06</v>
       </c>
       <c r="AA15">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AB15">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AC15">
-        <v>4.17</v>
+        <v>3.48</v>
       </c>
       <c r="AD15">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF15">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG15">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK15">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="P16">
-        <v>4.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q16">
-        <v>2.42</v>
+        <v>3.88</v>
       </c>
       <c r="R16">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="S16">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="T16">
-        <v>2.88</v>
+        <v>2.49</v>
       </c>
       <c r="U16">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="V16">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="W16">
         <v>1.05</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
+        <v>1.44</v>
+      </c>
+      <c r="Z16">
+        <v>2.69</v>
+      </c>
+      <c r="AA16">
+        <v>2.26</v>
+      </c>
+      <c r="AB16">
+        <v>1.63</v>
+      </c>
+      <c r="AC16">
+        <v>4.17</v>
+      </c>
+      <c r="AD16">
+        <v>1.19</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>1.95</v>
+      </c>
+      <c r="AG16">
+        <v>1.74</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
         <v>1.28</v>
       </c>
-      <c r="Z16">
-        <v>3.4</v>
-      </c>
-      <c r="AA16">
-        <v>1.9</v>
-      </c>
-      <c r="AB16">
-        <v>1.9</v>
-      </c>
-      <c r="AC16">
-        <v>3.09</v>
-      </c>
-      <c r="AD16">
-        <v>1.34</v>
-      </c>
-      <c r="AE16">
-        <v>1.08</v>
-      </c>
-      <c r="AF16">
-        <v>1.78</v>
-      </c>
-      <c r="AG16">
-        <v>1.91</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.19</v>
-      </c>
       <c r="AK16">
-        <v>1.96</v>
+        <v>1.3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="Q17">
-        <v>3.11</v>
+        <v>2.42</v>
       </c>
       <c r="R17">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="S17">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T17">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="U17">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="V17">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z17">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB17">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AC17">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="AD17">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE17">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG17">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK17">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="G44">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N44">
@@ -7602,22 +7602,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G45">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N45">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="O47">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="P47">
-        <v>11.2</v>
+        <v>4.93</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O48">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8254,22 +8254,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8498,10 +8498,10 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="AB50">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="AC50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X51">
         <v>0</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA51">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AB51">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="O52">
-        <v>3.96</v>
+        <v>4.56</v>
       </c>
       <c r="P52">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="Q52">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R52">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="S52">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U52">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="V52">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W52">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X52">
         <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z52">
-        <v>3.9</v>
+        <v>4.06</v>
       </c>
       <c r="AA52">
         <v>1.71</v>
       </c>
       <c r="AB52">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="AC52">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="AD52">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AE52">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF52">
         <v>1.65</v>
       </c>
       <c r="AG52">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK52">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.57</v>
+        <v>13.66</v>
       </c>
       <c r="O53">
-        <v>4.56</v>
+        <v>8.76</v>
       </c>
       <c r="P53">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="Q53">
-        <v>2.3</v>
+        <v>10</v>
       </c>
       <c r="R53">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="S53">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="T53">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U53">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="V53">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="W53">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="Z53">
-        <v>4.06</v>
+        <v>6.36</v>
       </c>
       <c r="AA53">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="AB53">
-        <v>2.13</v>
+        <v>2.87</v>
       </c>
       <c r="AC53">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="AD53">
-        <v>1.46</v>
+        <v>1.87</v>
       </c>
       <c r="AE53">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AF53">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG53">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="AK53">
-        <v>1.95</v>
+        <v>1.03</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>13.66</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>8.76</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q54">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R54">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S54">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T54">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U54">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="V54">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="W54">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X54">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y54">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z54">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="AA54">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AB54">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC54">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD54">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE54">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AF54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG54">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK54">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-10-04 10:00:00</t>
+          <t>2026-10-04 11:00:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
+        <v>3</v>
+      </c>
+      <c r="O15">
+        <v>2.9</v>
+      </c>
+      <c r="P15">
+        <v>2.3</v>
+      </c>
+      <c r="Q15">
+        <v>3.88</v>
+      </c>
+      <c r="R15">
+        <v>2.06</v>
+      </c>
+      <c r="S15">
+        <v>1.52</v>
+      </c>
+      <c r="T15">
+        <v>2.49</v>
+      </c>
+      <c r="U15">
+        <v>3.2</v>
+      </c>
+      <c r="V15">
+        <v>1.31</v>
+      </c>
+      <c r="W15">
+        <v>1.05</v>
+      </c>
+      <c r="X15">
+        <v>1.03</v>
+      </c>
+      <c r="Y15">
+        <v>1.44</v>
+      </c>
+      <c r="Z15">
+        <v>2.69</v>
+      </c>
+      <c r="AA15">
+        <v>2.26</v>
+      </c>
+      <c r="AB15">
+        <v>1.63</v>
+      </c>
+      <c r="AC15">
+        <v>4.17</v>
+      </c>
+      <c r="AD15">
+        <v>1.19</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
         <v>1.95</v>
       </c>
-      <c r="O15">
-        <v>3.2</v>
-      </c>
-      <c r="P15">
-        <v>3.5</v>
-      </c>
-      <c r="Q15">
-        <v>2.62</v>
-      </c>
-      <c r="R15">
-        <v>2</v>
-      </c>
-      <c r="S15">
-        <v>1.45</v>
-      </c>
-      <c r="T15">
-        <v>2.65</v>
-      </c>
-      <c r="U15">
-        <v>2.94</v>
-      </c>
-      <c r="V15">
-        <v>1.37</v>
-      </c>
-      <c r="W15">
-        <v>1.02</v>
-      </c>
-      <c r="X15">
-        <v>1.02</v>
-      </c>
-      <c r="Y15">
-        <v>1.34</v>
-      </c>
-      <c r="Z15">
-        <v>3.06</v>
-      </c>
-      <c r="AA15">
-        <v>2.15</v>
-      </c>
-      <c r="AB15">
-        <v>1.66</v>
-      </c>
-      <c r="AC15">
-        <v>3.48</v>
-      </c>
-      <c r="AD15">
-        <v>1.27</v>
-      </c>
-      <c r="AE15">
-        <v>1.04</v>
-      </c>
-      <c r="AF15">
-        <v>1.86</v>
-      </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK15">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="O16">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q16">
-        <v>3.88</v>
+        <v>2.62</v>
       </c>
       <c r="R16">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S16">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="T16">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="U16">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="V16">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="Z16">
-        <v>2.69</v>
+        <v>3.06</v>
       </c>
       <c r="AA16">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AB16">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AC16">
-        <v>4.17</v>
+        <v>3.48</v>
       </c>
       <c r="AD16">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF16">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG16">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>1.3</v>
+        <v>1.68</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.57</v>
+        <v>13.66</v>
       </c>
       <c r="O52">
-        <v>4.56</v>
+        <v>8.76</v>
       </c>
       <c r="P52">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="Q52">
-        <v>2.3</v>
+        <v>10</v>
       </c>
       <c r="R52">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="T52">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U52">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="V52">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="W52">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="Z52">
-        <v>4.06</v>
+        <v>6.36</v>
       </c>
       <c r="AA52">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="AB52">
-        <v>2.13</v>
+        <v>2.87</v>
       </c>
       <c r="AC52">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="AD52">
-        <v>1.46</v>
+        <v>1.87</v>
       </c>
       <c r="AE52">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AF52">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG52">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.25</v>
+        <v>5</v>
       </c>
       <c r="AK52">
-        <v>1.95</v>
+        <v>1.03</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,80 +8948,80 @@
         </is>
       </c>
       <c r="N53">
-        <v>13.66</v>
+        <v>1.57</v>
       </c>
       <c r="O53">
-        <v>8.76</v>
+        <v>4.56</v>
       </c>
       <c r="P53">
-        <v>1.1</v>
+        <v>5.2</v>
       </c>
       <c r="Q53">
-        <v>10</v>
+        <v>2.3</v>
       </c>
       <c r="R53">
-        <v>2.9</v>
+        <v>2.36</v>
       </c>
       <c r="S53">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="T53">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U53">
+        <v>2.4</v>
+      </c>
+      <c r="V53">
+        <v>1.51</v>
+      </c>
+      <c r="W53">
+        <v>1.12</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>1.2</v>
+      </c>
+      <c r="Z53">
+        <v>4.06</v>
+      </c>
+      <c r="AA53">
+        <v>1.71</v>
+      </c>
+      <c r="AB53">
+        <v>2.13</v>
+      </c>
+      <c r="AC53">
+        <v>2.62</v>
+      </c>
+      <c r="AD53">
+        <v>1.46</v>
+      </c>
+      <c r="AE53">
+        <v>1.14</v>
+      </c>
+      <c r="AF53">
+        <v>1.65</v>
+      </c>
+      <c r="AG53">
+        <v>2.15</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ53">
+        <v>1.25</v>
+      </c>
+      <c r="AK53">
         <v>1.95</v>
-      </c>
-      <c r="V53">
-        <v>1.73</v>
-      </c>
-      <c r="W53">
-        <v>1.2</v>
-      </c>
-      <c r="X53">
-        <v>1.01</v>
-      </c>
-      <c r="Y53">
-        <v>1.07</v>
-      </c>
-      <c r="Z53">
-        <v>6.36</v>
-      </c>
-      <c r="AA53">
-        <v>1.39</v>
-      </c>
-      <c r="AB53">
-        <v>2.87</v>
-      </c>
-      <c r="AC53">
-        <v>1.87</v>
-      </c>
-      <c r="AD53">
-        <v>1.87</v>
-      </c>
-      <c r="AE53">
-        <v>1.35</v>
-      </c>
-      <c r="AF53">
-        <v>2</v>
-      </c>
-      <c r="AG53">
-        <v>1.75</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ53">
-        <v>5</v>
-      </c>
-      <c r="AK53">
-        <v>1.03</v>
       </c>
       <c r="AL53">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="Q16">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="R16">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
+        <v>1.38</v>
+      </c>
+      <c r="T16">
+        <v>2.88</v>
+      </c>
+      <c r="U16">
+        <v>2.67</v>
+      </c>
+      <c r="V16">
         <v>1.45</v>
       </c>
-      <c r="T16">
-        <v>2.65</v>
-      </c>
-      <c r="U16">
-        <v>2.94</v>
-      </c>
-      <c r="V16">
-        <v>1.37</v>
-      </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y16">
+        <v>1.28</v>
+      </c>
+      <c r="Z16">
+        <v>3.4</v>
+      </c>
+      <c r="AA16">
+        <v>1.9</v>
+      </c>
+      <c r="AB16">
+        <v>1.9</v>
+      </c>
+      <c r="AC16">
+        <v>3.09</v>
+      </c>
+      <c r="AD16">
         <v>1.34</v>
       </c>
-      <c r="Z16">
-        <v>3.06</v>
-      </c>
-      <c r="AA16">
-        <v>2.15</v>
-      </c>
-      <c r="AB16">
-        <v>1.66</v>
-      </c>
-      <c r="AC16">
-        <v>3.48</v>
-      </c>
-      <c r="AD16">
-        <v>1.27</v>
-      </c>
       <c r="AE16">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF16">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AG16">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK16">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q17">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="R17">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T17">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
-        <v>2.67</v>
+        <v>2.94</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z17">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="AA17">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AB17">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AC17">
-        <v>3.09</v>
+        <v>3.48</v>
       </c>
       <c r="AD17">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AG17">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK17">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mijas Las Lagunas</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="Q19">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="R19">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="T19">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="U19">
-        <v>2.78</v>
+        <v>3.07</v>
       </c>
       <c r="V19">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z19">
-        <v>3.34</v>
+        <v>2.81</v>
       </c>
       <c r="AA19">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="AB19">
-        <v>1.88</v>
+        <v>1.68</v>
       </c>
       <c r="AC19">
-        <v>3.14</v>
+        <v>3.91</v>
       </c>
       <c r="AD19">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AE19">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>1.84</v>
+        <v>2.23</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK19">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Mijas Las Lagunas</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,80 +3569,80 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q20">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="R20">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S20">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="T20">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="U20">
-        <v>3.07</v>
+        <v>2.78</v>
       </c>
       <c r="V20">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="W20">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Z20">
-        <v>2.81</v>
+        <v>3.34</v>
       </c>
       <c r="AA20">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="AB20">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AC20">
-        <v>3.91</v>
+        <v>3.14</v>
       </c>
       <c r="AD20">
+        <v>1.32</v>
+      </c>
+      <c r="AE20">
+        <v>1.07</v>
+      </c>
+      <c r="AF20">
+        <v>1.84</v>
+      </c>
+      <c r="AG20">
+        <v>1.85</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
         <v>1.21</v>
       </c>
-      <c r="AE20">
-        <v>1.02</v>
-      </c>
-      <c r="AF20">
-        <v>2.23</v>
-      </c>
-      <c r="AG20">
-        <v>1.55</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ20">
-        <v>1.18</v>
-      </c>
       <c r="AK20">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mallorca II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="O23">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>4.33</v>
       </c>
       <c r="Q23">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="R23">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="S23">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="T23">
-        <v>2.35</v>
+        <v>2.64</v>
       </c>
       <c r="U23">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="V23">
+        <v>1.37</v>
+      </c>
+      <c r="W23">
+        <v>1.02</v>
+      </c>
+      <c r="X23">
+        <v>1.01</v>
+      </c>
+      <c r="Y23">
+        <v>1.35</v>
+      </c>
+      <c r="Z23">
+        <v>3.01</v>
+      </c>
+      <c r="AA23">
+        <v>2.06</v>
+      </c>
+      <c r="AB23">
+        <v>1.76</v>
+      </c>
+      <c r="AC23">
+        <v>3.56</v>
+      </c>
+      <c r="AD23">
         <v>1.26</v>
       </c>
-      <c r="W23">
+      <c r="AE23">
         <v>1.04</v>
       </c>
-      <c r="X23">
-        <v>1.04</v>
-      </c>
-      <c r="Y23">
-        <v>1.44</v>
-      </c>
-      <c r="Z23">
-        <v>2.43</v>
-      </c>
-      <c r="AA23">
-        <v>2.44</v>
-      </c>
-      <c r="AB23">
-        <v>1.47</v>
-      </c>
-      <c r="AC23">
-        <v>4.85</v>
-      </c>
-      <c r="AD23">
-        <v>1.11</v>
-      </c>
-      <c r="AE23">
-        <v>1.01</v>
-      </c>
       <c r="AF23">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AG23">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK23">
-        <v>1.19</v>
+        <v>1.83</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="O24">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P24">
-        <v>4.33</v>
+        <v>3.98</v>
       </c>
       <c r="Q24">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="R24">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="S24">
+        <v>1.53</v>
+      </c>
+      <c r="T24">
+        <v>2.38</v>
+      </c>
+      <c r="U24">
+        <v>3.52</v>
+      </c>
+      <c r="V24">
+        <v>1.22</v>
+      </c>
+      <c r="W24">
+        <v>1.03</v>
+      </c>
+      <c r="X24">
+        <v>1.07</v>
+      </c>
+      <c r="Y24">
+        <v>1.59</v>
+      </c>
+      <c r="Z24">
+        <v>2.33</v>
+      </c>
+      <c r="AA24">
+        <v>2.64</v>
+      </c>
+      <c r="AB24">
         <v>1.46</v>
       </c>
-      <c r="T24">
-        <v>2.64</v>
-      </c>
-      <c r="U24">
-        <v>2.96</v>
-      </c>
-      <c r="V24">
-        <v>1.37</v>
-      </c>
-      <c r="W24">
-        <v>1.02</v>
-      </c>
-      <c r="X24">
+      <c r="AC24">
+        <v>5.38</v>
+      </c>
+      <c r="AD24">
+        <v>1.11</v>
+      </c>
+      <c r="AE24">
         <v>1.01</v>
       </c>
-      <c r="Y24">
-        <v>1.35</v>
-      </c>
-      <c r="Z24">
-        <v>3.01</v>
-      </c>
-      <c r="AA24">
-        <v>2.06</v>
-      </c>
-      <c r="AB24">
-        <v>1.76</v>
-      </c>
-      <c r="AC24">
-        <v>3.56</v>
-      </c>
-      <c r="AD24">
-        <v>1.26</v>
-      </c>
-      <c r="AE24">
-        <v>1.04</v>
-      </c>
       <c r="AF24">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="AG24">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AK24">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Mallorca II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,52 +4384,52 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.04</v>
+        <v>3.5</v>
       </c>
       <c r="O25">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="P25">
-        <v>3.98</v>
+        <v>2</v>
       </c>
       <c r="Q25">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="R25">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="S25">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="T25">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="U25">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="V25">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="W25">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="Z25">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AA25">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="AB25">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AC25">
-        <v>5.38</v>
+        <v>4.85</v>
       </c>
       <c r="AD25">
         <v>1.11</v>
@@ -4438,10 +4438,10 @@
         <v>1.01</v>
       </c>
       <c r="AF25">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="AG25">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK25">
-        <v>1.73</v>
+        <v>1.19</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19217,13 +19217,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q116">
         <v>0</v>
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q122">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="O15">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="P15">
+        <v>4.25</v>
+      </c>
+      <c r="Q15">
+        <v>2.42</v>
+      </c>
+      <c r="R15">
         <v>2.3</v>
       </c>
-      <c r="Q15">
-        <v>3.88</v>
-      </c>
-      <c r="R15">
-        <v>2.06</v>
-      </c>
       <c r="S15">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="T15">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="U15">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="V15">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
         <v>1.05</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="Z15">
-        <v>2.69</v>
+        <v>3.4</v>
       </c>
       <c r="AA15">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="AB15">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="AC15">
-        <v>4.17</v>
+        <v>3.09</v>
       </c>
       <c r="AD15">
+        <v>1.34</v>
+      </c>
+      <c r="AE15">
+        <v>1.08</v>
+      </c>
+      <c r="AF15">
+        <v>1.78</v>
+      </c>
+      <c r="AG15">
+        <v>1.91</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.19</v>
       </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>1.95</v>
-      </c>
-      <c r="AG15">
-        <v>1.74</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.28</v>
-      </c>
       <c r="AK15">
-        <v>1.3</v>
+        <v>1.96</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q16">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="R16">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S16">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T16">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U16">
-        <v>2.67</v>
+        <v>2.94</v>
       </c>
       <c r="V16">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z16">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="AA16">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AB16">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
       <c r="AC16">
-        <v>3.09</v>
+        <v>3.48</v>
       </c>
       <c r="AD16">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AE16">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF16">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AG16">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
+        <v>3</v>
+      </c>
+      <c r="O17">
+        <v>2.9</v>
+      </c>
+      <c r="P17">
+        <v>2.3</v>
+      </c>
+      <c r="Q17">
+        <v>3.88</v>
+      </c>
+      <c r="R17">
+        <v>2.06</v>
+      </c>
+      <c r="S17">
+        <v>1.52</v>
+      </c>
+      <c r="T17">
+        <v>2.49</v>
+      </c>
+      <c r="U17">
+        <v>3.2</v>
+      </c>
+      <c r="V17">
+        <v>1.31</v>
+      </c>
+      <c r="W17">
+        <v>1.05</v>
+      </c>
+      <c r="X17">
+        <v>1.03</v>
+      </c>
+      <c r="Y17">
+        <v>1.44</v>
+      </c>
+      <c r="Z17">
+        <v>2.69</v>
+      </c>
+      <c r="AA17">
+        <v>2.26</v>
+      </c>
+      <c r="AB17">
+        <v>1.63</v>
+      </c>
+      <c r="AC17">
+        <v>4.17</v>
+      </c>
+      <c r="AD17">
+        <v>1.19</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
         <v>1.95</v>
       </c>
-      <c r="O17">
-        <v>3.2</v>
-      </c>
-      <c r="P17">
-        <v>3.5</v>
-      </c>
-      <c r="Q17">
-        <v>2.62</v>
-      </c>
-      <c r="R17">
-        <v>2</v>
-      </c>
-      <c r="S17">
-        <v>1.45</v>
-      </c>
-      <c r="T17">
-        <v>2.65</v>
-      </c>
-      <c r="U17">
-        <v>2.94</v>
-      </c>
-      <c r="V17">
-        <v>1.37</v>
-      </c>
-      <c r="W17">
-        <v>1.02</v>
-      </c>
-      <c r="X17">
-        <v>1.02</v>
-      </c>
-      <c r="Y17">
-        <v>1.34</v>
-      </c>
-      <c r="Z17">
-        <v>3.06</v>
-      </c>
-      <c r="AA17">
-        <v>2.15</v>
-      </c>
-      <c r="AB17">
-        <v>1.66</v>
-      </c>
-      <c r="AC17">
-        <v>3.48</v>
-      </c>
-      <c r="AD17">
-        <v>1.27</v>
-      </c>
-      <c r="AE17">
-        <v>1.04</v>
-      </c>
-      <c r="AF17">
-        <v>1.86</v>
-      </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AK17">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -8652,7 +8652,7 @@
         <v>1.11</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
         <v>1.21</v>
@@ -8978,7 +8978,7 @@
         <v>1.12</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
         <v>1.2</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.85</v>
+        <v>2.72</v>
       </c>
       <c r="O69">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="P69">
-        <v>3.75</v>
+        <v>2.59</v>
       </c>
       <c r="Q69">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R69">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S69">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T69">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="U69">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="V69">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W69">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X69">
         <v>0</v>
       </c>
       <c r="Y69">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z69">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AA69">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="AB69">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AC69">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AD69">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE69">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF69">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG69">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK69">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="O70">
-        <v>3.33</v>
+        <v>3.48</v>
       </c>
       <c r="P70">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA70">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AB70">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.68</v>
+        <v>1.85</v>
       </c>
       <c r="O71">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P71">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="Q71">
-        <v>3.46</v>
+        <v>2.63</v>
       </c>
       <c r="R71">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S71">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T71">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="U71">
-        <v>2.93</v>
+        <v>2.78</v>
       </c>
       <c r="V71">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W71">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y71">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z71">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="AA71">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB71">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AC71">
-        <v>3.66</v>
+        <v>3.32</v>
       </c>
       <c r="AD71">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE71">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF71">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG71">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK71">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="AL71">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="O10">
-        <v>3.65</v>
+        <v>4.13</v>
       </c>
       <c r="P10">
-        <v>3.32</v>
+        <v>4.82</v>
       </c>
       <c r="Q10">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="R10">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S10">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T10">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="U10">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z10">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="AA10">
+        <v>1.88</v>
+      </c>
+      <c r="AB10">
+        <v>1.93</v>
+      </c>
+      <c r="AC10">
+        <v>3.42</v>
+      </c>
+      <c r="AD10">
+        <v>1.28</v>
+      </c>
+      <c r="AE10">
+        <v>1.05</v>
+      </c>
+      <c r="AF10">
         <v>2.05</v>
       </c>
-      <c r="AB10">
-        <v>1.75</v>
-      </c>
-      <c r="AC10">
-        <v>3.3</v>
-      </c>
-      <c r="AD10">
+      <c r="AG10">
+        <v>1.67</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
         <v>1.3</v>
       </c>
-      <c r="AE10">
-        <v>1.06</v>
-      </c>
-      <c r="AF10">
-        <v>1.83</v>
-      </c>
-      <c r="AG10">
-        <v>1.86</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.24</v>
-      </c>
       <c r="AK10">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="O11">
-        <v>4.13</v>
+        <v>3.65</v>
       </c>
       <c r="P11">
-        <v>4.82</v>
+        <v>3.32</v>
       </c>
       <c r="Q11">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="R11">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S11">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T11">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="U11">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z11">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="AA11">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AB11">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AC11">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AD11">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK11">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -6186,55 +6186,55 @@
         <v>2.27</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X36">
         <v>0</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7816,55 +7816,55 @@
         <v>11.2</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X46">
         <v>0</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>6.86</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7979,55 +7979,55 @@
         <v>4.93</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X47">
         <v>0</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -10913,16 +10913,16 @@
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U65">
         <v>0</v>
@@ -10937,31 +10937,31 @@
         <v>0</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE65">
         <v>0</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>UD Logroñés II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Calamocha</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.8</v>
+        <v>2.72</v>
       </c>
       <c r="O68">
-        <v>3.69</v>
+        <v>3.33</v>
       </c>
       <c r="P68">
-        <v>4.52</v>
+        <v>2.59</v>
       </c>
       <c r="Q68">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S68">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T68">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U68">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V68">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W68">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y68">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z68">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AA68">
-        <v>2.13</v>
+        <v>2.35</v>
       </c>
       <c r="AB68">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC68">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AD68">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE68">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF68">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG68">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK68">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UD Logroñés II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="O69">
-        <v>3.33</v>
+        <v>3.48</v>
       </c>
       <c r="P69">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA69">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="AB69">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Manresa</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.68</v>
+        <v>1.85</v>
       </c>
       <c r="O70">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="P70">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="Q70">
-        <v>3.46</v>
+        <v>2.63</v>
       </c>
       <c r="R70">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S70">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T70">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="U70">
-        <v>2.93</v>
+        <v>2.78</v>
       </c>
       <c r="V70">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W70">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X70">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y70">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Z70">
-        <v>2.95</v>
+        <v>3.19</v>
       </c>
       <c r="AA70">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB70">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AC70">
-        <v>3.66</v>
+        <v>3.32</v>
       </c>
       <c r="AD70">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AE70">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF70">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG70">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK70">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Manresa</t>
+          <t>Calamocha</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="O71">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="P71">
-        <v>3.75</v>
+        <v>4.52</v>
       </c>
       <c r="Q71">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="R71">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="S71">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T71">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="U71">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="V71">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="W71">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z71">
-        <v>3.19</v>
+        <v>2.74</v>
       </c>
       <c r="AA71">
+        <v>2.13</v>
+      </c>
+      <c r="AB71">
+        <v>1.61</v>
+      </c>
+      <c r="AC71">
+        <v>3.82</v>
+      </c>
+      <c r="AD71">
+        <v>1.18</v>
+      </c>
+      <c r="AE71">
+        <v>1.03</v>
+      </c>
+      <c r="AF71">
         <v>1.98</v>
       </c>
-      <c r="AB71">
-        <v>1.83</v>
-      </c>
-      <c r="AC71">
-        <v>3.32</v>
-      </c>
-      <c r="AD71">
-        <v>1.29</v>
-      </c>
-      <c r="AE71">
-        <v>1.06</v>
-      </c>
-      <c r="AF71">
-        <v>1.8</v>
-      </c>
       <c r="AG71">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.22</v>
       </c>
       <c r="AK71">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -17540,7 +17540,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="O106">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="P106">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17626,10 +17626,10 @@
         <v>0</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC106">
         <v>0</v>
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-10-04 17:00:00</t>
+          <t>2026-10-04 16:30:00</t>
         </is>
       </c>
     </row>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="O107">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="P107">
-        <v>3.33</v>
+        <v>3.65</v>
       </c>
       <c r="Q107">
         <v>0</v>
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18761,10 +18761,10 @@
         <v>0</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA113">
         <v>0</v>
@@ -19543,13 +19543,13 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q118">
         <v>0</v>
@@ -19576,10 +19576,10 @@
         <v>0</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA118">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="Q47">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T47">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="U47">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V47">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W47">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X47">
         <v>0</v>
       </c>
       <c r="Y47">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z47">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AA47">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB47">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC47">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AD47">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AE47">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF47">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK47">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
         <v>0</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL48">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="O6">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P6">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="Q6">
-        <v>3.64</v>
+        <v>3.47</v>
       </c>
       <c r="R6">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S6">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="T6">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="U6">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="V6">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W6">
         <v>1.06</v>
       </c>
       <c r="X6">
+        <v>1.03</v>
+      </c>
+      <c r="Y6">
+        <v>1.39</v>
+      </c>
+      <c r="Z6">
+        <v>2.69</v>
+      </c>
+      <c r="AA6">
+        <v>2.27</v>
+      </c>
+      <c r="AB6">
+        <v>1.62</v>
+      </c>
+      <c r="AC6">
+        <v>4.2</v>
+      </c>
+      <c r="AD6">
+        <v>1.15</v>
+      </c>
+      <c r="AE6">
         <v>1.01</v>
       </c>
-      <c r="Y6">
-        <v>1.33</v>
-      </c>
-      <c r="Z6">
-        <v>2.83</v>
-      </c>
-      <c r="AA6">
-        <v>2.14</v>
-      </c>
-      <c r="AB6">
-        <v>1.71</v>
-      </c>
-      <c r="AC6">
-        <v>3.78</v>
-      </c>
-      <c r="AD6">
-        <v>1.19</v>
-      </c>
-      <c r="AE6">
-        <v>1.02</v>
-      </c>
       <c r="AF6">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG6">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="P8">
-        <v>4.1</v>
+        <v>3.96</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="O9">
         <v>3.5</v>
       </c>
       <c r="P9">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q9">
+        <v>2.3</v>
+      </c>
+      <c r="R9">
         <v>2.26</v>
       </c>
-      <c r="R9">
-        <v>2.13</v>
-      </c>
       <c r="S9">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T9">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="U9">
-        <v>2.61</v>
+        <v>2.8</v>
       </c>
       <c r="V9">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
+        <v>1.28</v>
+      </c>
+      <c r="Z9">
+        <v>3.38</v>
+      </c>
+      <c r="AA9">
+        <v>1.9</v>
+      </c>
+      <c r="AB9">
+        <v>1.9</v>
+      </c>
+      <c r="AC9">
+        <v>3.1</v>
+      </c>
+      <c r="AD9">
         <v>1.26</v>
-      </c>
-      <c r="Z9">
-        <v>3.2</v>
-      </c>
-      <c r="AA9">
-        <v>1.98</v>
-      </c>
-      <c r="AB9">
-        <v>1.83</v>
-      </c>
-      <c r="AC9">
-        <v>3.14</v>
-      </c>
-      <c r="AD9">
-        <v>1.27</v>
       </c>
       <c r="AE9">
         <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK9">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O23">
         <v>3.3</v>
@@ -4067,55 +4067,55 @@
         <v>4.33</v>
       </c>
       <c r="Q23">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="R23">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="S23">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="T23">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="U23">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="V23">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W23">
+        <v>1.05</v>
+      </c>
+      <c r="X23">
         <v>1.02</v>
       </c>
-      <c r="X23">
-        <v>1.01</v>
-      </c>
       <c r="Y23">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="Z23">
-        <v>3.01</v>
+        <v>2.69</v>
       </c>
       <c r="AA23">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="AB23">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AC23">
-        <v>3.56</v>
+        <v>4.2</v>
       </c>
       <c r="AD23">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE23">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF23">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AG23">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="O24">
-        <v>3.24</v>
+        <v>2.9</v>
       </c>
       <c r="P24">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="Q24">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="R24">
         <v>1.91</v>
       </c>
       <c r="S24">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="T24">
+        <v>2.5</v>
+      </c>
+      <c r="U24">
+        <v>3.2</v>
+      </c>
+      <c r="V24">
+        <v>1.3</v>
+      </c>
+      <c r="W24">
+        <v>1.04</v>
+      </c>
+      <c r="X24">
+        <v>1.04</v>
+      </c>
+      <c r="Y24">
+        <v>1.42</v>
+      </c>
+      <c r="Z24">
+        <v>2.69</v>
+      </c>
+      <c r="AA24">
         <v>2.38</v>
       </c>
-      <c r="U24">
-        <v>3.52</v>
-      </c>
-      <c r="V24">
-        <v>1.22</v>
-      </c>
-      <c r="W24">
-        <v>1.03</v>
-      </c>
-      <c r="X24">
-        <v>1.07</v>
-      </c>
-      <c r="Y24">
-        <v>1.59</v>
-      </c>
-      <c r="Z24">
-        <v>2.33</v>
-      </c>
-      <c r="AA24">
-        <v>2.64</v>
-      </c>
       <c r="AB24">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="AC24">
-        <v>5.38</v>
+        <v>4.01</v>
       </c>
       <c r="AD24">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AE24">
         <v>1.01</v>
       </c>
       <c r="AF24">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="AG24">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK24">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,52 +4384,52 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="O25">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="P25">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q25">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="R25">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="S25">
+        <v>1.5</v>
+      </c>
+      <c r="T25">
+        <v>2.45</v>
+      </c>
+      <c r="U25">
+        <v>3.4</v>
+      </c>
+      <c r="V25">
+        <v>1.25</v>
+      </c>
+      <c r="W25">
+        <v>1.05</v>
+      </c>
+      <c r="X25">
+        <v>1.07</v>
+      </c>
+      <c r="Y25">
         <v>1.49</v>
       </c>
-      <c r="T25">
-        <v>2.35</v>
-      </c>
-      <c r="U25">
-        <v>3.5</v>
-      </c>
-      <c r="V25">
-        <v>1.26</v>
-      </c>
-      <c r="W25">
-        <v>1.04</v>
-      </c>
-      <c r="X25">
-        <v>1.04</v>
-      </c>
-      <c r="Y25">
-        <v>1.44</v>
-      </c>
       <c r="Z25">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="AA25">
-        <v>2.44</v>
+        <v>2.61</v>
       </c>
       <c r="AB25">
         <v>1.47</v>
       </c>
       <c r="AC25">
-        <v>4.85</v>
+        <v>5.35</v>
       </c>
       <c r="AD25">
         <v>1.11</v>
@@ -4441,7 +4441,7 @@
         <v>2.1</v>
       </c>
       <c r="AG25">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC115">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC116">
         <v>0</v>
@@ -19869,13 +19869,13 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q120">
         <v>0</v>
@@ -19908,10 +19908,10 @@
         <v>0</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC120">
         <v>0</v>
@@ -20234,10 +20234,10 @@
         <v>0</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC122">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -644,19 +644,19 @@
         <v>2.8</v>
       </c>
       <c r="Q2">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R2">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="U2">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="V2">
         <v>1.44</v>
@@ -668,25 +668,25 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z2">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AA2">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AB2">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AC2">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="AD2">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF2">
         <v>1.57</v>
@@ -708,7 +708,7 @@
         <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,55 +798,55 @@
         </is>
       </c>
       <c r="N3">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O3">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P3">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="Q3">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R3">
         <v>2.14</v>
       </c>
       <c r="S3">
+        <v>1.4</v>
+      </c>
+      <c r="T3">
+        <v>2.66</v>
+      </c>
+      <c r="U3">
+        <v>2.88</v>
+      </c>
+      <c r="V3">
         <v>1.36</v>
       </c>
-      <c r="T3">
-        <v>2.92</v>
-      </c>
-      <c r="U3">
-        <v>2.61</v>
-      </c>
-      <c r="V3">
-        <v>1.39</v>
-      </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z3">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="AA3">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB3">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC3">
-        <v>3.49</v>
+        <v>3.4</v>
       </c>
       <c r="AD3">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE3">
         <v>1.06</v>
@@ -871,7 +871,7 @@
         <v>1.21</v>
       </c>
       <c r="AK3">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="O4">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="P4">
         <v>2.2</v>
       </c>
       <c r="Q4">
-        <v>3.75</v>
+        <v>3.57</v>
       </c>
       <c r="R4">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S4">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T4">
         <v>2.51</v>
       </c>
       <c r="U4">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="V4">
         <v>1.3</v>
       </c>
       <c r="W4">
+        <v>1.04</v>
+      </c>
+      <c r="X4">
         <v>1.05</v>
       </c>
-      <c r="X4">
-        <v>1.03</v>
-      </c>
       <c r="Y4">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z4">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AA4">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AB4">
         <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="AD4">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE4">
         <v>1.03</v>
       </c>
       <c r="AF4">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG4">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AK4">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="O5">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P5">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="Q5">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R5">
         <v>2.1</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="T5">
         <v>2.88</v>
       </c>
       <c r="U5">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z5">
-        <v>3.27</v>
+        <v>2.97</v>
       </c>
       <c r="AA5">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AB5">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC5">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="AD5">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AE5">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AG5">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1954,10 +1954,10 @@
         <v>2.15</v>
       </c>
       <c r="S10">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T10">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="U10">
         <v>2.8</v>
@@ -1966,37 +1966,37 @@
         <v>1.36</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z10">
-        <v>3.11</v>
+        <v>3.27</v>
       </c>
       <c r="AA10">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AB10">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AC10">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="AD10">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE10">
         <v>1.05</v>
       </c>
       <c r="AF10">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG10">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,55 +2102,55 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="O11">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>3.32</v>
+        <v>3.89</v>
       </c>
       <c r="Q11">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="R11">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="U11">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="V11">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
         <v>1.31</v>
       </c>
       <c r="Z11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AA11">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB11">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AC11">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AD11">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE11">
         <v>1.06</v>
@@ -2159,7 +2159,7 @@
         <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,28 +2265,28 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="O12">
-        <v>3.32</v>
+        <v>3.51</v>
       </c>
       <c r="P12">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="Q12">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="R12">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="S12">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U12">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="V12">
         <v>1.44</v>
@@ -2295,34 +2295,34 @@
         <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
         <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.86</v>
+        <v>3.91</v>
       </c>
       <c r="AA12">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB12">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AC12">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="AD12">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
         <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG12">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2434,55 +2434,55 @@
         <v>3.2</v>
       </c>
       <c r="P13">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q13">
+        <v>2.51</v>
+      </c>
+      <c r="R13">
+        <v>2.06</v>
+      </c>
+      <c r="S13">
+        <v>1.37</v>
+      </c>
+      <c r="T13">
+        <v>2.98</v>
+      </c>
+      <c r="U13">
         <v>2.75</v>
       </c>
-      <c r="R13">
-        <v>1.99</v>
-      </c>
-      <c r="S13">
-        <v>1.41</v>
-      </c>
-      <c r="T13">
-        <v>2.76</v>
-      </c>
-      <c r="U13">
-        <v>3.05</v>
-      </c>
       <c r="V13">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W13">
+        <v>1.08</v>
+      </c>
+      <c r="X13">
         <v>1.02</v>
       </c>
-      <c r="X13">
-        <v>1.01</v>
-      </c>
       <c r="Y13">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z13">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA13">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB13">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AC13">
-        <v>3.58</v>
+        <v>3.13</v>
       </c>
       <c r="AD13">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE13">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF13">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AG13">
         <v>1.83</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4710,16 +4710,16 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O27">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>4.46</v>
+        <v>4.2</v>
       </c>
       <c r="Q27">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="R27">
         <v>2.1</v>
@@ -4728,46 +4728,46 @@
         <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U27">
+        <v>2.7</v>
+      </c>
+      <c r="V27">
+        <v>1.4</v>
+      </c>
+      <c r="W27">
+        <v>1.07</v>
+      </c>
+      <c r="X27">
+        <v>1.04</v>
+      </c>
+      <c r="Y27">
+        <v>1.31</v>
+      </c>
+      <c r="Z27">
         <v>3.12</v>
       </c>
-      <c r="V27">
-        <v>1.28</v>
-      </c>
-      <c r="W27">
-        <v>1.01</v>
-      </c>
-      <c r="X27">
-        <v>1.01</v>
-      </c>
-      <c r="Y27">
-        <v>1.33</v>
-      </c>
-      <c r="Z27">
-        <v>2.83</v>
-      </c>
       <c r="AA27">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AB27">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AC27">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="AD27">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE27">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AG27">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.66</v>
+        <v>3.97</v>
       </c>
       <c r="O28">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P28">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="Q28">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S28">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T28">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="U28">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="V28">
         <v>1.3</v>
       </c>
       <c r="W28">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="Z28">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="AA28">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AB28">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC28">
-        <v>3.8</v>
+        <v>3.94</v>
       </c>
       <c r="AD28">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE28">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG28">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AK28">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.52</v>
+        <v>2.23</v>
       </c>
       <c r="O34">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="P34">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="Q34">
         <v>3.14</v>
@@ -5869,13 +5869,13 @@
         <v>1.43</v>
       </c>
       <c r="T34">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="U34">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="V34">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W34">
         <v>1.03</v>
@@ -5884,22 +5884,22 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z34">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="AA34">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AB34">
         <v>1.73</v>
       </c>
       <c r="AC34">
-        <v>3.87</v>
+        <v>3.9</v>
       </c>
       <c r="AD34">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE34">
         <v>1.03</v>
@@ -6014,16 +6014,16 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="P35">
-        <v>2.94</v>
+        <v>2.47</v>
       </c>
       <c r="Q35">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="R35">
         <v>2.04</v>
@@ -6041,28 +6041,28 @@
         <v>1.4</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
         <v>1</v>
       </c>
       <c r="Y35">
+        <v>1.23</v>
+      </c>
+      <c r="Z35">
+        <v>3.42</v>
+      </c>
+      <c r="AA35">
+        <v>1.85</v>
+      </c>
+      <c r="AB35">
+        <v>1.88</v>
+      </c>
+      <c r="AC35">
+        <v>3.3</v>
+      </c>
+      <c r="AD35">
         <v>1.3</v>
-      </c>
-      <c r="Z35">
-        <v>3.4</v>
-      </c>
-      <c r="AA35">
-        <v>1.96</v>
-      </c>
-      <c r="AB35">
-        <v>1.85</v>
-      </c>
-      <c r="AC35">
-        <v>3.4</v>
-      </c>
-      <c r="AD35">
-        <v>1.29</v>
       </c>
       <c r="AE35">
         <v>1.07</v>
@@ -6087,7 +6087,7 @@
         <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="O37">
         <v>3.25</v>
       </c>
       <c r="P37">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>4.37</v>
+        <v>3.8</v>
       </c>
       <c r="O38">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="Q38">
-        <v>5.55</v>
+        <v>4.33</v>
       </c>
       <c r="R38">
         <v>2.2</v>
       </c>
       <c r="S38">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="T38">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U38">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="V38">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="W38">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z38">
-        <v>3.02</v>
+        <v>3.44</v>
       </c>
       <c r="AA38">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AB38">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AC38">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="AD38">
+        <v>1.34</v>
+      </c>
+      <c r="AE38">
+        <v>1.08</v>
+      </c>
+      <c r="AF38">
+        <v>1.78</v>
+      </c>
+      <c r="AG38">
+        <v>1.95</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
+        <v>1.25</v>
+      </c>
+      <c r="AK38">
         <v>1.22</v>
-      </c>
-      <c r="AE38">
-        <v>1.05</v>
-      </c>
-      <c r="AF38">
-        <v>1.93</v>
-      </c>
-      <c r="AG38">
-        <v>1.75</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.22</v>
-      </c>
-      <c r="AK38">
-        <v>1.13</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,55 +6675,55 @@
         <v>3.41</v>
       </c>
       <c r="Q39">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="R39">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S39">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T39">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="U39">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="V39">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W39">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
         <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Z39">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="AA39">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AB39">
         <v>1.61</v>
       </c>
       <c r="AC39">
-        <v>3.92</v>
+        <v>4.07</v>
       </c>
       <c r="AD39">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE39">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF39">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AG39">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="O40">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P40">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="Q40">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="R40">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="S40">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T40">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="U40">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V40">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W40">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Z40">
-        <v>3.16</v>
+        <v>3.62</v>
       </c>
       <c r="AA40">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB40">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AC40">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AD40">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AE40">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF40">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AG40">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="O41">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="P41">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="Q41">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="R41">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="S41">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T41">
         <v>2.66</v>
       </c>
       <c r="U41">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="V41">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W41">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z41">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA41">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB41">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC41">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="AD41">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE41">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF41">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AG41">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK41">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,31 +7155,31 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="O42">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
-        <v>3.89</v>
+        <v>3.15</v>
       </c>
       <c r="Q42">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="R42">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="S42">
         <v>1.25</v>
       </c>
       <c r="T42">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U42">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V42">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W42">
         <v>1.15</v>
@@ -7197,22 +7197,22 @@
         <v>1.5</v>
       </c>
       <c r="AB42">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AC42">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AD42">
         <v>1.58</v>
       </c>
       <c r="AE42">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF42">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG42">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,10 +7318,10 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="O43">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
         <v>2.5</v>
@@ -7339,34 +7339,34 @@
         <v>3.75</v>
       </c>
       <c r="U43">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="V43">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W43">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z43">
         <v>5</v>
       </c>
       <c r="AA43">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AB43">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC43">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AD43">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE43">
         <v>1.19</v>
@@ -7375,7 +7375,7 @@
         <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -8631,46 +8631,46 @@
         <v>3.75</v>
       </c>
       <c r="Q51">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="R51">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="S51">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T51">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U51">
-        <v>2.54</v>
+        <v>2.39</v>
       </c>
       <c r="V51">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W51">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X51">
         <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z51">
         <v>3.9</v>
       </c>
       <c r="AA51">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB51">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AC51">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="AD51">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE51">
         <v>1.09</v>
@@ -8679,7 +8679,7 @@
         <v>1.65</v>
       </c>
       <c r="AG51">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8794,55 +8794,55 @@
         <v>1.1</v>
       </c>
       <c r="Q52">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="R52">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="S52">
         <v>1.19</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>4.16</v>
       </c>
       <c r="U52">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V52">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W52">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z52">
-        <v>6.36</v>
+        <v>6.48</v>
       </c>
       <c r="AA52">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AB52">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="AC52">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AD52">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AE52">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AF52">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG52">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>5</v>
+        <v>1.02</v>
       </c>
       <c r="AK52">
         <v>1.03</v>
@@ -8960,13 +8960,13 @@
         <v>2.3</v>
       </c>
       <c r="R53">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="S53">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T53">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U53">
         <v>2.4</v>
@@ -8975,34 +8975,34 @@
         <v>1.51</v>
       </c>
       <c r="W53">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z53">
-        <v>4.06</v>
+        <v>4.33</v>
       </c>
       <c r="AA53">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AB53">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="AC53">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AD53">
         <v>1.46</v>
       </c>
       <c r="AE53">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF53">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG53">
         <v>2.15</v>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK53">
         <v>1.95</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O55">
-        <v>6.35</v>
+        <v>5.6</v>
       </c>
       <c r="P55">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="Q55">
         <v>8.699999999999999</v>
@@ -9295,13 +9295,13 @@
         <v>4.5</v>
       </c>
       <c r="U55">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V55">
         <v>1.67</v>
       </c>
       <c r="W55">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X55">
         <v>1.01</v>
@@ -9316,22 +9316,22 @@
         <v>1.38</v>
       </c>
       <c r="AB55">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AC55">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AD55">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AE55">
         <v>1.32</v>
       </c>
       <c r="AF55">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG55">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="AK55">
         <v>1.02</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O56">
         <v>3.5</v>
       </c>
       <c r="P56">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9612,7 +9612,7 @@
         <v>1.96</v>
       </c>
       <c r="R57">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="S57">
         <v>1.3</v>
@@ -9621,13 +9621,13 @@
         <v>3.2</v>
       </c>
       <c r="U57">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="V57">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W57">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X57">
         <v>1.02</v>
@@ -9636,19 +9636,19 @@
         <v>1.18</v>
       </c>
       <c r="Z57">
-        <v>3.97</v>
+        <v>4.01</v>
       </c>
       <c r="AA57">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB57">
         <v>2.09</v>
       </c>
       <c r="AC57">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="AD57">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE57">
         <v>1.12</v>
@@ -9657,7 +9657,7 @@
         <v>1.8</v>
       </c>
       <c r="AG57">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>1.19</v>
       </c>
       <c r="AK57">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="O58">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="P58">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="Q58">
         <v>3.4</v>
       </c>
       <c r="R58">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="S58">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T58">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U58">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="V58">
         <v>1.35</v>
       </c>
       <c r="W58">
+        <v>1.07</v>
+      </c>
+      <c r="X58">
+        <v>1.01</v>
+      </c>
+      <c r="Y58">
+        <v>1.33</v>
+      </c>
+      <c r="Z58">
+        <v>3.1</v>
+      </c>
+      <c r="AA58">
+        <v>2.05</v>
+      </c>
+      <c r="AB58">
+        <v>1.71</v>
+      </c>
+      <c r="AC58">
+        <v>3.9</v>
+      </c>
+      <c r="AD58">
+        <v>1.22</v>
+      </c>
+      <c r="AE58">
         <v>1.02</v>
       </c>
-      <c r="X58">
-        <v>1.02</v>
-      </c>
-      <c r="Y58">
-        <v>1.42</v>
-      </c>
-      <c r="Z58">
-        <v>2.74</v>
-      </c>
-      <c r="AA58">
-        <v>2.25</v>
-      </c>
-      <c r="AB58">
-        <v>1.61</v>
-      </c>
-      <c r="AC58">
-        <v>3.96</v>
-      </c>
-      <c r="AD58">
-        <v>1.17</v>
-      </c>
-      <c r="AE58">
-        <v>1.01</v>
-      </c>
       <c r="AF58">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG58">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK58">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9935,13 +9935,13 @@
         <v>4.53</v>
       </c>
       <c r="Q59">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="R59">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="S59">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T59">
         <v>3</v>
@@ -9953,34 +9953,34 @@
         <v>1.44</v>
       </c>
       <c r="W59">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X59">
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z59">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AA59">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AB59">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AC59">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="AD59">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE59">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF59">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG59">
         <v>2</v>
@@ -9999,7 +9999,7 @@
         <v>1.25</v>
       </c>
       <c r="AK59">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -12543,55 +12543,55 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X75">
         <v>0</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="O80">
         <v>4</v>
       </c>
       <c r="P80">
-        <v>7.1</v>
+        <v>5.16</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13521,55 +13521,55 @@
         <v>2.66</v>
       </c>
       <c r="Q81">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="R81">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="S81">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="T81">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U81">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="V81">
         <v>1.4</v>
       </c>
       <c r="W81">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X81">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z81">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="AA81">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="AB81">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AC81">
-        <v>3.47</v>
+        <v>3.17</v>
       </c>
       <c r="AD81">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE81">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF81">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AG81">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK81">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,55 +13684,55 @@
         <v>2.44</v>
       </c>
       <c r="Q82">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="R82">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="S82">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T82">
-        <v>3.26</v>
+        <v>3.08</v>
       </c>
       <c r="U82">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V82">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W82">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X82">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y82">
         <v>1.18</v>
       </c>
       <c r="Z82">
-        <v>4.24</v>
+        <v>3.85</v>
       </c>
       <c r="AA82">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AB82">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AC82">
-        <v>2.53</v>
+        <v>2.74</v>
       </c>
       <c r="AD82">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE82">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF82">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG82">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK82">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.21</v>
+        <v>2.62</v>
       </c>
       <c r="O83">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="P83">
-        <v>3.13</v>
+        <v>2.62</v>
       </c>
       <c r="Q83">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R83">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S83">
         <v>1.44</v>
       </c>
       <c r="T83">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="U83">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="V83">
+        <v>1.29</v>
+      </c>
+      <c r="W83">
+        <v>1.05</v>
+      </c>
+      <c r="X83">
+        <v>1.05</v>
+      </c>
+      <c r="Y83">
+        <v>1.41</v>
+      </c>
+      <c r="Z83">
+        <v>2.56</v>
+      </c>
+      <c r="AA83">
+        <v>2.47</v>
+      </c>
+      <c r="AB83">
+        <v>1.5</v>
+      </c>
+      <c r="AC83">
+        <v>4.5</v>
+      </c>
+      <c r="AD83">
+        <v>1.16</v>
+      </c>
+      <c r="AE83">
+        <v>1.03</v>
+      </c>
+      <c r="AF83">
+        <v>1.95</v>
+      </c>
+      <c r="AG83">
+        <v>1.73</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
         <v>1.33</v>
       </c>
-      <c r="W83">
-        <v>1.01</v>
-      </c>
-      <c r="X83">
-        <v>1.03</v>
-      </c>
-      <c r="Y83">
-        <v>1.42</v>
-      </c>
-      <c r="Z83">
-        <v>2.76</v>
-      </c>
-      <c r="AA83">
-        <v>2.22</v>
-      </c>
-      <c r="AB83">
-        <v>1.66</v>
-      </c>
-      <c r="AC83">
-        <v>4.05</v>
-      </c>
-      <c r="AD83">
-        <v>1.17</v>
-      </c>
-      <c r="AE83">
-        <v>1.01</v>
-      </c>
-      <c r="AF83">
-        <v>1.85</v>
-      </c>
-      <c r="AG83">
-        <v>1.82</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.28</v>
-      </c>
       <c r="AK83">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="O88">
         <v>4.2</v>
       </c>
       <c r="P88">
-        <v>5.95</v>
+        <v>5.8</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14816,19 +14816,19 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="O89">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="P89">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Q89">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="R89">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="S89">
         <v>1.17</v>
@@ -14840,7 +14840,7 @@
         <v>1.95</v>
       </c>
       <c r="V89">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="W89">
         <v>1.2</v>
@@ -14858,7 +14858,7 @@
         <v>1.3</v>
       </c>
       <c r="AB89">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="AC89">
         <v>1.86</v>
@@ -14870,10 +14870,10 @@
         <v>1.35</v>
       </c>
       <c r="AF89">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG89">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AK89">
-        <v>3.84</v>
+        <v>3.55</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,34 +14979,34 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="O90">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P90">
-        <v>3.67</v>
+        <v>3.36</v>
       </c>
       <c r="Q90">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="R90">
         <v>2.1</v>
       </c>
       <c r="S90">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T90">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="U90">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="V90">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W90">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X90">
         <v>1.01</v>
@@ -15015,13 +15015,13 @@
         <v>1.26</v>
       </c>
       <c r="Z90">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA90">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AB90">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC90">
         <v>3.14</v>
@@ -15033,10 +15033,10 @@
         <v>1.06</v>
       </c>
       <c r="AF90">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG90">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK90">
         <v>1.65</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="O92">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P92">
-        <v>2.98</v>
+        <v>3.31</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15344,10 +15344,10 @@
         <v>0</v>
       </c>
       <c r="AA92">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AB92">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AC92">
         <v>0</v>
@@ -15477,25 +15477,25 @@
         <v>3.88</v>
       </c>
       <c r="Q93">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R93">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S93">
         <v>1.3</v>
       </c>
       <c r="T93">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U93">
-        <v>2.53</v>
+        <v>2.06</v>
       </c>
       <c r="V93">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W93">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X93">
         <v>1</v>
@@ -15504,28 +15504,28 @@
         <v>1.2</v>
       </c>
       <c r="Z93">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="AA93">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB93">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AC93">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AD93">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AE93">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF93">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AG93">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="AK93">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15803,55 +15803,55 @@
         <v>0</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X95">
         <v>0</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15960,13 +15960,13 @@
         <v>2.75</v>
       </c>
       <c r="O96">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P96">
-        <v>2.37</v>
+        <v>2.13</v>
       </c>
       <c r="Q96">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R96">
         <v>2.1</v>
@@ -15975,16 +15975,16 @@
         <v>1.38</v>
       </c>
       <c r="T96">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="U96">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="V96">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W96">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X96">
         <v>1.02</v>
@@ -15993,10 +15993,10 @@
         <v>1.29</v>
       </c>
       <c r="Z96">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AA96">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AB96">
         <v>1.82</v>
@@ -16008,13 +16008,13 @@
         <v>1.25</v>
       </c>
       <c r="AE96">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF96">
         <v>1.7</v>
       </c>
       <c r="AG96">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>1.29</v>
       </c>
       <c r="AK96">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="O98">
-        <v>3.57</v>
+        <v>3.3</v>
       </c>
       <c r="P98">
-        <v>3.26</v>
+        <v>4</v>
       </c>
       <c r="Q98">
-        <v>2.94</v>
+        <v>2.38</v>
       </c>
       <c r="R98">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S98">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T98">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="U98">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="V98">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W98">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X98">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y98">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z98">
-        <v>2.88</v>
+        <v>3.27</v>
       </c>
       <c r="AA98">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB98">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC98">
-        <v>3.74</v>
+        <v>3.42</v>
       </c>
       <c r="AD98">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE98">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF98">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG98">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>1.25</v>
       </c>
       <c r="AK98">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="O101">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="P101">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="Q101">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R101">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="S101">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T101">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U101">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="V101">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="W101">
+        <v>1.04</v>
+      </c>
+      <c r="X101">
+        <v>1.01</v>
+      </c>
+      <c r="Y101">
+        <v>1.36</v>
+      </c>
+      <c r="Z101">
+        <v>2.88</v>
+      </c>
+      <c r="AA101">
+        <v>1.98</v>
+      </c>
+      <c r="AB101">
+        <v>1.85</v>
+      </c>
+      <c r="AC101">
+        <v>3.5</v>
+      </c>
+      <c r="AD101">
+        <v>1.29</v>
+      </c>
+      <c r="AE101">
         <v>1.06</v>
       </c>
-      <c r="X101">
-        <v>1.02</v>
-      </c>
-      <c r="Y101">
-        <v>1.34</v>
-      </c>
-      <c r="Z101">
-        <v>2.78</v>
-      </c>
-      <c r="AA101">
-        <v>2.12</v>
-      </c>
-      <c r="AB101">
-        <v>1.65</v>
-      </c>
-      <c r="AC101">
-        <v>3.85</v>
-      </c>
-      <c r="AD101">
-        <v>1.18</v>
-      </c>
-      <c r="AE101">
-        <v>1.02</v>
-      </c>
       <c r="AF101">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AG101">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK101">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="O102">
-        <v>4.16</v>
+        <v>3.6</v>
       </c>
       <c r="P102">
-        <v>4.37</v>
+        <v>3.9</v>
       </c>
       <c r="Q102">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R102">
-        <v>2.41</v>
+        <v>2.24</v>
       </c>
       <c r="S102">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T102">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="U102">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="V102">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W102">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X102">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z102">
-        <v>3.83</v>
+        <v>3.4</v>
       </c>
       <c r="AA102">
+        <v>1.87</v>
+      </c>
+      <c r="AB102">
         <v>1.8</v>
       </c>
-      <c r="AB102">
-        <v>2</v>
-      </c>
       <c r="AC102">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="AD102">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE102">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF102">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG102">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>1.17</v>
       </c>
       <c r="AK102">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,43 +17098,43 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="O103">
-        <v>4.01</v>
+        <v>3.5</v>
       </c>
       <c r="P103">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="Q103">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="R103">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S103">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="T103">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="U103">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="V103">
         <v>1.4</v>
       </c>
       <c r="W103">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X103">
         <v>1.02</v>
       </c>
       <c r="Y103">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z103">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="AA103">
         <v>2.05</v>
@@ -17143,19 +17143,19 @@
         <v>1.75</v>
       </c>
       <c r="AC103">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AD103">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE103">
         <v>1.06</v>
       </c>
       <c r="AF103">
+        <v>1.8</v>
+      </c>
+      <c r="AG103">
         <v>1.83</v>
-      </c>
-      <c r="AG103">
-        <v>1.81</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>1.25</v>
       </c>
       <c r="AK103">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17270,55 +17270,55 @@
         <v>2.47</v>
       </c>
       <c r="Q104">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="R104">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="S104">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="T104">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="U104">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="V104">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W104">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X104">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y104">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z104">
-        <v>2.87</v>
+        <v>3.12</v>
       </c>
       <c r="AA104">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="AB104">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC104">
-        <v>3.85</v>
+        <v>3.34</v>
       </c>
       <c r="AD104">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AE104">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF104">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG104">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -17331,10 +17331,10 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK104">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AL104">
         <v>0</v>
@@ -17424,16 +17424,16 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="O105">
-        <v>3.63</v>
+        <v>3.2</v>
       </c>
       <c r="P105">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q105">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R105">
         <v>2.15</v>
@@ -17442,10 +17442,10 @@
         <v>1.33</v>
       </c>
       <c r="T105">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="U105">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="V105">
         <v>1.43</v>
@@ -17457,31 +17457,31 @@
         <v>1</v>
       </c>
       <c r="Y105">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z105">
         <v>3.7</v>
       </c>
       <c r="AA105">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AB105">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC105">
         <v>3.1</v>
       </c>
       <c r="AD105">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE105">
         <v>1.1</v>
       </c>
       <c r="AF105">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG105">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK105">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18239,10 +18239,10 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="O110">
-        <v>3.88</v>
+        <v>4.56</v>
       </c>
       <c r="P110">
         <v>4.2</v>
@@ -18417,13 +18417,13 @@
         <v>2.62</v>
       </c>
       <c r="S111">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T111">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="U111">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="V111">
         <v>1.65</v>
@@ -18435,22 +18435,22 @@
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z111">
-        <v>5.69</v>
+        <v>3.6</v>
       </c>
       <c r="AA111">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AB111">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="AC111">
         <v>2.13</v>
       </c>
       <c r="AD111">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AE111">
         <v>1.3</v>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.14</v>
+        <v>2.8</v>
       </c>
       <c r="AK111">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18574,55 +18574,55 @@
         <v>2.85</v>
       </c>
       <c r="Q112">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="R112">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="S112">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T112">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="U112">
-        <v>2.51</v>
+        <v>2.66</v>
       </c>
       <c r="V112">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W112">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X112">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y112">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z112">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="AA112">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AB112">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="AC112">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AD112">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE112">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF112">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG112">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK112">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -20068,13 +20068,13 @@
         <v>1.17</v>
       </c>
       <c r="Z121">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="AA121">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AB121">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AC121">
         <v>2.38</v>
@@ -20086,10 +20086,10 @@
         <v>1.09</v>
       </c>
       <c r="AF121">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG121">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O14">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P14">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q14">
-        <v>3.11</v>
+        <v>2.7</v>
       </c>
       <c r="R14">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S14">
         <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="U14">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="V14">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W14">
         <v>1.04</v>
@@ -2627,28 +2627,28 @@
         <v>1.31</v>
       </c>
       <c r="Z14">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="AA14">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AB14">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AC14">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="AD14">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE14">
         <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AG14">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK14">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>4.25</v>
       </c>
       <c r="Q15">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S15">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T15">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="U15">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
         <v>0</v>
       </c>
       <c r="Y15">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z15">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AA15">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AB15">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC15">
-        <v>3.09</v>
+        <v>2.97</v>
       </c>
       <c r="AD15">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE15">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF15">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG15">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK15">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="O16">
         <v>3.2</v>
       </c>
       <c r="P16">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q16">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="R16">
         <v>2</v>
       </c>
       <c r="S16">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T16">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="U16">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="V16">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="Z16">
-        <v>3.06</v>
+        <v>2.7</v>
       </c>
       <c r="AA16">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AB16">
+        <v>1.6</v>
+      </c>
+      <c r="AC16">
+        <v>3.92</v>
+      </c>
+      <c r="AD16">
+        <v>1.21</v>
+      </c>
+      <c r="AE16">
+        <v>1.02</v>
+      </c>
+      <c r="AF16">
+        <v>1.95</v>
+      </c>
+      <c r="AG16">
+        <v>1.75</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.26</v>
+      </c>
+      <c r="AK16">
         <v>1.66</v>
-      </c>
-      <c r="AC16">
-        <v>3.48</v>
-      </c>
-      <c r="AD16">
-        <v>1.27</v>
-      </c>
-      <c r="AE16">
-        <v>1.04</v>
-      </c>
-      <c r="AF16">
-        <v>1.86</v>
-      </c>
-      <c r="AG16">
-        <v>1.8</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.24</v>
-      </c>
-      <c r="AK16">
-        <v>1.68</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,61 +3083,61 @@
         <v>3</v>
       </c>
       <c r="O17">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P17">
         <v>2.3</v>
       </c>
       <c r="Q17">
-        <v>3.88</v>
+        <v>4.07</v>
       </c>
       <c r="R17">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="S17">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="T17">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="U17">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V17">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W17">
         <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
         <v>1.44</v>
       </c>
       <c r="Z17">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="AA17">
-        <v>2.26</v>
+        <v>2.53</v>
       </c>
       <c r="AB17">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AC17">
-        <v>4.17</v>
+        <v>4.52</v>
       </c>
       <c r="AD17">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG17">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.28</v>
       </c>
       <c r="AK17">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -5857,7 +5857,7 @@
         <v>3.15</v>
       </c>
       <c r="P34">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="Q34">
         <v>3.14</v>
@@ -6186,25 +6186,25 @@
         <v>2.27</v>
       </c>
       <c r="Q36">
-        <v>3.54</v>
+        <v>3.84</v>
       </c>
       <c r="R36">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="S36">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.13</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
         <v>2.46</v>
       </c>
       <c r="V36">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W36">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X36">
         <v>0</v>
@@ -6213,28 +6213,28 @@
         <v>1.19</v>
       </c>
       <c r="Z36">
-        <v>4.17</v>
+        <v>4.04</v>
       </c>
       <c r="AA36">
         <v>1.68</v>
       </c>
       <c r="AB36">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AC36">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AD36">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE36">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF36">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG36">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK36">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7816,10 +7816,10 @@
         <v>11.2</v>
       </c>
       <c r="Q46">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R46">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="S46">
         <v>1.18</v>
@@ -7828,10 +7828,10 @@
         <v>4.2</v>
       </c>
       <c r="U46">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V46">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W46">
         <v>1.22</v>
@@ -7843,28 +7843,28 @@
         <v>1.05</v>
       </c>
       <c r="Z46">
-        <v>6.86</v>
+        <v>6.87</v>
       </c>
       <c r="AA46">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AB46">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="AC46">
+        <v>1.84</v>
+      </c>
+      <c r="AD46">
+        <v>1.83</v>
+      </c>
+      <c r="AE46">
+        <v>1.4</v>
+      </c>
+      <c r="AF46">
         <v>1.9</v>
       </c>
-      <c r="AD46">
-        <v>1.9</v>
-      </c>
-      <c r="AE46">
-        <v>1.39</v>
-      </c>
-      <c r="AF46">
-        <v>1.87</v>
-      </c>
       <c r="AG46">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK46">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8148,10 +8148,10 @@
         <v>2.38</v>
       </c>
       <c r="S48">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T48">
-        <v>3.26</v>
+        <v>3.6</v>
       </c>
       <c r="U48">
         <v>2.4</v>
@@ -8160,7 +8160,7 @@
         <v>1.5</v>
       </c>
       <c r="W48">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
         <v>0</v>
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q65">
         <v>2.8</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="O72">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P72">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB72">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.63</v>
+        <v>2.91</v>
       </c>
       <c r="O73">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="P73">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,22 +16772,22 @@
         </is>
       </c>
       <c r="N101">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="O101">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P101">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="Q101">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="R101">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="S101">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T101">
         <v>2.9</v>
@@ -16796,56 +16796,56 @@
         <v>2.76</v>
       </c>
       <c r="V101">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W101">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X101">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y101">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z101">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AA101">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB101">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC101">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD101">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE101">
         <v>1.06</v>
       </c>
       <c r="AF101">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG101">
+        <v>1.83</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ101">
+        <v>1.25</v>
+      </c>
+      <c r="AK101">
         <v>1.95</v>
-      </c>
-      <c r="AH101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ101">
-        <v>1.24</v>
-      </c>
-      <c r="AK101">
-        <v>1.67</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="O102">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P102">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q102">
-        <v>2.18</v>
+        <v>2.88</v>
       </c>
       <c r="R102">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="S102">
         <v>1.35</v>
       </c>
       <c r="T102">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="U102">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="V102">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W102">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X102">
         <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="Z102">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="AA102">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB102">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC102">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AD102">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE102">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF102">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AG102">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AK102">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="O103">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P103">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q103">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R103">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="S103">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T103">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="U103">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="V103">
         <v>1.4</v>
       </c>
       <c r="W103">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X103">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z103">
+        <v>3.4</v>
+      </c>
+      <c r="AA103">
+        <v>1.87</v>
+      </c>
+      <c r="AB103">
+        <v>1.8</v>
+      </c>
+      <c r="AC103">
         <v>3.14</v>
       </c>
-      <c r="AA103">
-        <v>2.05</v>
-      </c>
-      <c r="AB103">
-        <v>1.75</v>
-      </c>
-      <c r="AC103">
-        <v>3.4</v>
-      </c>
       <c r="AD103">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE103">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF103">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG103">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK103">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -19706,31 +19706,31 @@
         </is>
       </c>
       <c r="N119">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="O119">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P119">
-        <v>3.09</v>
+        <v>2.35</v>
       </c>
       <c r="Q119">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="R119">
         <v>2.3</v>
       </c>
       <c r="S119">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T119">
-        <v>3.44</v>
+        <v>3.7</v>
       </c>
       <c r="U119">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="V119">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W119">
         <v>1.1</v>
@@ -19739,47 +19739,47 @@
         <v>1</v>
       </c>
       <c r="Y119">
+        <v>1.12</v>
+      </c>
+      <c r="Z119">
+        <v>4.7</v>
+      </c>
+      <c r="AA119">
+        <v>1.53</v>
+      </c>
+      <c r="AB119">
+        <v>2.29</v>
+      </c>
+      <c r="AC119">
+        <v>2.33</v>
+      </c>
+      <c r="AD119">
+        <v>1.48</v>
+      </c>
+      <c r="AE119">
         <v>1.16</v>
       </c>
-      <c r="Z119">
-        <v>4.65</v>
-      </c>
-      <c r="AA119">
-        <v>1.54</v>
-      </c>
-      <c r="AB119">
-        <v>2.27</v>
-      </c>
-      <c r="AC119">
-        <v>2.35</v>
-      </c>
-      <c r="AD119">
+      <c r="AF119">
+        <v>1.45</v>
+      </c>
+      <c r="AG119">
+        <v>2.53</v>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ119">
+        <v>1.2</v>
+      </c>
+      <c r="AK119">
         <v>1.47</v>
-      </c>
-      <c r="AE119">
-        <v>1.15</v>
-      </c>
-      <c r="AF119">
-        <v>1.48</v>
-      </c>
-      <c r="AG119">
-        <v>2.45</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ119">
-        <v>1.19</v>
-      </c>
-      <c r="AK119">
-        <v>1.62</v>
       </c>
       <c r="AL119">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -677,7 +677,7 @@
         <v>1.68</v>
       </c>
       <c r="AB2">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC2">
         <v>2.72</v>
@@ -804,7 +804,7 @@
         <v>3.65</v>
       </c>
       <c r="P3">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q3">
         <v>4.75</v>
@@ -816,7 +816,7 @@
         <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="U3">
         <v>2.88</v>
@@ -828,7 +828,7 @@
         <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
         <v>1.29</v>
@@ -846,7 +846,7 @@
         <v>3.4</v>
       </c>
       <c r="AD3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE3">
         <v>1.06</v>
@@ -982,7 +982,7 @@
         <v>2.51</v>
       </c>
       <c r="U4">
-        <v>2.95</v>
+        <v>3.29</v>
       </c>
       <c r="V4">
         <v>1.3</v>
@@ -1006,7 +1006,7 @@
         <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="AD4">
         <v>1.23</v>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="O5">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P5">
         <v>3.2</v>
@@ -1160,10 +1160,10 @@
         <v>1.33</v>
       </c>
       <c r="Z5">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA5">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AB5">
         <v>1.8</v>
@@ -1175,7 +1175,7 @@
         <v>1.25</v>
       </c>
       <c r="AE5">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF5">
         <v>1.81</v>
@@ -3904,25 +3904,25 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R22">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S22">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="T22">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="U22">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="V22">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W22">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
         <v>1.02</v>
@@ -3931,16 +3931,16 @@
         <v>1.42</v>
       </c>
       <c r="Z22">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="AA22">
         <v>2.21</v>
       </c>
       <c r="AB22">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AC22">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AD22">
         <v>1.17</v>
@@ -3949,10 +3949,10 @@
         <v>1.01</v>
       </c>
       <c r="AF22">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG22">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -6186,55 +6186,55 @@
         <v>2.27</v>
       </c>
       <c r="Q36">
+        <v>3.4</v>
+      </c>
+      <c r="R36">
+        <v>2.2</v>
+      </c>
+      <c r="S36">
+        <v>1.35</v>
+      </c>
+      <c r="T36">
+        <v>2.97</v>
+      </c>
+      <c r="U36">
+        <v>2.64</v>
+      </c>
+      <c r="V36">
+        <v>1.43</v>
+      </c>
+      <c r="W36">
+        <v>1.1</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>1.21</v>
+      </c>
+      <c r="Z36">
         <v>3.84</v>
       </c>
-      <c r="R36">
-        <v>2.37</v>
-      </c>
-      <c r="S36">
-        <v>1.29</v>
-      </c>
-      <c r="T36">
-        <v>3.3</v>
-      </c>
-      <c r="U36">
-        <v>2.46</v>
-      </c>
-      <c r="V36">
-        <v>1.5</v>
-      </c>
-      <c r="W36">
-        <v>1.09</v>
-      </c>
-      <c r="X36">
-        <v>0</v>
-      </c>
-      <c r="Y36">
-        <v>1.19</v>
-      </c>
-      <c r="Z36">
-        <v>4.04</v>
-      </c>
       <c r="AA36">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AB36">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AC36">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="AD36">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AE36">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF36">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG36">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7816,22 +7816,22 @@
         <v>11.2</v>
       </c>
       <c r="Q46">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="R46">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="S46">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T46">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="U46">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="V46">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="W46">
         <v>1.22</v>
@@ -7840,31 +7840,31 @@
         <v>0</v>
       </c>
       <c r="Y46">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Z46">
-        <v>6.87</v>
+        <v>7.29</v>
       </c>
       <c r="AA46">
+        <v>1.33</v>
+      </c>
+      <c r="AB46">
+        <v>3.25</v>
+      </c>
+      <c r="AC46">
+        <v>1.81</v>
+      </c>
+      <c r="AD46">
+        <v>1.97</v>
+      </c>
+      <c r="AE46">
         <v>1.36</v>
       </c>
-      <c r="AB46">
-        <v>3</v>
-      </c>
-      <c r="AC46">
-        <v>1.84</v>
-      </c>
-      <c r="AD46">
-        <v>1.83</v>
-      </c>
-      <c r="AE46">
-        <v>1.4</v>
-      </c>
       <c r="AF46">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AG46">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AK46">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8142,71 +8142,71 @@
         <v>4.93</v>
       </c>
       <c r="Q48">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="R48">
+        <v>2.4</v>
+      </c>
+      <c r="S48">
+        <v>1.32</v>
+      </c>
+      <c r="T48">
+        <v>3.16</v>
+      </c>
+      <c r="U48">
+        <v>2.42</v>
+      </c>
+      <c r="V48">
+        <v>1.51</v>
+      </c>
+      <c r="W48">
+        <v>1.09</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>1.2</v>
+      </c>
+      <c r="Z48">
+        <v>3.99</v>
+      </c>
+      <c r="AA48">
+        <v>1.67</v>
+      </c>
+      <c r="AB48">
+        <v>2.11</v>
+      </c>
+      <c r="AC48">
+        <v>2.64</v>
+      </c>
+      <c r="AD48">
+        <v>1.44</v>
+      </c>
+      <c r="AE48">
+        <v>1.12</v>
+      </c>
+      <c r="AF48">
+        <v>1.75</v>
+      </c>
+      <c r="AG48">
+        <v>1.95</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.06</v>
+      </c>
+      <c r="AK48">
         <v>2.38</v>
-      </c>
-      <c r="S48">
-        <v>1.25</v>
-      </c>
-      <c r="T48">
-        <v>3.6</v>
-      </c>
-      <c r="U48">
-        <v>2.4</v>
-      </c>
-      <c r="V48">
-        <v>1.5</v>
-      </c>
-      <c r="W48">
-        <v>1.11</v>
-      </c>
-      <c r="X48">
-        <v>0</v>
-      </c>
-      <c r="Y48">
-        <v>1.18</v>
-      </c>
-      <c r="Z48">
-        <v>4.28</v>
-      </c>
-      <c r="AA48">
-        <v>1.6</v>
-      </c>
-      <c r="AB48">
-        <v>2.2</v>
-      </c>
-      <c r="AC48">
-        <v>2.49</v>
-      </c>
-      <c r="AD48">
-        <v>1.42</v>
-      </c>
-      <c r="AE48">
-        <v>1.14</v>
-      </c>
-      <c r="AF48">
-        <v>1.7</v>
-      </c>
-      <c r="AG48">
-        <v>2</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.18</v>
-      </c>
-      <c r="AK48">
-        <v>2.45</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -12543,10 +12543,10 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R75">
-        <v>3.28</v>
+        <v>3.13</v>
       </c>
       <c r="S75">
         <v>1.18</v>
@@ -15803,25 +15803,25 @@
         <v>0</v>
       </c>
       <c r="Q95">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="R95">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S95">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T95">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U95">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="V95">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W95">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X95">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -1296,7 +1296,7 @@
         <v>2.65</v>
       </c>
       <c r="Q6">
-        <v>3.47</v>
+        <v>3.53</v>
       </c>
       <c r="R6">
         <v>2</v>
@@ -1305,10 +1305,10 @@
         <v>1.44</v>
       </c>
       <c r="T6">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U6">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V6">
         <v>1.33</v>
@@ -1323,10 +1323,10 @@
         <v>1.39</v>
       </c>
       <c r="Z6">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AA6">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AB6">
         <v>1.62</v>
@@ -1341,10 +1341,10 @@
         <v>1.01</v>
       </c>
       <c r="AF6">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG6">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="O7">
-        <v>3.68</v>
+        <v>3.15</v>
       </c>
       <c r="P7">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="Q7">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="R7">
-        <v>2.24</v>
+        <v>1.9</v>
       </c>
       <c r="S7">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="T7">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="U7">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="Z7">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="AA7">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB7">
+        <v>1.5</v>
+      </c>
+      <c r="AC7">
+        <v>3.58</v>
+      </c>
+      <c r="AD7">
+        <v>1.25</v>
+      </c>
+      <c r="AE7">
+        <v>1.04</v>
+      </c>
+      <c r="AF7">
         <v>1.85</v>
       </c>
-      <c r="AC7">
-        <v>3.06</v>
-      </c>
-      <c r="AD7">
-        <v>1.34</v>
-      </c>
-      <c r="AE7">
-        <v>1.08</v>
-      </c>
-      <c r="AF7">
-        <v>1.71</v>
-      </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK7">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="O9">
         <v>3.5</v>
@@ -1785,49 +1785,49 @@
         <v>3.9</v>
       </c>
       <c r="Q9">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="R9">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="S9">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T9">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U9">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V9">
         <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z9">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="AA9">
         <v>1.9</v>
       </c>
       <c r="AB9">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AC9">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="AD9">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF9">
         <v>1.85</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="O14">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P14">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="Q14">
         <v>2.7</v>
@@ -2606,19 +2606,19 @@
         <v>2.1</v>
       </c>
       <c r="S14">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T14">
         <v>2.75</v>
       </c>
       <c r="U14">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="V14">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X14">
         <v>0</v>
@@ -2630,10 +2630,10 @@
         <v>3.2</v>
       </c>
       <c r="AA14">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AB14">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC14">
         <v>3.24</v>
@@ -2645,10 +2645,10 @@
         <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2763,10 +2763,10 @@
         <v>4.25</v>
       </c>
       <c r="Q15">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R15">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S15">
         <v>1.33</v>
@@ -2775,10 +2775,10 @@
         <v>2.89</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
         <v>1.06</v>
@@ -2793,10 +2793,10 @@
         <v>3.58</v>
       </c>
       <c r="AA15">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB15">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AC15">
         <v>2.97</v>
@@ -2808,10 +2808,10 @@
         <v>1.07</v>
       </c>
       <c r="AF15">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG15">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
         <v>2</v>
@@ -2935,10 +2935,10 @@
         <v>1.44</v>
       </c>
       <c r="T16">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="U16">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="V16">
         <v>1.3</v>
@@ -2971,7 +2971,7 @@
         <v>1.02</v>
       </c>
       <c r="AF16">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG16">
         <v>1.75</v>
@@ -3083,13 +3083,13 @@
         <v>3</v>
       </c>
       <c r="O17">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P17">
         <v>2.3</v>
       </c>
       <c r="Q17">
-        <v>4.07</v>
+        <v>4</v>
       </c>
       <c r="R17">
         <v>1.95</v>
@@ -3098,7 +3098,7 @@
         <v>1.44</v>
       </c>
       <c r="T17">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U17">
         <v>3.3</v>
@@ -3119,16 +3119,16 @@
         <v>2.54</v>
       </c>
       <c r="AA17">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="AB17">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC17">
-        <v>4.52</v>
+        <v>4.49</v>
       </c>
       <c r="AD17">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AE17">
         <v>0</v>
@@ -3137,7 +3137,7 @@
         <v>2</v>
       </c>
       <c r="AG17">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK17">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.39</v>
+        <v>2.06</v>
       </c>
       <c r="O18">
-        <v>3.43</v>
+        <v>2.9</v>
       </c>
       <c r="P18">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="Q18">
-        <v>3.22</v>
+        <v>2.38</v>
       </c>
       <c r="R18">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="S18">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="T18">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="U18">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V18">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W18">
+        <v>1.07</v>
+      </c>
+      <c r="X18">
         <v>1.01</v>
       </c>
-      <c r="X18">
-        <v>1.02</v>
-      </c>
       <c r="Y18">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z18">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="AA18">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AB18">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AC18">
-        <v>3.91</v>
+        <v>3.64</v>
       </c>
       <c r="AD18">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF18">
         <v>1.91</v>
       </c>
       <c r="AG18">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK18">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3412,58 +3412,58 @@
         <v>3.6</v>
       </c>
       <c r="P19">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="Q19">
-        <v>2.21</v>
+        <v>1.9</v>
       </c>
       <c r="R19">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="T19">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="U19">
-        <v>3.07</v>
+        <v>2.8</v>
       </c>
       <c r="V19">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z19">
-        <v>2.81</v>
+        <v>2.92</v>
       </c>
       <c r="AA19">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AB19">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AC19">
-        <v>3.91</v>
+        <v>3.59</v>
       </c>
       <c r="AD19">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE19">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="AG19">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.18</v>
       </c>
       <c r="AK19">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>4.2</v>
       </c>
       <c r="Q20">
-        <v>2.29</v>
+        <v>2.71</v>
       </c>
       <c r="R20">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="S20">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
-        <v>2.78</v>
+        <v>2.2</v>
       </c>
       <c r="U20">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="V20">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W20">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
         <v>0</v>
       </c>
       <c r="Y20">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Z20">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AA20">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AB20">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AC20">
-        <v>3.14</v>
+        <v>3.44</v>
       </c>
       <c r="AD20">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AG20">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3910,19 +3910,19 @@
         <v>2.05</v>
       </c>
       <c r="S22">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="T22">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="U22">
         <v>2.9</v>
       </c>
       <c r="V22">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
         <v>1.02</v>
@@ -3949,10 +3949,10 @@
         <v>1.01</v>
       </c>
       <c r="AF22">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG22">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4061,10 +4061,10 @@
         <v>1.73</v>
       </c>
       <c r="O23">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P23">
-        <v>4.33</v>
+        <v>4.88</v>
       </c>
       <c r="Q23">
         <v>2.25</v>
@@ -4073,7 +4073,7 @@
         <v>2</v>
       </c>
       <c r="S23">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="T23">
         <v>2.5</v>
@@ -4091,16 +4091,16 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Z23">
         <v>2.69</v>
       </c>
       <c r="AA23">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AB23">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC23">
         <v>4.2</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK23">
         <v>1.95</v>
@@ -4230,7 +4230,7 @@
         <v>3.9</v>
       </c>
       <c r="Q24">
-        <v>2.73</v>
+        <v>2.86</v>
       </c>
       <c r="R24">
         <v>1.91</v>
@@ -4242,7 +4242,7 @@
         <v>2.5</v>
       </c>
       <c r="U24">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V24">
         <v>1.3</v>
@@ -4254,19 +4254,19 @@
         <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z24">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="AA24">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AB24">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC24">
-        <v>4.01</v>
+        <v>4.07</v>
       </c>
       <c r="AD24">
         <v>1.2</v>
@@ -4294,7 +4294,7 @@
         <v>1.36</v>
       </c>
       <c r="AK24">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4396,13 +4396,13 @@
         <v>4.2</v>
       </c>
       <c r="R25">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S25">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="T25">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="U25">
         <v>3.4</v>
@@ -4417,10 +4417,10 @@
         <v>1.07</v>
       </c>
       <c r="Y25">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="Z25">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="AA25">
         <v>2.61</v>
@@ -4438,10 +4438,10 @@
         <v>1.01</v>
       </c>
       <c r="AF25">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG25">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK25">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4710,19 +4710,19 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="O27">
         <v>3.4</v>
       </c>
       <c r="P27">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q27">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="R27">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="S27">
         <v>1.4</v>
@@ -4740,50 +4740,50 @@
         <v>1.07</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z27">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="AA27">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AB27">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC27">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD27">
+        <v>1.22</v>
+      </c>
+      <c r="AE27">
+        <v>1.05</v>
+      </c>
+      <c r="AF27">
+        <v>1.86</v>
+      </c>
+      <c r="AG27">
+        <v>1.81</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.25</v>
       </c>
-      <c r="AE27">
-        <v>1.06</v>
-      </c>
-      <c r="AF27">
-        <v>1.85</v>
-      </c>
-      <c r="AG27">
-        <v>1.82</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.22</v>
-      </c>
       <c r="AK27">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.97</v>
+        <v>3.8</v>
       </c>
       <c r="O28">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P28">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="Q28">
         <v>4.8</v>
@@ -4909,10 +4909,10 @@
         <v>1.41</v>
       </c>
       <c r="Z28">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="AA28">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="AB28">
         <v>1.64</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="O33">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="P33">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q33">
-        <v>2.86</v>
+        <v>3.13</v>
       </c>
       <c r="R33">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="S33">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T33">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="U33">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="V33">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W33">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z33">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="AA33">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AB33">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AC33">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="AD33">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE33">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF33">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AG33">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK33">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="O35">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="P35">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="Q35">
         <v>3.16</v>
@@ -6503,25 +6503,25 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P38">
         <v>1.7</v>
       </c>
       <c r="Q38">
-        <v>4.33</v>
+        <v>4.86</v>
       </c>
       <c r="R38">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="S38">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T38">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="U38">
         <v>2.62</v>
@@ -6530,7 +6530,7 @@
         <v>1.4</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
         <v>1.03</v>
@@ -6542,25 +6542,25 @@
         <v>3.44</v>
       </c>
       <c r="AA38">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AB38">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AC38">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AD38">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE38">
         <v>1.08</v>
       </c>
       <c r="AF38">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG38">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK38">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6705,13 +6705,13 @@
         <v>2.77</v>
       </c>
       <c r="AA39">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="AB39">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC39">
-        <v>4.07</v>
+        <v>4.5</v>
       </c>
       <c r="AD39">
         <v>1.2</v>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="O40">
         <v>3.25</v>
       </c>
       <c r="P40">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q40">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R40">
         <v>2.2</v>
@@ -6856,37 +6856,37 @@
         <v>1.44</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X40">
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z40">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="AA40">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB40">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC40">
         <v>3.25</v>
       </c>
       <c r="AD40">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE40">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF40">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG40">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6998,19 +6998,19 @@
         <v>3.1</v>
       </c>
       <c r="P41">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="Q41">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R41">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="S41">
         <v>1.4</v>
       </c>
       <c r="T41">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="U41">
         <v>2.9</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK41">
         <v>1.34</v>
@@ -7158,13 +7158,13 @@
         <v>1.78</v>
       </c>
       <c r="O42">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P42">
-        <v>3.15</v>
+        <v>3.44</v>
       </c>
       <c r="Q42">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="R42">
         <v>2.33</v>
@@ -7173,7 +7173,7 @@
         <v>1.25</v>
       </c>
       <c r="T42">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U42">
         <v>2.2</v>
@@ -7336,13 +7336,13 @@
         <v>1.25</v>
       </c>
       <c r="T43">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U43">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="V43">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W43">
         <v>1.14</v>
@@ -7363,7 +7363,7 @@
         <v>2.35</v>
       </c>
       <c r="AC43">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AD43">
         <v>1.57</v>
@@ -8655,7 +8655,7 @@
         <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z51">
         <v>3.9</v>
@@ -8806,7 +8806,7 @@
         <v>4.16</v>
       </c>
       <c r="U52">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V52">
         <v>1.74</v>
@@ -8990,10 +8990,10 @@
         <v>1.65</v>
       </c>
       <c r="AB53">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AC53">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="AD53">
         <v>1.46</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>11</v>
+        <v>8.09</v>
       </c>
       <c r="O55">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="P55">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Q55">
         <v>8.699999999999999</v>
@@ -9313,16 +9313,16 @@
         <v>6.05</v>
       </c>
       <c r="AA55">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AB55">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AC55">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AD55">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AE55">
         <v>1.32</v>
@@ -9621,7 +9621,7 @@
         <v>3.2</v>
       </c>
       <c r="U57">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="V57">
         <v>1.47</v>
@@ -9636,7 +9636,7 @@
         <v>1.18</v>
       </c>
       <c r="Z57">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="AA57">
         <v>1.75</v>
@@ -9645,7 +9645,7 @@
         <v>2.09</v>
       </c>
       <c r="AC57">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AD57">
         <v>1.41</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="O67">
-        <v>4.64</v>
+        <v>3.6</v>
       </c>
       <c r="P67">
+        <v>1.5</v>
+      </c>
+      <c r="Q67">
+        <v>5.75</v>
+      </c>
+      <c r="R67">
+        <v>2</v>
+      </c>
+      <c r="S67">
+        <v>1.44</v>
+      </c>
+      <c r="T67">
+        <v>2.65</v>
+      </c>
+      <c r="U67">
+        <v>2.87</v>
+      </c>
+      <c r="V67">
         <v>1.39</v>
       </c>
-      <c r="Q67">
-        <v>6.5</v>
-      </c>
-      <c r="R67">
-        <v>2.04</v>
-      </c>
-      <c r="S67">
-        <v>1.42</v>
-      </c>
-      <c r="T67">
-        <v>2.51</v>
-      </c>
-      <c r="U67">
-        <v>2.98</v>
-      </c>
-      <c r="V67">
-        <v>1.33</v>
-      </c>
       <c r="W67">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X67">
         <v>0</v>
       </c>
       <c r="Y67">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z67">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="AA67">
-        <v>2.06</v>
+        <v>1.8</v>
       </c>
       <c r="AB67">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AC67">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="AD67">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE67">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF67">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AG67">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AK67">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="O68">
-        <v>3.33</v>
+        <v>2.9</v>
       </c>
       <c r="P68">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.68</v>
+        <v>2.3</v>
       </c>
       <c r="O69">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="P69">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="Q69">
-        <v>3.46</v>
+        <v>3.16</v>
       </c>
       <c r="R69">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S69">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T69">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U69">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="V69">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W69">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="Z69">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AA69">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB69">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AC69">
-        <v>3.66</v>
+        <v>3.89</v>
       </c>
       <c r="AD69">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE69">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF69">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG69">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK69">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11728,55 +11728,55 @@
         <v>3.75</v>
       </c>
       <c r="Q70">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="R70">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="S70">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="U70">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V70">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="W70">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X70">
         <v>0</v>
       </c>
       <c r="Y70">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z70">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="AA70">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AB70">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AC70">
-        <v>3.32</v>
+        <v>3.48</v>
       </c>
       <c r="AD70">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE70">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF70">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG70">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK70">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,65 +11882,65 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="O71">
-        <v>3.69</v>
+        <v>4</v>
       </c>
       <c r="P71">
-        <v>4.52</v>
+        <v>6.5</v>
       </c>
       <c r="Q71">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="R71">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S71">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T71">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U71">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="V71">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="W71">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z71">
-        <v>2.74</v>
+        <v>3.37</v>
       </c>
       <c r="AA71">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="AB71">
+        <v>1.89</v>
+      </c>
+      <c r="AC71">
+        <v>3.12</v>
+      </c>
+      <c r="AD71">
+        <v>1.26</v>
+      </c>
+      <c r="AE71">
+        <v>1.08</v>
+      </c>
+      <c r="AF71">
+        <v>2.15</v>
+      </c>
+      <c r="AG71">
         <v>1.61</v>
       </c>
-      <c r="AC71">
-        <v>3.82</v>
-      </c>
-      <c r="AD71">
-        <v>1.18</v>
-      </c>
-      <c r="AE71">
-        <v>1.03</v>
-      </c>
-      <c r="AF71">
-        <v>1.98</v>
-      </c>
-      <c r="AG71">
-        <v>1.72</v>
-      </c>
       <c r="AH71" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK71">
-        <v>1.86</v>
+        <v>2.75</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.91</v>
+        <v>2.6</v>
       </c>
       <c r="O73">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P73">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12380,55 +12380,55 @@
         <v>2.06</v>
       </c>
       <c r="Q74">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="R74">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="S74">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="T74">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="U74">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="V74">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W74">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X74">
         <v>0</v>
       </c>
       <c r="Y74">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z74">
-        <v>3.34</v>
+        <v>3.52</v>
       </c>
       <c r="AA74">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AB74">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC74">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="AD74">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE74">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AF74">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG74">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK74">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12546,52 +12546,52 @@
         <v>1.45</v>
       </c>
       <c r="R75">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="S75">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T75">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="U75">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="V75">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="W75">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X75">
         <v>0</v>
       </c>
       <c r="Y75">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Z75">
-        <v>6.67</v>
+        <v>7.41</v>
       </c>
       <c r="AA75">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB75">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="AC75">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AD75">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AE75">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AF75">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AG75">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK75">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12706,55 +12706,55 @@
         <v>2.45</v>
       </c>
       <c r="Q76">
-        <v>3.32</v>
+        <v>2.7</v>
       </c>
       <c r="R76">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S76">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T76">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="U76">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="V76">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W76">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X76">
         <v>0</v>
       </c>
       <c r="Y76">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z76">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="AA76">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB76">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC76">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="AD76">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AE76">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF76">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AG76">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,55 +12860,55 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="O77">
-        <v>3.27</v>
+        <v>2.7</v>
       </c>
       <c r="P77">
-        <v>3.17</v>
+        <v>2.65</v>
       </c>
       <c r="Q77">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R77">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="S77">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T77">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="U77">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="V77">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W77">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X77">
         <v>1.05</v>
       </c>
       <c r="Y77">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="Z77">
+        <v>2.45</v>
+      </c>
+      <c r="AA77">
         <v>2.5</v>
       </c>
-      <c r="AA77">
-        <v>2.43</v>
-      </c>
       <c r="AB77">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AC77">
-        <v>4.69</v>
+        <v>4.88</v>
       </c>
       <c r="AD77">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE77">
         <v>0</v>
@@ -12917,7 +12917,7 @@
         <v>2.05</v>
       </c>
       <c r="AG77">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK77">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,31 +13023,31 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.33</v>
+        <v>2.09</v>
       </c>
       <c r="O78">
-        <v>3.48</v>
+        <v>3.2</v>
       </c>
       <c r="P78">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="Q78">
-        <v>3.12</v>
+        <v>2.82</v>
       </c>
       <c r="R78">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="S78">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T78">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="U78">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="V78">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W78">
         <v>1.02</v>
@@ -13056,25 +13056,25 @@
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z78">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AA78">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="AB78">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC78">
-        <v>3.74</v>
+        <v>3.47</v>
       </c>
       <c r="AD78">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AE78">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF78">
         <v>1.86</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK78">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="O79">
-        <v>3.39</v>
+        <v>3</v>
       </c>
       <c r="P79">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="Q79">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="R79">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S79">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T79">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U79">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V79">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W79">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X79">
         <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="Z79">
-        <v>2.79</v>
+        <v>2.94</v>
       </c>
       <c r="AA79">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AB79">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AC79">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="AD79">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AE79">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF79">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG79">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK79">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13711,19 +13711,19 @@
         <v>1.18</v>
       </c>
       <c r="Z82">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="AA82">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AB82">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AC82">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD82">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE82">
         <v>1.14</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O83">
         <v>2.95</v>
       </c>
       <c r="P83">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q83">
         <v>3.5</v>
@@ -13880,7 +13880,7 @@
         <v>2.47</v>
       </c>
       <c r="AB83">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AC83">
         <v>4.5</v>
@@ -14001,19 +14001,19 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.38</v>
+        <v>1.82</v>
       </c>
       <c r="O84">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="P84">
-        <v>2.94</v>
+        <v>3.9</v>
       </c>
       <c r="Q84">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="R84">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S84">
         <v>1.4</v>
@@ -14022,44 +14022,44 @@
         <v>2.75</v>
       </c>
       <c r="U84">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="V84">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W84">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X84">
         <v>1.01</v>
       </c>
       <c r="Y84">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z84">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="AA84">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="AB84">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AC84">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="AD84">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AE84">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF84">
+        <v>1.85</v>
+      </c>
+      <c r="AG84">
         <v>1.83</v>
       </c>
-      <c r="AG84">
-        <v>1.86</v>
-      </c>
       <c r="AH84" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK84">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14173,19 +14173,19 @@
         <v>1.83</v>
       </c>
       <c r="Q85">
-        <v>4.78</v>
+        <v>4.68</v>
       </c>
       <c r="R85">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="S85">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="T85">
-        <v>2.71</v>
+        <v>2.3</v>
       </c>
       <c r="U85">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="V85">
         <v>1.39</v>
@@ -14197,31 +14197,31 @@
         <v>0</v>
       </c>
       <c r="Y85">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z85">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="AA85">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="AB85">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AC85">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="AD85">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE85">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF85">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AG85">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AK85">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,40 +14327,40 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="O86">
+        <v>3.25</v>
+      </c>
+      <c r="P86">
         <v>3.3</v>
       </c>
-      <c r="P86">
-        <v>2.5</v>
-      </c>
       <c r="Q86">
-        <v>3.28</v>
+        <v>2.54</v>
       </c>
       <c r="R86">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="S86">
+        <v>1.4</v>
+      </c>
+      <c r="T86">
+        <v>2.8</v>
+      </c>
+      <c r="U86">
+        <v>2.9</v>
+      </c>
+      <c r="V86">
         <v>1.36</v>
       </c>
-      <c r="T86">
-        <v>2.88</v>
-      </c>
-      <c r="U86">
-        <v>2.89</v>
-      </c>
-      <c r="V86">
-        <v>1.32</v>
-      </c>
       <c r="W86">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X86">
         <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z86">
         <v>3.04</v>
@@ -14369,22 +14369,22 @@
         <v>2.05</v>
       </c>
       <c r="AB86">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC86">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="AD86">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE86">
         <v>1.04</v>
       </c>
       <c r="AF86">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG86">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>1.25</v>
       </c>
       <c r="AK86">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14819,7 +14819,7 @@
         <v>1.22</v>
       </c>
       <c r="O89">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="P89">
         <v>10</v>
@@ -14889,7 +14889,7 @@
         <v>1.09</v>
       </c>
       <c r="AK89">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14994,10 +14994,10 @@
         <v>2.1</v>
       </c>
       <c r="S90">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T90">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="U90">
         <v>2.74</v>
@@ -15015,10 +15015,10 @@
         <v>1.26</v>
       </c>
       <c r="Z90">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="AA90">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AB90">
         <v>1.75</v>
@@ -15631,28 +15631,28 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="O94">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P94">
-        <v>2.8</v>
+        <v>3.83</v>
       </c>
       <c r="Q94">
-        <v>3.04</v>
+        <v>2.64</v>
       </c>
       <c r="R94">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="S94">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T94">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="U94">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V94">
         <v>1.38</v>
@@ -15664,31 +15664,31 @@
         <v>0</v>
       </c>
       <c r="Y94">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z94">
-        <v>3.04</v>
+        <v>3.12</v>
       </c>
       <c r="AA94">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AB94">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AC94">
-        <v>3.51</v>
+        <v>3.68</v>
       </c>
       <c r="AD94">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE94">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF94">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG94">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AK94">
-        <v>1.46</v>
+        <v>1.78</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15848,10 +15848,10 @@
         <v>1.13</v>
       </c>
       <c r="AF95">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG95">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -16286,13 +16286,13 @@
         <v>1.8</v>
       </c>
       <c r="O98">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P98">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q98">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="R98">
         <v>2.15</v>
@@ -16301,40 +16301,40 @@
         <v>1.36</v>
       </c>
       <c r="T98">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U98">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V98">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W98">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X98">
         <v>1.04</v>
       </c>
       <c r="Y98">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z98">
         <v>3.27</v>
       </c>
       <c r="AA98">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB98">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC98">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AD98">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE98">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF98">
         <v>1.8</v>
@@ -16356,7 +16356,7 @@
         <v>1.25</v>
       </c>
       <c r="AK98">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16775,7 +16775,7 @@
         <v>1.8</v>
       </c>
       <c r="O101">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P101">
         <v>4</v>
@@ -16799,7 +16799,7 @@
         <v>1.4</v>
       </c>
       <c r="W101">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X101">
         <v>1.02</v>
@@ -16941,13 +16941,13 @@
         <v>3.2</v>
       </c>
       <c r="P102">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q102">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="R102">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="S102">
         <v>1.35</v>
@@ -16956,28 +16956,28 @@
         <v>2.9</v>
       </c>
       <c r="U102">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="V102">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W102">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y102">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z102">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="AA102">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AB102">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC102">
         <v>3.5</v>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK102">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17101,22 +17101,22 @@
         <v>1.71</v>
       </c>
       <c r="O103">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P103">
-        <v>3.9</v>
+        <v>4.88</v>
       </c>
       <c r="Q103">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="R103">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="S103">
         <v>1.35</v>
       </c>
       <c r="T103">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="U103">
         <v>2.75</v>
@@ -17125,22 +17125,22 @@
         <v>1.4</v>
       </c>
       <c r="W103">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X103">
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z103">
         <v>3.4</v>
       </c>
       <c r="AA103">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB103">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC103">
         <v>3.14</v>
@@ -17149,10 +17149,10 @@
         <v>1.27</v>
       </c>
       <c r="AE103">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF103">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG103">
         <v>1.77</v>
@@ -17276,7 +17276,7 @@
         <v>2.15</v>
       </c>
       <c r="S104">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="T104">
         <v>2.88</v>
@@ -17291,7 +17291,7 @@
         <v>1.08</v>
       </c>
       <c r="X104">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y104">
         <v>1.3</v>
@@ -17424,7 +17424,7 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="O105">
         <v>3.2</v>
@@ -17433,7 +17433,7 @@
         <v>3.15</v>
       </c>
       <c r="Q105">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="R105">
         <v>2.15</v>
@@ -17442,10 +17442,10 @@
         <v>1.33</v>
       </c>
       <c r="T105">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="U105">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="V105">
         <v>1.43</v>
@@ -17497,7 +17497,7 @@
         <v>1.36</v>
       </c>
       <c r="AK105">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="O115">
         <v>4.7</v>
       </c>
       <c r="P115">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AA115">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB115">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
+        <v>1.58</v>
+      </c>
+      <c r="O116">
+        <v>3.95</v>
+      </c>
+      <c r="P116">
+        <v>5.2</v>
+      </c>
+      <c r="Q116">
+        <v>2.21</v>
+      </c>
+      <c r="R116">
+        <v>2.46</v>
+      </c>
+      <c r="S116">
+        <v>1.32</v>
+      </c>
+      <c r="T116">
+        <v>3.19</v>
+      </c>
+      <c r="U116">
+        <v>2.42</v>
+      </c>
+      <c r="V116">
+        <v>1.55</v>
+      </c>
+      <c r="W116">
+        <v>1.09</v>
+      </c>
+      <c r="X116">
+        <v>1.02</v>
+      </c>
+      <c r="Y116">
+        <v>1.17</v>
+      </c>
+      <c r="Z116">
+        <v>4.39</v>
+      </c>
+      <c r="AA116">
+        <v>1.64</v>
+      </c>
+      <c r="AB116">
+        <v>2.24</v>
+      </c>
+      <c r="AC116">
+        <v>2.46</v>
+      </c>
+      <c r="AD116">
         <v>1.53</v>
       </c>
-      <c r="O116">
-        <v>4</v>
-      </c>
-      <c r="P116">
-        <v>5</v>
-      </c>
-      <c r="Q116">
-        <v>0</v>
-      </c>
-      <c r="R116">
-        <v>0</v>
-      </c>
-      <c r="S116">
-        <v>0</v>
-      </c>
-      <c r="T116">
-        <v>0</v>
-      </c>
-      <c r="U116">
-        <v>0</v>
-      </c>
-      <c r="V116">
-        <v>0</v>
-      </c>
-      <c r="W116">
-        <v>0</v>
-      </c>
-      <c r="X116">
-        <v>0</v>
-      </c>
-      <c r="Y116">
-        <v>0</v>
-      </c>
-      <c r="Z116">
-        <v>0</v>
-      </c>
-      <c r="AA116">
+      <c r="AE116">
+        <v>1.18</v>
+      </c>
+      <c r="AF116">
         <v>1.65</v>
       </c>
-      <c r="AB116">
-        <v>2.2</v>
-      </c>
-      <c r="AC116">
-        <v>0</v>
-      </c>
-      <c r="AD116">
-        <v>0</v>
-      </c>
-      <c r="AE116">
-        <v>0</v>
-      </c>
-      <c r="AF116">
-        <v>0</v>
-      </c>
       <c r="AG116">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O120">
+        <v>3.55</v>
+      </c>
+      <c r="P120">
+        <v>2.21</v>
+      </c>
+      <c r="Q120">
+        <v>3.44</v>
+      </c>
+      <c r="R120">
+        <v>2.4</v>
+      </c>
+      <c r="S120">
+        <v>1.29</v>
+      </c>
+      <c r="T120">
         <v>3.4</v>
       </c>
-      <c r="P120">
-        <v>2.1</v>
-      </c>
-      <c r="Q120">
-        <v>0</v>
-      </c>
-      <c r="R120">
-        <v>0</v>
-      </c>
-      <c r="S120">
-        <v>0</v>
-      </c>
-      <c r="T120">
-        <v>0</v>
-      </c>
       <c r="U120">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AA120">
         <v>1.65</v>
       </c>
       <c r="AB120">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="O122">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="P122">
-        <v>3.46</v>
+        <v>3.35</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA122">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AB122">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL122">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -647,7 +647,7 @@
         <v>2.88</v>
       </c>
       <c r="R2">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S2">
         <v>1.3</v>
@@ -674,10 +674,10 @@
         <v>4.1</v>
       </c>
       <c r="AA2">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB2">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC2">
         <v>2.72</v>
@@ -708,7 +708,7 @@
         <v>1.22</v>
       </c>
       <c r="AK2">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -967,7 +967,7 @@
         <v>3.25</v>
       </c>
       <c r="P4">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q4">
         <v>3.57</v>
@@ -982,7 +982,7 @@
         <v>2.51</v>
       </c>
       <c r="U4">
-        <v>3.29</v>
+        <v>2.95</v>
       </c>
       <c r="V4">
         <v>1.3</v>
@@ -1006,7 +1006,7 @@
         <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="AD4">
         <v>1.23</v>
@@ -1127,61 +1127,61 @@
         <v>2.1</v>
       </c>
       <c r="O5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
         <v>3.2</v>
       </c>
       <c r="Q5">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R5">
         <v>2.1</v>
       </c>
       <c r="S5">
+        <v>1.39</v>
+      </c>
+      <c r="T5">
+        <v>3</v>
+      </c>
+      <c r="U5">
+        <v>2.62</v>
+      </c>
+      <c r="V5">
         <v>1.41</v>
       </c>
-      <c r="T5">
-        <v>2.88</v>
-      </c>
-      <c r="U5">
-        <v>2.71</v>
-      </c>
-      <c r="V5">
-        <v>1.39</v>
-      </c>
       <c r="W5">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="Z5">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AA5">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB5">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC5">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AD5">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE5">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF5">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AG5">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
         <v>1.63</v>
@@ -1948,10 +1948,10 @@
         <v>4.82</v>
       </c>
       <c r="Q10">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R10">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
         <v>1.36</v>
@@ -1966,31 +1966,31 @@
         <v>1.36</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
         <v>1.31</v>
       </c>
       <c r="Z10">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="AA10">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AB10">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AC10">
-        <v>3.22</v>
+        <v>3.29</v>
       </c>
       <c r="AD10">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE10">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF10">
         <v>1.95</v>
@@ -2012,7 +2012,7 @@
         <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="O11">
         <v>3.2</v>
       </c>
       <c r="P11">
-        <v>3.89</v>
+        <v>3.2</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -2120,7 +2120,7 @@
         <v>1.36</v>
       </c>
       <c r="T11">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="U11">
         <v>2.8</v>
@@ -2138,13 +2138,13 @@
         <v>1.31</v>
       </c>
       <c r="Z11">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="AA11">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AB11">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC11">
         <v>3.34</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>2.45</v>
       </c>
       <c r="O12">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="P12">
         <v>2.6</v>
@@ -2301,19 +2301,19 @@
         <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.91</v>
+        <v>3.95</v>
       </c>
       <c r="AA12">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB12">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC12">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AE12">
         <v>1.1</v>
@@ -2443,10 +2443,10 @@
         <v>2.06</v>
       </c>
       <c r="S13">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T13">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="U13">
         <v>2.75</v>
@@ -2476,7 +2476,7 @@
         <v>3.13</v>
       </c>
       <c r="AD13">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE13">
         <v>1.07</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Q22">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S22">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="T22">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V22">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W22">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z22">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC22">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK22">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.63</v>
+        <v>3.8</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P27">
-        <v>4.4</v>
+        <v>1.87</v>
       </c>
       <c r="Q27">
-        <v>2.39</v>
+        <v>4.8</v>
       </c>
       <c r="R27">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S27">
         <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U27">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="V27">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="Z27">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="AA27">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AB27">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AC27">
-        <v>3.7</v>
+        <v>3.94</v>
       </c>
       <c r="AD27">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF27">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG27">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="AK27">
-        <v>1.91</v>
+        <v>1.15</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.8</v>
+        <v>1.63</v>
       </c>
       <c r="O28">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>1.87</v>
+        <v>4.4</v>
       </c>
       <c r="Q28">
-        <v>4.8</v>
+        <v>2.39</v>
       </c>
       <c r="R28">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S28">
         <v>1.4</v>
       </c>
       <c r="T28">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="U28">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="V28">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
+        <v>1.01</v>
+      </c>
+      <c r="Y28">
+        <v>1.32</v>
+      </c>
+      <c r="Z28">
+        <v>3.04</v>
+      </c>
+      <c r="AA28">
+        <v>2.05</v>
+      </c>
+      <c r="AB28">
+        <v>1.74</v>
+      </c>
+      <c r="AC28">
+        <v>3.7</v>
+      </c>
+      <c r="AD28">
+        <v>1.22</v>
+      </c>
+      <c r="AE28">
         <v>1.05</v>
       </c>
-      <c r="Y28">
-        <v>1.41</v>
-      </c>
-      <c r="Z28">
-        <v>2.96</v>
-      </c>
-      <c r="AA28">
-        <v>2.21</v>
-      </c>
-      <c r="AB28">
-        <v>1.64</v>
-      </c>
-      <c r="AC28">
-        <v>3.94</v>
-      </c>
-      <c r="AD28">
-        <v>1.21</v>
-      </c>
-      <c r="AE28">
-        <v>1.04</v>
-      </c>
       <c r="AF28">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG28">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.15</v>
+        <v>1.91</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>5.77</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5851,28 +5851,28 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="O34">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="Q34">
         <v>3.14</v>
       </c>
       <c r="R34">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S34">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T34">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="U34">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="V34">
         <v>1.38</v>
@@ -5887,16 +5887,16 @@
         <v>1.38</v>
       </c>
       <c r="Z34">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="AA34">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AB34">
         <v>1.73</v>
       </c>
       <c r="AC34">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="AD34">
         <v>1.24</v>
@@ -6204,7 +6204,7 @@
         <v>1.43</v>
       </c>
       <c r="W36">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
         <v>0</v>
@@ -6231,10 +6231,10 @@
         <v>1.12</v>
       </c>
       <c r="AF36">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG36">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6346,58 +6346,58 @@
         <v>3.25</v>
       </c>
       <c r="P37">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>3.5</v>
       </c>
       <c r="P38">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q38">
         <v>4.86</v>
@@ -6542,7 +6542,7 @@
         <v>3.44</v>
       </c>
       <c r="AA38">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AB38">
         <v>1.83</v>
@@ -6557,7 +6557,7 @@
         <v>1.08</v>
       </c>
       <c r="AF38">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG38">
         <v>1.91</v>
@@ -6705,7 +6705,7 @@
         <v>2.77</v>
       </c>
       <c r="AA39">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AB39">
         <v>1.57</v>
@@ -6835,7 +6835,7 @@
         <v>3.25</v>
       </c>
       <c r="P40">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q40">
         <v>2.88</v>
@@ -6902,7 +6902,7 @@
         <v>1.25</v>
       </c>
       <c r="AK40">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7825,16 +7825,16 @@
         <v>1.17</v>
       </c>
       <c r="T46">
-        <v>4.4</v>
+        <v>4.34</v>
       </c>
       <c r="U46">
         <v>1.88</v>
       </c>
       <c r="V46">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="W46">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X46">
         <v>0</v>
@@ -7861,10 +7861,10 @@
         <v>1.36</v>
       </c>
       <c r="AF46">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AG46">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.07</v>
       </c>
       <c r="AK46">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>13.66</v>
+        <v>1.57</v>
       </c>
       <c r="O52">
-        <v>8.76</v>
+        <v>4.56</v>
       </c>
       <c r="P52">
+        <v>5.2</v>
+      </c>
+      <c r="Q52">
+        <v>2.3</v>
+      </c>
+      <c r="R52">
+        <v>2.26</v>
+      </c>
+      <c r="S52">
+        <v>1.28</v>
+      </c>
+      <c r="T52">
+        <v>3.25</v>
+      </c>
+      <c r="U52">
+        <v>2.4</v>
+      </c>
+      <c r="V52">
+        <v>1.51</v>
+      </c>
+      <c r="W52">
         <v>1.1</v>
-      </c>
-      <c r="Q52">
-        <v>10.5</v>
-      </c>
-      <c r="R52">
-        <v>3</v>
-      </c>
-      <c r="S52">
-        <v>1.19</v>
-      </c>
-      <c r="T52">
-        <v>4.16</v>
-      </c>
-      <c r="U52">
-        <v>1.93</v>
-      </c>
-      <c r="V52">
-        <v>1.74</v>
-      </c>
-      <c r="W52">
-        <v>1.21</v>
       </c>
       <c r="X52">
         <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="Z52">
-        <v>6.48</v>
+        <v>4.33</v>
       </c>
       <c r="AA52">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AB52">
-        <v>3</v>
+        <v>2.06</v>
       </c>
       <c r="AC52">
-        <v>1.89</v>
+        <v>2.62</v>
       </c>
       <c r="AD52">
-        <v>1.81</v>
+        <v>1.46</v>
       </c>
       <c r="AE52">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AF52">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AG52">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AK52">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>1.57</v>
+        <v>13.66</v>
       </c>
       <c r="O53">
-        <v>4.56</v>
+        <v>8.76</v>
       </c>
       <c r="P53">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="Q53">
-        <v>2.3</v>
+        <v>10.5</v>
       </c>
       <c r="R53">
-        <v>2.26</v>
+        <v>3</v>
       </c>
       <c r="S53">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="T53">
-        <v>3.25</v>
+        <v>4.16</v>
       </c>
       <c r="U53">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="V53">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="W53">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="Z53">
-        <v>4.33</v>
+        <v>6.48</v>
       </c>
       <c r="AA53">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AB53">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="AC53">
-        <v>2.62</v>
+        <v>1.89</v>
       </c>
       <c r="AD53">
-        <v>1.46</v>
+        <v>1.81</v>
       </c>
       <c r="AE53">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AF53">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AG53">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AK53">
-        <v>1.95</v>
+        <v>1.03</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="O56">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P56">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="O58">
         <v>3</v>
       </c>
       <c r="P58">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="Q58">
         <v>3.4</v>
@@ -9781,7 +9781,7 @@
         <v>1.4</v>
       </c>
       <c r="T58">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="U58">
         <v>2.9</v>
@@ -9796,22 +9796,22 @@
         <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z58">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="AA58">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AB58">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC58">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD58">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE58">
         <v>1.02</v>
@@ -9941,7 +9941,7 @@
         <v>2.32</v>
       </c>
       <c r="S59">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T59">
         <v>3</v>
@@ -9953,7 +9953,7 @@
         <v>1.44</v>
       </c>
       <c r="W59">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X59">
         <v>1.01</v>
@@ -9965,7 +9965,7 @@
         <v>3.62</v>
       </c>
       <c r="AA59">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB59">
         <v>2</v>
@@ -10904,58 +10904,58 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O65">
         <v>3.3</v>
       </c>
       <c r="P65">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q65">
-        <v>2.8</v>
+        <v>3.21</v>
       </c>
       <c r="R65">
         <v>2.12</v>
       </c>
       <c r="S65">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="T65">
         <v>2.75</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y65">
         <v>1.23</v>
       </c>
       <c r="Z65">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="AA65">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="AB65">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC65">
-        <v>3.15</v>
+        <v>3.48</v>
       </c>
       <c r="AD65">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF65">
         <v>1.62</v>
@@ -10974,7 +10974,7 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK65">
         <v>1.45</v>
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -12543,55 +12543,55 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="R75">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S75">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T75">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U75">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V75">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="W75">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X75">
         <v>0</v>
       </c>
       <c r="Y75">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z75">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="AA75">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB75">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AC75">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD75">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE75">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AF75">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG75">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK75">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O80">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P80">
-        <v>5.16</v>
+        <v>4.4</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14662,55 +14662,55 @@
         <v>5.8</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -15015,13 +15015,13 @@
         <v>1.26</v>
       </c>
       <c r="Z90">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="AA90">
         <v>2.06</v>
       </c>
       <c r="AB90">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC90">
         <v>3.14</v>
@@ -15311,7 +15311,7 @@
         <v>3.45</v>
       </c>
       <c r="P92">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15344,10 +15344,10 @@
         <v>0</v>
       </c>
       <c r="AA92">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AB92">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC92">
         <v>0</v>
@@ -15963,13 +15963,13 @@
         <v>3.2</v>
       </c>
       <c r="P96">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="Q96">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R96">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S96">
         <v>1.38</v>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK96">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="O97">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="P97">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="Q97">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R97">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S97">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T97">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U97">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="V97">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W97">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X97">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y97">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z97">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC97">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD97">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE97">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF97">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG97">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK97">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16313,7 +16313,7 @@
         <v>1.08</v>
       </c>
       <c r="X98">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y98">
         <v>1.3</v>
@@ -16322,7 +16322,7 @@
         <v>3.27</v>
       </c>
       <c r="AA98">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AB98">
         <v>1.74</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="O99">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="P99">
-        <v>3.79</v>
+        <v>2.8</v>
       </c>
       <c r="Q99">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R99">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S99">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T99">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="V99">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W99">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X99">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y99">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z99">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA99">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB99">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC99">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD99">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE99">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF99">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG99">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK99">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="O100">
-        <v>2.61</v>
+        <v>3</v>
       </c>
       <c r="P100">
-        <v>3.11</v>
+        <v>3.7</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,65 +16935,65 @@
         </is>
       </c>
       <c r="N102">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="O102">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P102">
-        <v>3.3</v>
+        <v>4.88</v>
       </c>
       <c r="Q102">
-        <v>2.81</v>
+        <v>2.15</v>
       </c>
       <c r="R102">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="S102">
         <v>1.35</v>
       </c>
       <c r="T102">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="U102">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="V102">
         <v>1.4</v>
       </c>
       <c r="W102">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X102">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z102">
+        <v>3.5</v>
+      </c>
+      <c r="AA102">
+        <v>1.88</v>
+      </c>
+      <c r="AB102">
+        <v>1.79</v>
+      </c>
+      <c r="AC102">
         <v>3.14</v>
       </c>
-      <c r="AA102">
-        <v>1.96</v>
-      </c>
-      <c r="AB102">
+      <c r="AD102">
+        <v>1.27</v>
+      </c>
+      <c r="AE102">
+        <v>1.07</v>
+      </c>
+      <c r="AF102">
+        <v>1.91</v>
+      </c>
+      <c r="AG102">
         <v>1.77</v>
       </c>
-      <c r="AC102">
-        <v>3.5</v>
-      </c>
-      <c r="AD102">
-        <v>1.29</v>
-      </c>
-      <c r="AE102">
-        <v>1.06</v>
-      </c>
-      <c r="AF102">
-        <v>1.73</v>
-      </c>
-      <c r="AG102">
-        <v>1.95</v>
-      </c>
       <c r="AH102" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK102">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,65 +17098,65 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="O103">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="P103">
-        <v>4.88</v>
+        <v>3.3</v>
       </c>
       <c r="Q103">
-        <v>2.19</v>
+        <v>2.81</v>
       </c>
       <c r="R103">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S103">
         <v>1.35</v>
       </c>
       <c r="T103">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U103">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="V103">
         <v>1.4</v>
       </c>
       <c r="W103">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X103">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y103">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z103">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA103">
+        <v>1.96</v>
+      </c>
+      <c r="AB103">
+        <v>1.77</v>
+      </c>
+      <c r="AC103">
+        <v>3.5</v>
+      </c>
+      <c r="AD103">
+        <v>1.29</v>
+      </c>
+      <c r="AE103">
+        <v>1.06</v>
+      </c>
+      <c r="AF103">
+        <v>1.73</v>
+      </c>
+      <c r="AG103">
         <v>1.95</v>
       </c>
-      <c r="AB103">
-        <v>1.85</v>
-      </c>
-      <c r="AC103">
-        <v>3.14</v>
-      </c>
-      <c r="AD103">
-        <v>1.27</v>
-      </c>
-      <c r="AE103">
-        <v>1.07</v>
-      </c>
-      <c r="AF103">
-        <v>1.91</v>
-      </c>
-      <c r="AG103">
-        <v>1.77</v>
-      </c>
       <c r="AH103" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK103">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17424,7 +17424,7 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="O105">
         <v>3.2</v>
@@ -17445,7 +17445,7 @@
         <v>2.78</v>
       </c>
       <c r="U105">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="V105">
         <v>1.43</v>
@@ -17460,7 +17460,7 @@
         <v>1.25</v>
       </c>
       <c r="Z105">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA105">
         <v>1.87</v>
@@ -17497,7 +17497,7 @@
         <v>1.36</v>
       </c>
       <c r="AK105">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17587,13 +17587,13 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="O106">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="P106">
-        <v>3.33</v>
+        <v>3.46</v>
       </c>
       <c r="Q106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2.16</v>
+        <v>1.64</v>
       </c>
       <c r="O107">
-        <v>2.71</v>
+        <v>3.35</v>
       </c>
       <c r="P107">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="O109">
-        <v>3.52</v>
+        <v>2.87</v>
       </c>
       <c r="P109">
-        <v>6.63</v>
+        <v>4.01</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>5.76</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="O110">
-        <v>4.56</v>
+        <v>4</v>
       </c>
       <c r="P110">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA110">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB110">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18417,13 +18417,13 @@
         <v>2.62</v>
       </c>
       <c r="S111">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T111">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U111">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="V111">
         <v>1.65</v>
@@ -18435,10 +18435,10 @@
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z111">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA111">
         <v>1.33</v>
@@ -18447,13 +18447,13 @@
         <v>2.2</v>
       </c>
       <c r="AC111">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AD111">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AE111">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AF111">
         <v>1.62</v>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="AK111">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18583,16 +18583,16 @@
         <v>1.33</v>
       </c>
       <c r="T112">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="U112">
         <v>2.66</v>
       </c>
       <c r="V112">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W112">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X112">
         <v>1.04</v>
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="O113">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P113">
-        <v>3.06</v>
+        <v>2.87</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y113">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z113">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,28 +19054,28 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="O115">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="P115">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="Q115">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="R115">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="S115">
         <v>1.32</v>
       </c>
       <c r="T115">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="U115">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="V115">
         <v>1.55</v>
@@ -19084,34 +19084,34 @@
         <v>1.09</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z115">
-        <v>4.14</v>
+        <v>4.39</v>
       </c>
       <c r="AA115">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AB115">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="AC115">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AD115">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE115">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF115">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AG115">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AK115">
-        <v>2.89</v>
+        <v>2.18</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,28 +19217,28 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="O116">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="P116">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="Q116">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="R116">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="S116">
         <v>1.32</v>
       </c>
       <c r="T116">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="U116">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="V116">
         <v>1.55</v>
@@ -19247,34 +19247,34 @@
         <v>1.09</v>
       </c>
       <c r="X116">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z116">
-        <v>4.39</v>
+        <v>4.14</v>
       </c>
       <c r="AA116">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AB116">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="AC116">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="AD116">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE116">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF116">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AG116">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AK116">
-        <v>2.18</v>
+        <v>2.89</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="O117">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="P117">
-        <v>6.31</v>
+        <v>5.25</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="O118">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P118">
-        <v>3.91</v>
+        <v>4.2</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y118">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Z118">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19724,10 +19724,10 @@
         <v>1.25</v>
       </c>
       <c r="T119">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U119">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V119">
         <v>1.62</v>
@@ -19739,10 +19739,10 @@
         <v>1</v>
       </c>
       <c r="Y119">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z119">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AA119">
         <v>1.53</v>
@@ -19751,19 +19751,19 @@
         <v>2.29</v>
       </c>
       <c r="AC119">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="AD119">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AE119">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF119">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AG119">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>1.2</v>
       </c>
       <c r="AK119">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -20041,10 +20041,10 @@
         <v>1.77</v>
       </c>
       <c r="Q121">
-        <v>4.2</v>
+        <v>4.52</v>
       </c>
       <c r="R121">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S121">
         <v>1.29</v>
@@ -20056,7 +20056,7 @@
         <v>2.45</v>
       </c>
       <c r="V121">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W121">
         <v>1.08</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -3086,7 +3086,7 @@
         <v>2.75</v>
       </c>
       <c r="P17">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q17">
         <v>4</v>
@@ -3098,7 +3098,7 @@
         <v>1.44</v>
       </c>
       <c r="T17">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U17">
         <v>3.3</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.8</v>
+        <v>1.63</v>
       </c>
       <c r="O27">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>1.87</v>
+        <v>4.4</v>
       </c>
       <c r="Q27">
-        <v>4.8</v>
+        <v>2.39</v>
       </c>
       <c r="R27">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S27">
         <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="U27">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="V27">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X27">
+        <v>1.01</v>
+      </c>
+      <c r="Y27">
+        <v>1.32</v>
+      </c>
+      <c r="Z27">
+        <v>3.04</v>
+      </c>
+      <c r="AA27">
+        <v>2.05</v>
+      </c>
+      <c r="AB27">
+        <v>1.74</v>
+      </c>
+      <c r="AC27">
+        <v>3.75</v>
+      </c>
+      <c r="AD27">
+        <v>1.22</v>
+      </c>
+      <c r="AE27">
         <v>1.05</v>
       </c>
-      <c r="Y27">
-        <v>1.41</v>
-      </c>
-      <c r="Z27">
-        <v>2.96</v>
-      </c>
-      <c r="AA27">
-        <v>2.21</v>
-      </c>
-      <c r="AB27">
-        <v>1.64</v>
-      </c>
-      <c r="AC27">
-        <v>3.94</v>
-      </c>
-      <c r="AD27">
-        <v>1.21</v>
-      </c>
-      <c r="AE27">
-        <v>1.04</v>
-      </c>
       <c r="AF27">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG27">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>1.15</v>
+        <v>1.87</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.63</v>
+        <v>3.8</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P28">
-        <v>4.4</v>
+        <v>1.87</v>
       </c>
       <c r="Q28">
-        <v>2.39</v>
+        <v>4.8</v>
       </c>
       <c r="R28">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S28">
         <v>1.4</v>
       </c>
       <c r="T28">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U28">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="V28">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="Z28">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="AA28">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AB28">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AC28">
-        <v>3.7</v>
+        <v>3.94</v>
       </c>
       <c r="AD28">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE28">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG28">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="AK28">
-        <v>1.91</v>
+        <v>1.15</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -7001,7 +7001,7 @@
         <v>2.55</v>
       </c>
       <c r="Q41">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R41">
         <v>2</v>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AK41">
         <v>1.34</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="O73">
         <v>3.2</v>
       </c>
       <c r="P73">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O80">
         <v>3.75</v>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O83">
         <v>2.95</v>
@@ -13880,7 +13880,7 @@
         <v>2.47</v>
       </c>
       <c r="AB83">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC83">
         <v>4.5</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK83">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15960,16 +15960,16 @@
         <v>2.75</v>
       </c>
       <c r="O96">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P96">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="Q96">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R96">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S96">
         <v>1.38</v>
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="O97">
         <v>2.87</v>
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="O99">
+        <v>3</v>
+      </c>
+      <c r="P99">
+        <v>3.7</v>
+      </c>
+      <c r="Q99">
+        <v>2.75</v>
+      </c>
+      <c r="R99">
+        <v>1.93</v>
+      </c>
+      <c r="S99">
+        <v>1.57</v>
+      </c>
+      <c r="T99">
+        <v>2.18</v>
+      </c>
+      <c r="U99">
+        <v>3.78</v>
+      </c>
+      <c r="V99">
+        <v>1.23</v>
+      </c>
+      <c r="W99">
+        <v>1</v>
+      </c>
+      <c r="X99">
+        <v>1.07</v>
+      </c>
+      <c r="Y99">
+        <v>1.54</v>
+      </c>
+      <c r="Z99">
+        <v>2.36</v>
+      </c>
+      <c r="AA99">
         <v>2.7</v>
       </c>
-      <c r="P99">
-        <v>2.8</v>
-      </c>
-      <c r="Q99">
-        <v>3.7</v>
-      </c>
-      <c r="R99">
-        <v>1.83</v>
-      </c>
-      <c r="S99">
-        <v>1.65</v>
-      </c>
-      <c r="T99">
-        <v>2.07</v>
-      </c>
-      <c r="U99">
-        <v>4.06</v>
-      </c>
-      <c r="V99">
-        <v>1.19</v>
-      </c>
-      <c r="W99">
-        <v>1.03</v>
-      </c>
-      <c r="X99">
+      <c r="AB99">
+        <v>1.44</v>
+      </c>
+      <c r="AC99">
+        <v>5.75</v>
+      </c>
+      <c r="AD99">
         <v>1.11</v>
       </c>
-      <c r="Y99">
-        <v>1.63</v>
-      </c>
-      <c r="Z99">
-        <v>2.1</v>
-      </c>
-      <c r="AA99">
-        <v>3</v>
-      </c>
-      <c r="AB99">
-        <v>1.36</v>
-      </c>
-      <c r="AC99">
-        <v>7</v>
-      </c>
-      <c r="AD99">
-        <v>1.07</v>
-      </c>
       <c r="AE99">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF99">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG99">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK99">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.95</v>
+        <v>2.6</v>
       </c>
       <c r="O100">
+        <v>2.7</v>
+      </c>
+      <c r="P100">
+        <v>2.8</v>
+      </c>
+      <c r="Q100">
+        <v>3.7</v>
+      </c>
+      <c r="R100">
+        <v>1.83</v>
+      </c>
+      <c r="S100">
+        <v>1.65</v>
+      </c>
+      <c r="T100">
+        <v>2.07</v>
+      </c>
+      <c r="U100">
+        <v>4.06</v>
+      </c>
+      <c r="V100">
+        <v>1.19</v>
+      </c>
+      <c r="W100">
+        <v>1.03</v>
+      </c>
+      <c r="X100">
+        <v>1.11</v>
+      </c>
+      <c r="Y100">
+        <v>1.63</v>
+      </c>
+      <c r="Z100">
+        <v>2.19</v>
+      </c>
+      <c r="AA100">
         <v>3</v>
       </c>
-      <c r="P100">
-        <v>3.7</v>
-      </c>
-      <c r="Q100">
-        <v>2.75</v>
-      </c>
-      <c r="R100">
-        <v>1.93</v>
-      </c>
-      <c r="S100">
-        <v>1.57</v>
-      </c>
-      <c r="T100">
-        <v>2.18</v>
-      </c>
-      <c r="U100">
-        <v>3.78</v>
-      </c>
-      <c r="V100">
-        <v>1.23</v>
-      </c>
-      <c r="W100">
-        <v>1</v>
-      </c>
-      <c r="X100">
+      <c r="AB100">
+        <v>1.36</v>
+      </c>
+      <c r="AC100">
+        <v>7</v>
+      </c>
+      <c r="AD100">
         <v>1.07</v>
       </c>
-      <c r="Y100">
-        <v>1.54</v>
-      </c>
-      <c r="Z100">
-        <v>2.27</v>
-      </c>
-      <c r="AA100">
-        <v>2.7</v>
-      </c>
-      <c r="AB100">
-        <v>1.44</v>
-      </c>
-      <c r="AC100">
-        <v>5.75</v>
-      </c>
-      <c r="AD100">
-        <v>1.11</v>
-      </c>
       <c r="AE100">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF100">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG100">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK100">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16775,10 +16775,10 @@
         <v>1.8</v>
       </c>
       <c r="O101">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P101">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q101">
         <v>2.2</v>
@@ -16799,7 +16799,7 @@
         <v>1.4</v>
       </c>
       <c r="W101">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X101">
         <v>1.02</v>
@@ -16823,7 +16823,7 @@
         <v>1.33</v>
       </c>
       <c r="AE101">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF101">
         <v>1.8</v>
@@ -16989,7 +16989,7 @@
         <v>1.07</v>
       </c>
       <c r="AF102">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG102">
         <v>1.77</v>
@@ -17116,13 +17116,13 @@
         <v>1.35</v>
       </c>
       <c r="T103">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U103">
         <v>2.72</v>
       </c>
       <c r="V103">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W103">
         <v>1.05</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="O108">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P108">
-        <v>2.15</v>
+        <v>4.01</v>
       </c>
       <c r="Q108">
-        <v>4.33</v>
+        <v>2.88</v>
       </c>
       <c r="R108">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="S108">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="T108">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="U108">
-        <v>3.66</v>
+        <v>3.78</v>
       </c>
       <c r="V108">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W108">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X108">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y108">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="Z108">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="AA108">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AB108">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC108">
-        <v>6</v>
+        <v>5.76</v>
       </c>
       <c r="AD108">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE108">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF108">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AG108">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK108">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="O109">
         <v>2.87</v>
       </c>
       <c r="P109">
-        <v>4.01</v>
+        <v>2.15</v>
       </c>
       <c r="Q109">
-        <v>2.9</v>
+        <v>4.33</v>
       </c>
       <c r="R109">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="S109">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="T109">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="U109">
-        <v>3.78</v>
+        <v>3.66</v>
       </c>
       <c r="V109">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W109">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X109">
+        <v>1.08</v>
+      </c>
+      <c r="Y109">
+        <v>1.56</v>
+      </c>
+      <c r="Z109">
+        <v>2.23</v>
+      </c>
+      <c r="AA109">
+        <v>2.75</v>
+      </c>
+      <c r="AB109">
+        <v>1.4</v>
+      </c>
+      <c r="AC109">
+        <v>6</v>
+      </c>
+      <c r="AD109">
         <v>1.1</v>
       </c>
-      <c r="Y109">
-        <v>1.61</v>
-      </c>
-      <c r="Z109">
-        <v>2.13</v>
-      </c>
-      <c r="AA109">
-        <v>3.1</v>
-      </c>
-      <c r="AB109">
-        <v>1.36</v>
-      </c>
-      <c r="AC109">
-        <v>5.76</v>
-      </c>
-      <c r="AD109">
-        <v>1.07</v>
-      </c>
       <c r="AE109">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF109">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AG109">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK109">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18731,22 +18731,22 @@
         <v>2.55</v>
       </c>
       <c r="O113">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P113">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q113">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R113">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S113">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="T113">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="U113">
         <v>4</v>
@@ -18758,25 +18758,25 @@
         <v>1.03</v>
       </c>
       <c r="X113">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y113">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Z113">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AA113">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="AB113">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC113">
-        <v>7</v>
+        <v>6.02</v>
       </c>
       <c r="AD113">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE113">
         <v>1.02</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,28 +19054,28 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="O115">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="P115">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="Q115">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="R115">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="S115">
         <v>1.32</v>
       </c>
       <c r="T115">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="U115">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="V115">
         <v>1.55</v>
@@ -19084,34 +19084,34 @@
         <v>1.09</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z115">
-        <v>4.39</v>
+        <v>4.14</v>
       </c>
       <c r="AA115">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AB115">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="AC115">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="AD115">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AE115">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF115">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AG115">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AK115">
-        <v>2.18</v>
+        <v>2.89</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,28 +19217,28 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="O116">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="P116">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="Q116">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="R116">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="S116">
         <v>1.32</v>
       </c>
       <c r="T116">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="U116">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="V116">
         <v>1.55</v>
@@ -19247,34 +19247,34 @@
         <v>1.09</v>
       </c>
       <c r="X116">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z116">
-        <v>4.14</v>
+        <v>4.39</v>
       </c>
       <c r="AA116">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AB116">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="AC116">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AD116">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE116">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF116">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AG116">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AK116">
-        <v>2.89</v>
+        <v>2.18</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19552,7 +19552,7 @@
         <v>4.2</v>
       </c>
       <c r="Q118">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R118">
         <v>1.87</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.63</v>
+        <v>3.8</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P27">
-        <v>4.4</v>
+        <v>1.87</v>
       </c>
       <c r="Q27">
-        <v>2.39</v>
+        <v>4.8</v>
       </c>
       <c r="R27">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S27">
         <v>1.4</v>
       </c>
       <c r="T27">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U27">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="V27">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W27">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y27">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="Z27">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="AA27">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AB27">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AC27">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="AD27">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE27">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF27">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG27">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="AK27">
-        <v>1.87</v>
+        <v>1.15</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.8</v>
+        <v>1.63</v>
       </c>
       <c r="O28">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>1.87</v>
+        <v>4.4</v>
       </c>
       <c r="Q28">
-        <v>4.8</v>
+        <v>2.39</v>
       </c>
       <c r="R28">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S28">
         <v>1.4</v>
       </c>
       <c r="T28">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="U28">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="V28">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
+        <v>1.01</v>
+      </c>
+      <c r="Y28">
+        <v>1.32</v>
+      </c>
+      <c r="Z28">
+        <v>3.04</v>
+      </c>
+      <c r="AA28">
+        <v>2.05</v>
+      </c>
+      <c r="AB28">
+        <v>1.74</v>
+      </c>
+      <c r="AC28">
+        <v>3.75</v>
+      </c>
+      <c r="AD28">
+        <v>1.22</v>
+      </c>
+      <c r="AE28">
         <v>1.05</v>
       </c>
-      <c r="Y28">
-        <v>1.41</v>
-      </c>
-      <c r="Z28">
-        <v>2.96</v>
-      </c>
-      <c r="AA28">
-        <v>2.21</v>
-      </c>
-      <c r="AB28">
-        <v>1.64</v>
-      </c>
-      <c r="AC28">
-        <v>3.94</v>
-      </c>
-      <c r="AD28">
-        <v>1.21</v>
-      </c>
-      <c r="AE28">
-        <v>1.04</v>
-      </c>
       <c r="AF28">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG28">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.15</v>
+        <v>1.87</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="O46">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="P46">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="Q46">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="R46">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S46">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T46">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="U46">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="V46">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="W46">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X46">
         <v>0</v>
       </c>
       <c r="Y46">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z46">
-        <v>7.29</v>
+        <v>0</v>
       </c>
       <c r="AA46">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AB46">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AC46">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD46">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AE46">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF46">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG46">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK46">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X47">
         <v>0</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.61</v>
+        <v>1.18</v>
       </c>
       <c r="O48">
-        <v>3.75</v>
+        <v>6.4</v>
       </c>
       <c r="P48">
-        <v>4.93</v>
+        <v>11.2</v>
       </c>
       <c r="Q48">
+        <v>1.4</v>
+      </c>
+      <c r="R48">
+        <v>3.1</v>
+      </c>
+      <c r="S48">
+        <v>1.17</v>
+      </c>
+      <c r="T48">
+        <v>4.34</v>
+      </c>
+      <c r="U48">
+        <v>1.88</v>
+      </c>
+      <c r="V48">
+        <v>1.87</v>
+      </c>
+      <c r="W48">
+        <v>1.24</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>1.04</v>
+      </c>
+      <c r="Z48">
+        <v>7.29</v>
+      </c>
+      <c r="AA48">
+        <v>1.33</v>
+      </c>
+      <c r="AB48">
+        <v>3.25</v>
+      </c>
+      <c r="AC48">
+        <v>1.81</v>
+      </c>
+      <c r="AD48">
+        <v>1.97</v>
+      </c>
+      <c r="AE48">
+        <v>1.36</v>
+      </c>
+      <c r="AF48">
         <v>2.08</v>
       </c>
-      <c r="R48">
-        <v>2.4</v>
-      </c>
-      <c r="S48">
-        <v>1.32</v>
-      </c>
-      <c r="T48">
-        <v>3.16</v>
-      </c>
-      <c r="U48">
-        <v>2.42</v>
-      </c>
-      <c r="V48">
-        <v>1.51</v>
-      </c>
-      <c r="W48">
-        <v>1.09</v>
-      </c>
-      <c r="X48">
-        <v>0</v>
-      </c>
-      <c r="Y48">
-        <v>1.2</v>
-      </c>
-      <c r="Z48">
-        <v>3.99</v>
-      </c>
-      <c r="AA48">
-        <v>1.67</v>
-      </c>
-      <c r="AB48">
-        <v>2.11</v>
-      </c>
-      <c r="AC48">
-        <v>2.64</v>
-      </c>
-      <c r="AD48">
-        <v>1.44</v>
-      </c>
-      <c r="AE48">
-        <v>1.12</v>
-      </c>
-      <c r="AF48">
-        <v>1.75</v>
-      </c>
       <c r="AG48">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK48">
-        <v>2.38</v>
+        <v>6</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -13345,7 +13345,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N80">
@@ -15953,7 +15953,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N96">
@@ -15966,19 +15966,19 @@
         <v>2.33</v>
       </c>
       <c r="Q96">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R96">
         <v>2.1</v>
       </c>
       <c r="S96">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T96">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="U96">
-        <v>2.63</v>
+        <v>2.84</v>
       </c>
       <c r="V96">
         <v>1.38</v>
@@ -15999,7 +15999,7 @@
         <v>1.91</v>
       </c>
       <c r="AB96">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AC96">
         <v>3.3</v>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK96">
         <v>1.36</v>
@@ -16159,7 +16159,7 @@
         <v>2.44</v>
       </c>
       <c r="AA97">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="AB97">
         <v>1.51</v>
@@ -16630,7 +16630,7 @@
         <v>2.07</v>
       </c>
       <c r="U100">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="V100">
         <v>1.19</v>
@@ -17626,10 +17626,10 @@
         <v>0</v>
       </c>
       <c r="AA106">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="AB106">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC106">
         <v>0</v>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,58 +17750,58 @@
         </is>
       </c>
       <c r="N107">
+        <v>2</v>
+      </c>
+      <c r="O107">
+        <v>2.87</v>
+      </c>
+      <c r="P107">
+        <v>4.01</v>
+      </c>
+      <c r="Q107">
+        <v>2.88</v>
+      </c>
+      <c r="R107">
+        <v>1.85</v>
+      </c>
+      <c r="S107">
         <v>1.64</v>
       </c>
-      <c r="O107">
-        <v>3.35</v>
-      </c>
-      <c r="P107">
-        <v>4.7</v>
-      </c>
-      <c r="Q107">
-        <v>2.3</v>
-      </c>
-      <c r="R107">
-        <v>2</v>
-      </c>
-      <c r="S107">
-        <v>1.53</v>
-      </c>
       <c r="T107">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="U107">
-        <v>3.42</v>
+        <v>3.78</v>
       </c>
       <c r="V107">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="W107">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X107">
         <v>1.1</v>
       </c>
       <c r="Y107">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="Z107">
-        <v>2.39</v>
+        <v>2.13</v>
       </c>
       <c r="AA107">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB107">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AC107">
-        <v>5.25</v>
+        <v>5.76</v>
       </c>
       <c r="AD107">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AE107">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF107">
         <v>2.4</v>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK107">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="O108">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P108">
-        <v>4.01</v>
+        <v>2.15</v>
       </c>
       <c r="Q108">
-        <v>2.88</v>
+        <v>4.33</v>
       </c>
       <c r="R108">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="S108">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="T108">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="U108">
-        <v>3.78</v>
+        <v>3.66</v>
       </c>
       <c r="V108">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W108">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X108">
+        <v>1.08</v>
+      </c>
+      <c r="Y108">
+        <v>1.56</v>
+      </c>
+      <c r="Z108">
+        <v>2.23</v>
+      </c>
+      <c r="AA108">
+        <v>2.75</v>
+      </c>
+      <c r="AB108">
+        <v>1.4</v>
+      </c>
+      <c r="AC108">
+        <v>6</v>
+      </c>
+      <c r="AD108">
         <v>1.1</v>
       </c>
-      <c r="Y108">
-        <v>1.61</v>
-      </c>
-      <c r="Z108">
-        <v>2.13</v>
-      </c>
-      <c r="AA108">
-        <v>3.1</v>
-      </c>
-      <c r="AB108">
-        <v>1.36</v>
-      </c>
-      <c r="AC108">
-        <v>5.76</v>
-      </c>
-      <c r="AD108">
-        <v>1.07</v>
-      </c>
       <c r="AE108">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF108">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AG108">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK108">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,80 +18076,80 @@
         </is>
       </c>
       <c r="N109">
-        <v>3.25</v>
+        <v>1.64</v>
       </c>
       <c r="O109">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="P109">
+        <v>4.7</v>
+      </c>
+      <c r="Q109">
+        <v>2.3</v>
+      </c>
+      <c r="R109">
+        <v>2</v>
+      </c>
+      <c r="S109">
+        <v>1.53</v>
+      </c>
+      <c r="T109">
+        <v>2.5</v>
+      </c>
+      <c r="U109">
+        <v>3.42</v>
+      </c>
+      <c r="V109">
+        <v>1.29</v>
+      </c>
+      <c r="W109">
+        <v>1.02</v>
+      </c>
+      <c r="X109">
+        <v>1.06</v>
+      </c>
+      <c r="Y109">
+        <v>1.49</v>
+      </c>
+      <c r="Z109">
+        <v>2.39</v>
+      </c>
+      <c r="AA109">
+        <v>2.4</v>
+      </c>
+      <c r="AB109">
+        <v>1.49</v>
+      </c>
+      <c r="AC109">
+        <v>5.25</v>
+      </c>
+      <c r="AD109">
+        <v>1.13</v>
+      </c>
+      <c r="AE109">
+        <v>1.02</v>
+      </c>
+      <c r="AF109">
+        <v>2.4</v>
+      </c>
+      <c r="AG109">
+        <v>1.5</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ109">
+        <v>1.22</v>
+      </c>
+      <c r="AK109">
         <v>2.15</v>
-      </c>
-      <c r="Q109">
-        <v>4.33</v>
-      </c>
-      <c r="R109">
-        <v>1.9</v>
-      </c>
-      <c r="S109">
-        <v>1.58</v>
-      </c>
-      <c r="T109">
-        <v>2.19</v>
-      </c>
-      <c r="U109">
-        <v>3.66</v>
-      </c>
-      <c r="V109">
-        <v>1.25</v>
-      </c>
-      <c r="W109">
-        <v>1.04</v>
-      </c>
-      <c r="X109">
-        <v>1.08</v>
-      </c>
-      <c r="Y109">
-        <v>1.56</v>
-      </c>
-      <c r="Z109">
-        <v>2.23</v>
-      </c>
-      <c r="AA109">
-        <v>2.75</v>
-      </c>
-      <c r="AB109">
-        <v>1.4</v>
-      </c>
-      <c r="AC109">
-        <v>6</v>
-      </c>
-      <c r="AD109">
-        <v>1.1</v>
-      </c>
-      <c r="AE109">
-        <v>1.01</v>
-      </c>
-      <c r="AF109">
-        <v>2.25</v>
-      </c>
-      <c r="AG109">
-        <v>1.57</v>
-      </c>
-      <c r="AH109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ109">
-        <v>1.3</v>
-      </c>
-      <c r="AK109">
-        <v>1.24</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18423,7 +18423,7 @@
         <v>3</v>
       </c>
       <c r="U111">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V111">
         <v>1.65</v>
@@ -18447,7 +18447,7 @@
         <v>2.2</v>
       </c>
       <c r="AC111">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AD111">
         <v>1.53</v>
@@ -18561,7 +18561,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N112">
@@ -18746,7 +18746,7 @@
         <v>1.64</v>
       </c>
       <c r="T113">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="U113">
         <v>4</v>
@@ -18761,10 +18761,10 @@
         <v>1.09</v>
       </c>
       <c r="Y113">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Z113">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AA113">
         <v>2.82</v>
@@ -19558,10 +19558,10 @@
         <v>1.87</v>
       </c>
       <c r="S118">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="T118">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="U118">
         <v>3.75</v>
@@ -19715,7 +19715,7 @@
         <v>2.35</v>
       </c>
       <c r="Q119">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="R119">
         <v>2.3</v>
@@ -20044,7 +20044,7 @@
         <v>4.52</v>
       </c>
       <c r="R121">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S121">
         <v>1.29</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O6">
         <v>3.05</v>
@@ -1296,7 +1296,7 @@
         <v>2.65</v>
       </c>
       <c r="Q6">
-        <v>3.53</v>
+        <v>3.38</v>
       </c>
       <c r="R6">
         <v>2</v>
@@ -1456,7 +1456,7 @@
         <v>3.15</v>
       </c>
       <c r="P7">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="Q7">
         <v>2.8</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AB8">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1782,7 +1782,7 @@
         <v>3.5</v>
       </c>
       <c r="P9">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="Q9">
         <v>2.63</v>
@@ -1815,10 +1815,10 @@
         <v>3.26</v>
       </c>
       <c r="AA9">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AB9">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AC9">
         <v>3.24</v>
@@ -2594,10 +2594,10 @@
         <v>1.83</v>
       </c>
       <c r="O14">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="Q14">
         <v>2.7</v>
@@ -2630,10 +2630,10 @@
         <v>3.2</v>
       </c>
       <c r="AA14">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB14">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC14">
         <v>3.24</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O17">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="P17">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q17">
         <v>4</v>
@@ -3113,7 +3113,7 @@
         <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z17">
         <v>2.54</v>
@@ -3249,28 +3249,28 @@
         <v>2.9</v>
       </c>
       <c r="P18">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q18">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R18">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T18">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="U18">
         <v>3</v>
       </c>
       <c r="V18">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3279,16 +3279,16 @@
         <v>1.37</v>
       </c>
       <c r="Z18">
-        <v>2.96</v>
+        <v>2.93</v>
       </c>
       <c r="AA18">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AB18">
         <v>1.47</v>
       </c>
       <c r="AC18">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="AD18">
         <v>1.17</v>
@@ -3300,23 +3300,23 @@
         <v>1.91</v>
       </c>
       <c r="AG18">
+        <v>1.62</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>1.18</v>
+      </c>
+      <c r="AK18">
         <v>1.6</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18">
-        <v>1.15</v>
-      </c>
-      <c r="AK18">
-        <v>1.7</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="R19">
         <v>2.25</v>
@@ -3608,10 +3608,10 @@
         <v>3.1</v>
       </c>
       <c r="AA20">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB20">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC20">
         <v>3.44</v>
@@ -4221,55 +4221,55 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O24">
+        <v>2.95</v>
+      </c>
+      <c r="P24">
+        <v>3.6</v>
+      </c>
+      <c r="Q24">
         <v>2.9</v>
-      </c>
-      <c r="P24">
-        <v>3.9</v>
-      </c>
-      <c r="Q24">
-        <v>2.86</v>
       </c>
       <c r="R24">
         <v>1.91</v>
       </c>
       <c r="S24">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="T24">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U24">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V24">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W24">
         <v>1.04</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y24">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Z24">
-        <v>2.67</v>
+        <v>2.52</v>
       </c>
       <c r="AA24">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB24">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="AC24">
-        <v>4.07</v>
+        <v>4.53</v>
       </c>
       <c r="AD24">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE24">
         <v>1.01</v>
@@ -4294,7 +4294,7 @@
         <v>1.36</v>
       </c>
       <c r="AK24">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O25">
         <v>2.87</v>
@@ -4417,10 +4417,10 @@
         <v>1.07</v>
       </c>
       <c r="Y25">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="Z25">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AA25">
         <v>2.61</v>
@@ -4438,10 +4438,10 @@
         <v>1.01</v>
       </c>
       <c r="AF25">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG25">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5688,31 +5688,31 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="O33">
+        <v>3.1</v>
+      </c>
+      <c r="P33">
+        <v>2.65</v>
+      </c>
+      <c r="Q33">
         <v>2.9</v>
       </c>
-      <c r="P33">
-        <v>2.55</v>
-      </c>
-      <c r="Q33">
-        <v>3.13</v>
-      </c>
       <c r="R33">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="S33">
         <v>1.4</v>
       </c>
       <c r="T33">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U33">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V33">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
         <v>1.07</v>
@@ -5721,10 +5721,10 @@
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z33">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AA33">
         <v>2.15</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -7477,17 +7477,17 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N44">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="O44">
-        <v>3.98</v>
+        <v>3.35</v>
       </c>
       <c r="P44">
-        <v>4.98</v>
+        <v>3.55</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O60">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="P60">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -11230,7 +11230,7 @@
         </is>
       </c>
       <c r="N67">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="O67">
         <v>3.6</v>
@@ -11263,16 +11263,16 @@
         <v>0</v>
       </c>
       <c r="Y67">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z67">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AA67">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB67">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC67">
         <v>3.38</v>
@@ -11284,7 +11284,7 @@
         <v>1.05</v>
       </c>
       <c r="AF67">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AG67">
         <v>1.5</v>
@@ -11396,7 +11396,7 @@
         <v>2.63</v>
       </c>
       <c r="O68">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="P68">
         <v>2.45</v>
@@ -11595,7 +11595,7 @@
         <v>2.82</v>
       </c>
       <c r="AA69">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AB69">
         <v>1.47</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK69">
         <v>1.49</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O70">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P70">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q70">
         <v>2.3</v>
@@ -11773,10 +11773,10 @@
         <v>1.05</v>
       </c>
       <c r="AF70">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG70">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>1.14</v>
       </c>
       <c r="AK70">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
+        <v>1.38</v>
+      </c>
+      <c r="O71">
+        <v>4.2</v>
+      </c>
+      <c r="P71">
+        <v>6.75</v>
+      </c>
+      <c r="Q71">
+        <v>1.8</v>
+      </c>
+      <c r="R71">
+        <v>2.4</v>
+      </c>
+      <c r="S71">
+        <v>1.33</v>
+      </c>
+      <c r="T71">
+        <v>3</v>
+      </c>
+      <c r="U71">
+        <v>2.75</v>
+      </c>
+      <c r="V71">
         <v>1.41</v>
       </c>
-      <c r="O71">
-        <v>4</v>
-      </c>
-      <c r="P71">
-        <v>6.5</v>
-      </c>
-      <c r="Q71">
-        <v>1.91</v>
-      </c>
-      <c r="R71">
-        <v>2.25</v>
-      </c>
-      <c r="S71">
-        <v>1.36</v>
-      </c>
-      <c r="T71">
-        <v>2.88</v>
-      </c>
-      <c r="U71">
-        <v>2.88</v>
-      </c>
-      <c r="V71">
-        <v>1.39</v>
-      </c>
       <c r="W71">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X71">
         <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z71">
-        <v>3.37</v>
+        <v>3.54</v>
       </c>
       <c r="AA71">
         <v>1.95</v>
       </c>
       <c r="AB71">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC71">
-        <v>3.12</v>
+        <v>2.97</v>
       </c>
       <c r="AD71">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE71">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF71">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AG71">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK71">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA73">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB73">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC73">
         <v>0</v>
@@ -12380,7 +12380,7 @@
         <v>2.06</v>
       </c>
       <c r="Q74">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R74">
         <v>1.95</v>
@@ -12392,10 +12392,10 @@
         <v>2.3</v>
       </c>
       <c r="U74">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="V74">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W74">
         <v>1.08</v>
@@ -12416,10 +12416,10 @@
         <v>1.95</v>
       </c>
       <c r="AC74">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD74">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE74">
         <v>1.09</v>
@@ -12733,7 +12733,7 @@
         <v>1.28</v>
       </c>
       <c r="Z76">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="AA76">
         <v>2</v>
@@ -12899,7 +12899,7 @@
         <v>2.45</v>
       </c>
       <c r="AA77">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AB77">
         <v>1.5</v>
@@ -13186,16 +13186,16 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="O79">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P79">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q79">
-        <v>2.79</v>
+        <v>2.55</v>
       </c>
       <c r="R79">
         <v>2.1</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="O84">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P84">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q84">
         <v>2.5</v>
@@ -14043,7 +14043,7 @@
         <v>2.03</v>
       </c>
       <c r="AB84">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC84">
         <v>3.6</v>
@@ -14237,7 +14237,7 @@
         <v>1.14</v>
       </c>
       <c r="AK85">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O86">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P86">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q86">
         <v>2.54</v>
@@ -14366,10 +14366,10 @@
         <v>3.04</v>
       </c>
       <c r="AA86">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB86">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC86">
         <v>3.58</v>
@@ -14400,7 +14400,7 @@
         <v>1.25</v>
       </c>
       <c r="AK86">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -15634,10 +15634,10 @@
         <v>1.83</v>
       </c>
       <c r="O94">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P94">
-        <v>3.83</v>
+        <v>3.7</v>
       </c>
       <c r="Q94">
         <v>2.64</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,28 +19054,28 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="O115">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="P115">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="Q115">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="R115">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="S115">
         <v>1.32</v>
       </c>
       <c r="T115">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="U115">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="V115">
         <v>1.55</v>
@@ -19084,34 +19084,34 @@
         <v>1.09</v>
       </c>
       <c r="X115">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y115">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z115">
-        <v>4.14</v>
+        <v>4.39</v>
       </c>
       <c r="AA115">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AB115">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="AC115">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AD115">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AE115">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF115">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AG115">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AK115">
-        <v>2.89</v>
+        <v>2.18</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,80 +19217,80 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="O116">
-        <v>3.95</v>
+        <v>5.4</v>
       </c>
       <c r="P116">
-        <v>5.2</v>
+        <v>10</v>
       </c>
       <c r="Q116">
-        <v>2.21</v>
+        <v>1.75</v>
       </c>
       <c r="R116">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="S116">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T116">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="U116">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V116">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W116">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X116">
+        <v>1.01</v>
+      </c>
+      <c r="Y116">
+        <v>1.16</v>
+      </c>
+      <c r="Z116">
+        <v>4.44</v>
+      </c>
+      <c r="AA116">
+        <v>1.63</v>
+      </c>
+      <c r="AB116">
+        <v>2.26</v>
+      </c>
+      <c r="AC116">
+        <v>2.63</v>
+      </c>
+      <c r="AD116">
+        <v>1.54</v>
+      </c>
+      <c r="AE116">
+        <v>1.17</v>
+      </c>
+      <c r="AF116">
+        <v>2.22</v>
+      </c>
+      <c r="AG116">
+        <v>1.54</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ116">
         <v>1.02</v>
       </c>
-      <c r="Y116">
-        <v>1.17</v>
-      </c>
-      <c r="Z116">
-        <v>4.39</v>
-      </c>
-      <c r="AA116">
-        <v>1.64</v>
-      </c>
-      <c r="AB116">
-        <v>2.24</v>
-      </c>
-      <c r="AC116">
-        <v>2.46</v>
-      </c>
-      <c r="AD116">
-        <v>1.53</v>
-      </c>
-      <c r="AE116">
-        <v>1.18</v>
-      </c>
-      <c r="AF116">
-        <v>1.65</v>
-      </c>
-      <c r="AG116">
-        <v>2.07</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ116">
-        <v>1.16</v>
-      </c>
       <c r="AK116">
-        <v>2.18</v>
+        <v>3.68</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="O120">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="P120">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="Q120">
-        <v>3.44</v>
+        <v>3.27</v>
       </c>
       <c r="R120">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="S120">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="T120">
-        <v>3.4</v>
+        <v>2.76</v>
       </c>
       <c r="U120">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V120">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="W120">
         <v>1.1</v>
       </c>
       <c r="X120">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y120">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z120">
-        <v>4.32</v>
+        <v>3.61</v>
       </c>
       <c r="AA120">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AB120">
-        <v>2.22</v>
+        <v>1.98</v>
       </c>
       <c r="AC120">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AD120">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AE120">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AF120">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG120">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK120">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="O122">
+        <v>3.5</v>
+      </c>
+      <c r="P122">
         <v>3.4</v>
       </c>
-      <c r="P122">
-        <v>3.35</v>
-      </c>
       <c r="Q122">
-        <v>2.79</v>
+        <v>2.66</v>
       </c>
       <c r="R122">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S122">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T122">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="U122">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="V122">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="W122">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X122">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y122">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z122">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="AA122">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AB122">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AC122">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="AD122">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE122">
         <v>1.06</v>
       </c>
       <c r="AF122">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG122">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK122">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AL122">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -612,26 +612,26 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -647,19 +647,19 @@
         <v>2.88</v>
       </c>
       <c r="R2">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T2">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="U2">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W2">
         <v>1.11</v>
@@ -668,7 +668,7 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z2">
         <v>4.1</v>
@@ -680,7 +680,7 @@
         <v>2.11</v>
       </c>
       <c r="AC2">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="AD2">
         <v>1.43</v>
@@ -689,19 +689,19 @@
         <v>1.16</v>
       </c>
       <c r="AF2">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG2">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "60"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -778,13 +778,13 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -794,7 +794,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -804,7 +804,7 @@
         <v>3.65</v>
       </c>
       <c r="P3">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Q3">
         <v>4.75</v>
@@ -816,19 +816,19 @@
         <v>1.4</v>
       </c>
       <c r="T3">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="U3">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
         <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
         <v>1.29</v>
@@ -846,7 +846,7 @@
         <v>3.4</v>
       </c>
       <c r="AD3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE3">
         <v>1.06</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "45"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -950,14 +950,14 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1006,7 +1006,7 @@
         <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>4.04</v>
+        <v>4.06</v>
       </c>
       <c r="AD4">
         <v>1.23</v>
@@ -1018,11 +1018,11 @@
         <v>1.87</v>
       </c>
       <c r="AG4">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1127,10 +1127,10 @@
         <v>2.1</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q5">
         <v>2.75</v>
@@ -1145,10 +1145,10 @@
         <v>3</v>
       </c>
       <c r="U5">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V5">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
         <v>1.06</v>
@@ -2301,7 +2301,7 @@
         <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.95</v>
+        <v>3.99</v>
       </c>
       <c r="AA12">
         <v>1.73</v>
@@ -2310,7 +2310,7 @@
         <v>2</v>
       </c>
       <c r="AC12">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="AD12">
         <v>1.39</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Calvo Sotelo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.67</v>
+        <v>2.11</v>
       </c>
       <c r="O15">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>4.25</v>
+        <v>3.45</v>
       </c>
       <c r="Q15">
-        <v>2.3</v>
+        <v>2.67</v>
       </c>
       <c r="R15">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S15">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T15">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="U15">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W15">
         <v>1.06</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
+        <v>1.42</v>
+      </c>
+      <c r="Z15">
+        <v>2.7</v>
+      </c>
+      <c r="AA15">
+        <v>2.3</v>
+      </c>
+      <c r="AB15">
+        <v>1.6</v>
+      </c>
+      <c r="AC15">
+        <v>3.92</v>
+      </c>
+      <c r="AD15">
+        <v>1.21</v>
+      </c>
+      <c r="AE15">
+        <v>1.02</v>
+      </c>
+      <c r="AF15">
+        <v>2</v>
+      </c>
+      <c r="AG15">
+        <v>1.75</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.26</v>
       </c>
-      <c r="Z15">
-        <v>3.58</v>
-      </c>
-      <c r="AA15">
-        <v>1.8</v>
-      </c>
-      <c r="AB15">
-        <v>1.87</v>
-      </c>
-      <c r="AC15">
-        <v>2.97</v>
-      </c>
-      <c r="AD15">
-        <v>1.3</v>
-      </c>
-      <c r="AE15">
-        <v>1.07</v>
-      </c>
-      <c r="AF15">
-        <v>1.75</v>
-      </c>
-      <c r="AG15">
-        <v>1.95</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.25</v>
-      </c>
       <c r="AK15">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.11</v>
+        <v>2.9</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P16">
-        <v>3.45</v>
+        <v>2.3</v>
       </c>
       <c r="Q16">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="R16">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S16">
         <v>1.44</v>
       </c>
       <c r="T16">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U16">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="V16">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z16">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AA16">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AB16">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC16">
-        <v>3.92</v>
+        <v>4.49</v>
       </c>
       <c r="AD16">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AE16">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF16">
         <v>2</v>
       </c>
       <c r="AG16">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK16">
-        <v>1.66</v>
+        <v>1.29</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Calvo Sotelo</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.9</v>
+        <v>1.67</v>
       </c>
       <c r="O17">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
+        <v>4.25</v>
+      </c>
+      <c r="Q17">
         <v>2.3</v>
       </c>
-      <c r="Q17">
-        <v>4</v>
-      </c>
       <c r="R17">
+        <v>2.2</v>
+      </c>
+      <c r="S17">
+        <v>1.33</v>
+      </c>
+      <c r="T17">
+        <v>2.89</v>
+      </c>
+      <c r="U17">
+        <v>2.75</v>
+      </c>
+      <c r="V17">
+        <v>1.4</v>
+      </c>
+      <c r="W17">
+        <v>1.06</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>1.26</v>
+      </c>
+      <c r="Z17">
+        <v>3.58</v>
+      </c>
+      <c r="AA17">
+        <v>1.8</v>
+      </c>
+      <c r="AB17">
+        <v>1.87</v>
+      </c>
+      <c r="AC17">
+        <v>2.97</v>
+      </c>
+      <c r="AD17">
+        <v>1.3</v>
+      </c>
+      <c r="AE17">
+        <v>1.07</v>
+      </c>
+      <c r="AF17">
+        <v>1.75</v>
+      </c>
+      <c r="AG17">
         <v>1.95</v>
       </c>
-      <c r="S17">
-        <v>1.44</v>
-      </c>
-      <c r="T17">
-        <v>2.4</v>
-      </c>
-      <c r="U17">
-        <v>3.3</v>
-      </c>
-      <c r="V17">
-        <v>1.29</v>
-      </c>
-      <c r="W17">
-        <v>1.05</v>
-      </c>
-      <c r="X17">
-        <v>1.04</v>
-      </c>
-      <c r="Y17">
-        <v>1.43</v>
-      </c>
-      <c r="Z17">
-        <v>2.54</v>
-      </c>
-      <c r="AA17">
-        <v>2.37</v>
-      </c>
-      <c r="AB17">
-        <v>1.53</v>
-      </c>
-      <c r="AC17">
-        <v>4.49</v>
-      </c>
-      <c r="AD17">
-        <v>1.11</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.25</v>
+      </c>
+      <c r="AK17">
         <v>2</v>
-      </c>
-      <c r="AG17">
-        <v>1.66</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.33</v>
-      </c>
-      <c r="AK17">
-        <v>1.29</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AB21">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>3.52</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Santa Clara II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Real SC</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>3.8</v>
+        <v>2.37</v>
       </c>
       <c r="O27">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="P27">
-        <v>1.87</v>
+        <v>2.81</v>
       </c>
       <c r="Q27">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.63</v>
+        <v>3.8</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P28">
-        <v>4.4</v>
+        <v>1.87</v>
       </c>
       <c r="Q28">
-        <v>2.39</v>
+        <v>4.8</v>
       </c>
       <c r="R28">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S28">
         <v>1.4</v>
       </c>
       <c r="T28">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U28">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="V28">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W28">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y28">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="Z28">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="AA28">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AB28">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AC28">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="AD28">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE28">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF28">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG28">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="AK28">
-        <v>1.87</v>
+        <v>1.15</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="O29">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>4.26</v>
+        <v>4.4</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-10-04 08:00:00</t>
+          <t>2026-10-04 07:30:00</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.31</v>
+        <v>3.25</v>
       </c>
       <c r="O32">
-        <v>5.77</v>
+        <v>4.03</v>
       </c>
       <c r="P32">
-        <v>8.699999999999999</v>
+        <v>2.03</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tamaraceite</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.45</v>
+        <v>1.31</v>
       </c>
       <c r="O33">
-        <v>3.1</v>
+        <v>5.77</v>
       </c>
       <c r="P33">
-        <v>2.65</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q33">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK33">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Tamaraceite</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,52 +5851,52 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="O34">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P34">
+        <v>2.65</v>
+      </c>
+      <c r="Q34">
         <v>2.9</v>
       </c>
-      <c r="Q34">
-        <v>3.14</v>
-      </c>
       <c r="R34">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S34">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T34">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="U34">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="V34">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W34">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z34">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AA34">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AB34">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AC34">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="AD34">
         <v>1.24</v>
@@ -5905,10 +5905,10 @@
         <v>1.03</v>
       </c>
       <c r="AF34">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG34">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-10-04 08:30:00</t>
+          <t>2026-10-04 08:00:00</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="O35">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P35">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q35">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="R35">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="S35">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T35">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="U35">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="V35">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="Z35">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="AA35">
+        <v>2.18</v>
+      </c>
+      <c r="AB35">
+        <v>1.73</v>
+      </c>
+      <c r="AC35">
+        <v>3.94</v>
+      </c>
+      <c r="AD35">
+        <v>1.24</v>
+      </c>
+      <c r="AE35">
+        <v>1.03</v>
+      </c>
+      <c r="AF35">
         <v>1.85</v>
       </c>
-      <c r="AB35">
-        <v>1.88</v>
-      </c>
-      <c r="AC35">
-        <v>3.3</v>
-      </c>
-      <c r="AD35">
+      <c r="AG35">
+        <v>1.83</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.3</v>
       </c>
-      <c r="AE35">
-        <v>1.07</v>
-      </c>
-      <c r="AF35">
-        <v>1.73</v>
-      </c>
-      <c r="AG35">
-        <v>2</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.25</v>
-      </c>
       <c r="AK35">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-10-04 09:00:00</t>
+          <t>2026-10-04 08:30:00</t>
         </is>
       </c>
     </row>
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="O36">
         <v>3.3</v>
       </c>
       <c r="P36">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="Q36">
-        <v>3.4</v>
+        <v>3.16</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S36">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="U36">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="V36">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W36">
         <v>1.07</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z36">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="AA36">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB36">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AC36">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="AD36">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AE36">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF36">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AG36">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.25</v>
       </c>
       <c r="AK36">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6298,22 +6298,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.9</v>
+        <v>2.85</v>
       </c>
       <c r="O37">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P37">
-        <v>3.8</v>
+        <v>2.27</v>
       </c>
       <c r="Q37">
-        <v>2.76</v>
+        <v>3.4</v>
       </c>
       <c r="R37">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="T37">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="U37">
-        <v>2.98</v>
+        <v>2.64</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W37">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="Z37">
-        <v>2.94</v>
+        <v>3.84</v>
       </c>
       <c r="AA37">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="AB37">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AC37">
-        <v>3.68</v>
+        <v>2.74</v>
       </c>
       <c r="AD37">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="AE37">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF37">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="AG37">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,81 +6503,81 @@
         </is>
       </c>
       <c r="N38">
-        <v>4.9</v>
+        <v>1.9</v>
       </c>
       <c r="O38">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P38">
-        <v>1.67</v>
+        <v>3.8</v>
       </c>
       <c r="Q38">
-        <v>4.86</v>
+        <v>2.76</v>
       </c>
       <c r="R38">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="S38">
+        <v>1.46</v>
+      </c>
+      <c r="T38">
+        <v>2.62</v>
+      </c>
+      <c r="U38">
+        <v>2.98</v>
+      </c>
+      <c r="V38">
+        <v>1.36</v>
+      </c>
+      <c r="W38">
+        <v>1.02</v>
+      </c>
+      <c r="X38">
+        <v>1.02</v>
+      </c>
+      <c r="Y38">
         <v>1.37</v>
       </c>
-      <c r="T38">
-        <v>2.93</v>
-      </c>
-      <c r="U38">
-        <v>2.62</v>
-      </c>
-      <c r="V38">
-        <v>1.4</v>
-      </c>
-      <c r="W38">
-        <v>1.06</v>
-      </c>
-      <c r="X38">
+      <c r="Z38">
+        <v>2.94</v>
+      </c>
+      <c r="AA38">
+        <v>2.11</v>
+      </c>
+      <c r="AB38">
+        <v>1.73</v>
+      </c>
+      <c r="AC38">
+        <v>3.68</v>
+      </c>
+      <c r="AD38">
+        <v>1.24</v>
+      </c>
+      <c r="AE38">
         <v>1.03</v>
       </c>
-      <c r="Y38">
-        <v>1.34</v>
-      </c>
-      <c r="Z38">
-        <v>3.44</v>
-      </c>
-      <c r="AA38">
-        <v>1.84</v>
-      </c>
-      <c r="AB38">
-        <v>1.83</v>
-      </c>
-      <c r="AC38">
-        <v>3.25</v>
-      </c>
-      <c r="AD38">
-        <v>1.35</v>
-      </c>
-      <c r="AE38">
-        <v>1.08</v>
-      </c>
       <c r="AF38">
+        <v>1.98</v>
+      </c>
+      <c r="AG38">
+        <v>1.75</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
+        <v>1.29</v>
+      </c>
+      <c r="AK38">
         <v>1.78</v>
       </c>
-      <c r="AG38">
-        <v>1.91</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.19</v>
-      </c>
-      <c r="AK38">
-        <v>1.12</v>
-      </c>
       <c r="AL38">
         <v>0</v>
       </c>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-10-04 09:30:00</t>
+          <t>2026-10-04 09:00:00</t>
         </is>
       </c>
     </row>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.12</v>
+        <v>4.9</v>
       </c>
       <c r="O39">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
-        <v>3.41</v>
+        <v>1.67</v>
       </c>
       <c r="Q39">
-        <v>2.75</v>
+        <v>4.86</v>
       </c>
       <c r="R39">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="S39">
+        <v>1.37</v>
+      </c>
+      <c r="T39">
+        <v>2.93</v>
+      </c>
+      <c r="U39">
+        <v>2.62</v>
+      </c>
+      <c r="V39">
         <v>1.4</v>
-      </c>
-      <c r="T39">
-        <v>2.54</v>
-      </c>
-      <c r="U39">
-        <v>3</v>
-      </c>
-      <c r="V39">
-        <v>1.3</v>
       </c>
       <c r="W39">
         <v>1.06</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="Z39">
-        <v>2.77</v>
+        <v>3.44</v>
       </c>
       <c r="AA39">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="AB39">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AC39">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="AD39">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AE39">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AF39">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AG39">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK39">
-        <v>1.65</v>
+        <v>1.12</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="O40">
-        <v>3.25</v>
+        <v>3.53</v>
       </c>
       <c r="P40">
-        <v>2.8</v>
+        <v>3.41</v>
       </c>
       <c r="Q40">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R40">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S40">
+        <v>1.4</v>
+      </c>
+      <c r="T40">
+        <v>2.54</v>
+      </c>
+      <c r="U40">
+        <v>3</v>
+      </c>
+      <c r="V40">
         <v>1.3</v>
       </c>
-      <c r="T40">
-        <v>3</v>
-      </c>
-      <c r="U40">
-        <v>2.75</v>
-      </c>
-      <c r="V40">
-        <v>1.44</v>
-      </c>
       <c r="W40">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
         <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="Z40">
-        <v>3.5</v>
+        <v>2.77</v>
       </c>
       <c r="AA40">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AB40">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="AC40">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD40">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AE40">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AF40">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AG40">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK40">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
+        <v>2.25</v>
+      </c>
+      <c r="O41">
+        <v>3.25</v>
+      </c>
+      <c r="P41">
         <v>2.8</v>
       </c>
-      <c r="O41">
-        <v>3.1</v>
-      </c>
-      <c r="P41">
-        <v>2.55</v>
-      </c>
       <c r="Q41">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R41">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S41">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T41">
+        <v>3</v>
+      </c>
+      <c r="U41">
         <v>2.75</v>
       </c>
-      <c r="U41">
-        <v>2.9</v>
-      </c>
       <c r="V41">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AA41">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AB41">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AC41">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="AD41">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AE41">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF41">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AG41">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,80 +7155,80 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.78</v>
+        <v>2.8</v>
       </c>
       <c r="O42">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="P42">
-        <v>3.44</v>
+        <v>2.55</v>
       </c>
       <c r="Q42">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="R42">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="S42">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T42">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="U42">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="V42">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="W42">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="Z42">
-        <v>5.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA42">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="AB42">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AC42">
-        <v>2.2</v>
+        <v>3.68</v>
       </c>
       <c r="AD42">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AE42">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AF42">
+        <v>1.81</v>
+      </c>
+      <c r="AG42">
+        <v>1.86</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
         <v>1.44</v>
       </c>
-      <c r="AG42">
-        <v>2.5</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.25</v>
-      </c>
       <c r="AK42">
-        <v>1.85</v>
+        <v>1.34</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7276,22 +7276,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,58 +7318,58 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.27</v>
+        <v>1.78</v>
       </c>
       <c r="O43">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P43">
-        <v>2.5</v>
+        <v>3.44</v>
       </c>
       <c r="Q43">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="R43">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="S43">
         <v>1.25</v>
       </c>
       <c r="T43">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U43">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V43">
         <v>1.62</v>
       </c>
       <c r="W43">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z43">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA43">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB43">
         <v>2.35</v>
       </c>
       <c r="AC43">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AD43">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE43">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF43">
         <v>1.44</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Castro Daire</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Estrela Calheta</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="O44">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P44">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-10-04 10:00:00</t>
+          <t>2026-10-04 09:30:00</t>
         </is>
       </c>
     </row>
@@ -7602,22 +7602,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Castro Daire</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Estrela Calheta</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.18</v>
+        <v>2.13</v>
       </c>
       <c r="O45">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="P45">
-        <v>10</v>
+        <v>3.55</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="Q47">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S47">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T47">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U47">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="V47">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W47">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X47">
         <v>0</v>
       </c>
       <c r="Y47">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z47">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="AA47">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB47">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AC47">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AD47">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE47">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF47">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG47">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK47">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="O48">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="P48">
-        <v>11.2</v>
+        <v>4.93</v>
       </c>
       <c r="Q48">
-        <v>1.4</v>
+        <v>2.08</v>
       </c>
       <c r="R48">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="S48">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="T48">
-        <v>4.34</v>
+        <v>3.16</v>
       </c>
       <c r="U48">
-        <v>1.88</v>
+        <v>2.42</v>
       </c>
       <c r="V48">
-        <v>1.87</v>
+        <v>1.51</v>
       </c>
       <c r="W48">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="X48">
         <v>0</v>
       </c>
       <c r="Y48">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>7.29</v>
+        <v>3.99</v>
       </c>
       <c r="AA48">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AB48">
-        <v>3.25</v>
+        <v>2.11</v>
       </c>
       <c r="AC48">
-        <v>1.81</v>
+        <v>2.64</v>
       </c>
       <c r="AD48">
-        <v>1.97</v>
+        <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AF48">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="AG48">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK48">
-        <v>6</v>
+        <v>2.38</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8254,22 +8254,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.4</v>
+        <v>1.18</v>
       </c>
       <c r="O49">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="P49">
-        <v>2.51</v>
+        <v>11.2</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X49">
         <v>0</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>7.29</v>
       </c>
       <c r="AA49">
-        <v>1.82</v>
+        <v>1.33</v>
       </c>
       <c r="AB49">
-        <v>1.93</v>
+        <v>3.25</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Charlton Athletic Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8498,10 +8498,10 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AB50">
-        <v>2.62</v>
+        <v>1.93</v>
       </c>
       <c r="AC50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Birmingham City Women</t>
+          <t>Charlton Athletic Ladies</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S51">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T51">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U51">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V51">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W51">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y51">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z51">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA51">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AB51">
-        <v>1.98</v>
+        <v>2.62</v>
       </c>
       <c r="AC51">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD51">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE51">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF51">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG51">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK51">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Crystal Palace Ladies</t>
+          <t>Birmingham City Women</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,61 +8785,61 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="O52">
-        <v>4.56</v>
+        <v>3.96</v>
       </c>
       <c r="P52">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q52">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R52">
-        <v>2.26</v>
+        <v>2.37</v>
       </c>
       <c r="S52">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
         <v>3.25</v>
       </c>
       <c r="U52">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="V52">
         <v>1.51</v>
       </c>
       <c r="W52">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
         <v>1.18</v>
       </c>
       <c r="Z52">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AA52">
+        <v>1.7</v>
+      </c>
+      <c r="AB52">
+        <v>1.98</v>
+      </c>
+      <c r="AC52">
+        <v>2.66</v>
+      </c>
+      <c r="AD52">
+        <v>1.4</v>
+      </c>
+      <c r="AE52">
+        <v>1.09</v>
+      </c>
+      <c r="AF52">
         <v>1.65</v>
-      </c>
-      <c r="AB52">
-        <v>2.06</v>
-      </c>
-      <c r="AC52">
-        <v>2.62</v>
-      </c>
-      <c r="AD52">
-        <v>1.46</v>
-      </c>
-      <c r="AE52">
-        <v>1.13</v>
-      </c>
-      <c r="AF52">
-        <v>1.62</v>
       </c>
       <c r="AG52">
         <v>2.15</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK52">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Crystal Palace Ladies</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>13.66</v>
+        <v>1.57</v>
       </c>
       <c r="O53">
-        <v>8.76</v>
+        <v>4.56</v>
       </c>
       <c r="P53">
+        <v>5.2</v>
+      </c>
+      <c r="Q53">
+        <v>2.3</v>
+      </c>
+      <c r="R53">
+        <v>2.26</v>
+      </c>
+      <c r="S53">
+        <v>1.28</v>
+      </c>
+      <c r="T53">
+        <v>3.25</v>
+      </c>
+      <c r="U53">
+        <v>2.4</v>
+      </c>
+      <c r="V53">
+        <v>1.51</v>
+      </c>
+      <c r="W53">
         <v>1.1</v>
-      </c>
-      <c r="Q53">
-        <v>10.5</v>
-      </c>
-      <c r="R53">
-        <v>3</v>
-      </c>
-      <c r="S53">
-        <v>1.19</v>
-      </c>
-      <c r="T53">
-        <v>4.16</v>
-      </c>
-      <c r="U53">
-        <v>1.93</v>
-      </c>
-      <c r="V53">
-        <v>1.74</v>
-      </c>
-      <c r="W53">
-        <v>1.21</v>
       </c>
       <c r="X53">
         <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="Z53">
-        <v>6.48</v>
+        <v>4.33</v>
       </c>
       <c r="AA53">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AB53">
-        <v>3</v>
+        <v>2.06</v>
       </c>
       <c r="AC53">
-        <v>1.89</v>
+        <v>2.62</v>
       </c>
       <c r="AD53">
-        <v>1.81</v>
+        <v>1.46</v>
       </c>
       <c r="AE53">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AF53">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AG53">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AK53">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9064,12 +9064,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.35</v>
+        <v>13.66</v>
       </c>
       <c r="O54">
-        <v>3.25</v>
+        <v>8.76</v>
       </c>
       <c r="P54">
-        <v>2.63</v>
+        <v>1.1</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>6.48</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-10-04 11:00:00</t>
+          <t>2026-10-04 10:00:00</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>8.09</v>
+        <v>2.35</v>
       </c>
       <c r="O55">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="P55">
-        <v>1.22</v>
+        <v>2.63</v>
       </c>
       <c r="Q55">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="R55">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S55">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T55">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="U55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V55">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W55">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X55">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y55">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z55">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA55">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AB55">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC55">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AD55">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE55">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF55">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG55">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AK55">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,80 +9437,80 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.87</v>
+        <v>8.09</v>
       </c>
       <c r="O56">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="P56">
-        <v>3.7</v>
+        <v>1.22</v>
       </c>
       <c r="Q56">
-        <v>2.51</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R56">
-        <v>2.3</v>
+        <v>3.06</v>
       </c>
       <c r="S56">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="T56">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="U56">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="V56">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="W56">
+        <v>1.17</v>
+      </c>
+      <c r="X56">
+        <v>1.01</v>
+      </c>
+      <c r="Y56">
         <v>1.06</v>
       </c>
-      <c r="X56">
+      <c r="Z56">
+        <v>6.05</v>
+      </c>
+      <c r="AA56">
+        <v>1.39</v>
+      </c>
+      <c r="AB56">
+        <v>2.75</v>
+      </c>
+      <c r="AC56">
+        <v>2.02</v>
+      </c>
+      <c r="AD56">
+        <v>1.79</v>
+      </c>
+      <c r="AE56">
+        <v>1.32</v>
+      </c>
+      <c r="AF56">
+        <v>1.81</v>
+      </c>
+      <c r="AG56">
+        <v>1.85</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ56">
+        <v>4.5</v>
+      </c>
+      <c r="AK56">
         <v>1.02</v>
-      </c>
-      <c r="Y56">
-        <v>1.26</v>
-      </c>
-      <c r="Z56">
-        <v>3.52</v>
-      </c>
-      <c r="AA56">
-        <v>1.86</v>
-      </c>
-      <c r="AB56">
-        <v>1.94</v>
-      </c>
-      <c r="AC56">
-        <v>2.98</v>
-      </c>
-      <c r="AD56">
-        <v>1.36</v>
-      </c>
-      <c r="AE56">
-        <v>1.09</v>
-      </c>
-      <c r="AF56">
-        <v>1.79</v>
-      </c>
-      <c r="AG56">
-        <v>1.92</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ56">
-        <v>1.26</v>
-      </c>
-      <c r="AK56">
-        <v>1.93</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.56</v>
+        <v>1.87</v>
       </c>
       <c r="O57">
-        <v>4.38</v>
+        <v>3.4</v>
       </c>
       <c r="P57">
-        <v>5.82</v>
+        <v>3.7</v>
       </c>
       <c r="Q57">
-        <v>1.96</v>
+        <v>2.51</v>
       </c>
       <c r="R57">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S57">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T57">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U57">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="V57">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W57">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z57">
-        <v>4.05</v>
+        <v>3.52</v>
       </c>
       <c r="AA57">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AB57">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="AC57">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="AD57">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE57">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AF57">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG57">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AK57">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-10-04 11:15:00</t>
+          <t>2026-10-04 11:00:00</t>
         </is>
       </c>
     </row>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.5</v>
+        <v>1.56</v>
       </c>
       <c r="O58">
-        <v>3</v>
+        <v>4.38</v>
       </c>
       <c r="P58">
-        <v>2.5</v>
+        <v>5.82</v>
       </c>
       <c r="Q58">
-        <v>3.4</v>
+        <v>1.96</v>
       </c>
       <c r="R58">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="S58">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T58">
-        <v>2.61</v>
+        <v>3.2</v>
       </c>
       <c r="U58">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="V58">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="W58">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y58">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="Z58">
-        <v>3.03</v>
+        <v>4.05</v>
       </c>
       <c r="AA58">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="AB58">
-        <v>1.65</v>
+        <v>2.09</v>
       </c>
       <c r="AC58">
-        <v>4</v>
+        <v>2.97</v>
       </c>
       <c r="AD58">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AE58">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AF58">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG58">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AK58">
-        <v>1.4</v>
+        <v>2.28</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-10-04 11:30:00</t>
+          <t>2026-10-04 11:15:00</t>
         </is>
       </c>
     </row>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.76</v>
+        <v>2.5</v>
       </c>
       <c r="O59">
-        <v>3.82</v>
+        <v>3</v>
       </c>
       <c r="P59">
-        <v>4.53</v>
+        <v>2.5</v>
       </c>
       <c r="Q59">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="R59">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="S59">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T59">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="U59">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="V59">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="W59">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X59">
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z59">
-        <v>3.62</v>
+        <v>3.03</v>
       </c>
       <c r="AA59">
-        <v>1.79</v>
+        <v>2.18</v>
       </c>
       <c r="AB59">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AC59">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="AD59">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AE59">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF59">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG59">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK59">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Santa Clara II</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Real SC</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
+        <v>1.76</v>
+      </c>
+      <c r="O60">
+        <v>3.82</v>
+      </c>
+      <c r="P60">
+        <v>4.53</v>
+      </c>
+      <c r="Q60">
         <v>2.37</v>
       </c>
-      <c r="O60">
-        <v>3.42</v>
-      </c>
-      <c r="P60">
-        <v>2.81</v>
-      </c>
-      <c r="Q60">
-        <v>0</v>
-      </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Arosa</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X75">
         <v>0</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Arosa</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,80 +12697,80 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="O76">
-        <v>3.68</v>
+        <v>2.7</v>
       </c>
       <c r="P76">
+        <v>2.65</v>
+      </c>
+      <c r="Q76">
+        <v>3.4</v>
+      </c>
+      <c r="R76">
+        <v>1.95</v>
+      </c>
+      <c r="S76">
+        <v>1.5</v>
+      </c>
+      <c r="T76">
         <v>2.45</v>
       </c>
-      <c r="Q76">
-        <v>2.7</v>
-      </c>
-      <c r="R76">
-        <v>2.1</v>
-      </c>
-      <c r="S76">
-        <v>1.36</v>
-      </c>
-      <c r="T76">
-        <v>2.9</v>
-      </c>
       <c r="U76">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="V76">
+        <v>1.25</v>
+      </c>
+      <c r="W76">
+        <v>1.05</v>
+      </c>
+      <c r="X76">
+        <v>1.05</v>
+      </c>
+      <c r="Y76">
+        <v>1.47</v>
+      </c>
+      <c r="Z76">
+        <v>2.45</v>
+      </c>
+      <c r="AA76">
+        <v>2.48</v>
+      </c>
+      <c r="AB76">
+        <v>1.5</v>
+      </c>
+      <c r="AC76">
+        <v>4.88</v>
+      </c>
+      <c r="AD76">
+        <v>1.13</v>
+      </c>
+      <c r="AE76">
+        <v>0</v>
+      </c>
+      <c r="AF76">
+        <v>2.05</v>
+      </c>
+      <c r="AG76">
+        <v>1.7</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
         <v>1.4</v>
       </c>
-      <c r="W76">
-        <v>1.08</v>
-      </c>
-      <c r="X76">
-        <v>0</v>
-      </c>
-      <c r="Y76">
-        <v>1.28</v>
-      </c>
-      <c r="Z76">
-        <v>3.41</v>
-      </c>
-      <c r="AA76">
-        <v>2</v>
-      </c>
-      <c r="AB76">
-        <v>1.75</v>
-      </c>
-      <c r="AC76">
-        <v>3.2</v>
-      </c>
-      <c r="AD76">
-        <v>1.31</v>
-      </c>
-      <c r="AE76">
-        <v>1.07</v>
-      </c>
-      <c r="AF76">
-        <v>1.85</v>
-      </c>
-      <c r="AG76">
-        <v>1.85</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ76">
-        <v>1.22</v>
-      </c>
       <c r="AK76">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.69</v>
+        <v>2.09</v>
       </c>
       <c r="O77">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="P77">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="Q77">
-        <v>3.4</v>
+        <v>2.82</v>
       </c>
       <c r="R77">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="S77">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="T77">
-        <v>2.45</v>
+        <v>2.64</v>
       </c>
       <c r="U77">
-        <v>3.4</v>
+        <v>3.01</v>
       </c>
       <c r="V77">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="W77">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X77">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="Z77">
-        <v>2.45</v>
+        <v>3.08</v>
       </c>
       <c r="AA77">
-        <v>2.48</v>
+        <v>2.03</v>
       </c>
       <c r="AB77">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AC77">
-        <v>4.88</v>
+        <v>3.47</v>
       </c>
       <c r="AD77">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF77">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AG77">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK77">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="O78">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P78">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q78">
-        <v>2.82</v>
+        <v>2.55</v>
       </c>
       <c r="R78">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S78">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T78">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="U78">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="V78">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W78">
+        <v>1.06</v>
+      </c>
+      <c r="X78">
         <v>1.02</v>
       </c>
-      <c r="X78">
-        <v>1.01</v>
-      </c>
       <c r="Y78">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Z78">
-        <v>3.08</v>
+        <v>2.94</v>
       </c>
       <c r="AA78">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AB78">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC78">
-        <v>3.47</v>
+        <v>3.9</v>
       </c>
       <c r="AD78">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE78">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF78">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AG78">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK78">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13139,27 +13139,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.98</v>
+        <v>1.55</v>
       </c>
       <c r="O79">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="P79">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="Q79">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R79">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S79">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T79">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U79">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V79">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W79">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X79">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y79">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z79">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AA79">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB79">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AC79">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD79">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE79">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF79">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG79">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK79">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>2026-10-04 12:00:00</t>
+          <t>2026-10-04 12:30:00</t>
         </is>
       </c>
     </row>
@@ -13307,22 +13307,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.55</v>
+        <v>2.53</v>
       </c>
       <c r="O80">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="P80">
-        <v>4.4</v>
+        <v>2.66</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA80">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AB80">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,31 +13512,31 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="O81">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="P81">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="Q81">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R81">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="S81">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T81">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="U81">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V81">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W81">
         <v>1.08</v>
@@ -13545,31 +13545,31 @@
         <v>1.03</v>
       </c>
       <c r="Y81">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="Z81">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="AA81">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AB81">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AC81">
-        <v>3.17</v>
+        <v>2.78</v>
       </c>
       <c r="AD81">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AE81">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF81">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG81">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK81">
         <v>1.44</v>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="O82">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="P82">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q82">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R82">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="S82">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="T82">
-        <v>3.08</v>
+        <v>2.45</v>
       </c>
       <c r="U82">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="V82">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="W82">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X82">
+        <v>1.05</v>
+      </c>
+      <c r="Y82">
+        <v>1.41</v>
+      </c>
+      <c r="Z82">
+        <v>2.56</v>
+      </c>
+      <c r="AA82">
+        <v>2.47</v>
+      </c>
+      <c r="AB82">
+        <v>1.53</v>
+      </c>
+      <c r="AC82">
+        <v>4.5</v>
+      </c>
+      <c r="AD82">
+        <v>1.16</v>
+      </c>
+      <c r="AE82">
         <v>1.03</v>
       </c>
-      <c r="Y82">
-        <v>1.18</v>
-      </c>
-      <c r="Z82">
-        <v>3.78</v>
-      </c>
-      <c r="AA82">
-        <v>1.78</v>
-      </c>
-      <c r="AB82">
-        <v>1.98</v>
-      </c>
-      <c r="AC82">
-        <v>2.78</v>
-      </c>
-      <c r="AD82">
-        <v>1.41</v>
-      </c>
-      <c r="AE82">
-        <v>1.14</v>
-      </c>
       <c r="AF82">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AG82">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK82">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.7</v>
+        <v>1.83</v>
       </c>
       <c r="O83">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="P83">
+        <v>4.2</v>
+      </c>
+      <c r="Q83">
         <v>2.5</v>
       </c>
-      <c r="Q83">
-        <v>3.5</v>
-      </c>
       <c r="R83">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="S83">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T83">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="U83">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="V83">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="W83">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X83">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="Z83">
-        <v>2.56</v>
+        <v>2.97</v>
       </c>
       <c r="AA83">
-        <v>2.47</v>
+        <v>2.03</v>
       </c>
       <c r="AB83">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AC83">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD83">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE83">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF83">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG83">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK83">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-10-04 12:30:00</t>
+          <t>2026-10-04 13:00:00</t>
         </is>
       </c>
     </row>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,65 +14001,65 @@
         </is>
       </c>
       <c r="N84">
+        <v>4.3</v>
+      </c>
+      <c r="O84">
+        <v>3.74</v>
+      </c>
+      <c r="P84">
         <v>1.83</v>
       </c>
-      <c r="O84">
+      <c r="Q84">
+        <v>4.68</v>
+      </c>
+      <c r="R84">
+        <v>1.95</v>
+      </c>
+      <c r="S84">
+        <v>1.3</v>
+      </c>
+      <c r="T84">
+        <v>2.3</v>
+      </c>
+      <c r="U84">
+        <v>2.87</v>
+      </c>
+      <c r="V84">
+        <v>1.39</v>
+      </c>
+      <c r="W84">
+        <v>1.03</v>
+      </c>
+      <c r="X84">
+        <v>0</v>
+      </c>
+      <c r="Y84">
+        <v>1.31</v>
+      </c>
+      <c r="Z84">
+        <v>3.2</v>
+      </c>
+      <c r="AA84">
+        <v>1.74</v>
+      </c>
+      <c r="AB84">
+        <v>1.6</v>
+      </c>
+      <c r="AC84">
         <v>3.3</v>
       </c>
-      <c r="P84">
-        <v>4.2</v>
-      </c>
-      <c r="Q84">
-        <v>2.5</v>
-      </c>
-      <c r="R84">
-        <v>2.1</v>
-      </c>
-      <c r="S84">
-        <v>1.4</v>
-      </c>
-      <c r="T84">
-        <v>2.75</v>
-      </c>
-      <c r="U84">
-        <v>2.9</v>
-      </c>
-      <c r="V84">
-        <v>1.36</v>
-      </c>
-      <c r="W84">
-        <v>1.07</v>
-      </c>
-      <c r="X84">
-        <v>1.01</v>
-      </c>
-      <c r="Y84">
+      <c r="AD84">
         <v>1.3</v>
       </c>
-      <c r="Z84">
-        <v>2.97</v>
-      </c>
-      <c r="AA84">
-        <v>2.03</v>
-      </c>
-      <c r="AB84">
+      <c r="AE84">
+        <v>1.06</v>
+      </c>
+      <c r="AF84">
+        <v>1.65</v>
+      </c>
+      <c r="AG84">
         <v>1.7</v>
       </c>
-      <c r="AC84">
-        <v>3.6</v>
-      </c>
-      <c r="AD84">
-        <v>1.21</v>
-      </c>
-      <c r="AE84">
-        <v>1.04</v>
-      </c>
-      <c r="AF84">
-        <v>1.85</v>
-      </c>
-      <c r="AG84">
-        <v>1.83</v>
-      </c>
       <c r="AH84" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK84">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Cieza</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>4.3</v>
+        <v>1.93</v>
       </c>
       <c r="O85">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="P85">
-        <v>1.83</v>
+        <v>3.5</v>
       </c>
       <c r="Q85">
-        <v>4.68</v>
+        <v>2.54</v>
       </c>
       <c r="R85">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="S85">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T85">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="U85">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="V85">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W85">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z85">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AA85">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AB85">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC85">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AD85">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE85">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF85">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG85">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK85">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cieza</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="O86">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P86">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q86">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="R86">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S86">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T86">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U86">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V86">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W86">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y86">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z86">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA86">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB86">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC86">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD86">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE86">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF86">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG86">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK86">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="O87">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="P87">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="O88">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="P88">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="Q88">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="R88">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="S88">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="T88">
-        <v>3.32</v>
+        <v>4.5</v>
       </c>
       <c r="U88">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="V88">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="W88">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="X88">
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="Z88">
-        <v>4.38</v>
+        <v>6.25</v>
       </c>
       <c r="AA88">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AB88">
-        <v>2.25</v>
+        <v>2.87</v>
       </c>
       <c r="AC88">
-        <v>2.47</v>
+        <v>1.86</v>
       </c>
       <c r="AD88">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="AE88">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AF88">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG88">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AK88">
-        <v>2.75</v>
+        <v>3.57</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-10-04 13:00:00</t>
+          <t>2026-10-04 13:30:00</t>
         </is>
       </c>
     </row>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,80 +14816,80 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.22</v>
+        <v>2.19</v>
       </c>
       <c r="O89">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="P89">
-        <v>10</v>
+        <v>3.36</v>
       </c>
       <c r="Q89">
-        <v>1.54</v>
+        <v>2.56</v>
       </c>
       <c r="R89">
-        <v>2.78</v>
+        <v>2.1</v>
       </c>
       <c r="S89">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="T89">
-        <v>4.5</v>
+        <v>2.59</v>
       </c>
       <c r="U89">
-        <v>1.95</v>
+        <v>2.74</v>
       </c>
       <c r="V89">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="W89">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="X89">
         <v>1.01</v>
       </c>
       <c r="Y89">
+        <v>1.26</v>
+      </c>
+      <c r="Z89">
+        <v>3.35</v>
+      </c>
+      <c r="AA89">
+        <v>2.06</v>
+      </c>
+      <c r="AB89">
+        <v>1.79</v>
+      </c>
+      <c r="AC89">
+        <v>3.14</v>
+      </c>
+      <c r="AD89">
+        <v>1.27</v>
+      </c>
+      <c r="AE89">
         <v>1.06</v>
       </c>
-      <c r="Z89">
-        <v>6.25</v>
-      </c>
-      <c r="AA89">
-        <v>1.3</v>
-      </c>
-      <c r="AB89">
-        <v>2.87</v>
-      </c>
-      <c r="AC89">
-        <v>1.86</v>
-      </c>
-      <c r="AD89">
-        <v>1.88</v>
-      </c>
-      <c r="AE89">
+      <c r="AF89">
+        <v>1.75</v>
+      </c>
+      <c r="AG89">
+        <v>1.98</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ89">
         <v>1.35</v>
       </c>
-      <c r="AF89">
-        <v>1.7</v>
-      </c>
-      <c r="AG89">
-        <v>2.03</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ89">
-        <v>1.09</v>
-      </c>
       <c r="AK89">
-        <v>3.57</v>
+        <v>1.65</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Atlético Central</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="O90">
-        <v>3.2</v>
+        <v>3.49</v>
       </c>
       <c r="P90">
-        <v>3.36</v>
+        <v>3.16</v>
       </c>
       <c r="Q90">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R90">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S90">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T90">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U90">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="V90">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W90">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y90">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z90">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA90">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AB90">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AC90">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD90">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE90">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF90">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG90">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK90">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15095,12 +15095,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Atlético Central</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="O91">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="P91">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15181,10 +15181,10 @@
         <v>0</v>
       </c>
       <c r="AA91">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB91">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AC91">
         <v>0</v>
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-10-04 13:30:00</t>
+          <t>2026-10-04 13:45:00</t>
         </is>
       </c>
     </row>
@@ -15258,27 +15258,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
+        <v>1.77</v>
+      </c>
+      <c r="O92">
+        <v>3.5</v>
+      </c>
+      <c r="P92">
+        <v>3.88</v>
+      </c>
+      <c r="Q92">
+        <v>2.15</v>
+      </c>
+      <c r="R92">
         <v>2.1</v>
       </c>
-      <c r="O92">
-        <v>3.45</v>
-      </c>
-      <c r="P92">
+      <c r="S92">
+        <v>1.3</v>
+      </c>
+      <c r="T92">
         <v>3.2</v>
       </c>
-      <c r="Q92">
-        <v>0</v>
-      </c>
-      <c r="R92">
-        <v>0</v>
-      </c>
-      <c r="S92">
-        <v>0</v>
-      </c>
-      <c r="T92">
-        <v>0</v>
-      </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA92">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB92">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE92">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK92">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-10-04 13:45:00</t>
+          <t>2026-10-04 14:00:00</t>
         </is>
       </c>
     </row>
@@ -15426,22 +15426,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Ciudad de Lucena</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="O93">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P93">
-        <v>3.88</v>
+        <v>3.7</v>
       </c>
       <c r="Q93">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="R93">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="S93">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T93">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="U93">
-        <v>2.06</v>
+        <v>2.88</v>
       </c>
       <c r="V93">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W93">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y93">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z93">
+        <v>3.12</v>
+      </c>
+      <c r="AA93">
+        <v>1.83</v>
+      </c>
+      <c r="AB93">
+        <v>1.53</v>
+      </c>
+      <c r="AC93">
         <v>3.68</v>
       </c>
-      <c r="AA93">
-        <v>1.75</v>
-      </c>
-      <c r="AB93">
-        <v>2.08</v>
-      </c>
-      <c r="AC93">
-        <v>2.38</v>
-      </c>
       <c r="AD93">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE93">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF93">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AG93">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AK93">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ciudad de Lucena</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>1.44</v>
+      </c>
+      <c r="R94">
         <v>3.25</v>
       </c>
-      <c r="P94">
-        <v>3.7</v>
-      </c>
-      <c r="Q94">
-        <v>2.64</v>
-      </c>
-      <c r="R94">
-        <v>2.19</v>
-      </c>
       <c r="S94">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="T94">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="U94">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="V94">
+        <v>1.87</v>
+      </c>
+      <c r="W94">
+        <v>1.25</v>
+      </c>
+      <c r="X94">
+        <v>0</v>
+      </c>
+      <c r="Y94">
+        <v>1.03</v>
+      </c>
+      <c r="Z94">
+        <v>7.95</v>
+      </c>
+      <c r="AA94">
+        <v>1.3</v>
+      </c>
+      <c r="AB94">
+        <v>3.28</v>
+      </c>
+      <c r="AC94">
+        <v>1.74</v>
+      </c>
+      <c r="AD94">
+        <v>2.05</v>
+      </c>
+      <c r="AE94">
         <v>1.38</v>
       </c>
-      <c r="W94">
-        <v>1.03</v>
-      </c>
-      <c r="X94">
-        <v>0</v>
-      </c>
-      <c r="Y94">
-        <v>1.33</v>
-      </c>
-      <c r="Z94">
-        <v>3.12</v>
-      </c>
-      <c r="AA94">
-        <v>1.83</v>
-      </c>
-      <c r="AB94">
-        <v>1.53</v>
-      </c>
-      <c r="AC94">
-        <v>3.68</v>
-      </c>
-      <c r="AD94">
-        <v>1.28</v>
-      </c>
-      <c r="AE94">
-        <v>1.05</v>
-      </c>
       <c r="AF94">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AG94">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AK94">
-        <v>1.78</v>
+        <v>5.5</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15803,55 +15803,55 @@
         <v>0</v>
       </c>
       <c r="Q95">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="R95">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S95">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T95">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="U95">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="V95">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W95">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z95">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="AA95">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB95">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AC95">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AD95">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE95">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF95">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG95">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK95">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -19706,10 +19706,10 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.35</v>
+        <v>2.11</v>
       </c>
       <c r="O119">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P119">
         <v>2.35</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -1101,26 +1101,26 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2", "90+4"]</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,39 +1264,39 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="O6">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="P6">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="Q6">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="R6">
         <v>2</v>
@@ -1320,22 +1320,22 @@
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z6">
         <v>2.62</v>
       </c>
       <c r="AA6">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AB6">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC6">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD6">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE6">
         <v>1.01</v>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "76"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1360,34 +1360,34 @@
         <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P9">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="Q9">
-        <v>2.63</v>
+        <v>3.06</v>
       </c>
       <c r="R9">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="S9">
         <v>1.4</v>
@@ -1797,10 +1797,10 @@
         <v>2.75</v>
       </c>
       <c r="U9">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
         <v>1.07</v>
@@ -1809,22 +1809,22 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z9">
-        <v>3.26</v>
+        <v>2.97</v>
       </c>
       <c r="AA9">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AB9">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC9">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="AD9">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE9">
         <v>1.06</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK9">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O12">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="P12">
         <v>2.6</v>
@@ -2280,13 +2280,13 @@
         <v>2.13</v>
       </c>
       <c r="S12">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="V12">
         <v>1.44</v>
@@ -2295,13 +2295,13 @@
         <v>1.07</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.99</v>
+        <v>3.89</v>
       </c>
       <c r="AA12">
         <v>1.73</v>
@@ -2310,19 +2310,19 @@
         <v>2</v>
       </c>
       <c r="AC12">
-        <v>2.96</v>
+        <v>3.03</v>
       </c>
       <c r="AD12">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG12">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="O23">
         <v>3.2</v>
       </c>
       <c r="P23">
-        <v>4.88</v>
+        <v>4.6</v>
       </c>
       <c r="Q23">
         <v>2.25</v>
@@ -4094,7 +4094,7 @@
         <v>1.41</v>
       </c>
       <c r="Z23">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AA23">
         <v>2.3</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
         <v>1.95</v>
@@ -4221,10 +4221,10 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="O24">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="P24">
         <v>3.6</v>
@@ -4251,7 +4251,7 @@
         <v>1.04</v>
       </c>
       <c r="X24">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y24">
         <v>1.47</v>
@@ -4263,13 +4263,13 @@
         <v>2.5</v>
       </c>
       <c r="AB24">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AC24">
-        <v>4.53</v>
+        <v>4.62</v>
       </c>
       <c r="AD24">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE24">
         <v>1.01</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="O25">
         <v>2.87</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>3.8</v>
+        <v>1.63</v>
       </c>
       <c r="O28">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>1.87</v>
+        <v>4.4</v>
       </c>
       <c r="Q28">
-        <v>4.8</v>
+        <v>2.39</v>
       </c>
       <c r="R28">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="S28">
         <v>1.4</v>
       </c>
       <c r="T28">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="U28">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="V28">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X28">
+        <v>1.01</v>
+      </c>
+      <c r="Y28">
+        <v>1.32</v>
+      </c>
+      <c r="Z28">
+        <v>3.04</v>
+      </c>
+      <c r="AA28">
+        <v>2.05</v>
+      </c>
+      <c r="AB28">
+        <v>1.74</v>
+      </c>
+      <c r="AC28">
+        <v>3.75</v>
+      </c>
+      <c r="AD28">
+        <v>1.22</v>
+      </c>
+      <c r="AE28">
         <v>1.05</v>
       </c>
-      <c r="Y28">
-        <v>1.41</v>
-      </c>
-      <c r="Z28">
-        <v>2.96</v>
-      </c>
-      <c r="AA28">
-        <v>2.21</v>
-      </c>
-      <c r="AB28">
-        <v>1.64</v>
-      </c>
-      <c r="AC28">
-        <v>3.94</v>
-      </c>
-      <c r="AD28">
-        <v>1.21</v>
-      </c>
-      <c r="AE28">
-        <v>1.04</v>
-      </c>
       <c r="AF28">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG28">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.15</v>
+        <v>1.87</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.63</v>
+        <v>3.8</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="P29">
-        <v>4.4</v>
+        <v>1.87</v>
       </c>
       <c r="Q29">
-        <v>2.39</v>
+        <v>4.8</v>
       </c>
       <c r="R29">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="S29">
         <v>1.4</v>
       </c>
       <c r="T29">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="U29">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="V29">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="Z29">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="AA29">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="AB29">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AC29">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="AD29">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE29">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG29">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="AK29">
-        <v>1.87</v>
+        <v>1.15</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -14164,25 +14164,25 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O85">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P85">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q85">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="R85">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="S85">
         <v>1.4</v>
       </c>
       <c r="T85">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U85">
         <v>2.9</v>
@@ -14200,7 +14200,7 @@
         <v>1.34</v>
       </c>
       <c r="Z85">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="AA85">
         <v>2.1</v>
@@ -14209,13 +14209,13 @@
         <v>1.67</v>
       </c>
       <c r="AC85">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AD85">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE85">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF85">
         <v>1.85</v>
@@ -14237,7 +14237,7 @@
         <v>1.25</v>
       </c>
       <c r="AK85">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -15326,10 +15326,10 @@
         <v>3.2</v>
       </c>
       <c r="U92">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V92">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W92">
         <v>1.06</v>
@@ -15362,7 +15362,7 @@
         <v>1.5</v>
       </c>
       <c r="AG92">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -18435,25 +18435,25 @@
         <v>1.01</v>
       </c>
       <c r="Y111">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z111">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA111">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AB111">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC111">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="AD111">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE111">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AF111">
         <v>1.62</v>
@@ -20077,7 +20077,7 @@
         <v>1.99</v>
       </c>
       <c r="AC121">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AD121">
         <v>1.42</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -1427,26 +1427,26 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "38"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42", "81"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,16 +1529,16 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ7">
         <v>0</v>
@@ -1590,26 +1590,26 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "16", "68"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["32", "43"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,26 +1753,26 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37", "41", "74"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,26 +1916,26 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -1948,13 +1948,13 @@
         <v>4.82</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="R10">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S10">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T10">
         <v>2.75</v>
@@ -1972,25 +1972,25 @@
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z10">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AA10">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AB10">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AC10">
-        <v>3.29</v>
+        <v>3.43</v>
       </c>
       <c r="AD10">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AE10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF10">
         <v>1.95</v>
@@ -2000,46 +2000,46 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "80"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["32"]</t>
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,42 +2079,42 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S11">
         <v>1.36</v>
@@ -2163,46 +2163,46 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "23", "77"]</t>
         </is>
       </c>
       <c r="AJ11">
         <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2257,11 +2257,11 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["82"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,26 +2405,26 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "45+2", "49", "80"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2568,30 +2568,30 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="O14">
         <v>3.2</v>
@@ -2630,10 +2630,10 @@
         <v>3.2</v>
       </c>
       <c r="AA14">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AB14">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC14">
         <v>3.24</v>
@@ -2645,53 +2645,53 @@
         <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG14">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1", "30", "56"]</t>
         </is>
       </c>
       <c r="AJ14">
         <v>1.29</v>
       </c>
       <c r="AK14">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15">
         <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2793,10 +2793,10 @@
         <v>2.7</v>
       </c>
       <c r="AA15">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AB15">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC15">
         <v>3.92</v>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "88", "90+1"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2935,7 +2935,7 @@
         <v>1.44</v>
       </c>
       <c r="T16">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U16">
         <v>3.3</v>
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,26 +3057,26 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15", "31", "90+2"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,26 +3220,26 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3255,7 +3255,7 @@
         <v>2.5</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S18">
         <v>1.36</v>
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["55", "78"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18"]</t>
         </is>
       </c>
       <c r="AJ18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3383,33 +3383,33 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
         <v>1.55</v>
       </c>
       <c r="O19">
-        <v>3.7</v>
+        <v>4.06</v>
       </c>
       <c r="P19">
         <v>5</v>
@@ -3445,7 +3445,7 @@
         <v>2.92</v>
       </c>
       <c r="AA19">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB19">
         <v>1.75</v>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "54", "70", "81"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -3485,28 +3485,28 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3546,26 +3546,26 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51", "82"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "42"]</t>
         </is>
       </c>
       <c r="AJ20">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -3721,14 +3721,14 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75", "90+3"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53"]</t>
         </is>
       </c>
       <c r="AJ21">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4035,10 +4035,10 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -4047,14 +4047,14 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["80", "86"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+2"]</t>
         </is>
       </c>
       <c r="AJ23">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,13 +4198,13 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -4213,11 +4213,11 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+5"]</t>
         </is>
       </c>
       <c r="AJ24">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -4376,11 +4376,11 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66"]</t>
         </is>
       </c>
       <c r="AJ25">
@@ -4463,28 +4463,28 @@
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4524,13 +4524,13 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
@@ -4608,14 +4608,14 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
+          <t>["44", "45+2"]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ26">
         <v>0</v>
       </c>
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -4706,17 +4706,17 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O27">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="P27">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["-1"]</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["-1"]</t>
         </is>
       </c>
       <c r="AJ27">
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4869,20 +4869,20 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.76</v>
       </c>
       <c r="P28">
-        <v>4.4</v>
+        <v>4.42</v>
       </c>
       <c r="Q28">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="R28">
         <v>2.17</v>
@@ -4891,13 +4891,13 @@
         <v>1.4</v>
       </c>
       <c r="T28">
+        <v>2.7</v>
+      </c>
+      <c r="U28">
         <v>2.88</v>
       </c>
-      <c r="U28">
-        <v>2.7</v>
-      </c>
       <c r="V28">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W28">
         <v>1.07</v>
@@ -4918,7 +4918,7 @@
         <v>1.74</v>
       </c>
       <c r="AC28">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AD28">
         <v>1.22</v>
@@ -4943,37 +4943,37 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AL28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5013,26 +5013,26 @@
         </is>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N29">
@@ -5072,13 +5072,13 @@
         <v>1.41</v>
       </c>
       <c r="Z29">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="AA29">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AB29">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AC29">
         <v>3.94</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "90+2"]</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73", "90+7"]</t>
         </is>
       </c>
       <c r="AJ29">
@@ -5115,28 +5115,28 @@
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP29">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
@@ -5176,26 +5176,26 @@
         </is>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N30">
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5260,12 +5260,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "45", "46", "58"]</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "63", "90+4"]</t>
         </is>
       </c>
       <c r="AJ30">
@@ -5278,28 +5278,28 @@
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP30">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
@@ -5339,10 +5339,10 @@
         </is>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5351,14 +5351,14 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N31">
@@ -5371,98 +5371,98 @@
         <v>0</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X31">
         <v>0</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53", "59"]</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["71"]</t>
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL31">
         <v>0</v>
       </c>
       <c r="AM31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP31">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ31">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AR31">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AS31">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT31">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
@@ -5505,23 +5505,23 @@
         <v>0</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I32">
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N32">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36", "38", "47"]</t>
         </is>
       </c>
       <c r="AJ32">
@@ -5604,28 +5604,28 @@
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN32">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ32">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR32">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS32">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="AT32">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
@@ -5665,26 +5665,26 @@
         </is>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33">
         <v>0</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N33">
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5749,14 +5749,14 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
+          <t>["16", "83", "90"]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ33">
         <v>0</v>
       </c>
@@ -5767,28 +5767,28 @@
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN33">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP33">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ33">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AR33">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="AS33">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT33">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
@@ -5828,13 +5828,13 @@
         </is>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
         <v>0</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N34">
@@ -5857,10 +5857,10 @@
         <v>3.1</v>
       </c>
       <c r="P34">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="Q34">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R34">
         <v>2.14</v>
@@ -5905,14 +5905,14 @@
         <v>1.03</v>
       </c>
       <c r="AF34">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG34">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
@@ -5930,28 +5930,28 @@
         <v>0</v>
       </c>
       <c r="AM34">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN34">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP34">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ34">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR34">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS34">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AT34">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
@@ -5991,48 +5991,48 @@
         </is>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35">
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N35">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="O35">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="P35">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="Q35">
         <v>3.14</v>
       </c>
       <c r="R35">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S35">
         <v>1.44</v>
       </c>
       <c r="T35">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="U35">
         <v>2.91</v>
@@ -6050,19 +6050,19 @@
         <v>1.38</v>
       </c>
       <c r="Z35">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA35">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AB35">
         <v>1.73</v>
       </c>
       <c r="AC35">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="AD35">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE35">
         <v>1.03</v>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["35", "45"]</t>
         </is>
       </c>
       <c r="AJ35">
@@ -6093,28 +6093,28 @@
         <v>0</v>
       </c>
       <c r="AM35">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN35">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ35">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AR35">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS35">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT35">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
@@ -6154,13 +6154,13 @@
         </is>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -6169,21 +6169,21 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N36">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O36">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P36">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="Q36">
         <v>3.16</v>
@@ -6198,13 +6198,13 @@
         <v>3</v>
       </c>
       <c r="U36">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="V36">
         <v>1.4</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
         <v>1</v>
@@ -6238,46 +6238,46 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "29"]</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63", "69", "90+3"]</t>
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK36">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL36">
         <v>0</v>
       </c>
       <c r="AM36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO36">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP36">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AQ36">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AR36">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS36">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT36">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
@@ -6317,26 +6317,26 @@
         </is>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37">
         <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37">
         <v>0</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N37">
@@ -6355,92 +6355,92 @@
         <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
-        <v>2.97</v>
+        <v>3.16</v>
       </c>
       <c r="U37">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="V37">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X37">
         <v>0</v>
       </c>
       <c r="Y37">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z37">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AA37">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AB37">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="AC37">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="AD37">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE37">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF37">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG37">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75", "90+3"]</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17"]</t>
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="AK37">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AL37">
         <v>0</v>
       </c>
       <c r="AM37">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN37">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP37">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR37">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS37">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT37">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -6499,65 +6499,65 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N38">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="O38">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="P38">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q38">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="R38">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="S38">
         <v>1.46</v>
       </c>
       <c r="T38">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="U38">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="V38">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W38">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X38">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y38">
         <v>1.37</v>
       </c>
       <c r="Z38">
-        <v>2.94</v>
+        <v>2.79</v>
       </c>
       <c r="AA38">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AB38">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AC38">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="AD38">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE38">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF38">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AG38">
         <v>1.75</v>
@@ -6573,37 +6573,37 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK38">
-        <v>1.78</v>
+        <v>1.41</v>
       </c>
       <c r="AL38">
         <v>0</v>
       </c>
       <c r="AM38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN38">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP38">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ38">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR38">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="AS38">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT38">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -6666,34 +6666,34 @@
         </is>
       </c>
       <c r="N39">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="O39">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P39">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q39">
-        <v>4.86</v>
+        <v>4.37</v>
       </c>
       <c r="R39">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="S39">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T39">
-        <v>2.93</v>
+        <v>2.86</v>
       </c>
       <c r="U39">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="V39">
         <v>1.4</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
         <v>1.03</v>
@@ -6702,28 +6702,28 @@
         <v>1.34</v>
       </c>
       <c r="Z39">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AA39">
         <v>1.84</v>
       </c>
       <c r="AB39">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AC39">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD39">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AE39">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF39">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AG39">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.19</v>
       </c>
       <c r="AK39">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6847,7 +6847,7 @@
         <v>1.4</v>
       </c>
       <c r="T40">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="U40">
         <v>3</v>
@@ -6856,37 +6856,37 @@
         <v>1.3</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="Z40">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="AA40">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB40">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC40">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AD40">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF40">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG40">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK40">
         <v>1.65</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="O41">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P41">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q41">
         <v>2.88</v>
@@ -7013,7 +7013,7 @@
         <v>3</v>
       </c>
       <c r="U41">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V41">
         <v>1.44</v>
@@ -7028,16 +7028,16 @@
         <v>1.22</v>
       </c>
       <c r="Z41">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA41">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB41">
         <v>1.92</v>
       </c>
       <c r="AC41">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AD41">
         <v>1.41</v>
@@ -7049,7 +7049,7 @@
         <v>1.62</v>
       </c>
       <c r="AG41">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,19 +7155,19 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="O42">
         <v>3.1</v>
       </c>
       <c r="P42">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q42">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="R42">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S42">
         <v>1.4</v>
@@ -7182,25 +7182,25 @@
         <v>1.33</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X42">
         <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z42">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="AA42">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB42">
         <v>1.65</v>
       </c>
       <c r="AC42">
-        <v>3.68</v>
+        <v>3.71</v>
       </c>
       <c r="AD42">
         <v>1.21</v>
@@ -7209,10 +7209,10 @@
         <v>1.04</v>
       </c>
       <c r="AF42">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG42">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.44</v>
       </c>
       <c r="AK42">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7295,13 +7295,13 @@
         </is>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -7314,17 +7314,17 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N43">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="O43">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P43">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="Q43">
         <v>2.25</v>
@@ -7333,43 +7333,43 @@
         <v>2.33</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="U43">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V43">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W43">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z43">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="AA43">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB43">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AC43">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AD43">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AE43">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AF43">
         <v>1.44</v>
@@ -7379,16 +7379,16 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
+          <t>["19"]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK43">
         <v>1.85</v>
@@ -7397,28 +7397,28 @@
         <v>0</v>
       </c>
       <c r="AM43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN43">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO43">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ43">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR43">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS43">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT43">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -7470,45 +7470,45 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44">
         <v>0</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N44">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="O44">
         <v>3.6</v>
       </c>
       <c r="P44">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q44">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R44">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="S44">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T44">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U44">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V44">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W44">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X44">
         <v>1.02</v>
@@ -7517,71 +7517,71 @@
         <v>1.11</v>
       </c>
       <c r="Z44">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA44">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB44">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC44">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AD44">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AE44">
         <v>1.19</v>
       </c>
       <c r="AF44">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG44">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
+          <t>["53", "90+1"]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ44">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK44">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL44">
         <v>0</v>
       </c>
       <c r="AM44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN44">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO44">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
@@ -7846,10 +7846,10 @@
         <v>0</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC46">
         <v>0</v>
@@ -7979,25 +7979,25 @@
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X47">
         <v>0</v>
@@ -8009,25 +8009,25 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>0</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8142,22 +8142,22 @@
         <v>4.93</v>
       </c>
       <c r="Q48">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="R48">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="S48">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="T48">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="U48">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="V48">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="W48">
         <v>1.09</v>
@@ -8166,16 +8166,16 @@
         <v>0</v>
       </c>
       <c r="Y48">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z48">
-        <v>3.99</v>
+        <v>4.06</v>
       </c>
       <c r="AA48">
         <v>1.67</v>
       </c>
       <c r="AB48">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AC48">
         <v>2.64</v>
@@ -8187,10 +8187,10 @@
         <v>1.12</v>
       </c>
       <c r="AF48">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG48">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AK48">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,22 +8305,22 @@
         <v>11.2</v>
       </c>
       <c r="Q49">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="R49">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="S49">
         <v>1.17</v>
       </c>
       <c r="T49">
-        <v>4.34</v>
+        <v>4.38</v>
       </c>
       <c r="U49">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V49">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="W49">
         <v>1.24</v>
@@ -8332,7 +8332,7 @@
         <v>1.04</v>
       </c>
       <c r="Z49">
-        <v>7.29</v>
+        <v>7.36</v>
       </c>
       <c r="AA49">
         <v>1.33</v>
@@ -8341,19 +8341,19 @@
         <v>3.25</v>
       </c>
       <c r="AC49">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AD49">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AE49">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF49">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AG49">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>1.07</v>
       </c>
       <c r="AK49">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8468,55 +8468,55 @@
         <v>2.51</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA50">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AB50">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8631,55 +8631,55 @@
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="AA51">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB51">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8794,46 +8794,46 @@
         <v>3.75</v>
       </c>
       <c r="Q52">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R52">
-        <v>2.37</v>
+        <v>2.19</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T52">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U52">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="V52">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W52">
         <v>1.08</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z52">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="AA52">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB52">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AC52">
-        <v>2.66</v>
+        <v>2.71</v>
       </c>
       <c r="AD52">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE52">
         <v>1.09</v>
@@ -8842,7 +8842,7 @@
         <v>1.65</v>
       </c>
       <c r="AG52">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8960,19 +8960,19 @@
         <v>2.3</v>
       </c>
       <c r="R53">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S53">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T53">
         <v>3.25</v>
       </c>
       <c r="U53">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="V53">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W53">
         <v>1.1</v>
@@ -8984,28 +8984,28 @@
         <v>1.18</v>
       </c>
       <c r="Z53">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA53">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB53">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="AC53">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AD53">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE53">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF53">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG53">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK53">
         <v>1.95</v>
@@ -9132,10 +9132,10 @@
         <v>4.16</v>
       </c>
       <c r="U54">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V54">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W54">
         <v>1.21</v>
@@ -9144,25 +9144,25 @@
         <v>1.01</v>
       </c>
       <c r="Y54">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z54">
-        <v>6.48</v>
+        <v>7</v>
       </c>
       <c r="AA54">
+        <v>1.4</v>
+      </c>
+      <c r="AB54">
+        <v>2.75</v>
+      </c>
+      <c r="AC54">
+        <v>1.95</v>
+      </c>
+      <c r="AD54">
+        <v>1.75</v>
+      </c>
+      <c r="AE54">
         <v>1.36</v>
-      </c>
-      <c r="AB54">
-        <v>3</v>
-      </c>
-      <c r="AC54">
-        <v>1.89</v>
-      </c>
-      <c r="AD54">
-        <v>1.81</v>
-      </c>
-      <c r="AE54">
-        <v>1.3</v>
       </c>
       <c r="AF54">
         <v>1.93</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="O57">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P57">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q57">
-        <v>2.51</v>
+        <v>2.42</v>
       </c>
       <c r="R57">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S57">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T57">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U57">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="V57">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="W57">
+        <v>1.07</v>
+      </c>
+      <c r="X57">
+        <v>1.03</v>
+      </c>
+      <c r="Y57">
+        <v>1.27</v>
+      </c>
+      <c r="Z57">
+        <v>3.24</v>
+      </c>
+      <c r="AA57">
+        <v>1.9</v>
+      </c>
+      <c r="AB57">
+        <v>1.77</v>
+      </c>
+      <c r="AC57">
+        <v>3.08</v>
+      </c>
+      <c r="AD57">
+        <v>1.28</v>
+      </c>
+      <c r="AE57">
         <v>1.06</v>
       </c>
-      <c r="X57">
-        <v>1.02</v>
-      </c>
-      <c r="Y57">
-        <v>1.26</v>
-      </c>
-      <c r="Z57">
-        <v>3.52</v>
-      </c>
-      <c r="AA57">
-        <v>1.86</v>
-      </c>
-      <c r="AB57">
-        <v>1.94</v>
-      </c>
-      <c r="AC57">
-        <v>2.98</v>
-      </c>
-      <c r="AD57">
-        <v>1.36</v>
-      </c>
-      <c r="AE57">
-        <v>1.09</v>
-      </c>
       <c r="AF57">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG57">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AK57">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9778,43 +9778,43 @@
         <v>2.22</v>
       </c>
       <c r="S58">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T58">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U58">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="V58">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W58">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y58">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z58">
-        <v>4.05</v>
+        <v>3.61</v>
       </c>
       <c r="AA58">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB58">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AC58">
-        <v>2.97</v>
+        <v>3.37</v>
       </c>
       <c r="AD58">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AE58">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF58">
         <v>1.8</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="O59">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P59">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q59">
         <v>3.4</v>
@@ -9941,7 +9941,7 @@
         <v>2.05</v>
       </c>
       <c r="S59">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T59">
         <v>2.61</v>
@@ -9950,10 +9950,10 @@
         <v>2.9</v>
       </c>
       <c r="V59">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W59">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X59">
         <v>1.01</v>
@@ -9965,13 +9965,13 @@
         <v>3.03</v>
       </c>
       <c r="AA59">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AB59">
         <v>1.65</v>
       </c>
       <c r="AC59">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD59">
         <v>1.2</v>
@@ -9980,11 +9980,11 @@
         <v>1.02</v>
       </c>
       <c r="AF59">
+        <v>1.83</v>
+      </c>
+      <c r="AG59">
         <v>1.85</v>
       </c>
-      <c r="AG59">
-        <v>1.8</v>
-      </c>
       <c r="AH59" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9996,7 +9996,7 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK59">
         <v>1.4</v>
@@ -10104,7 +10104,7 @@
         <v>2.32</v>
       </c>
       <c r="S60">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T60">
         <v>3</v>
@@ -10128,7 +10128,7 @@
         <v>3.62</v>
       </c>
       <c r="AA60">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB60">
         <v>2</v>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK60">
         <v>2</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="O66">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="P66">
-        <v>3.13</v>
+        <v>2.33</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X66">
         <v>0</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O72">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P72">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O73">
         <v>3.2</v>
       </c>
       <c r="P73">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12380,10 +12380,10 @@
         <v>2.06</v>
       </c>
       <c r="Q74">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="R74">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="S74">
         <v>1.3</v>
@@ -12407,13 +12407,13 @@
         <v>1.26</v>
       </c>
       <c r="Z74">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="AA74">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AB74">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC74">
         <v>3.14</v>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK74">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>SD Compostela</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="O77">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P77">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q77">
-        <v>2.82</v>
+        <v>2.55</v>
       </c>
       <c r="R77">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S77">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T77">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="U77">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="V77">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W77">
+        <v>1.06</v>
+      </c>
+      <c r="X77">
         <v>1.02</v>
       </c>
-      <c r="X77">
-        <v>1.01</v>
-      </c>
       <c r="Y77">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="Z77">
-        <v>3.08</v>
+        <v>2.94</v>
       </c>
       <c r="AA77">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AB77">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC77">
-        <v>3.47</v>
+        <v>3.9</v>
       </c>
       <c r="AD77">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE77">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF77">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AG77">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK77">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SD Compostela</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="O78">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="P78">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q78">
-        <v>2.55</v>
+        <v>2.82</v>
       </c>
       <c r="R78">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S78">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T78">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="U78">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="V78">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W78">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="Z78">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
       <c r="AA78">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AB78">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC78">
-        <v>3.9</v>
+        <v>3.47</v>
       </c>
       <c r="AD78">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AE78">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF78">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AG78">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK78">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13358,10 +13358,10 @@
         <v>2.66</v>
       </c>
       <c r="Q80">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="R80">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="S80">
         <v>1.33</v>
@@ -13388,16 +13388,16 @@
         <v>3.4</v>
       </c>
       <c r="AA80">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB80">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AC80">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="AD80">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE80">
         <v>1.06</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK80">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13521,55 +13521,55 @@
         <v>2.44</v>
       </c>
       <c r="Q81">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R81">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="S81">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="T81">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U81">
         <v>2.5</v>
       </c>
       <c r="V81">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="W81">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X81">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z81">
-        <v>3.78</v>
+        <v>4.33</v>
       </c>
       <c r="AA81">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AB81">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC81">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AD81">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AE81">
         <v>1.14</v>
       </c>
       <c r="AF81">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG81">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AK81">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,25 +13675,25 @@
         </is>
       </c>
       <c r="N82">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="O82">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="P82">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q82">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R82">
         <v>1.91</v>
       </c>
       <c r="S82">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T82">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U82">
         <v>3.3</v>
@@ -13705,7 +13705,7 @@
         <v>1.05</v>
       </c>
       <c r="X82">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y82">
         <v>1.41</v>
@@ -13714,7 +13714,7 @@
         <v>2.56</v>
       </c>
       <c r="AA82">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="AB82">
         <v>1.53</v>
@@ -13726,10 +13726,10 @@
         <v>1.16</v>
       </c>
       <c r="AE82">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF82">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG82">
         <v>1.73</v>
@@ -13748,7 +13748,7 @@
         <v>1.3</v>
       </c>
       <c r="AK82">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14167,16 +14167,16 @@
         <v>1.95</v>
       </c>
       <c r="O85">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P85">
         <v>3.85</v>
       </c>
       <c r="Q85">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="R85">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="S85">
         <v>1.4</v>
@@ -14200,7 +14200,7 @@
         <v>1.34</v>
       </c>
       <c r="Z85">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="AA85">
         <v>2.1</v>
@@ -14209,7 +14209,7 @@
         <v>1.67</v>
       </c>
       <c r="AC85">
-        <v>3.68</v>
+        <v>3.62</v>
       </c>
       <c r="AD85">
         <v>1.25</v>
@@ -14221,7 +14221,7 @@
         <v>1.85</v>
       </c>
       <c r="AG85">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK85">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
+        <v>1.49</v>
+      </c>
+      <c r="O86">
+        <v>4.1</v>
+      </c>
+      <c r="P86">
+        <v>5.4</v>
+      </c>
+      <c r="Q86">
         <v>2.1</v>
       </c>
-      <c r="O86">
-        <v>3.3</v>
-      </c>
-      <c r="P86">
-        <v>3</v>
-      </c>
-      <c r="Q86">
-        <v>0</v>
-      </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,64 +14490,64 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="O87">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="P87">
-        <v>5.8</v>
+        <v>2.95</v>
       </c>
       <c r="Q87">
-        <v>1.85</v>
+        <v>3.04</v>
       </c>
       <c r="R87">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="S87">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="T87">
-        <v>3.32</v>
+        <v>2.78</v>
       </c>
       <c r="U87">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="V87">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="W87">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X87">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y87">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="Z87">
-        <v>4.38</v>
+        <v>3.36</v>
       </c>
       <c r="AA87">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AB87">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AC87">
-        <v>2.47</v>
+        <v>3.12</v>
       </c>
       <c r="AD87">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AE87">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AF87">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG87">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AK87">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="O88">
         <v>5.8</v>
       </c>
       <c r="P88">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Q88">
         <v>1.54</v>
@@ -14677,10 +14677,10 @@
         <v>1.95</v>
       </c>
       <c r="V88">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W88">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X88">
         <v>1.01</v>
@@ -14689,28 +14689,28 @@
         <v>1.06</v>
       </c>
       <c r="Z88">
-        <v>6.25</v>
+        <v>6.1</v>
       </c>
       <c r="AA88">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AB88">
         <v>2.87</v>
       </c>
       <c r="AC88">
+        <v>1.97</v>
+      </c>
+      <c r="AD88">
         <v>1.86</v>
       </c>
-      <c r="AD88">
-        <v>1.88</v>
-      </c>
       <c r="AE88">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AF88">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG88">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14819,25 +14819,25 @@
         <v>2.19</v>
       </c>
       <c r="O89">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P89">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="Q89">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="R89">
         <v>2.1</v>
       </c>
       <c r="S89">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T89">
         <v>2.59</v>
       </c>
       <c r="U89">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="V89">
         <v>1.38</v>
@@ -14852,13 +14852,13 @@
         <v>1.26</v>
       </c>
       <c r="Z89">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="AA89">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB89">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AC89">
         <v>3.14</v>
@@ -14867,13 +14867,13 @@
         <v>1.27</v>
       </c>
       <c r="AE89">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF89">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG89">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK89">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15018,10 +15018,10 @@
         <v>0</v>
       </c>
       <c r="AA90">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB90">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC90">
         <v>0</v>
@@ -15142,7 +15142,7 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="O91">
         <v>3.45</v>
@@ -15181,10 +15181,10 @@
         <v>0</v>
       </c>
       <c r="AA91">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB91">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC91">
         <v>0</v>
@@ -15471,31 +15471,31 @@
         <v>1.83</v>
       </c>
       <c r="O93">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P93">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q93">
-        <v>2.64</v>
+        <v>2.39</v>
       </c>
       <c r="R93">
-        <v>2.19</v>
+        <v>1.97</v>
       </c>
       <c r="S93">
         <v>1.33</v>
       </c>
       <c r="T93">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="U93">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V93">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W93">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X93">
         <v>0</v>
@@ -15522,10 +15522,10 @@
         <v>1.05</v>
       </c>
       <c r="AF93">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG93">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK93">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15640,10 +15640,10 @@
         <v>0</v>
       </c>
       <c r="Q94">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="R94">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="S94">
         <v>1.14</v>
@@ -15652,10 +15652,10 @@
         <v>4.8</v>
       </c>
       <c r="U94">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="V94">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="W94">
         <v>1.25</v>
@@ -15676,10 +15676,10 @@
         <v>3.28</v>
       </c>
       <c r="AC94">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AD94">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="AE94">
         <v>1.38</v>
@@ -15688,7 +15688,7 @@
         <v>2.05</v>
       </c>
       <c r="AG94">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15803,22 +15803,22 @@
         <v>0</v>
       </c>
       <c r="Q95">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="R95">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="S95">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T95">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="U95">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="V95">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W95">
         <v>1.08</v>
@@ -15827,47 +15827,47 @@
         <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z95">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="AA95">
         <v>1.8</v>
       </c>
       <c r="AB95">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AC95">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AD95">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE95">
+        <v>1.12</v>
+      </c>
+      <c r="AF95">
+        <v>1.72</v>
+      </c>
+      <c r="AG95">
+        <v>2</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ95">
+        <v>1.99</v>
+      </c>
+      <c r="AK95">
         <v>1.11</v>
-      </c>
-      <c r="AF95">
-        <v>1.67</v>
-      </c>
-      <c r="AG95">
-        <v>2.05</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ95">
-        <v>1.19</v>
-      </c>
-      <c r="AK95">
-        <v>1.17</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -16283,58 +16283,58 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="O98">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P98">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="Q98">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R98">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S98">
         <v>1.36</v>
       </c>
       <c r="T98">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U98">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="V98">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W98">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X98">
         <v>1.01</v>
       </c>
       <c r="Y98">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z98">
-        <v>3.27</v>
+        <v>3.18</v>
       </c>
       <c r="AA98">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AB98">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AC98">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="AD98">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE98">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF98">
         <v>1.8</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK98">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16775,10 +16775,10 @@
         <v>1.8</v>
       </c>
       <c r="O101">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P101">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q101">
         <v>2.2</v>
@@ -16799,7 +16799,7 @@
         <v>1.4</v>
       </c>
       <c r="W101">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X101">
         <v>1.02</v>
@@ -16811,10 +16811,10 @@
         <v>3.14</v>
       </c>
       <c r="AA101">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AB101">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC101">
         <v>3.4</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK101">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -16935,10 +16935,10 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="O102">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="P102">
         <v>4.88</v>
@@ -16947,13 +16947,13 @@
         <v>2.15</v>
       </c>
       <c r="R102">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="S102">
         <v>1.35</v>
       </c>
       <c r="T102">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="U102">
         <v>2.75</v>
@@ -16965,34 +16965,34 @@
         <v>1.07</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y102">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z102">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA102">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AB102">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AC102">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AD102">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE102">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF102">
         <v>1.87</v>
       </c>
       <c r="AG102">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>1.17</v>
       </c>
       <c r="AK102">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17098,34 +17098,34 @@
         </is>
       </c>
       <c r="N103">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O103">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P103">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="Q103">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="R103">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="S103">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T103">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U103">
-        <v>2.72</v>
+        <v>2.85</v>
       </c>
       <c r="V103">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W103">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X103">
         <v>1</v>
@@ -17137,19 +17137,19 @@
         <v>3.14</v>
       </c>
       <c r="AA103">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AB103">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC103">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD103">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE103">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF103">
         <v>1.73</v>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK103">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17276,16 +17276,16 @@
         <v>2.15</v>
       </c>
       <c r="S104">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T104">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U104">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V104">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W104">
         <v>1.08</v>
@@ -17331,7 +17331,7 @@
         </is>
       </c>
       <c r="AJ104">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK104">
         <v>1.24</v>
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="O105">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="P105">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="Q105">
-        <v>2.89</v>
+        <v>3.11</v>
       </c>
       <c r="R105">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S105">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T105">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="U105">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="V105">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W105">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X105">
         <v>1</v>
       </c>
       <c r="Y105">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z105">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA105">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AB105">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AC105">
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="AD105">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE105">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF105">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AG105">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17497,7 +17497,7 @@
         <v>1.36</v>
       </c>
       <c r="AK105">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AL105">
         <v>0</v>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -6643,26 +6643,26 @@
         </is>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39">
         <v>0</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N39">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "58"]</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20"]</t>
         </is>
       </c>
       <c r="AJ39">
@@ -6745,28 +6745,28 @@
         <v>0</v>
       </c>
       <c r="AM39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP39">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR39">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AS39">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT39">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         </is>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -6818,14 +6818,14 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N40">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76"]</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
@@ -6908,28 +6908,28 @@
         <v>0</v>
       </c>
       <c r="AM40">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN40">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO40">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
@@ -6969,13 +6969,13 @@
         </is>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -6984,11 +6984,11 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N41">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2"]</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AJ41">
@@ -7071,28 +7071,28 @@
         <v>0</v>
       </c>
       <c r="AM41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN41">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO41">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU41" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>0</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -7147,11 +7147,11 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N42">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["54", "90+7"]</t>
         </is>
       </c>
       <c r="AJ42">
@@ -7234,28 +7234,28 @@
         <v>0</v>
       </c>
       <c r="AM42">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN42">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP42">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
@@ -7621,36 +7621,36 @@
         </is>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H45">
         <v>0</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45">
         <v>0</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45">
         <v>0</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N45">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="O45">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="P45">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7705,14 +7705,14 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
+          <t>["3", "20", "71"]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ45">
         <v>0</v>
       </c>
@@ -7723,28 +7723,28 @@
         <v>0</v>
       </c>
       <c r="AM45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN45">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO45">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP45">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ45">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AR45">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AS45">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT45">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
@@ -7784,26 +7784,26 @@
         </is>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46">
         <v>0</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N46">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+7"]</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["1", "32"]</t>
         </is>
       </c>
       <c r="AJ46">
@@ -7886,28 +7886,28 @@
         <v>0</v>
       </c>
       <c r="AM46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO46">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP46">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AS46">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AT46">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
@@ -7947,26 +7947,26 @@
         </is>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H47">
         <v>0</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J47">
         <v>0</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L47">
         <v>0</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N47">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "17", "20", "22", "37", "39", "53", "77", "86"]</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
@@ -8049,16 +8049,16 @@
         <v>0</v>
       </c>
       <c r="AM47">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AN47">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO47">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP47">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ47">
         <v>0</v>
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -8122,14 +8122,14 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48">
         <v>0</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N48">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["47"]</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
@@ -8212,28 +8212,28 @@
         <v>0</v>
       </c>
       <c r="AM48">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN48">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO48">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP48">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ48">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AR48">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AS48">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT48">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
@@ -8273,13 +8273,13 @@
         </is>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H49">
         <v>0</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N49">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28", "39"]</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
@@ -8375,28 +8375,28 @@
         <v>0</v>
       </c>
       <c r="AM49">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN49">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO49">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP49">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ49">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AR49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS49">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="AT49">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
@@ -8436,26 +8436,26 @@
         </is>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N50">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53"]</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "22", "34", "52", "74", "90+4"]</t>
         </is>
       </c>
       <c r="AJ50">
@@ -8538,28 +8538,28 @@
         <v>0</v>
       </c>
       <c r="AM50">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN50">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO50">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP50">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ50">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR50">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AS50">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT50">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
@@ -8599,26 +8599,26 @@
         </is>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L51">
         <v>0</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N51">
@@ -8683,12 +8683,12 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "45+1", "54", "90+3", "90+9"]</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3"]</t>
         </is>
       </c>
       <c r="AJ51">
@@ -8701,28 +8701,28 @@
         <v>0</v>
       </c>
       <c r="AM51">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN51">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO51">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP51">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ51">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AR51">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AS51">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AT51">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
@@ -8762,26 +8762,26 @@
         </is>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52">
         <v>0</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N52">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "72"]</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["15"]</t>
         </is>
       </c>
       <c r="AJ52">
@@ -8864,28 +8864,28 @@
         <v>0</v>
       </c>
       <c r="AM52">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN52">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO52">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP52">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ52">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS52">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT52">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
@@ -8925,10 +8925,10 @@
         </is>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -8937,14 +8937,14 @@
         <v>0</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N53">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["55"]</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["74"]</t>
         </is>
       </c>
       <c r="AJ53">
@@ -9027,28 +9027,28 @@
         <v>0</v>
       </c>
       <c r="AM53">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN53">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO53">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP53">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ53">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AR53">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS53">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AT53">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
@@ -9091,23 +9091,23 @@
         <v>0</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I54">
         <v>0</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N54">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "80", "87"]</t>
         </is>
       </c>
       <c r="AJ54">
@@ -9190,28 +9190,28 @@
         <v>0</v>
       </c>
       <c r="AM54">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN54">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO54">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP54">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ54">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AR54">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS54">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AT54">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
@@ -9251,26 +9251,26 @@
         </is>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H55">
         <v>0</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55">
         <v>0</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55">
         <v>0</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N55">
@@ -9335,14 +9335,14 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
+          <t>["3", "90+5"]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ55">
         <v>0</v>
       </c>
@@ -9353,28 +9353,28 @@
         <v>0</v>
       </c>
       <c r="AM55">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN55">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO55">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP55">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ55">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR55">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS55">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT55">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
@@ -9414,26 +9414,26 @@
         </is>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N56">
@@ -9446,10 +9446,10 @@
         <v>1.22</v>
       </c>
       <c r="Q56">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="R56">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="S56">
         <v>1.17</v>
@@ -9470,74 +9470,74 @@
         <v>1.01</v>
       </c>
       <c r="Y56">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z56">
-        <v>6.05</v>
+        <v>5.7</v>
       </c>
       <c r="AA56">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AB56">
         <v>2.75</v>
       </c>
       <c r="AC56">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AD56">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AE56">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AF56">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AG56">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "90+1"]</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "44", "73"]</t>
         </is>
       </c>
       <c r="AJ56">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AK56">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AL56">
         <v>0</v>
       </c>
       <c r="AM56">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN56">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO56">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP56">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ56">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AR56">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AS56">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT56">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
@@ -9577,26 +9577,26 @@
         </is>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J57">
         <v>0</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N57">
@@ -9661,12 +9661,12 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["37", "45+1", "69"]</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62"]</t>
         </is>
       </c>
       <c r="AJ57">
@@ -9679,28 +9679,28 @@
         <v>0</v>
       </c>
       <c r="AM57">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN57">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO57">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP57">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ57">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR57">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AS57">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AT57">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
@@ -9740,26 +9740,26 @@
         </is>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N58">
@@ -9824,12 +9824,12 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "45+11", "60"]</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "78"]</t>
         </is>
       </c>
       <c r="AJ58">
@@ -9842,28 +9842,28 @@
         <v>0</v>
       </c>
       <c r="AM58">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN58">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO58">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP58">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ58">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR58">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS58">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT58">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
@@ -9903,13 +9903,13 @@
         </is>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N59">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20"]</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
@@ -10005,28 +10005,28 @@
         <v>0</v>
       </c>
       <c r="AM59">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN59">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO59">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP59">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ59">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR59">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AS59">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT59">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
@@ -10066,26 +10066,26 @@
         </is>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H60">
         <v>0</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60">
         <v>0</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60">
         <v>0</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N60">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "90+2"]</t>
         </is>
       </c>
       <c r="AI60" t="inlineStr">
@@ -10168,28 +10168,28 @@
         <v>0</v>
       </c>
       <c r="AM60">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN60">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO60">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP60">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ60">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AR60">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="AS60">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AT60">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
@@ -10229,26 +10229,26 @@
         </is>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H61">
         <v>0</v>
       </c>
       <c r="I61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61">
         <v>0</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61">
         <v>0</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N61">
@@ -10313,14 +10313,14 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
+          <t>["1", "83", "89"]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ61">
         <v>0</v>
       </c>
@@ -10331,28 +10331,28 @@
         <v>0</v>
       </c>
       <c r="AM61">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN61">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO61">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP61">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ61">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AR61">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS61">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT61">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
@@ -10392,26 +10392,26 @@
         </is>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I62">
         <v>0</v>
       </c>
       <c r="J62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N62">
@@ -10476,12 +10476,12 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48"]</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "37", "68", "90+7"]</t>
         </is>
       </c>
       <c r="AJ62">
@@ -10494,28 +10494,28 @@
         <v>0</v>
       </c>
       <c r="AM62">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN62">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO62">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP62">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ62">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AR62">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AS62">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT62">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
@@ -10558,23 +10558,23 @@
         <v>0</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I63">
         <v>0</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K63">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N63">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3", "43", "65"]</t>
         </is>
       </c>
       <c r="AJ63">
@@ -10657,28 +10657,28 @@
         <v>0</v>
       </c>
       <c r="AM63">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN63">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO63">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP63">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ63">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AR63">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AS63">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT63">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
@@ -10718,26 +10718,26 @@
         </is>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I64">
         <v>0</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N64">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88", "90+3"]</t>
         </is>
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "48"]</t>
         </is>
       </c>
       <c r="AJ64">
@@ -10820,28 +10820,28 @@
         <v>0</v>
       </c>
       <c r="AM64">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AN64">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO64">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="AP64">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ64">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AR64">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AS64">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT64">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
@@ -10881,81 +10881,81 @@
         </is>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I65">
         <v>0</v>
       </c>
       <c r="J65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N65">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O65">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P65">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q65">
-        <v>3.21</v>
+        <v>2.99</v>
       </c>
       <c r="R65">
         <v>2.12</v>
       </c>
       <c r="S65">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T65">
         <v>2.75</v>
       </c>
       <c r="U65">
-        <v>2.91</v>
+        <v>2.61</v>
       </c>
       <c r="V65">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W65">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X65">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
         <v>1.23</v>
       </c>
       <c r="Z65">
-        <v>3.06</v>
+        <v>3.42</v>
       </c>
       <c r="AA65">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="AB65">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC65">
-        <v>3.48</v>
+        <v>3.08</v>
       </c>
       <c r="AD65">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AE65">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF65">
         <v>1.62</v>
@@ -10965,46 +10965,46 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["79"]</t>
         </is>
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "71"]</t>
         </is>
       </c>
       <c r="AJ65">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK65">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL65">
         <v>0</v>
       </c>
       <c r="AM65">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN65">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO65">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP65">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ65">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR65">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AS65">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT65">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
@@ -11044,16 +11044,16 @@
         </is>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -11063,7 +11063,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N66">
@@ -11128,12 +11128,12 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8"]</t>
         </is>
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38"]</t>
         </is>
       </c>
       <c r="AJ66">
@@ -11146,28 +11146,28 @@
         <v>0</v>
       </c>
       <c r="AM66">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN66">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO66">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP66">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ66">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR66">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS66">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT66">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
@@ -11207,10 +11207,10 @@
         </is>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -11219,18 +11219,18 @@
         <v>0</v>
       </c>
       <c r="K67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N67">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="O67">
         <v>3.6</v>
@@ -11239,7 +11239,7 @@
         <v>1.5</v>
       </c>
       <c r="Q67">
-        <v>5.75</v>
+        <v>4.8</v>
       </c>
       <c r="R67">
         <v>2</v>
@@ -11251,10 +11251,10 @@
         <v>2.65</v>
       </c>
       <c r="U67">
-        <v>2.87</v>
+        <v>2.73</v>
       </c>
       <c r="V67">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W67">
         <v>1.03</v>
@@ -11263,10 +11263,10 @@
         <v>0</v>
       </c>
       <c r="Y67">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z67">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="AA67">
         <v>1.78</v>
@@ -11275,7 +11275,7 @@
         <v>1.57</v>
       </c>
       <c r="AC67">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="AD67">
         <v>1.28</v>
@@ -11284,26 +11284,26 @@
         <v>1.05</v>
       </c>
       <c r="AF67">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AG67">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["69"]</t>
         </is>
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87", "90+4"]</t>
         </is>
       </c>
       <c r="AJ67">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AK67">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="O68">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="P68">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11432,10 +11432,10 @@
         <v>0</v>
       </c>
       <c r="AA68">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB68">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC68">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         </is>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -11545,42 +11545,42 @@
         <v>0</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N69">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O69">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P69">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="Q69">
-        <v>3.16</v>
+        <v>2.45</v>
       </c>
       <c r="R69">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="S69">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T69">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="U69">
         <v>3.1</v>
       </c>
       <c r="V69">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W69">
         <v>1.06</v>
@@ -11589,74 +11589,74 @@
         <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z69">
-        <v>2.82</v>
+        <v>2.93</v>
       </c>
       <c r="AA69">
         <v>2.2</v>
       </c>
       <c r="AB69">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="AC69">
-        <v>3.89</v>
+        <v>3.78</v>
       </c>
       <c r="AD69">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE69">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF69">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG69">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["62"]</t>
         </is>
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53"]</t>
         </is>
       </c>
       <c r="AJ69">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK69">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AL69">
         <v>0</v>
       </c>
       <c r="AM69">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN69">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO69">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP69">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ69">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR69">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS69">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT69">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
@@ -11696,48 +11696,48 @@
         </is>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I70">
         <v>0</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N70">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="O70">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P70">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q70">
         <v>2.3</v>
       </c>
       <c r="R70">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T70">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U70">
         <v>2.8</v>
@@ -11780,46 +11780,46 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72"]</t>
         </is>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "66", "83", "90+4"]</t>
         </is>
       </c>
       <c r="AJ70">
         <v>1.14</v>
       </c>
       <c r="AK70">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL70">
         <v>0</v>
       </c>
       <c r="AM70">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN70">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO70">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP70">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ70">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AR70">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS70">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT70">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         </is>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -11871,30 +11871,30 @@
         <v>0</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71">
         <v>0</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N71">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="O71">
         <v>4.2</v>
       </c>
       <c r="P71">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="Q71">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R71">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="S71">
         <v>1.33</v>
@@ -11906,7 +11906,7 @@
         <v>2.75</v>
       </c>
       <c r="V71">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W71">
         <v>1.05</v>
@@ -11921,7 +11921,7 @@
         <v>3.54</v>
       </c>
       <c r="AA71">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB71">
         <v>1.95</v>
@@ -11939,11 +11939,11 @@
         <v>2.21</v>
       </c>
       <c r="AG71">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["86", "90+3"]</t>
         </is>
       </c>
       <c r="AI71" t="inlineStr">
@@ -11961,28 +11961,28 @@
         <v>0</v>
       </c>
       <c r="AM71">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN71">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO71">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP71">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ71">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AR71">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AS71">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT71">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
@@ -12022,26 +12022,26 @@
         </is>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N72">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "53", "72"]</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39", "90+7"]</t>
         </is>
       </c>
       <c r="AJ72">
@@ -12124,28 +12124,28 @@
         <v>0</v>
       </c>
       <c r="AM72">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN72">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO72">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP72">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ72">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR72">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS72">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT72">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>0</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -12363,11 +12363,11 @@
         <v>0</v>
       </c>
       <c r="L74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N74">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["80", "88"]</t>
         </is>
       </c>
       <c r="AJ74">
@@ -12450,28 +12450,28 @@
         <v>0</v>
       </c>
       <c r="AM74">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN74">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO74">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP74">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ74">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AR74">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS74">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT74">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N75">
@@ -12543,22 +12543,22 @@
         <v>2.45</v>
       </c>
       <c r="Q75">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="R75">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="S75">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T75">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="U75">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="V75">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W75">
         <v>1.08</v>
@@ -12573,68 +12573,68 @@
         <v>3.41</v>
       </c>
       <c r="AA75">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB75">
+        <v>1.93</v>
+      </c>
+      <c r="AC75">
+        <v>3.03</v>
+      </c>
+      <c r="AD75">
+        <v>1.35</v>
+      </c>
+      <c r="AE75">
+        <v>1.08</v>
+      </c>
+      <c r="AF75">
         <v>1.75</v>
       </c>
-      <c r="AC75">
-        <v>3.2</v>
-      </c>
-      <c r="AD75">
-        <v>1.31</v>
-      </c>
-      <c r="AE75">
-        <v>1.07</v>
-      </c>
-      <c r="AF75">
+      <c r="AG75">
+        <v>1.95</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
+        <v>1.12</v>
+      </c>
+      <c r="AK75">
         <v>1.85</v>
       </c>
-      <c r="AG75">
-        <v>1.85</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ75">
-        <v>1.22</v>
-      </c>
-      <c r="AK75">
-        <v>1.71</v>
-      </c>
       <c r="AL75">
         <v>0</v>
       </c>
       <c r="AM75">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN75">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO75">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP75">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ75">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AR75">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS75">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT75">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
@@ -12674,13 +12674,13 @@
         </is>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -12689,115 +12689,115 @@
         <v>0</v>
       </c>
       <c r="L76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N76">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="O76">
+        <v>3</v>
+      </c>
+      <c r="P76">
         <v>2.7</v>
       </c>
-      <c r="P76">
-        <v>2.65</v>
-      </c>
       <c r="Q76">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="R76">
+        <v>1.86</v>
+      </c>
+      <c r="S76">
+        <v>1.44</v>
+      </c>
+      <c r="T76">
+        <v>2.62</v>
+      </c>
+      <c r="U76">
+        <v>3.1</v>
+      </c>
+      <c r="V76">
+        <v>1.32</v>
+      </c>
+      <c r="W76">
+        <v>1.06</v>
+      </c>
+      <c r="X76">
+        <v>1.04</v>
+      </c>
+      <c r="Y76">
+        <v>1.48</v>
+      </c>
+      <c r="Z76">
+        <v>2.58</v>
+      </c>
+      <c r="AA76">
+        <v>2.05</v>
+      </c>
+      <c r="AB76">
+        <v>1.4</v>
+      </c>
+      <c r="AC76">
+        <v>4.5</v>
+      </c>
+      <c r="AD76">
+        <v>1.16</v>
+      </c>
+      <c r="AE76">
+        <v>0</v>
+      </c>
+      <c r="AF76">
         <v>1.95</v>
       </c>
-      <c r="S76">
-        <v>1.5</v>
-      </c>
-      <c r="T76">
-        <v>2.45</v>
-      </c>
-      <c r="U76">
-        <v>3.4</v>
-      </c>
-      <c r="V76">
-        <v>1.25</v>
-      </c>
-      <c r="W76">
-        <v>1.05</v>
-      </c>
-      <c r="X76">
-        <v>1.05</v>
-      </c>
-      <c r="Y76">
-        <v>1.47</v>
-      </c>
-      <c r="Z76">
-        <v>2.45</v>
-      </c>
-      <c r="AA76">
-        <v>2.48</v>
-      </c>
-      <c r="AB76">
-        <v>1.5</v>
-      </c>
-      <c r="AC76">
-        <v>4.88</v>
-      </c>
-      <c r="AD76">
-        <v>1.13</v>
-      </c>
-      <c r="AE76">
-        <v>0</v>
-      </c>
-      <c r="AF76">
-        <v>2.05</v>
-      </c>
       <c r="AG76">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5"]</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["87", "90+4"]</t>
         </is>
       </c>
       <c r="AJ76">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AK76">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AL76">
         <v>0</v>
       </c>
       <c r="AM76">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN76">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO76">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP76">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ76">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AR76">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS76">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT76">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
@@ -12837,16 +12837,16 @@
         </is>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K77">
         <v>0</v>
@@ -12856,111 +12856,111 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N77">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="O77">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P77">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="Q77">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="R77">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="S77">
         <v>1.4</v>
       </c>
       <c r="T77">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U77">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="V77">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W77">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X77">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y77">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z77">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AA77">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AB77">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC77">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="AD77">
         <v>1.18</v>
       </c>
       <c r="AE77">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF77">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AG77">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18"]</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "45+3"]</t>
         </is>
       </c>
       <c r="AJ77">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK77">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AL77">
         <v>0</v>
       </c>
       <c r="AM77">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN77">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO77">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP77">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ77">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR77">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS77">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AT77">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
@@ -13000,103 +13000,103 @@
         </is>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78">
         <v>0</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N78">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="O78">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P78">
-        <v>3.25</v>
+        <v>3.97</v>
       </c>
       <c r="Q78">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="R78">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="S78">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T78">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="U78">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="V78">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W78">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X78">
         <v>1.01</v>
       </c>
       <c r="Y78">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z78">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA78">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB78">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AC78">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="AD78">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE78">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF78">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG78">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "45", "51"]</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AJ78">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AK78">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13364,7 +13364,7 @@
         <v>2.03</v>
       </c>
       <c r="S80">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T80">
         <v>2.9</v>
@@ -13524,7 +13524,7 @@
         <v>2.8</v>
       </c>
       <c r="R81">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S81">
         <v>1.27</v>
@@ -13533,7 +13533,7 @@
         <v>3.2</v>
       </c>
       <c r="U81">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V81">
         <v>1.55</v>
@@ -13542,7 +13542,7 @@
         <v>1.09</v>
       </c>
       <c r="X81">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
         <v>1.19</v>
@@ -13551,10 +13551,10 @@
         <v>4.33</v>
       </c>
       <c r="AA81">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB81">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC81">
         <v>2.6</v>
@@ -13563,7 +13563,7 @@
         <v>1.47</v>
       </c>
       <c r="AE81">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF81">
         <v>1.55</v>
@@ -13652,13 +13652,13 @@
         </is>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -13667,11 +13667,11 @@
         <v>0</v>
       </c>
       <c r="L82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N82">
@@ -13684,7 +13684,7 @@
         <v>2.3</v>
       </c>
       <c r="Q82">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="R82">
         <v>1.91</v>
@@ -13696,37 +13696,37 @@
         <v>2.5</v>
       </c>
       <c r="U82">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V82">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W82">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X82">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y82">
         <v>1.41</v>
       </c>
       <c r="Z82">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="AA82">
         <v>2.4</v>
       </c>
       <c r="AB82">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC82">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AD82">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE82">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF82">
         <v>2</v>
@@ -13736,46 +13736,46 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25"]</t>
         </is>
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["88", "90"]</t>
         </is>
       </c>
       <c r="AJ82">
         <v>1.3</v>
       </c>
       <c r="AK82">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL82">
         <v>0</v>
       </c>
       <c r="AM82">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN82">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO82">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP82">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ82">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR82">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS82">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT82">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
@@ -13834,20 +13834,20 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N83">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="O83">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P83">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q83">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="R83">
         <v>2.1</v>
@@ -13856,13 +13856,13 @@
         <v>1.4</v>
       </c>
       <c r="T83">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U83">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V83">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W83">
         <v>1.07</v>
@@ -13871,25 +13871,25 @@
         <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z83">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA83">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AB83">
         <v>1.7</v>
       </c>
       <c r="AC83">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="AD83">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE83">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF83">
         <v>1.85</v>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK83">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14013,7 +14013,7 @@
         <v>4.68</v>
       </c>
       <c r="R84">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S84">
         <v>1.3</v>
@@ -14022,10 +14022,10 @@
         <v>2.3</v>
       </c>
       <c r="U84">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="V84">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="W84">
         <v>1.03</v>
@@ -14040,10 +14040,10 @@
         <v>3.2</v>
       </c>
       <c r="AA84">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB84">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC84">
         <v>3.3</v>
@@ -14055,10 +14055,10 @@
         <v>1.06</v>
       </c>
       <c r="AF84">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG84">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK84">
         <v>1.11</v>
@@ -14144,7 +14144,7 @@
         <v>0</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -14156,15 +14156,15 @@
         <v>0</v>
       </c>
       <c r="L85">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N85">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="O85">
         <v>3.2</v>
@@ -14173,25 +14173,25 @@
         <v>3.85</v>
       </c>
       <c r="Q85">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="R85">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S85">
+        <v>1.36</v>
+      </c>
+      <c r="T85">
+        <v>2.9</v>
+      </c>
+      <c r="U85">
+        <v>2.82</v>
+      </c>
+      <c r="V85">
         <v>1.4</v>
       </c>
-      <c r="T85">
-        <v>2.75</v>
-      </c>
-      <c r="U85">
-        <v>2.9</v>
-      </c>
-      <c r="V85">
-        <v>1.36</v>
-      </c>
       <c r="W85">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X85">
         <v>1.02</v>
@@ -14200,28 +14200,28 @@
         <v>1.34</v>
       </c>
       <c r="Z85">
-        <v>2.98</v>
+        <v>3.03</v>
       </c>
       <c r="AA85">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AB85">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AC85">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="AD85">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE85">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF85">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG85">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53", "68", "86", "90+2"]</t>
         </is>
       </c>
       <c r="AJ85">
@@ -14243,28 +14243,28 @@
         <v>0</v>
       </c>
       <c r="AM85">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN85">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO85">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP85">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ85">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR85">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS85">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT85">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
@@ -14307,84 +14307,84 @@
         <v>0</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I86">
         <v>0</v>
       </c>
       <c r="J86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K86">
         <v>0</v>
       </c>
       <c r="L86">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N86">
         <v>1.49</v>
       </c>
       <c r="O86">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P86">
         <v>5.4</v>
       </c>
       <c r="Q86">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="R86">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="S86">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T86">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="U86">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V86">
         <v>1.4</v>
       </c>
       <c r="W86">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X86">
         <v>1.01</v>
       </c>
       <c r="Y86">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z86">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="AA86">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AB86">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC86">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD86">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE86">
         <v>1.08</v>
       </c>
       <c r="AF86">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG86">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14393,41 +14393,41 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "16", "41", "65", "74", "81"]</t>
         </is>
       </c>
       <c r="AJ86">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK86">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AL86">
         <v>0</v>
       </c>
       <c r="AM86">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN86">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO86">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP86">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ86">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AR86">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS86">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT86">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
@@ -14486,23 +14486,23 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N87">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O87">
         <v>3.25</v>
       </c>
       <c r="P87">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q87">
-        <v>3.04</v>
+        <v>2.6</v>
       </c>
       <c r="R87">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S87">
         <v>1.41</v>
@@ -14511,10 +14511,10 @@
         <v>2.78</v>
       </c>
       <c r="U87">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="V87">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W87">
         <v>1.04</v>
@@ -14560,37 +14560,37 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK87">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL87">
         <v>0</v>
       </c>
       <c r="AM87">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN87">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO87">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP87">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ87">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AR87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS87">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT87">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
@@ -14659,13 +14659,13 @@
         <v>5.8</v>
       </c>
       <c r="P88">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Q88">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="R88">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="S88">
         <v>1.17</v>
@@ -14674,10 +14674,10 @@
         <v>4.5</v>
       </c>
       <c r="U88">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V88">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W88">
         <v>1.22</v>
@@ -14686,25 +14686,25 @@
         <v>1.01</v>
       </c>
       <c r="Y88">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z88">
-        <v>6.1</v>
+        <v>6.45</v>
       </c>
       <c r="AA88">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AB88">
-        <v>2.87</v>
+        <v>3.08</v>
       </c>
       <c r="AC88">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AD88">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AE88">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF88">
         <v>1.67</v>
@@ -14726,7 +14726,7 @@
         <v>1.09</v>
       </c>
       <c r="AK88">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="O89">
         <v>3.1</v>
@@ -14825,10 +14825,10 @@
         <v>3</v>
       </c>
       <c r="Q89">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="R89">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S89">
         <v>1.42</v>
@@ -14837,7 +14837,7 @@
         <v>2.59</v>
       </c>
       <c r="U89">
-        <v>2.73</v>
+        <v>3.08</v>
       </c>
       <c r="V89">
         <v>1.38</v>
@@ -14852,13 +14852,13 @@
         <v>1.26</v>
       </c>
       <c r="Z89">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="AA89">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB89">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC89">
         <v>3.14</v>
@@ -14870,10 +14870,10 @@
         <v>1.1</v>
       </c>
       <c r="AF89">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG89">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK89">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15018,10 +15018,10 @@
         <v>0</v>
       </c>
       <c r="AA90">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB90">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC90">
         <v>0</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O91">
         <v>3.45</v>
       </c>
       <c r="P91">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15326,10 +15326,10 @@
         <v>3.2</v>
       </c>
       <c r="U92">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V92">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W92">
         <v>1.06</v>
@@ -15344,10 +15344,10 @@
         <v>3.68</v>
       </c>
       <c r="AA92">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB92">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AC92">
         <v>2.38</v>
@@ -15468,7 +15468,7 @@
         </is>
       </c>
       <c r="N93">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O93">
         <v>3.2</v>
@@ -15541,7 +15541,7 @@
         <v>1.13</v>
       </c>
       <c r="AK93">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Q94">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="R94">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S94">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T94">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="U94">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="V94">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="W94">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X94">
         <v>0</v>
       </c>
       <c r="Y94">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z94">
-        <v>7.95</v>
+        <v>0</v>
       </c>
       <c r="AA94">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB94">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AC94">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AD94">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AE94">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AF94">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG94">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK94">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q95">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R95">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S95">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T95">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="U95">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="V95">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W95">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X95">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y95">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z95">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AA95">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB95">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AC95">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AD95">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE95">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF95">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG95">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AK95">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -16289,7 +16289,7 @@
         <v>3.2</v>
       </c>
       <c r="P98">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="Q98">
         <v>2.3</v>
@@ -16941,7 +16941,7 @@
         <v>3.95</v>
       </c>
       <c r="P102">
-        <v>4.88</v>
+        <v>5.11</v>
       </c>
       <c r="Q102">
         <v>2.15</v>
@@ -16977,7 +16977,7 @@
         <v>1.9</v>
       </c>
       <c r="AB102">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AC102">
         <v>2.97</v>
@@ -17008,7 +17008,7 @@
         <v>1.17</v>
       </c>
       <c r="AK102">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17104,7 +17104,7 @@
         <v>3.1</v>
       </c>
       <c r="P103">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q103">
         <v>3</v>
@@ -17433,7 +17433,7 @@
         <v>2.9</v>
       </c>
       <c r="Q105">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="R105">
         <v>2.1</v>
@@ -17442,16 +17442,16 @@
         <v>1.36</v>
       </c>
       <c r="T105">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="U105">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="V105">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W105">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X105">
         <v>1</v>
@@ -17460,16 +17460,16 @@
         <v>1.3</v>
       </c>
       <c r="Z105">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA105">
         <v>1.91</v>
       </c>
       <c r="AB105">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AC105">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="AD105">
         <v>1.31</v>
@@ -17497,7 +17497,7 @@
         <v>1.36</v>
       </c>
       <c r="AK105">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="O110">
+        <v>3.8</v>
+      </c>
+      <c r="P110">
+        <v>3.6</v>
+      </c>
+      <c r="Q110">
+        <v>2.29</v>
+      </c>
+      <c r="R110">
+        <v>2.63</v>
+      </c>
+      <c r="S110">
+        <v>1.22</v>
+      </c>
+      <c r="T110">
         <v>4</v>
       </c>
-      <c r="P110">
-        <v>3.7</v>
-      </c>
-      <c r="Q110">
-        <v>2.36</v>
-      </c>
-      <c r="R110">
-        <v>2.58</v>
-      </c>
-      <c r="S110">
-        <v>1.25</v>
-      </c>
-      <c r="T110">
-        <v>3.64</v>
-      </c>
       <c r="U110">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="V110">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="W110">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X110">
         <v>1</v>
       </c>
       <c r="Y110">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Z110">
-        <v>5.4</v>
+        <v>5.84</v>
       </c>
       <c r="AA110">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AB110">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="AC110">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AD110">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AE110">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AF110">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG110">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK110">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18417,13 +18417,13 @@
         <v>2.62</v>
       </c>
       <c r="S111">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T111">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U111">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V111">
         <v>1.65</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="O114">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P114">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="Q114">
         <v>0</v>
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="O115">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="P115">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q115">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
       <c r="R115">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="S115">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T115">
-        <v>3.19</v>
+        <v>3.09</v>
       </c>
       <c r="U115">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V115">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W115">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X115">
         <v>1.02</v>
       </c>
       <c r="Y115">
+        <v>1.2</v>
+      </c>
+      <c r="Z115">
+        <v>4.33</v>
+      </c>
+      <c r="AA115">
+        <v>1.68</v>
+      </c>
+      <c r="AB115">
+        <v>2.17</v>
+      </c>
+      <c r="AC115">
+        <v>2.56</v>
+      </c>
+      <c r="AD115">
+        <v>1.48</v>
+      </c>
+      <c r="AE115">
         <v>1.17</v>
       </c>
-      <c r="Z115">
-        <v>4.39</v>
-      </c>
-      <c r="AA115">
-        <v>1.64</v>
-      </c>
-      <c r="AB115">
-        <v>2.24</v>
-      </c>
-      <c r="AC115">
-        <v>2.46</v>
-      </c>
-      <c r="AD115">
-        <v>1.53</v>
-      </c>
-      <c r="AE115">
-        <v>1.18</v>
-      </c>
       <c r="AF115">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG115">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK115">
-        <v>2.18</v>
+        <v>1.99</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="O116">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="P116">
-        <v>10</v>
+        <v>7.57</v>
       </c>
       <c r="Q116">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="R116">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="S116">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T116">
-        <v>3.12</v>
+        <v>2.99</v>
       </c>
       <c r="U116">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V116">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W116">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X116">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z116">
-        <v>4.44</v>
+        <v>3.94</v>
       </c>
       <c r="AA116">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AB116">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AC116">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="AD116">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="AE116">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF116">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="AG116">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>1.02</v>
       </c>
       <c r="AK116">
-        <v>3.68</v>
+        <v>3.18</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="O120">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P120">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="Q120">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="R120">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="S120">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T120">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="U120">
-        <v>2.45</v>
+        <v>2.72</v>
       </c>
       <c r="V120">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="W120">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X120">
         <v>1.04</v>
       </c>
       <c r="Y120">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z120">
-        <v>3.61</v>
+        <v>3.28</v>
       </c>
       <c r="AA120">
+        <v>1.84</v>
+      </c>
+      <c r="AB120">
         <v>1.83</v>
       </c>
-      <c r="AB120">
-        <v>1.98</v>
-      </c>
       <c r="AC120">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AD120">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE120">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF120">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG120">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK120">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20077,7 +20077,7 @@
         <v>1.99</v>
       </c>
       <c r="AC121">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AD121">
         <v>1.42</v>
@@ -20195,64 +20195,64 @@
         </is>
       </c>
       <c r="N122">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="O122">
+        <v>3.3</v>
+      </c>
+      <c r="P122">
         <v>3.5</v>
       </c>
-      <c r="P122">
-        <v>3.4</v>
-      </c>
       <c r="Q122">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="R122">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="S122">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T122">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="U122">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="V122">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W122">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X122">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z122">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="AA122">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AB122">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AC122">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD122">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE122">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF122">
+        <v>1.9</v>
+      </c>
+      <c r="AG122">
         <v>1.8</v>
-      </c>
-      <c r="AG122">
-        <v>1.87</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>

--- a/jogos_2026-10-04.xlsx
+++ b/jogos_2026-10-04.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU122"/>
+  <dimension ref="A1:AU123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11370,26 +11370,26 @@
         </is>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N68">
@@ -11454,12 +11454,12 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "51"]</t>
         </is>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "63", "71", "90+5"]</t>
         </is>
       </c>
       <c r="AJ68">
@@ -11472,28 +11472,28 @@
         <v>0</v>
       </c>
       <c r="AM68">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN68">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AO68">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP68">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ68">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR68">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AS68">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT68">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -12197,14 +12197,14 @@
         <v>0</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L73">
         <v>0</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N73">
@@ -12269,14 +12269,14 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
+          <t>["52", "90+4"]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ73">
         <v>0</v>
       </c>
@@ -12287,28 +12287,28 @@
         <v>0</v>
       </c>
       <c r="AM73">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN73">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO73">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP73">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ73">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AR73">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS73">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AT73">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         </is>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -13175,118 +13175,118 @@
         <v>0</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79">
         <v>0</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N79">
+        <v>1.71</v>
+      </c>
+      <c r="O79">
+        <v>3.6</v>
+      </c>
+      <c r="P79">
+        <v>4.2</v>
+      </c>
+      <c r="Q79">
+        <v>2.4</v>
+      </c>
+      <c r="R79">
+        <v>2.34</v>
+      </c>
+      <c r="S79">
+        <v>1.37</v>
+      </c>
+      <c r="T79">
+        <v>2.96</v>
+      </c>
+      <c r="U79">
+        <v>2.6</v>
+      </c>
+      <c r="V79">
+        <v>1.47</v>
+      </c>
+      <c r="W79">
+        <v>1.06</v>
+      </c>
+      <c r="X79">
+        <v>1.01</v>
+      </c>
+      <c r="Y79">
+        <v>1.26</v>
+      </c>
+      <c r="Z79">
+        <v>3.54</v>
+      </c>
+      <c r="AA79">
+        <v>1.9</v>
+      </c>
+      <c r="AB79">
+        <v>1.9</v>
+      </c>
+      <c r="AC79">
+        <v>2.97</v>
+      </c>
+      <c r="AD79">
+        <v>1.36</v>
+      </c>
+      <c r="AE79">
+        <v>1.09</v>
+      </c>
+      <c r="AF79">
+        <v>1.74</v>
+      </c>
+      <c r="AG79">
+        <v>1.96</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>["68", "80"]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
+        <v>1.2</v>
+      </c>
+      <c r="AK79">
+        <v>1.97</v>
+      </c>
+      <c r="AL79">
+        <v>0</v>
+      </c>
+      <c r="AM79">
+        <v>7</v>
+      </c>
+      <c r="AN79">
+        <v>4</v>
+      </c>
+      <c r="AO79">
+        <v>13</v>
+      </c>
+      <c r="AP79">
+        <v>13</v>
+      </c>
+      <c r="AQ79">
+        <v>1.96</v>
+      </c>
+      <c r="AR79">
         <v>1.55</v>
       </c>
-      <c r="O79">
-        <v>3.75</v>
-      </c>
-      <c r="P79">
-        <v>4.4</v>
-      </c>
-      <c r="Q79">
-        <v>0</v>
-      </c>
-      <c r="R79">
-        <v>0</v>
-      </c>
-      <c r="S79">
-        <v>0</v>
-      </c>
-      <c r="T79">
-        <v>0</v>
-      </c>
-      <c r="U79">
-        <v>0</v>
-      </c>
-      <c r="V79">
-        <v>0</v>
-      </c>
-      <c r="W79">
-        <v>0</v>
-      </c>
-      <c r="X79">
-        <v>0</v>
-      </c>
-      <c r="Y79">
-        <v>0</v>
-      </c>
-      <c r="Z79">
-        <v>0</v>
-      </c>
-      <c r="AA79">
-        <v>1.85</v>
-      </c>
-      <c r="AB79">
-        <v>1.95</v>
-      </c>
-      <c r="AC79">
-        <v>0</v>
-      </c>
-      <c r="AD79">
-        <v>0</v>
-      </c>
-      <c r="AE79">
-        <v>0</v>
-      </c>
-      <c r="AF79">
-        <v>0</v>
-      </c>
-      <c r="AG79">
-        <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>0</v>
-      </c>
-      <c r="AK79">
-        <v>0</v>
-      </c>
-      <c r="AL79">
-        <v>0</v>
-      </c>
-      <c r="AM79">
-        <v>-1</v>
-      </c>
-      <c r="AN79">
-        <v>-1</v>
-      </c>
-      <c r="AO79">
-        <v>-1</v>
-      </c>
-      <c r="AP79">
-        <v>-1</v>
-      </c>
-      <c r="AQ79">
-        <v>0</v>
-      </c>
-      <c r="AR79">
-        <v>0</v>
-      </c>
       <c r="AS79">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AT79">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>0</v>
       </c>
       <c r="H80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -13341,11 +13341,11 @@
         <v>0</v>
       </c>
       <c r="L80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N80">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["76"]</t>
         </is>
       </c>
       <c r="AJ80">
@@ -13428,28 +13428,28 @@
         <v>0</v>
       </c>
       <c r="AM80">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN80">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO80">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP80">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ80">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AR80">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AS80">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT80">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
@@ -13489,26 +13489,26 @@
         </is>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N81">
@@ -13573,12 +13573,12 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1", "63", "72", "84"]</t>
         </is>
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43", "49"]</t>
         </is>
       </c>
       <c r="AJ81">
@@ -13591,28 +13591,28 @@
         <v>0</v>
       </c>
       <c r="AM81">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN81">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO81">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP81">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ81">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR81">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS81">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT81">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
@@ -13978,13 +13978,13 @@
         </is>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -13993,11 +13993,11 @@
         <v>0</v>
       </c>
       <c r="L84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N84">
@@ -14062,12 +14062,12 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33"]</t>
         </is>
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63", "77"]</t>
         </is>
       </c>
       <c r="AJ84">
@@ -14630,13 +14630,13 @@
         </is>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -14645,11 +14645,11 @@
         <v>0</v>
       </c>
       <c r="L88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N88">
@@ -14714,12 +14714,12 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["2"]</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53"]</t>
         </is>
       </c>
       <c r="AJ88">
@@ -14732,28 +14732,28 @@
         <v>0</v>
       </c>
       <c r="AM88">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN88">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO88">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP88">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ88">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR88">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS88">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT88">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
@@ -14793,26 +14793,26 @@
         </is>
       </c>
       <c r="G89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89">
         <v>0</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N89">
@@ -14877,12 +14877,12 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "54"]</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "26"]</t>
         </is>
       </c>
       <c r="AJ89">
@@ -14895,28 +14895,28 @@
         <v>0</v>
       </c>
       <c r="AM89">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN89">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO89">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP89">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ89">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR89">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS89">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT89">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
@@ -14959,7 +14959,7 @@
         <v>0</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -14971,11 +14971,11 @@
         <v>0</v>
       </c>
       <c r="L90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N90">
@@ -15045,7 +15045,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["63"]</t>
         </is>
       </c>
       <c r="AJ90">
@@ -15058,28 +15058,28 @@
         <v>0</v>
       </c>
       <c r="AM90">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN90">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO90">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP90">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ90">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AR90">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="AS90">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT90">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         </is>
       </c>
       <c r="G91">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H91">
         <v>0</v>
@@ -15131,14 +15131,14 @@
         <v>0</v>
       </c>
       <c r="K91">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L91">
         <v>0</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N91">
@@ -15151,34 +15151,34 @@
         <v>3.4</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA91">
         <v>1.95</v>
@@ -15187,62 +15187,62 @@
         <v>1.85</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
+          <t>["47", "77"]</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL91">
         <v>0</v>
       </c>
       <c r="AM91">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN91">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO91">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP91">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AQ91">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AR91">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AS91">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT91">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
@@ -15282,10 +15282,10 @@
         </is>
       </c>
       <c r="G92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -15294,14 +15294,14 @@
         <v>0</v>
       </c>
       <c r="K92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N92">
@@ -15314,19 +15314,19 @@
         <v>3.88</v>
       </c>
       <c r="Q92">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R92">
         <v>2.1</v>
       </c>
       <c r="S92">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T92">
         <v>3.2</v>
       </c>
       <c r="U92">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="V92">
         <v>1.4</v>
@@ -15344,10 +15344,10 @@
         <v>3.68</v>
       </c>
       <c r="AA92">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB92">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC92">
         <v>2.38</v>
@@ -15366,12 +15366,12 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["66"]</t>
         </is>
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+1"]</t>
         </is>
       </c>
       <c r="AJ92">
@@ -15384,28 +15384,28 @@
         <v>0</v>
       </c>
       <c r="AM92">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN92">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO92">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP92">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ92">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR92">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS92">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AT92">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
@@ -15445,13 +15445,13 @@
         </is>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93">
         <v>0</v>
       </c>
       <c r="I93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N93">
@@ -15529,7 +15529,7 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["42"]</t>
         </is>
       </c>
       <c r="AI93" t="inlineStr">
@@ -15547,28 +15547,28 @@
         <v>0</v>
       </c>
       <c r="AM93">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN93">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO93">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP93">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ93">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR93">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AS93">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT93">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
@@ -15608,26 +15608,26 @@
         </is>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H94">
         <v>0</v>
       </c>
       <c r="I94">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J94">
         <v>0</v>
       </c>
       <c r="K94">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94">
         <v>0</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N94">
@@ -15640,40 +15640,40 @@
         <v>29</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S94">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="T94">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X94">
         <v>0</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AC94">
         <v>1.75</v>
@@ -15682,56 +15682,56 @@
         <v>1.93</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
+          <t>["4", "28", "32", "33", "45", "55", "88"]</t>
+        </is>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AL94">
         <v>0</v>
       </c>
       <c r="AM94">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN94">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO94">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AP94">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ94">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AR94">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AS94">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT94">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
@@ -15774,13 +15774,13 @@
         <v>0</v>
       </c>
       <c r="H95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95">
         <v>0</v>
       </c>
       <c r="J95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95">
         <v>0</v>
@@ -15790,7 +15790,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N95">
@@ -15803,34 +15803,34 @@
         <v>1.33</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA95">
         <v>1.73</v>
@@ -15839,19 +15839,19 @@
         <v>1.95</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE95">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15860,41 +15860,41 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23"]</t>
         </is>
       </c>
       <c r="AJ95">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AL95">
         <v>0</v>
       </c>
       <c r="AM95">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN95">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO95">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP95">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ95">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR95">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS95">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT95">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>0</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -15949,27 +15949,27 @@
         <v>0</v>
       </c>
       <c r="L96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N96">
         <v>2.75</v>
       </c>
       <c r="O96">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P96">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
       </c>
       <c r="R96">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S96">
         <v>1.39</v>
@@ -15978,7 +15978,7 @@
         <v>2.78</v>
       </c>
       <c r="U96">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="V96">
         <v>1.38</v>
@@ -15993,7 +15993,7 @@
         <v>1.29</v>
       </c>
       <c r="Z96">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA96">
         <v>1.91</v>
@@ -16011,7 +16011,7 @@
         <v>1.08</v>
       </c>
       <c r="AF96">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG96">
         <v>1.95</v>
@@ -16023,41 +16023,41 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["46", "78"]</t>
         </is>
       </c>
       <c r="AJ96">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AK96">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL96">
         <v>0</v>
       </c>
       <c r="AM96">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN96">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO96">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP96">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ96">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR96">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AS96">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT96">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
@@ -16120,25 +16120,25 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="O97">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="P97">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="Q97">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="R97">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S97">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T97">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="U97">
         <v>3.41</v>
@@ -16147,22 +16147,22 @@
         <v>1.28</v>
       </c>
       <c r="W97">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X97">
         <v>1.06</v>
       </c>
       <c r="Y97">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="Z97">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AA97">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AB97">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AC97">
         <v>5</v>
@@ -16193,7 +16193,7 @@
         <v>1.33</v>
       </c>
       <c r="AK97">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16446,22 +16446,22 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="O99">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P99">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Q99">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="R99">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="S99">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="T99">
         <v>2.18</v>
@@ -16479,7 +16479,7 @@
         <v>1.07</v>
       </c>
       <c r="Y99">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Z99">
         <v>2.36</v>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK99">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16615,13 +16615,13 @@
         <v>2.7</v>
       </c>
       <c r="P100">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q100">
         <v>3.7</v>
       </c>
       <c r="R100">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S100">
         <v>1.65</v>
@@ -16660,7 +16660,7 @@
         <v>1.07</v>
       </c>
       <c r="AE100">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF100">
         <v>2.3</v>
@@ -16682,7 +16682,7 @@
         <v>1.4</v>
       </c>
       <c r="AK100">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -17238,26 +17238,26 @@
         </is>
       </c>
       <c r="G104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N104">
@@ -17322,12 +17322,12 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "62"]</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "57"]</t>
         </is>
       </c>
       <c r="AJ104">
@@ -17340,28 +17340,28 @@
         <v>0</v>
       </c>
       <c r="AM104">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN104">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO104">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP104">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ104">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR104">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS104">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT104">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.28</v>
+        <v>1.9</v>
       </c>
       <c r="O105">
-        <v>3.37</v>
+        <v>3</v>
       </c>
       <c r="P105">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="Q105">
-        <v>3.09</v>
+        <v>2.54</v>
       </c>
       <c r="R105">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S105">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="T105">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="U105">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="V105">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W105">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X105">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="Y105">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="Z105">
-        <v>3.6</v>
+        <v>3.02</v>
       </c>
       <c r="AA105">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AB105">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="AC105">
-        <v>3.38</v>
+        <v>4.25</v>
       </c>
       <c r="AD105">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AE105">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF105">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AG105">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK105">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17540,27 +17540,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="O106">
+        <v>3.37</v>
+      </c>
+      <c r="P106">
+        <v>2.9</v>
+      </c>
+      <c r="Q106">
+        <v>3.09</v>
+      </c>
+      <c r="R106">
+        <v>2.1</v>
+      </c>
+      <c r="S106">
+        <v>1.36</v>
+      </c>
+      <c r="T106">
         <v>2.7</v>
       </c>
-      <c r="P106">
-        <v>3.46</v>
-      </c>
-      <c r="Q106">
-        <v>0</v>
-      </c>
-      <c r="R106">
-        <v>0</v>
-      </c>
-      <c r="S106">
-        <v>0</v>
-      </c>
-      <c r="T106">
-        <v>0</v>
-      </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA106">
-        <v>2.87</v>
+        <v>1.91</v>
       </c>
       <c r="AB106">
-        <v>1.4</v>
+        <v>1.92</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-10-04 16:30:00</t>
+          <t>2026-10-04 16:00:00</t>
         </is>
       </c>
     </row>
@@ -17703,7 +17703,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G107">
@@ -17750,64 +17750,64 @@
         </is>
       </c>
       <c r="N107">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="O107">
+        <v>2.76</v>
+      </c>
+      <c r="P107">
+        <v>3.46</v>
+      </c>
+      <c r="Q107">
+        <v>0</v>
+      </c>
+      <c r="R107">
+        <v>0</v>
+      </c>
+      <c r="S107">
+        <v>0</v>
+      </c>
+      <c r="T107">
+        <v>0</v>
+      </c>
+      <c r="U107">
+        <v>0</v>
+      </c>
+      <c r="V107">
+        <v>0</v>
+      </c>
+      <c r="W107">
+        <v>0</v>
+      </c>
+      <c r="X107">
+        <v>0</v>
+      </c>
+      <c r="Y107">
+        <v>0</v>
+      </c>
+      <c r="Z107">
+        <v>0</v>
+      </c>
+      <c r="AA107">
         <v>2.87</v>
       </c>
-      <c r="P107">
-        <v>4.01</v>
-      </c>
-      <c r="Q107">
-        <v>2.88</v>
-      </c>
-      <c r="R107">
-        <v>1.85</v>
-      </c>
-      <c r="S107">
-        <v>1.64</v>
-      </c>
-      <c r="T107">
-        <v>2.09</v>
-      </c>
-      <c r="U107">
-        <v>3.78</v>
-      </c>
-      <c r="V107">
-        <v>1.22</v>
-      </c>
-      <c r="W107">
-        <v>1.03</v>
-      </c>
-      <c r="X107">
-        <v>1.1</v>
-      </c>
-      <c r="Y107">
-        <v>1.61</v>
-      </c>
-      <c r="Z107">
-        <v>2.13</v>
-      </c>
-      <c r="AA107">
-        <v>3.1</v>
-      </c>
       <c r="AB107">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC107">
-        <v>5.76</v>
+        <v>0</v>
       </c>
       <c r="AD107">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AE107">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF107">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG107">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK107">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17854,7 +17854,7 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>2026-10-04 17:00:00</t>
+          <t>2026-10-04 16:30:00</t>
         </is>
       </c>
     </row>
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="O108">
+        <v>2.8</v>
+      </c>
+      <c r="P108">
+        <v>4.01</v>
+      </c>
+      <c r="Q108">
         <v>2.9</v>
       </c>
-      <c r="P108">
-        <v>2.15</v>
-      </c>
-      <c r="Q108">
-        <v>4.33</v>
-      </c>
       <c r="R108">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="S108">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="T108">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="U108">
-        <v>3.66</v>
+        <v>3.78</v>
       </c>
       <c r="V108">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W108">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X108">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y108">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="Z108">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AA108">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="AB108">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC108">
-        <v>6</v>
+        <v>5.81</v>
       </c>
       <c r="AD108">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE108">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF108">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AG108">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK108">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>1.64</v>
+        <v>3.2</v>
       </c>
       <c r="O109">
-        <v>3.35</v>
+        <v>2.95</v>
       </c>
       <c r="P109">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="Q109">
-        <v>2.3</v>
+        <v>3.78</v>
       </c>
       <c r="R109">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S109">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T109">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="U109">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="V109">
         <v>1.29</v>
       </c>
       <c r="W109">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X109">
         <v>1.06</v>
       </c>
       <c r="Y109">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Z109">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AA109">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AB109">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AC109">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AD109">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AE109">
         <v>1.02</v>
       </c>
       <c r="AF109">
-        <v>2.4</v>
+        <v>2.07</v>
       </c>
       <c r="AG109">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AK109">
-        <v>2.15</v>
+        <v>1.25</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="O110">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P110">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q110">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="R110">
-        <v>2.63</v>
+        <v>1.93</v>
       </c>
       <c r="S110">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="T110">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="U110">
-        <v>2.13</v>
+        <v>3.42</v>
       </c>
       <c r="V110">
-        <v>1.71</v>
+        <v>1.29</v>
       </c>
       <c r="W110">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="X110">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y110">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="Z110">
-        <v>5.84</v>
+        <v>2.5</v>
       </c>
       <c r="AA110">
-        <v>1.43</v>
+        <v>2.4</v>
       </c>
       <c r="AB110">
-        <v>2.7</v>
+        <v>1.54</v>
       </c>
       <c r="AC110">
-        <v>2.12</v>
+        <v>4.38</v>
       </c>
       <c r="AD110">
-        <v>1.69</v>
+        <v>1.17</v>
       </c>
       <c r="AE110">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="AF110">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="AG110">
-        <v>2.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AK110">
         <v>2.1</v>
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,80 +18402,80 @@
         </is>
       </c>
       <c r="N111">
-        <v>7.15</v>
+        <v>1.65</v>
       </c>
       <c r="O111">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="P111">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q111">
-        <v>6</v>
+        <v>2.29</v>
       </c>
       <c r="R111">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="S111">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T111">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="U111">
-        <v>1.81</v>
+        <v>2.13</v>
       </c>
       <c r="V111">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="W111">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y111">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z111">
-        <v>3.6</v>
+        <v>5.84</v>
       </c>
       <c r="AA111">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AB111">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC111">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AD111">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="AE111">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AF111">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AG111">
+        <v>2.53</v>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ111">
+        <v>1.15</v>
+      </c>
+      <c r="AK111">
         <v>2.1</v>
-      </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ111">
-        <v>2.84</v>
-      </c>
-      <c r="AK111">
-        <v>1.08</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18518,12 +18518,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.02</v>
+        <v>6.5</v>
       </c>
       <c r="O112">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P112">
-        <v>2.85</v>
+        <v>1.35</v>
       </c>
       <c r="Q112">
-        <v>2.25</v>
+        <v>6</v>
       </c>
       <c r="R112">
-        <v>2.29</v>
+        <v>2.62</v>
       </c>
       <c r="S112">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="T112">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U112">
-        <v>2.66</v>
+        <v>1.81</v>
       </c>
       <c r="V112">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="W112">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X112">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y112">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Z112">
         <v>3.6</v>
       </c>
       <c r="AA112">
-        <v>1.74</v>
+        <v>1.4</v>
       </c>
       <c r="AB112">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="AC112">
-        <v>2.85</v>
+        <v>1.85</v>
       </c>
       <c r="AD112">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AE112">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="AF112">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG112">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.25</v>
+        <v>2.84</v>
       </c>
       <c r="AK112">
-        <v>1.81</v>
+        <v>1.08</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-10-04 17:30:00</t>
+          <t>2026-10-04 17:00:00</t>
         </is>
       </c>
     </row>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>2.55</v>
+        <v>2.02</v>
       </c>
       <c r="O113">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="P113">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="Q113">
-        <v>3.7</v>
+        <v>2.25</v>
       </c>
       <c r="R113">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="S113">
+        <v>1.3</v>
+      </c>
+      <c r="T113">
+        <v>3.11</v>
+      </c>
+      <c r="U113">
+        <v>2.54</v>
+      </c>
+      <c r="V113">
+        <v>1.47</v>
+      </c>
+      <c r="W113">
+        <v>1.11</v>
+      </c>
+      <c r="X113">
+        <v>1.01</v>
+      </c>
+      <c r="Y113">
+        <v>1.22</v>
+      </c>
+      <c r="Z113">
+        <v>3.9</v>
+      </c>
+      <c r="AA113">
+        <v>1.74</v>
+      </c>
+      <c r="AB113">
+        <v>2</v>
+      </c>
+      <c r="AC113">
+        <v>2.85</v>
+      </c>
+      <c r="AD113">
+        <v>1.33</v>
+      </c>
+      <c r="AE113">
+        <v>1.11</v>
+      </c>
+      <c r="AF113">
         <v>1.64</v>
       </c>
-      <c r="T113">
-        <v>2.09</v>
-      </c>
-      <c r="U113">
-        <v>4</v>
-      </c>
-      <c r="V113">
-        <v>1.21</v>
-      </c>
-      <c r="W113">
-        <v>1.03</v>
-      </c>
-      <c r="X113">
-        <v>1.09</v>
-      </c>
-      <c r="Y113">
-        <v>1.65</v>
-      </c>
-      <c r="Z113">
-        <v>2.25</v>
-      </c>
-      <c r="AA113">
-        <v>2.82</v>
-      </c>
-      <c r="AB113">
-        <v>1.4</v>
-      </c>
-      <c r="AC113">
-        <v>6.02</v>
-      </c>
-      <c r="AD113">
-        <v>1.08</v>
-      </c>
-      <c r="AE113">
-        <v>1.02</v>
-      </c>
-      <c r="AF113">
-        <v>2.3</v>
-      </c>
       <c r="AG113">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AK113">
-        <v>1.37</v>
+        <v>1.89</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18849,22 +18849,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Tru-Juice</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O114">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="P114">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Tru-Juice</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Humble Lions</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="O115">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="P115">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q115">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="R115">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S115">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T115">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="U115">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V115">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W115">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X115">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y115">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z115">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AA115">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB115">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC115">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD115">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE115">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF115">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG115">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK115">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Humble Lions</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,65 +19217,65 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="O116">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="P116">
-        <v>7.57</v>
+        <v>4.6</v>
       </c>
       <c r="Q116">
-        <v>1.84</v>
+        <v>2.36</v>
       </c>
       <c r="R116">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="S116">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T116">
-        <v>2.99</v>
+        <v>3.09</v>
       </c>
       <c r="U116">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V116">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W116">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X116">
         <v>1.02</v>
       </c>
       <c r="Y116">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z116">
-        <v>3.94</v>
+        <v>4.33</v>
       </c>
       <c r="AA116">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AB116">
+        <v>2.17</v>
+      </c>
+      <c r="AC116">
+        <v>2.56</v>
+      </c>
+      <c r="AD116">
+        <v>1.48</v>
+      </c>
+      <c r="AE116">
+        <v>1.17</v>
+      </c>
+      <c r="AF116">
+        <v>1.63</v>
+      </c>
+      <c r="AG116">
         <v>2.1</v>
       </c>
-      <c r="AC116">
-        <v>2.88</v>
-      </c>
-      <c r="AD116">
-        <v>1.36</v>
-      </c>
-      <c r="AE116">
-        <v>1.13</v>
-      </c>
-      <c r="AF116">
-        <v>2.13</v>
-      </c>
-      <c r="AG116">
-        <v>1.59</v>
-      </c>
       <c r="AH116" t="inlineStr">
         <is>
           <t>[]</t>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.02</v>
+        <v>1.19</v>
       </c>
       <c r="AK116">
-        <v>3.18</v>
+        <v>1.99</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,80 +19380,80 @@
         </is>
       </c>
       <c r="N117">
-        <v>1.66</v>
+        <v>1.29</v>
       </c>
       <c r="O117">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="P117">
-        <v>5.25</v>
+        <v>7.57</v>
       </c>
       <c r="Q117">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="R117">
-        <v>1.95</v>
+        <v>2.54</v>
       </c>
       <c r="S117">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="T117">
+        <v>2.99</v>
+      </c>
+      <c r="U117">
+        <v>2.63</v>
+      </c>
+      <c r="V117">
+        <v>1.44</v>
+      </c>
+      <c r="W117">
+        <v>1.07</v>
+      </c>
+      <c r="X117">
+        <v>1.02</v>
+      </c>
+      <c r="Y117">
+        <v>1.22</v>
+      </c>
+      <c r="Z117">
+        <v>3.94</v>
+      </c>
+      <c r="AA117">
+        <v>1.74</v>
+      </c>
+      <c r="AB117">
+        <v>2.1</v>
+      </c>
+      <c r="AC117">
+        <v>2.88</v>
+      </c>
+      <c r="AD117">
+        <v>1.36</v>
+      </c>
+      <c r="AE117">
+        <v>1.13</v>
+      </c>
+      <c r="AF117">
         <v>2.13</v>
       </c>
-      <c r="U117">
-        <v>3.8</v>
-      </c>
-      <c r="V117">
-        <v>1.22</v>
-      </c>
-      <c r="W117">
-        <v>1.04</v>
-      </c>
-      <c r="X117">
-        <v>1.1</v>
-      </c>
-      <c r="Y117">
-        <v>1.6</v>
-      </c>
-      <c r="Z117">
-        <v>2.15</v>
-      </c>
-      <c r="AA117">
-        <v>2.87</v>
-      </c>
-      <c r="AB117">
-        <v>1.36</v>
-      </c>
-      <c r="AC117">
-        <v>7</v>
-      </c>
-      <c r="AD117">
-        <v>1.07</v>
-      </c>
-      <c r="AE117">
+      <c r="AG117">
+        <v>1.59</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ117">
         <v>1.02</v>
       </c>
-      <c r="AF117">
-        <v>2.7</v>
-      </c>
-      <c r="AG117">
-        <v>1.4</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ117">
-        <v>1.25</v>
-      </c>
       <c r="AK117">
-        <v>2.1</v>
+        <v>3.18</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-10-04 18:00:00</t>
+          <t>2026-10-04 17:30:00</t>
         </is>
       </c>
     </row>
@@ -19496,7 +19496,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="O118">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P118">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="Q118">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="R118">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="S118">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="T118">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="U118">
         <v>3.75</v>
       </c>
       <c r="V118">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W118">
         <v>1.04</v>
       </c>
       <c r="X118">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y118">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Z118">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AA118">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AB118">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AC118">
-        <v>6.19</v>
+        <v>7</v>
       </c>
       <c r="AD118">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE118">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF118">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AG118">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AK118">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>2026-10-04 18:30:00</t>
+          <t>2026-10-04 18:00:00</t>
         </is>
       </c>
     </row>
@@ -19659,12 +19659,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G119">
@@ -19706,64 +19706,64 @@
         </is>
       </c>
       <c r="N119">
-        <v>2.11</v>
+        <v>1.7</v>
       </c>
       <c r="O119">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="P119">
-        <v>2.35</v>
+        <v>5.25</v>
       </c>
       <c r="Q119">
-        <v>2.91</v>
+        <v>2.45</v>
       </c>
       <c r="R119">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="S119">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="T119">
-        <v>3.6</v>
+        <v>2.19</v>
       </c>
       <c r="U119">
-        <v>2.18</v>
+        <v>3.5</v>
       </c>
       <c r="V119">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="W119">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X119">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y119">
+        <v>1.52</v>
+      </c>
+      <c r="Z119">
+        <v>2.55</v>
+      </c>
+      <c r="AA119">
+        <v>2.59</v>
+      </c>
+      <c r="AB119">
+        <v>1.49</v>
+      </c>
+      <c r="AC119">
+        <v>5.37</v>
+      </c>
+      <c r="AD119">
         <v>1.14</v>
       </c>
-      <c r="Z119">
-        <v>5</v>
-      </c>
-      <c r="AA119">
-        <v>1.53</v>
-      </c>
-      <c r="AB119">
-        <v>2.29</v>
-      </c>
-      <c r="AC119">
-        <v>2.27</v>
-      </c>
-      <c r="AD119">
-        <v>1.54</v>
-      </c>
       <c r="AE119">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AF119">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="AG119">
-        <v>2.55</v>
+        <v>1.5</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         </is>
       </c>
       <c r="AJ119">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK119">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AL119">
         <v>0</v>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-10-04 19:00:00</t>
+          <t>2026-10-04 18:30:00</t>
         </is>
       </c>
     </row>
@@ -19827,22 +19827,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G120">
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="O120">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="P120">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="Q120">
-        <v>3.24</v>
+        <v>2.75</v>
       </c>
       <c r="R120">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="S120">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="T120">
-        <v>2.83</v>
+        <v>3.6</v>
       </c>
       <c r="U120">
-        <v>2.72</v>
+        <v>2.22</v>
       </c>
       <c r="V120">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="W120">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X120">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y120">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="Z120">
-        <v>3.28</v>
+        <v>4.67</v>
       </c>
       <c r="AA120">
-        <v>1.84</v>
+        <v>1.52</v>
       </c>
       <c r="AB120">
-        <v>1.83</v>
+        <v>2.31</v>
       </c>
       <c r="AC120">
-        <v>3.4</v>
+        <v>2.29</v>
       </c>
       <c r="AD120">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AE120">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AF120">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="AG120">
-        <v>2.07</v>
+        <v>2.55</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AK120">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -19985,27 +19985,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G121">
@@ -20032,64 +20032,64 @@
         </is>
       </c>
       <c r="N121">
-        <v>3.73</v>
+        <v>2.5</v>
       </c>
       <c r="O121">
-        <v>3.62</v>
+        <v>3</v>
       </c>
       <c r="P121">
-        <v>1.77</v>
+        <v>2.59</v>
       </c>
       <c r="Q121">
-        <v>4.52</v>
+        <v>3.24</v>
       </c>
       <c r="R121">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S121">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T121">
-        <v>3.3</v>
+        <v>2.83</v>
       </c>
       <c r="U121">
-        <v>2.45</v>
+        <v>2.72</v>
       </c>
       <c r="V121">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="W121">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X121">
         <v>1.04</v>
       </c>
       <c r="Y121">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="Z121">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="AA121">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AB121">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AC121">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="AD121">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AE121">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF121">
         <v>1.65</v>
       </c>
       <c r="AG121">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -20102,10 +20102,10 @@
         </is>
       </c>
       <c r="AJ121">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK121">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AL121">
         <v>0</v>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-10-04 20:00:00</t>
+          <t>2026-10-04 19:00:00</t>
         </is>
       </c>
     </row>
@@ -20148,27 +20148,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,80 +20195,80 @@
         </is>
       </c>
       <c r="N122">
-        <v>1.91</v>
+        <v>3.73</v>
       </c>
       <c r="O122">
-        <v>3.3</v>
+        <v>3.62</v>
       </c>
       <c r="P122">
-        <v>3.5</v>
+        <v>1.77</v>
       </c>
       <c r="Q122">
-        <v>2.67</v>
+        <v>4.52</v>
       </c>
       <c r="R122">
         <v>2.1</v>
       </c>
       <c r="S122">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="T122">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="U122">
-        <v>2.96</v>
+        <v>2.45</v>
       </c>
       <c r="V122">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W122">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X122">
         <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="Z122">
-        <v>2.97</v>
+        <v>4</v>
       </c>
       <c r="AA122">
-        <v>2.09</v>
+        <v>1.77</v>
       </c>
       <c r="AB122">
-        <v>1.68</v>
+        <v>1.99</v>
       </c>
       <c r="AC122">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="AD122">
+        <v>1.42</v>
+      </c>
+      <c r="AE122">
+        <v>1.09</v>
+      </c>
+      <c r="AF122">
+        <v>1.65</v>
+      </c>
+      <c r="AG122">
+        <v>2.1</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ122">
+        <v>1.25</v>
+      </c>
+      <c r="AK122">
         <v>1.22</v>
-      </c>
-      <c r="AE122">
-        <v>1.05</v>
-      </c>
-      <c r="AF122">
-        <v>1.9</v>
-      </c>
-      <c r="AG122">
-        <v>1.8</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ122">
-        <v>1.2</v>
-      </c>
-      <c r="AK122">
-        <v>1.83</v>
       </c>
       <c r="AL122">
         <v>0</v>
@@ -20298,6 +20298,169 @@
         <v>0</v>
       </c>
       <c r="AU122" t="inlineStr">
+        <is>
+          <t>2026-10-04 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Mount Pleasant Academy FC</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Cavalier</t>
+        </is>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N123">
+        <v>1.91</v>
+      </c>
+      <c r="O123">
+        <v>3.3</v>
+      </c>
+      <c r="P123">
+        <v>3.5</v>
+      </c>
+      <c r="Q123">
+        <v>2.67</v>
+      </c>
+      <c r="R123">
+        <v>2.1</v>
+      </c>
+      <c r="S123">
+        <v>1.41</v>
+      </c>
+      <c r="T123">
+        <v>2.63</v>
+      </c>
+      <c r="U123">
+        <v>2.96</v>
+      </c>
+      <c r="V123">
+        <v>1.33</v>
+      </c>
+      <c r="W123">
+        <v>1.07</v>
+      </c>
+      <c r="X123">
+        <v>1.04</v>
+      </c>
+      <c r="Y123">
+        <v>1.34</v>
+      </c>
+      <c r="Z123">
+        <v>2.97</v>
+      </c>
+      <c r="AA123">
+        <v>2.09</v>
+      </c>
+      <c r="AB123">
+        <v>1.68</v>
+      </c>
+      <c r="AC123">
+        <v>3.8</v>
+      </c>
+      <c r="AD123">
+        <v>1.22</v>
+      </c>
+      <c r="AE123">
+        <v>1.05</v>
+      </c>
+      <c r="AF123">
+        <v>1.9</v>
+      </c>
+      <c r="AG123">
+        <v>1.8</v>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ123">
+        <v>1.2</v>
+      </c>
+      <c r="AK123">
+        <v>1.83</v>
+      </c>
+      <c r="AL123">
+        <v>0</v>
+      </c>
+      <c r="AM123">
+        <v>-1</v>
+      </c>
+      <c r="AN123">
+        <v>-1</v>
+      </c>
+      <c r="AO123">
+        <v>-1</v>
+      </c>
+      <c r="AP123">
+        <v>-1</v>
+      </c>
+      <c r="AQ123">
+        <v>0</v>
+      </c>
+      <c r="AR123">
+        <v>0</v>
+      </c>
+      <c r="AS123">
+        <v>0</v>
+      </c>
+      <c r="AT123">
+        <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
         <is>
           <t>2026-10-04 21:30:00</t>
         </is>
